--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06196EA9-F1C8-4F56-983A-7647BAABC053}"/>
+  <xr:revisionPtr revIDLastSave="798" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC756A4-3334-4006-8A84-F538883D8EA0}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="105" windowWidth="36570" windowHeight="20550" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="165" yWindow="30" windowWidth="36255" windowHeight="20550" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="75">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t>Vecka 15 (6-10 april)</t>
-  </si>
-  <si>
-    <t>08:00-13:15</t>
   </si>
   <si>
     <t>Fredag (Långfredag)</t>
@@ -200,9 +197,6 @@
     <t>Veckans saldo (Nationadag lörd)</t>
   </si>
   <si>
-    <t>12:15-17:45</t>
-  </si>
-  <si>
     <t>Ledigt</t>
   </si>
   <si>
@@ -239,7 +233,37 @@
     <t>Vecka 34 (31 aug-4 sep)</t>
   </si>
   <si>
-    <t>Vill ha sommarjobbare som startar med mån-tis</t>
+    <t>Betyder att schemat är låst och utdelat</t>
+  </si>
+  <si>
+    <t>Plus ingående 10 h</t>
+  </si>
+  <si>
+    <t>Plus ingående 4 h</t>
+  </si>
+  <si>
+    <t>Plus ingående 17 h</t>
+  </si>
+  <si>
+    <t>Plus ingående 12 h</t>
+  </si>
+  <si>
+    <t>09:15-17:45</t>
+  </si>
+  <si>
+    <t>07:00-14:45 (Prod)</t>
+  </si>
+  <si>
+    <t>Ledog</t>
+  </si>
+  <si>
+    <t>Semester</t>
+  </si>
+  <si>
+    <t>10:15-15:45</t>
+  </si>
+  <si>
+    <t>Sommarjobb</t>
   </si>
 </sst>
 </file>
@@ -249,7 +273,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\+0;\-0;0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +313,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -575,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -694,12 +726,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -709,18 +735,18 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1070,7 +1096,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P274"/>
+  <dimension ref="A1:Q274"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1088,18 +1114,18 @@
     <col min="13" max="13" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1140,89 +1166,89 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="4">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="4">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="4">
+        <v>9</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="4">
+        <v>10</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="4">
+        <v>10</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="4">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C4" s="4">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="4">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E4" s="4">
+        <v>9</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="4">
-        <v>9</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="G4" s="4">
+        <v>8</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="4">
-        <v>10</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="I4" s="4">
+        <v>9</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="4">
-        <v>10</v>
-      </c>
-      <c r="L3" s="4" t="s">
+      <c r="K4" s="4">
+        <v>9</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="4">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="4">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="4">
-        <v>8</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="4">
-        <v>9</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="4">
-        <v>9</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="M4" s="12">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>9</v>
       </c>
@@ -1263,12 +1289,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4">
         <v>6</v>
@@ -1279,7 +1305,7 @@
       <c r="E6" s="4">
         <v>4</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="4">
@@ -1304,7 +1330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>11</v>
       </c>
@@ -1320,7 +1346,7 @@
       <c r="E7" s="14">
         <v>8</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G7" s="14">
@@ -1343,9 +1369,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="36"/>
       <c r="C8" s="36">
@@ -1378,9 +1404,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="39"/>
       <c r="C9" s="39">
@@ -1407,9 +1433,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="42"/>
       <c r="C10" s="42">
@@ -1435,14 +1461,18 @@
       <c r="M10" s="43">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N10" s="46"/>
+      <c r="O10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
       <c r="I11" s="2"/>
       <c r="K11" s="2"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>17</v>
       </c>
@@ -1483,89 +1513,89 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="4">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="4">
+        <v>10</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="4">
+        <v>9</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="4">
+        <v>10</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="4">
+        <v>10</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="4">
-        <v>10</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="C14" s="4">
+        <v>9</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="4">
-        <v>10</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E14" s="4">
+        <v>9</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="4">
-        <v>9</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="G14" s="4">
+        <v>8</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="4">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4" t="s">
+      <c r="I14" s="4">
+        <v>9</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K13" s="4">
-        <v>10</v>
-      </c>
-      <c r="L13" s="4" t="s">
+      <c r="K14" s="4">
+        <v>9</v>
+      </c>
+      <c r="L14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M13" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="4">
-        <v>9</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="4">
-        <v>9</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="4">
-        <v>8</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="4">
-        <v>9</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="4">
-        <v>9</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="M14" s="12">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>9</v>
       </c>
@@ -1606,12 +1636,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="4">
         <v>6</v>
@@ -1641,13 +1671,13 @@
         <v>4</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M16" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>11</v>
       </c>
@@ -1686,9 +1716,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="36"/>
       <c r="C18" s="36">
@@ -1721,9 +1751,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="39"/>
       <c r="C19" s="39">
@@ -1750,9 +1780,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="42">
@@ -1778,14 +1808,15 @@
       <c r="M20" s="43">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="46"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G21" s="2"/>
       <c r="I21" s="2"/>
       <c r="K21" s="2"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
@@ -1826,89 +1857,89 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="4">
+        <v>10</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="4">
+        <v>10</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="4">
+        <v>9</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" s="4">
+        <v>10</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="4">
+        <v>10</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="4">
-        <v>10</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="C24" s="4">
+        <v>9</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="4">
-        <v>10</v>
-      </c>
-      <c r="F23" s="4" t="s">
+      <c r="E24" s="4">
+        <v>9</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="4">
-        <v>9</v>
-      </c>
-      <c r="H23" s="4" t="s">
+      <c r="G24" s="4">
+        <v>8</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I23" s="4">
-        <v>10</v>
-      </c>
-      <c r="J23" s="4" t="s">
+      <c r="I24" s="4">
+        <v>9</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K23" s="4">
-        <v>10</v>
-      </c>
-      <c r="L23" s="4" t="s">
+      <c r="K24" s="4">
+        <v>9</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M23" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="4">
-        <v>9</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="4">
-        <v>9</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="4">
-        <v>8</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="4">
-        <v>9</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" s="4">
-        <v>9</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="M24" s="12">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>9</v>
       </c>
@@ -1949,12 +1980,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="4">
         <v>6</v>
@@ -1977,12 +2008,10 @@
       <c r="I26" s="4">
         <v>8</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K26" s="4">
-        <v>8</v>
-      </c>
+      <c r="J26" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="4"/>
       <c r="L26" s="4" t="s">
         <v>14</v>
       </c>
@@ -1990,7 +2019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>11</v>
       </c>
@@ -2022,14 +2051,14 @@
         <v>13</v>
       </c>
       <c r="K27" s="14"/>
-      <c r="L27" s="54" t="s">
+      <c r="L27" s="51" t="s">
         <v>13</v>
       </c>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="36"/>
       <c r="C28" s="36">
@@ -2054,7 +2083,7 @@
       <c r="J28" s="36"/>
       <c r="K28" s="36">
         <f>SUM(K23:K27)</f>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L28" s="36"/>
       <c r="M28" s="37">
@@ -2062,9 +2091,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="39"/>
       <c r="C29" s="39">
@@ -2084,16 +2113,16 @@
       </c>
       <c r="J29" s="39"/>
       <c r="K29" s="39">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L29" s="39"/>
       <c r="M29" s="40">
         <v>-6</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="42">
@@ -2113,15 +2142,16 @@
       </c>
       <c r="J30" s="42"/>
       <c r="K30" s="42">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L30" s="42"/>
       <c r="M30" s="43">
         <v>-6</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N30" s="46"/>
+    </row>
+    <row r="31" spans="1:14" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>20</v>
       </c>
@@ -2162,89 +2192,89 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="4">
+        <v>10</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="4">
+        <v>10</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="4">
+        <v>9</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="4">
+        <v>10</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="4">
+        <v>10</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="4">
-        <v>10</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="C34" s="4">
+        <v>9</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="4">
-        <v>10</v>
-      </c>
-      <c r="F33" s="4" t="s">
+      <c r="E34" s="4">
+        <v>9</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G33" s="4">
-        <v>9</v>
-      </c>
-      <c r="H33" s="4" t="s">
+      <c r="G34" s="4">
+        <v>8</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I33" s="4">
-        <v>10</v>
-      </c>
-      <c r="J33" s="4" t="s">
+      <c r="I34" s="4">
+        <v>9</v>
+      </c>
+      <c r="J34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K33" s="4">
-        <v>10</v>
-      </c>
-      <c r="L33" s="4" t="s">
+      <c r="K34" s="4">
+        <v>9</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M33" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="4">
-        <v>9</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="4">
-        <v>9</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G34" s="4">
-        <v>8</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="4">
-        <v>9</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K34" s="4">
-        <v>9</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="M34" s="12">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>9</v>
       </c>
@@ -2285,12 +2315,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" s="4">
         <v>6</v>
@@ -2318,13 +2348,13 @@
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M36" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>11</v>
       </c>
@@ -2363,9 +2393,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="36"/>
       <c r="C38" s="36">
@@ -2398,9 +2428,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="39"/>
       <c r="C39" s="39">
@@ -2427,9 +2457,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="42">
@@ -2449,15 +2479,16 @@
       </c>
       <c r="J40" s="42"/>
       <c r="K40" s="42">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L40" s="42"/>
       <c r="M40" s="43">
         <v>-7</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N40" s="46"/>
+    </row>
+    <row r="41" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>23</v>
       </c>
@@ -2498,89 +2529,89 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="4">
+        <v>10</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="4">
+        <v>10</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43" s="4">
+        <v>9</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43" s="4">
+        <v>10</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" s="4">
+        <v>10</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M43" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C43" s="4">
-        <v>10</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="C44" s="4">
+        <v>9</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="4">
-        <v>10</v>
-      </c>
-      <c r="F43" s="4" t="s">
+      <c r="E44" s="4">
+        <v>9</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G43" s="4">
-        <v>9</v>
-      </c>
-      <c r="H43" s="4" t="s">
+      <c r="G44" s="4">
+        <v>8</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I43" s="4">
-        <v>10</v>
-      </c>
-      <c r="J43" s="4" t="s">
+      <c r="I44" s="4">
+        <v>9</v>
+      </c>
+      <c r="J44" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K43" s="4">
-        <v>10</v>
-      </c>
-      <c r="L43" s="4" t="s">
+      <c r="K44" s="4">
+        <v>9</v>
+      </c>
+      <c r="L44" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M43" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="4">
-        <v>9</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="4">
-        <v>9</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G44" s="4">
-        <v>8</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="4">
-        <v>9</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K44" s="4">
-        <v>9</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="M44" s="12">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>9</v>
       </c>
@@ -2590,12 +2621,10 @@
       <c r="C45" s="4">
         <v>8</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="4">
-        <v>8</v>
-      </c>
+      <c r="D45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="4"/>
       <c r="F45" s="4" t="s">
         <v>16</v>
       </c>
@@ -2621,12 +2650,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" s="4">
         <v>6</v>
@@ -2652,15 +2681,15 @@
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M46" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B47" s="26" t="s">
         <v>13</v>
@@ -2687,9 +2716,9 @@
       </c>
       <c r="M47" s="27"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" s="36"/>
       <c r="C48" s="36">
@@ -2699,7 +2728,7 @@
       <c r="D48" s="36"/>
       <c r="E48" s="36">
         <f>SUM(E43:E47)</f>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F48" s="36"/>
       <c r="G48" s="36">
@@ -2724,7 +2753,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="39"/>
       <c r="C49" s="39">
@@ -2732,11 +2761,11 @@
       </c>
       <c r="D49" s="39"/>
       <c r="E49" s="39">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="F49" s="39"/>
       <c r="G49" s="39">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="H49" s="39"/>
       <c r="I49" s="39">
@@ -2744,7 +2773,7 @@
       </c>
       <c r="J49" s="39"/>
       <c r="K49" s="39">
-        <v>1.4</v>
+        <v>-5</v>
       </c>
       <c r="L49" s="39"/>
       <c r="M49" s="40">
@@ -2753,7 +2782,7 @@
     </row>
     <row r="50" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" s="42"/>
       <c r="C50" s="42">
@@ -2761,11 +2790,11 @@
       </c>
       <c r="D50" s="42"/>
       <c r="E50" s="42">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="F50" s="42"/>
       <c r="G50" s="42">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="H50" s="42"/>
       <c r="I50" s="42">
@@ -2773,13 +2802,13 @@
       </c>
       <c r="J50" s="42"/>
       <c r="K50" s="42">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="L50" s="42"/>
       <c r="M50" s="43">
         <v>-7</v>
       </c>
-      <c r="N50" s="48"/>
+      <c r="N50" s="46"/>
     </row>
     <row r="51" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -2825,16 +2854,16 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C53" s="20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E53" s="20">
         <v>10</v>
@@ -2844,19 +2873,19 @@
       </c>
       <c r="G53" s="16"/>
       <c r="H53" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I53" s="20">
         <v>10</v>
       </c>
       <c r="J53" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K53" s="20">
         <v>10</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M53" s="28">
         <v>10</v>
@@ -2867,37 +2896,37 @@
         <v>8</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C54" s="4">
         <v>9</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E54" s="4">
         <v>9</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G54" s="4">
         <v>8</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I54" s="4">
         <v>9</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K54" s="4">
         <v>9</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M54" s="12">
         <v>9</v>
@@ -2949,7 +2978,7 @@
         <v>10</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C56" s="4">
         <v>6</v>
@@ -2977,7 +3006,7 @@
       </c>
       <c r="K56" s="4"/>
       <c r="L56" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M56" s="12">
         <v>5</v>
@@ -2988,10 +3017,10 @@
         <v>11</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C57" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>12</v>
@@ -3005,11 +3034,11 @@
       <c r="G57" s="14">
         <v>7</v>
       </c>
-      <c r="H57" s="14" t="s">
-        <v>12</v>
+      <c r="H57" s="51" t="s">
+        <v>19</v>
       </c>
       <c r="I57" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J57" s="14" t="s">
         <v>13</v>
@@ -3024,12 +3053,12 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" s="36"/>
       <c r="C58" s="36">
         <f>SUM(C53:C57)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D58" s="36"/>
       <c r="E58" s="36">
@@ -3044,7 +3073,7 @@
       <c r="H58" s="36"/>
       <c r="I58" s="36">
         <f>SUM(I53:I57)</f>
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J58" s="36"/>
       <c r="K58" s="36">
@@ -3059,23 +3088,23 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" s="39"/>
       <c r="C59" s="39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" s="39"/>
       <c r="E59" s="39">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F59" s="39"/>
       <c r="G59" s="39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" s="39"/>
       <c r="I59" s="39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J59" s="39"/>
       <c r="K59" s="39">
@@ -3088,38 +3117,46 @@
     </row>
     <row r="60" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="42"/>
-      <c r="C60" s="42">
-        <v>4</v>
+        <v>42</v>
+      </c>
+      <c r="B60" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" s="55">
+        <v>15</v>
       </c>
       <c r="D60" s="42"/>
-      <c r="E60" s="42">
-        <v>18</v>
+      <c r="E60" s="55">
+        <v>8</v>
       </c>
       <c r="F60" s="42"/>
-      <c r="G60" s="42">
-        <v>-2</v>
-      </c>
-      <c r="H60" s="42"/>
-      <c r="I60" s="42">
+      <c r="G60" s="55">
+        <v>-3</v>
+      </c>
+      <c r="H60" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="I60" s="55">
         <v>14</v>
       </c>
-      <c r="J60" s="42"/>
-      <c r="K60" s="42">
-        <v>1</v>
-      </c>
-      <c r="L60" s="42"/>
-      <c r="M60" s="43">
-        <v>0</v>
-      </c>
-      <c r="N60" s="48"/>
+      <c r="J60" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="K60" s="55">
+        <v>9</v>
+      </c>
+      <c r="L60" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="M60" s="56">
+        <v>12</v>
+      </c>
+      <c r="N60" s="46"/>
     </row>
     <row r="61" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>2</v>
@@ -3163,37 +3200,37 @@
         <v>7</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C63" s="4">
         <v>10</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E63" s="4">
         <v>10</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G63" s="4">
         <v>9</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I63" s="4">
         <v>10</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K63" s="4">
         <v>10</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M63" s="12">
         <v>10</v>
@@ -3204,37 +3241,37 @@
         <v>8</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C64" s="4">
         <v>9</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E64" s="4">
         <v>9</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G64" s="4">
         <v>8</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I64" s="4">
         <v>9</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K64" s="4">
         <v>9</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M64" s="12">
         <v>9</v>
@@ -3286,7 +3323,7 @@
         <v>10</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C66" s="4">
         <v>6</v>
@@ -3362,8 +3399,8 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="49" t="s">
-        <v>41</v>
+      <c r="A68" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B68" s="44"/>
       <c r="C68" s="44">
@@ -3398,7 +3435,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" s="39"/>
       <c r="C69" s="39">
@@ -3427,19 +3464,19 @@
     </row>
     <row r="70" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B70" s="42"/>
       <c r="C70" s="42">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D70" s="42"/>
       <c r="E70" s="42">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F70" s="42"/>
       <c r="G70" s="42">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H70" s="42"/>
       <c r="I70" s="42">
@@ -3447,18 +3484,18 @@
       </c>
       <c r="J70" s="42"/>
       <c r="K70" s="42">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L70" s="42"/>
       <c r="M70" s="43">
-        <v>1</v>
-      </c>
-      <c r="N70" s="48"/>
+        <v>13</v>
+      </c>
+      <c r="N70" s="46"/>
     </row>
     <row r="71" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>2</v>
@@ -3502,37 +3539,37 @@
         <v>7</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C73" s="4">
         <v>10</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E73" s="4">
         <v>10</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G73" s="4">
         <v>9</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I73" s="4">
         <v>10</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K73" s="4">
         <v>10</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M73" s="12">
         <v>10</v>
@@ -3543,37 +3580,37 @@
         <v>8</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C74" s="4">
         <v>9</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E74" s="4">
         <v>9</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G74" s="4">
         <v>8</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I74" s="4">
         <v>9</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K74" s="4">
         <v>9</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M74" s="12">
         <v>9</v>
@@ -3625,7 +3662,7 @@
         <v>10</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C76" s="4">
         <v>6</v>
@@ -3655,7 +3692,7 @@
         <v>8</v>
       </c>
       <c r="L76" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M76" s="12">
         <v>5</v>
@@ -3702,7 +3739,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B78" s="44"/>
       <c r="C78" s="44">
@@ -3737,7 +3774,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B79" s="39"/>
       <c r="C79" s="39">
@@ -3766,19 +3803,19 @@
     </row>
     <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B80" s="42"/>
       <c r="C80" s="42">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D80" s="42"/>
       <c r="E80" s="42">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F80" s="42"/>
       <c r="G80" s="42">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H80" s="42"/>
       <c r="I80" s="42">
@@ -3786,13 +3823,13 @@
       </c>
       <c r="J80" s="42"/>
       <c r="K80" s="42">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L80" s="42"/>
       <c r="M80" s="43">
-        <v>0</v>
-      </c>
-      <c r="N80" s="48"/>
+        <v>12</v>
+      </c>
+      <c r="N80" s="46"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="33"/>
@@ -3827,7 +3864,7 @@
     <row r="83" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>2</v>
@@ -3871,37 +3908,37 @@
         <v>7</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C85" s="4">
         <v>10</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E85" s="4">
         <v>10</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G85" s="4">
         <v>9</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I85" s="4">
         <v>10</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K85" s="4">
         <v>10</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M85" s="12">
         <v>10</v>
@@ -3912,37 +3949,37 @@
         <v>8</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C86" s="4">
         <v>9</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E86" s="4">
         <v>9</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G86" s="4">
         <v>8</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I86" s="4">
         <v>9</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K86" s="4">
         <v>9</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M86" s="12">
         <v>9</v>
@@ -3994,7 +4031,7 @@
         <v>10</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C88" s="4">
         <v>6</v>
@@ -4022,7 +4059,7 @@
       </c>
       <c r="K88" s="4"/>
       <c r="L88" s="21" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="M88" s="12">
         <v>7</v>
@@ -4030,7 +4067,7 @@
     </row>
     <row r="89" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B89" s="30" t="s">
         <v>13</v>
@@ -4058,8 +4095,8 @@
       <c r="M89" s="31"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="49" t="s">
-        <v>41</v>
+      <c r="A90" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B90" s="44"/>
       <c r="C90" s="44">
@@ -4094,7 +4131,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B91" s="39"/>
       <c r="C91" s="39">
@@ -4123,19 +4160,19 @@
     </row>
     <row r="92" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B92" s="42"/>
       <c r="C92" s="42">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D92" s="42"/>
       <c r="E92" s="42">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F92" s="42"/>
       <c r="G92" s="42">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H92" s="42"/>
       <c r="I92" s="42">
@@ -4143,18 +4180,18 @@
       </c>
       <c r="J92" s="42"/>
       <c r="K92" s="42">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L92" s="42"/>
       <c r="M92" s="43">
-        <v>2</v>
-      </c>
-      <c r="N92" s="48"/>
+        <v>14</v>
+      </c>
+      <c r="N92" s="46"/>
     </row>
     <row r="93" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>2</v>
@@ -4198,37 +4235,37 @@
         <v>7</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C95" s="4">
         <v>10</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E95" s="4">
         <v>10</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G95" s="4">
         <v>9</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I95" s="4">
         <v>10</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K95" s="4">
         <v>10</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M95" s="12">
         <v>10</v>
@@ -4239,37 +4276,37 @@
         <v>8</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C96" s="4">
         <v>9</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E96" s="4">
         <v>9</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G96" s="4">
         <v>8</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I96" s="4">
         <v>9</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K96" s="4">
         <v>9</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M96" s="12">
         <v>9</v>
@@ -4321,7 +4358,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C98" s="4">
         <v>6</v>
@@ -4351,7 +4388,7 @@
         <v>8</v>
       </c>
       <c r="L98" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M98" s="12">
         <v>5</v>
@@ -4397,8 +4434,8 @@
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" s="49" t="s">
-        <v>41</v>
+      <c r="A100" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B100" s="44"/>
       <c r="C100" s="44">
@@ -4433,7 +4470,7 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B101" s="39"/>
       <c r="C101" s="39">
@@ -4462,19 +4499,19 @@
     </row>
     <row r="102" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B102" s="42"/>
       <c r="C102" s="42">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D102" s="42"/>
       <c r="E102" s="42">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F102" s="42"/>
       <c r="G102" s="42">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H102" s="42"/>
       <c r="I102" s="42">
@@ -4482,18 +4519,18 @@
       </c>
       <c r="J102" s="42"/>
       <c r="K102" s="42">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L102" s="42"/>
       <c r="M102" s="43">
-        <v>1</v>
-      </c>
-      <c r="N102" s="48"/>
+        <v>13</v>
+      </c>
+      <c r="N102" s="46"/>
     </row>
     <row r="103" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>2</v>
@@ -4531,49 +4568,50 @@
       <c r="M104" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O104" s="57" t="s">
-        <v>66</v>
-      </c>
+      <c r="O104" s="2"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C105" s="4">
         <v>10</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E105" s="4">
         <v>10</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G105" s="4">
         <v>9</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I105" s="4">
         <v>10</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K105" s="4">
         <v>10</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M105" s="12">
         <v>10</v>
+      </c>
+      <c r="N105" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
@@ -4581,37 +4619,37 @@
         <v>8</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C106" s="4">
         <v>9</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E106" s="4">
         <v>9</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G106" s="4">
         <v>8</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I106" s="4">
         <v>9</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K106" s="4">
         <v>9</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M106" s="12">
         <v>9</v>
@@ -4660,30 +4698,24 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C108" s="20">
-        <v>5</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C108" s="20"/>
       <c r="D108" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E108" s="20">
-        <v>5</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E108" s="20"/>
       <c r="F108" s="16" t="s">
         <v>13</v>
       </c>
       <c r="G108" s="16"/>
       <c r="H108" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="I108" s="20">
-        <v>5</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I108" s="20"/>
       <c r="J108" s="16" t="s">
         <v>13</v>
       </c>
@@ -4720,9 +4752,11 @@
         <v>8</v>
       </c>
       <c r="J109" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="K109" s="23"/>
+        <v>12</v>
+      </c>
+      <c r="K109" s="23">
+        <v>8</v>
+      </c>
       <c r="L109" s="23" t="s">
         <v>14</v>
       </c>
@@ -4731,18 +4765,18 @@
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A110" s="49" t="s">
-        <v>41</v>
+      <c r="A110" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B110" s="44"/>
       <c r="C110" s="44">
         <f>SUM(C105:C109)</f>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D110" s="44"/>
       <c r="E110" s="44">
         <f>SUM(E105:E109)</f>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F110" s="44"/>
       <c r="G110" s="44">
@@ -4752,12 +4786,12 @@
       <c r="H110" s="44"/>
       <c r="I110" s="44">
         <f>SUM(I105:I109)</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J110" s="44"/>
       <c r="K110" s="44">
         <f>SUM(K105:K109)</f>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L110" s="44"/>
       <c r="M110" s="45">
@@ -4767,27 +4801,27 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B111" s="39"/>
       <c r="C111" s="39">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D111" s="39"/>
       <c r="E111" s="39">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F111" s="39"/>
       <c r="G111" s="39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H111" s="39"/>
       <c r="I111" s="39">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J111" s="39"/>
       <c r="K111" s="39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L111" s="39"/>
       <c r="M111" s="40">
@@ -4796,38 +4830,38 @@
     </row>
     <row r="112" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B112" s="42"/>
       <c r="C112" s="42">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D112" s="42"/>
       <c r="E112" s="42">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F112" s="42"/>
       <c r="G112" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="42"/>
       <c r="I112" s="42">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J112" s="42"/>
       <c r="K112" s="42">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L112" s="42"/>
       <c r="M112" s="43">
-        <v>3</v>
-      </c>
-      <c r="N112" s="48"/>
+        <v>15</v>
+      </c>
+      <c r="N112" s="46"/>
     </row>
     <row r="113" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>2</v>
@@ -4871,37 +4905,35 @@
         <v>7</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C115" s="4">
         <v>10</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E115" s="4">
         <v>10</v>
       </c>
-      <c r="F115" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="G115" s="4">
-        <v>9</v>
-      </c>
+      <c r="F115" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I115" s="4">
         <v>10</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K115" s="4">
         <v>10</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M115" s="12">
         <v>10</v>
@@ -4912,37 +4944,35 @@
         <v>8</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C116" s="4">
         <v>9</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E116" s="4">
         <v>9</v>
       </c>
-      <c r="F116" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="G116" s="4">
-        <v>8</v>
-      </c>
+      <c r="F116" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I116" s="4">
         <v>9</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K116" s="4">
         <v>9</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M116" s="12">
         <v>9</v>
@@ -4964,12 +4994,10 @@
       <c r="E117" s="4">
         <v>8</v>
       </c>
-      <c r="F117" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="G117" s="4">
-        <v>7</v>
-      </c>
+      <c r="F117" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
         <v>12</v>
       </c>
@@ -4994,7 +5022,7 @@
         <v>10</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C118" s="4">
         <v>6</v>
@@ -5005,12 +5033,10 @@
       <c r="E118" s="4">
         <v>8</v>
       </c>
-      <c r="F118" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G118" s="4">
-        <v>5</v>
-      </c>
+      <c r="F118" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G118" s="4"/>
       <c r="H118" s="5" t="s">
         <v>19</v>
       </c>
@@ -5024,7 +5050,7 @@
         <v>8</v>
       </c>
       <c r="L118" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M118" s="12">
         <v>5</v>
@@ -5046,12 +5072,10 @@
       <c r="E119" s="23">
         <v>8</v>
       </c>
-      <c r="F119" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="G119" s="23">
-        <v>7</v>
-      </c>
+      <c r="F119" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G119" s="23"/>
       <c r="H119" s="23" t="s">
         <v>12</v>
       </c>
@@ -5070,8 +5094,8 @@
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A120" s="49" t="s">
-        <v>41</v>
+      <c r="A120" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B120" s="44"/>
       <c r="C120" s="44">
@@ -5086,7 +5110,7 @@
       <c r="F120" s="44"/>
       <c r="G120" s="44">
         <f>SUM(G115:G119)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H120" s="44"/>
       <c r="I120" s="44">
@@ -5106,7 +5130,7 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B121" s="39"/>
       <c r="C121" s="39">
@@ -5118,7 +5142,7 @@
       </c>
       <c r="F121" s="39"/>
       <c r="G121" s="39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" s="39"/>
       <c r="I121" s="39">
@@ -5135,15 +5159,15 @@
     </row>
     <row r="122" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B122" s="42"/>
       <c r="C122" s="42">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D122" s="42"/>
       <c r="E122" s="42">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F122" s="42"/>
       <c r="G122" s="42">
@@ -5151,17 +5175,17 @@
       </c>
       <c r="H122" s="42"/>
       <c r="I122" s="42">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J122" s="42"/>
       <c r="K122" s="42">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L122" s="42"/>
       <c r="M122" s="43">
-        <v>2</v>
-      </c>
-      <c r="N122" s="48"/>
+        <v>14</v>
+      </c>
+      <c r="N122" s="46"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="33"/>
@@ -5196,7 +5220,7 @@
     <row r="125" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B126" s="8" t="s">
         <v>2</v>
@@ -5240,37 +5264,35 @@
         <v>7</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C127" s="4">
         <v>10</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E127" s="4">
         <v>10</v>
       </c>
-      <c r="F127" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="G127" s="4">
-        <v>9</v>
-      </c>
+      <c r="F127" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G127" s="4"/>
       <c r="H127" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I127" s="4">
         <v>10</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K127" s="4">
         <v>10</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M127" s="12">
         <v>10</v>
@@ -5281,43 +5303,41 @@
         <v>8</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C128" s="4">
         <v>9</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E128" s="4">
         <v>9</v>
       </c>
-      <c r="F128" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="G128" s="4">
-        <v>8</v>
-      </c>
+      <c r="F128" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G128" s="4"/>
       <c r="H128" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I128" s="4">
         <v>9</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K128" s="4">
         <v>9</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M128" s="12">
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>9</v>
       </c>
@@ -5333,12 +5353,10 @@
       <c r="E129" s="4">
         <v>8</v>
       </c>
-      <c r="F129" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="G129" s="4">
-        <v>7</v>
-      </c>
+      <c r="F129" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
         <v>12</v>
       </c>
@@ -5358,12 +5376,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C130" s="4">
         <v>6</v>
@@ -5374,12 +5392,10 @@
       <c r="E130" s="4">
         <v>4</v>
       </c>
-      <c r="F130" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G130" s="4">
-        <v>5</v>
-      </c>
+      <c r="F130" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
         <v>12</v>
       </c>
@@ -5399,7 +5415,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>11</v>
       </c>
@@ -5415,12 +5431,10 @@
       <c r="E131" s="23">
         <v>8</v>
       </c>
-      <c r="F131" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G131" s="23">
-        <v>5</v>
-      </c>
+      <c r="F131" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G131" s="23"/>
       <c r="H131" s="23" t="s">
         <v>12</v>
       </c>
@@ -5432,13 +5446,13 @@
       </c>
       <c r="K131" s="23"/>
       <c r="L131" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M131" s="24"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A132" s="49" t="s">
-        <v>41</v>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B132" s="44"/>
       <c r="C132" s="44">
@@ -5453,7 +5467,7 @@
       <c r="F132" s="44"/>
       <c r="G132" s="44">
         <f>SUM(G127:G131)</f>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H132" s="44"/>
       <c r="I132" s="44">
@@ -5471,9 +5485,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B133" s="39"/>
       <c r="C133" s="39">
@@ -5485,7 +5499,7 @@
       </c>
       <c r="F133" s="39"/>
       <c r="G133" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H133" s="39"/>
       <c r="I133" s="39">
@@ -5500,40 +5514,40 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B134" s="42"/>
       <c r="C134" s="42">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D134" s="42"/>
       <c r="E134" s="42">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F134" s="42"/>
       <c r="G134" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" s="42"/>
       <c r="I134" s="42">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J134" s="42"/>
       <c r="K134" s="42">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L134" s="42"/>
       <c r="M134" s="43">
-        <v>-4</v>
-      </c>
-      <c r="N134" s="48"/>
-    </row>
-    <row r="135" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="N134" s="46"/>
+    </row>
+    <row r="135" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B136" s="8" t="s">
         <v>2</v>
@@ -5571,101 +5585,94 @@
       <c r="M136" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O136" s="55"/>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B137" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C137" s="4">
+        <v>10</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E137" s="4">
+        <v>10</v>
+      </c>
+      <c r="F137" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G137" s="4"/>
+      <c r="H137" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I137" s="4">
+        <v>10</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K137" s="4">
+        <v>10</v>
+      </c>
+      <c r="L137" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M137" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C137" s="4">
-        <v>10</v>
-      </c>
-      <c r="D137" s="4" t="s">
+      <c r="C138" s="4">
+        <v>9</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E137" s="4">
-        <v>10</v>
-      </c>
-      <c r="F137" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="G137" s="4">
-        <v>9</v>
-      </c>
-      <c r="H137" s="4" t="s">
+      <c r="E138" s="4">
+        <v>9</v>
+      </c>
+      <c r="F138" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G138" s="4"/>
+      <c r="H138" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I137" s="4">
-        <v>10</v>
-      </c>
-      <c r="J137" s="4" t="s">
+      <c r="I138" s="4">
+        <v>9</v>
+      </c>
+      <c r="J138" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K137" s="4">
-        <v>10</v>
-      </c>
-      <c r="L137" s="4" t="s">
+      <c r="K138" s="4">
+        <v>9</v>
+      </c>
+      <c r="L138" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M137" s="12">
-        <v>10</v>
-      </c>
-      <c r="O137" s="55"/>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A138" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C138" s="4">
-        <v>9</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E138" s="4">
-        <v>9</v>
-      </c>
-      <c r="F138" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="G138" s="4">
-        <v>8</v>
-      </c>
-      <c r="H138" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I138" s="4">
-        <v>9</v>
-      </c>
-      <c r="J138" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K138" s="4">
-        <v>9</v>
-      </c>
-      <c r="L138" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="M138" s="12">
         <v>9</v>
       </c>
-      <c r="O138" s="55"/>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C139" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>19</v>
@@ -5673,12 +5680,10 @@
       <c r="E139" s="4">
         <v>4</v>
       </c>
-      <c r="F139" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="G139" s="4">
-        <v>7</v>
-      </c>
+      <c r="F139" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
         <v>12</v>
       </c>
@@ -5697,17 +5702,16 @@
       <c r="M139" s="12">
         <v>8</v>
       </c>
-      <c r="O139" s="55"/>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C140" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>12</v>
@@ -5715,18 +5719,14 @@
       <c r="E140" s="4">
         <v>8</v>
       </c>
-      <c r="F140" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G140" s="4">
-        <v>5</v>
-      </c>
+      <c r="F140" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G140" s="4"/>
       <c r="H140" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I140" s="4">
-        <v>4</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I140" s="4"/>
       <c r="J140" s="4" t="s">
         <v>12</v>
       </c>
@@ -5734,35 +5734,28 @@
         <v>8</v>
       </c>
       <c r="L140" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="M140" s="12">
-        <v>5</v>
-      </c>
-      <c r="O140" s="55"/>
-    </row>
-    <row r="141" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="M140" s="12"/>
+    </row>
+    <row r="141" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B141" s="23" t="s">
-        <v>16</v>
+      <c r="B141" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C141" s="23">
-        <v>7</v>
-      </c>
-      <c r="D141" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E141" s="23">
-        <v>8</v>
-      </c>
-      <c r="F141" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="G141" s="23">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D141" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" s="23"/>
+      <c r="F141" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G141" s="23"/>
       <c r="H141" s="23" t="s">
         <v>12</v>
       </c>
@@ -5779,31 +5772,30 @@
       <c r="M141" s="24">
         <v>7</v>
       </c>
-      <c r="O141" s="55"/>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A142" s="49" t="s">
-        <v>41</v>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B142" s="44"/>
       <c r="C142" s="44">
         <f>SUM(C137:C141)</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D142" s="44"/>
       <c r="E142" s="44">
         <f>SUM(E137:E141)</f>
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F142" s="44"/>
       <c r="G142" s="44">
         <f>SUM(G137:G141)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H142" s="44"/>
       <c r="I142" s="44">
         <f>SUM(I137:I141)</f>
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J142" s="44"/>
       <c r="K142" s="44">
@@ -5813,43 +5805,41 @@
       <c r="L142" s="44"/>
       <c r="M142" s="45">
         <f>SUM(M137:M141)</f>
-        <v>39</v>
-      </c>
-      <c r="O142" s="55"/>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B143" s="39"/>
       <c r="C143" s="39">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D143" s="39"/>
       <c r="E143" s="39">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="F143" s="39"/>
       <c r="G143" s="39">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H143" s="39"/>
       <c r="I143" s="39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J143" s="39"/>
       <c r="K143" s="39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L143" s="39"/>
       <c r="M143" s="40">
-        <v>7</v>
-      </c>
-      <c r="O143" s="55"/>
-    </row>
-    <row r="144" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B144" s="42"/>
       <c r="C144" s="42">
@@ -5857,33 +5847,30 @@
       </c>
       <c r="D144" s="42"/>
       <c r="E144" s="42">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F144" s="42"/>
       <c r="G144" s="42">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H144" s="42"/>
       <c r="I144" s="42">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J144" s="42"/>
       <c r="K144" s="42">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L144" s="42"/>
       <c r="M144" s="43">
-        <v>3</v>
-      </c>
-      <c r="N144" s="48"/>
-      <c r="O144" s="55"/>
-    </row>
-    <row r="145" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O145" s="55"/>
-    </row>
+        <v>10</v>
+      </c>
+      <c r="N144" s="46"/>
+    </row>
+    <row r="145" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B146" s="8" t="s">
         <v>2</v>
@@ -5921,91 +5908,84 @@
       <c r="M146" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O146" s="55"/>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C147" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E147" s="4">
-        <v>10</v>
-      </c>
-      <c r="F147" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="G147" s="4">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F147" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G147" s="4"/>
       <c r="H147" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I147" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K147" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M147" s="12">
-        <v>10</v>
-      </c>
-      <c r="O147" s="55"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C148" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E148" s="4">
-        <v>9</v>
-      </c>
-      <c r="F148" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="G148" s="4">
-        <v>8</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F148" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G148" s="4"/>
       <c r="H148" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="I148" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K148" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="M148" s="12">
-        <v>9</v>
-      </c>
-      <c r="O148" s="55"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
@@ -6023,12 +6003,10 @@
       <c r="E149" s="4">
         <v>8</v>
       </c>
-      <c r="F149" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="G149" s="4">
-        <v>7</v>
-      </c>
+      <c r="F149" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G149" s="4"/>
       <c r="H149" s="4" t="s">
         <v>12</v>
       </c>
@@ -6047,7 +6025,6 @@
       <c r="M149" s="12">
         <v>8</v>
       </c>
-      <c r="O149" s="55"/>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
@@ -6057,37 +6034,32 @@
         <v>13</v>
       </c>
       <c r="C150" s="4"/>
-      <c r="D150" s="3" t="s">
-        <v>19</v>
+      <c r="D150" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E150" s="4">
-        <v>4</v>
-      </c>
-      <c r="F150" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G150" s="4">
-        <v>5</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F150" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G150" s="4"/>
       <c r="H150" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I150" s="4">
         <v>8</v>
       </c>
-      <c r="J150" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K150" s="4">
-        <v>8</v>
-      </c>
+      <c r="J150" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K150" s="4"/>
       <c r="L150" s="21" t="s">
         <v>16</v>
       </c>
       <c r="M150" s="12">
         <v>7</v>
       </c>
-      <c r="O150" s="55"/>
     </row>
     <row r="151" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="22" t="s">
@@ -6103,12 +6075,10 @@
       <c r="E151" s="23">
         <v>8</v>
       </c>
-      <c r="F151" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G151" s="23">
-        <v>5</v>
-      </c>
+      <c r="F151" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G151" s="23"/>
       <c r="H151" s="23" t="s">
         <v>12</v>
       </c>
@@ -6119,99 +6089,96 @@
         <v>13</v>
       </c>
       <c r="K151" s="23"/>
-      <c r="L151" s="50" t="s">
+      <c r="L151" s="48" t="s">
         <v>16</v>
       </c>
       <c r="M151" s="24">
         <v>7</v>
       </c>
-      <c r="O151" s="55"/>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B152" s="44"/>
       <c r="C152" s="44">
         <f>SUM(C147:C151)</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D152" s="44"/>
       <c r="E152" s="44">
         <f>SUM(E147:E151)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F152" s="44"/>
       <c r="G152" s="44">
         <f>SUM(G147:G151)</f>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H152" s="44"/>
       <c r="I152" s="44">
         <f>SUM(I147:I151)</f>
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J152" s="44"/>
       <c r="K152" s="44">
         <f>SUM(K147:K151)</f>
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L152" s="44"/>
       <c r="M152" s="45">
         <f>SUM(M147:M151)</f>
-        <v>41</v>
-      </c>
-      <c r="O152" s="55"/>
+        <v>38</v>
+      </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B153" s="39"/>
       <c r="C153" s="39">
-        <v>-13</v>
+        <v>-16</v>
       </c>
       <c r="D153" s="39"/>
       <c r="E153" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F153" s="39"/>
       <c r="G153" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H153" s="39"/>
       <c r="I153" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J153" s="39"/>
       <c r="K153" s="39">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L153" s="39"/>
       <c r="M153" s="40">
-        <v>1</v>
-      </c>
-      <c r="O153" s="55"/>
+        <v>-2</v>
+      </c>
     </row>
     <row r="154" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B154" s="42"/>
       <c r="C154" s="42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D154" s="42"/>
       <c r="E154" s="42">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F154" s="42"/>
       <c r="G154" s="42">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="H154" s="42"/>
       <c r="I154" s="42">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J154" s="42"/>
       <c r="K154" s="42">
@@ -6219,17 +6186,14 @@
       </c>
       <c r="L154" s="42"/>
       <c r="M154" s="43">
-        <v>4</v>
-      </c>
-      <c r="N154" s="48"/>
-      <c r="O154" s="55"/>
-    </row>
-    <row r="155" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O155" s="55"/>
-    </row>
+        <v>8</v>
+      </c>
+      <c r="N154" s="46"/>
+    </row>
+    <row r="155" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B156" s="8" t="s">
         <v>2</v>
@@ -6267,105 +6231,92 @@
       <c r="M156" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O156" s="55"/>
-      <c r="P156" s="56"/>
+      <c r="P156" s="52"/>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B157" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="C157" s="4">
-        <v>10</v>
-      </c>
+      <c r="B157" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C157" s="4"/>
       <c r="D157" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E157" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G157" s="4">
-        <v>9</v>
-      </c>
-      <c r="H157" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="I157" s="4">
-        <v>10</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H157" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I157" s="4"/>
       <c r="J157" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K157" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M157" s="12">
-        <v>10</v>
-      </c>
-      <c r="O157" s="55"/>
-      <c r="P157" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P157" s="52"/>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B158" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="C158" s="4">
-        <v>9</v>
-      </c>
+      <c r="B158" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C158" s="4"/>
       <c r="D158" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E158" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G158" s="4">
-        <v>8</v>
-      </c>
-      <c r="H158" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="I158" s="4">
-        <v>9</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I158" s="4"/>
       <c r="J158" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K158" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="M158" s="12">
-        <v>9</v>
-      </c>
-      <c r="O158" s="55"/>
-      <c r="P158" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P158" s="52"/>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B159" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="C159" s="4">
-        <v>8</v>
-      </c>
+      <c r="B159" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C159" s="4"/>
       <c r="D159" s="4" t="s">
         <v>12</v>
       </c>
@@ -6378,12 +6329,10 @@
       <c r="G159" s="4">
         <v>7</v>
       </c>
-      <c r="H159" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I159" s="4">
-        <v>8</v>
-      </c>
+      <c r="H159" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I159" s="4"/>
       <c r="J159" s="4" t="s">
         <v>12</v>
       </c>
@@ -6396,19 +6345,16 @@
       <c r="M159" s="12">
         <v>8</v>
       </c>
-      <c r="O159" s="55"/>
-      <c r="P159" s="56"/>
+      <c r="P159" s="52"/>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B160" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C160" s="4">
-        <v>6</v>
-      </c>
+      <c r="B160" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C160" s="4"/>
       <c r="D160" s="4" t="s">
         <v>12</v>
       </c>
@@ -6416,35 +6362,32 @@
         <v>8</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G160" s="4">
-        <v>5</v>
-      </c>
-      <c r="H160" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="I160" s="4">
-        <v>4</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I160" s="4"/>
       <c r="J160" s="5" t="s">
         <v>13</v>
       </c>
       <c r="K160" s="4"/>
-      <c r="L160" s="5" t="s">
-        <v>35</v>
+      <c r="L160" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="M160" s="12">
-        <v>5</v>
-      </c>
-      <c r="O160" s="55"/>
-      <c r="P160" s="56"/>
-    </row>
-    <row r="161" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="P160" s="52"/>
+    </row>
+    <row r="161" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="B161" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B161" s="30" t="s">
         <v>13</v>
       </c>
       <c r="C161" s="30"/>
@@ -6456,7 +6399,7 @@
         <v>13</v>
       </c>
       <c r="G161" s="30"/>
-      <c r="H161" s="53" t="s">
+      <c r="H161" s="30" t="s">
         <v>13</v>
       </c>
       <c r="I161" s="30"/>
@@ -6468,116 +6411,111 @@
         <v>13</v>
       </c>
       <c r="M161" s="31"/>
-      <c r="O161" s="55"/>
-      <c r="P161" s="56"/>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P161" s="52"/>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B162" s="44"/>
       <c r="C162" s="44">
         <f>SUM(C157:C161)</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D162" s="44"/>
       <c r="E162" s="44">
         <f>SUM(E157:E161)</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F162" s="44"/>
       <c r="G162" s="44">
         <f>SUM(G157:G161)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H162" s="44"/>
       <c r="I162" s="44">
         <f>SUM(I157:I161)</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J162" s="44"/>
       <c r="K162" s="44">
         <f>SUM(K157:K161)</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L162" s="44"/>
       <c r="M162" s="45">
         <f>SUM(M157:M161)</f>
         <v>32</v>
       </c>
-      <c r="O162" s="55"/>
-      <c r="P162" s="56"/>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P162" s="52"/>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B163" s="39"/>
       <c r="C163" s="39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D163" s="39"/>
       <c r="E163" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F163" s="39"/>
       <c r="G163" s="39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" s="39"/>
       <c r="I163" s="39">
-        <v>-1</v>
+        <v>-32</v>
       </c>
       <c r="J163" s="39"/>
       <c r="K163" s="39">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="L163" s="39"/>
       <c r="M163" s="40">
         <v>0</v>
       </c>
-      <c r="O163" s="55"/>
-      <c r="P163" s="56"/>
-    </row>
-    <row r="164" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P163" s="52"/>
+    </row>
+    <row r="164" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B164" s="42"/>
       <c r="C164" s="42">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D164" s="42"/>
       <c r="E164" s="42">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F164" s="42"/>
       <c r="G164" s="42">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="H164" s="42"/>
       <c r="I164" s="42">
-        <v>37</v>
+        <v>-6</v>
       </c>
       <c r="J164" s="42"/>
       <c r="K164" s="42">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L164" s="42"/>
       <c r="M164" s="43">
-        <v>4</v>
-      </c>
-      <c r="N164" s="48"/>
-      <c r="O164" s="55"/>
-      <c r="P164" s="56"/>
-    </row>
-    <row r="165" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O165" s="55"/>
-      <c r="P165" s="56"/>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="N164" s="46"/>
+      <c r="P164" s="52"/>
+    </row>
+    <row r="165" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P165" s="52"/>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B166" s="8" t="s">
         <v>2</v>
@@ -6615,105 +6553,92 @@
       <c r="M166" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O166" s="55"/>
-      <c r="P166" s="56"/>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P166" s="52"/>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B167" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="C167" s="4">
-        <v>10</v>
-      </c>
+      <c r="B167" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C167" s="4"/>
       <c r="D167" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E167" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G167" s="4">
-        <v>9</v>
-      </c>
-      <c r="H167" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="I167" s="4">
-        <v>10</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H167" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I167" s="4"/>
       <c r="J167" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K167" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L167" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M167" s="12">
-        <v>10</v>
-      </c>
-      <c r="O167" s="55"/>
-      <c r="P167" s="56"/>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="P167" s="52"/>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B168" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="C168" s="4">
-        <v>9</v>
-      </c>
+      <c r="B168" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C168" s="4"/>
       <c r="D168" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E168" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G168" s="4">
-        <v>8</v>
-      </c>
-      <c r="H168" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="I168" s="4">
-        <v>9</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H168" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I168" s="4"/>
       <c r="J168" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K168" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L168" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="M168" s="12">
-        <v>9</v>
-      </c>
-      <c r="O168" s="55"/>
-      <c r="P168" s="56"/>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="P168" s="52"/>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B169" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="C169" s="4">
-        <v>8</v>
-      </c>
+      <c r="B169" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C169" s="4"/>
       <c r="D169" s="4" t="s">
         <v>12</v>
       </c>
@@ -6726,12 +6651,10 @@
       <c r="G169" s="4">
         <v>7</v>
       </c>
-      <c r="H169" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I169" s="4">
-        <v>8</v>
-      </c>
+      <c r="H169" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I169" s="4"/>
       <c r="J169" s="4" t="s">
         <v>12</v>
       </c>
@@ -6744,19 +6667,16 @@
       <c r="M169" s="12">
         <v>8</v>
       </c>
-      <c r="O169" s="55"/>
-      <c r="P169" s="56"/>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P169" s="52"/>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B170" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C170" s="4">
-        <v>6</v>
-      </c>
+      <c r="B170" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C170" s="4"/>
       <c r="D170" s="3" t="s">
         <v>19</v>
       </c>
@@ -6769,12 +6689,10 @@
       <c r="G170" s="4">
         <v>5</v>
       </c>
-      <c r="H170" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I170" s="4">
-        <v>8</v>
-      </c>
+      <c r="H170" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I170" s="4"/>
       <c r="J170" s="4" t="s">
         <v>12</v>
       </c>
@@ -6782,29 +6700,26 @@
         <v>8</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M170" s="12">
-        <v>7</v>
-      </c>
-      <c r="O170" s="55"/>
-      <c r="P170" s="56"/>
-    </row>
-    <row r="171" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="P170" s="52"/>
+    </row>
+    <row r="171" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B171" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" s="23">
-        <v>7</v>
-      </c>
-      <c r="D171" s="23" t="s">
-        <v>12</v>
+      <c r="B171" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C171" s="23"/>
+      <c r="D171" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E171" s="23">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F171" s="23" t="s">
         <v>21</v>
@@ -6812,63 +6727,62 @@
       <c r="G171" s="23">
         <v>5</v>
       </c>
-      <c r="H171" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="I171" s="23">
-        <v>8</v>
-      </c>
+      <c r="H171" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I171" s="23"/>
       <c r="J171" s="23" t="s">
         <v>13</v>
       </c>
       <c r="K171" s="23"/>
-      <c r="L171" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="M171" s="24"/>
-      <c r="O171" s="55"/>
-      <c r="P171" s="56"/>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A172" s="49" t="s">
-        <v>41</v>
+      <c r="L171" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M171" s="24">
+        <v>8</v>
+      </c>
+      <c r="P171" s="52"/>
+      <c r="Q171" s="53"/>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A172" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B172" s="44"/>
       <c r="C172" s="44">
         <f>SUM(C167:C171)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D172" s="44"/>
       <c r="E172" s="44">
         <f>SUM(E167:E171)</f>
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F172" s="44"/>
       <c r="G172" s="44">
         <f>SUM(G167:G171)</f>
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H172" s="44"/>
       <c r="I172" s="44">
         <f>SUM(I167:I171)</f>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J172" s="44"/>
       <c r="K172" s="44">
         <f>SUM(K167:K171)</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L172" s="44"/>
       <c r="M172" s="45">
         <f>SUM(M167:M171)</f>
-        <v>34</v>
-      </c>
-      <c r="O172" s="55"/>
-      <c r="P172" s="56"/>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="P172" s="52"/>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B173" s="39"/>
       <c r="C173" s="39">
@@ -6876,66 +6790,63 @@
       </c>
       <c r="D173" s="39"/>
       <c r="E173" s="39">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="F173" s="39"/>
       <c r="G173" s="39">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="H173" s="39"/>
       <c r="I173" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J173" s="39"/>
       <c r="K173" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L173" s="39"/>
       <c r="M173" s="40">
-        <v>-6</v>
-      </c>
-      <c r="O173" s="55"/>
-      <c r="P173" s="56"/>
-    </row>
-    <row r="174" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P173" s="52"/>
+    </row>
+    <row r="174" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B174" s="42"/>
       <c r="C174" s="42">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D174" s="42"/>
       <c r="E174" s="42">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F174" s="42"/>
       <c r="G174" s="42">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H174" s="42"/>
       <c r="I174" s="42">
-        <v>28</v>
+        <v>-6</v>
       </c>
       <c r="J174" s="42"/>
       <c r="K174" s="42">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L174" s="42"/>
       <c r="M174" s="43">
-        <v>-2</v>
-      </c>
-      <c r="N174" s="51"/>
-      <c r="O174" s="55"/>
-      <c r="P174" s="56"/>
-    </row>
-    <row r="175" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O175" s="55"/>
-      <c r="P175" s="56"/>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="N174" s="46"/>
+      <c r="P174" s="52"/>
+    </row>
+    <row r="175" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P175" s="52"/>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B176" s="8" t="s">
         <v>2</v>
@@ -6973,123 +6884,102 @@
       <c r="M176" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O176" s="55"/>
-      <c r="P176" s="56"/>
+      <c r="P176" s="52"/>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B177" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="C177" s="4">
-        <v>10</v>
-      </c>
-      <c r="D177" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="E177" s="4">
-        <v>10</v>
-      </c>
+      <c r="B177" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C177" s="4"/>
+      <c r="D177" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E177" s="4"/>
       <c r="F177" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G177" s="4">
-        <v>9</v>
-      </c>
-      <c r="H177" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="I177" s="4">
-        <v>10</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H177" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I177" s="4"/>
       <c r="J177" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K177" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M177" s="12">
-        <v>10</v>
-      </c>
-      <c r="O177" s="55"/>
-      <c r="P177" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P177" s="52"/>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B178" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="C178" s="4">
-        <v>9</v>
-      </c>
-      <c r="D178" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="E178" s="4">
-        <v>9</v>
-      </c>
+      <c r="B178" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C178" s="4"/>
+      <c r="D178" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E178" s="4"/>
       <c r="F178" s="4" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G178" s="4">
-        <v>8</v>
-      </c>
-      <c r="H178" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="I178" s="4">
-        <v>9</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H178" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I178" s="4"/>
       <c r="J178" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K178" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="M178" s="12">
-        <v>9</v>
-      </c>
-      <c r="O178" s="55"/>
-      <c r="P178" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P178" s="52"/>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B179" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="C179" s="4">
-        <v>8</v>
-      </c>
-      <c r="D179" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="E179" s="4">
-        <v>8</v>
-      </c>
+      <c r="B179" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C179" s="4"/>
+      <c r="D179" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E179" s="4"/>
       <c r="F179" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G179" s="4">
         <v>7</v>
       </c>
-      <c r="H179" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I179" s="4">
-        <v>8</v>
-      </c>
+      <c r="H179" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I179" s="4"/>
       <c r="J179" s="4" t="s">
         <v>12</v>
       </c>
@@ -7102,37 +6992,30 @@
       <c r="M179" s="12">
         <v>8</v>
       </c>
-      <c r="O179" s="55"/>
-      <c r="P179" s="56"/>
+      <c r="P179" s="52"/>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B180" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C180" s="4">
-        <v>6</v>
-      </c>
-      <c r="D180" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E180" s="4">
-        <v>4</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>21</v>
+      <c r="B180" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C180" s="4"/>
+      <c r="D180" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E180" s="4"/>
+      <c r="F180" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="G180" s="4">
-        <v>5</v>
-      </c>
-      <c r="H180" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I180" s="4">
-        <v>8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H180" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I180" s="4"/>
       <c r="J180" s="4" t="s">
         <v>12</v>
       </c>
@@ -7140,93 +7023,86 @@
         <v>8</v>
       </c>
       <c r="L180" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M180" s="12">
-        <v>7</v>
-      </c>
-      <c r="O180" s="55"/>
-      <c r="P180" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P180" s="52"/>
     </row>
     <row r="181" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B181" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" s="23">
-        <v>7</v>
-      </c>
-      <c r="D181" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E181" s="23">
-        <v>8</v>
-      </c>
+      <c r="B181" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C181" s="23"/>
+      <c r="D181" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E181" s="23"/>
       <c r="F181" s="23" t="s">
         <v>16</v>
       </c>
       <c r="G181" s="23">
         <v>7</v>
       </c>
-      <c r="H181" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="I181" s="23">
-        <v>8</v>
-      </c>
+      <c r="H181" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I181" s="23"/>
       <c r="J181" s="23" t="s">
         <v>13</v>
       </c>
       <c r="K181" s="23"/>
-      <c r="L181" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="M181" s="24"/>
-      <c r="O181" s="55"/>
-      <c r="P181" s="56"/>
+      <c r="L181" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M181" s="24">
+        <v>8</v>
+      </c>
+      <c r="P181" s="52"/>
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A182" s="49" t="s">
-        <v>41</v>
+      <c r="A182" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B182" s="44"/>
       <c r="C182" s="44">
         <f>SUM(C177:C181)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D182" s="44"/>
       <c r="E182" s="44">
         <f>SUM(E177:E181)</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F182" s="44"/>
       <c r="G182" s="44">
         <f>SUM(G177:G181)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H182" s="44"/>
       <c r="I182" s="44">
         <f>SUM(I177:I181)</f>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J182" s="44"/>
       <c r="K182" s="44">
         <f>SUM(K177:K181)</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L182" s="44"/>
       <c r="M182" s="45">
         <f>SUM(M177:M181)</f>
-        <v>34</v>
-      </c>
-      <c r="O182" s="55"/>
-      <c r="P182" s="56"/>
+        <v>40</v>
+      </c>
+      <c r="P182" s="52"/>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B183" s="39"/>
       <c r="C183" s="39">
@@ -7234,66 +7110,63 @@
       </c>
       <c r="D183" s="39"/>
       <c r="E183" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F183" s="39"/>
       <c r="G183" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H183" s="39"/>
       <c r="I183" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J183" s="39"/>
       <c r="K183" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L183" s="39"/>
       <c r="M183" s="40">
-        <v>-6</v>
-      </c>
-      <c r="O183" s="55"/>
-      <c r="P183" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="P183" s="52"/>
     </row>
     <row r="184" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B184" s="42"/>
       <c r="C184" s="42">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D184" s="42"/>
       <c r="E184" s="42">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F184" s="42"/>
       <c r="G184" s="42">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H184" s="42"/>
       <c r="I184" s="42">
-        <v>28</v>
+        <v>-6</v>
       </c>
       <c r="J184" s="42"/>
       <c r="K184" s="42">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L184" s="42"/>
       <c r="M184" s="43">
-        <v>3</v>
-      </c>
-      <c r="N184" s="51"/>
-      <c r="O184" s="55"/>
-      <c r="P184" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="N184" s="46"/>
+      <c r="P184" s="52"/>
     </row>
     <row r="185" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O185" s="55"/>
-      <c r="P185" s="56"/>
+      <c r="P185" s="52"/>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>2</v>
@@ -7331,260 +7204,217 @@
       <c r="M186" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O186" s="55"/>
-      <c r="P186" s="56"/>
+      <c r="P186" s="52"/>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B187" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="C187" s="4">
-        <v>10</v>
-      </c>
-      <c r="D187" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="E187" s="4">
-        <v>10</v>
-      </c>
+      <c r="B187" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C187" s="4"/>
+      <c r="D187" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E187" s="4"/>
       <c r="F187" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G187" s="4">
-        <v>9</v>
-      </c>
-      <c r="H187" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="I187" s="4">
-        <v>10</v>
-      </c>
-      <c r="J187" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="K187" s="4">
-        <v>10</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H187" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I187" s="4"/>
+      <c r="J187" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K187" s="4"/>
       <c r="L187" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M187" s="12">
-        <v>10</v>
-      </c>
-      <c r="O187" s="55"/>
-      <c r="P187" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P187" s="52"/>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B188" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="C188" s="4">
-        <v>9</v>
-      </c>
-      <c r="D188" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="E188" s="4">
-        <v>9</v>
-      </c>
+      <c r="B188" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C188" s="4"/>
+      <c r="D188" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E188" s="4"/>
       <c r="F188" s="4" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G188" s="4">
-        <v>8</v>
-      </c>
-      <c r="H188" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="I188" s="4">
-        <v>9</v>
-      </c>
-      <c r="J188" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="K188" s="4">
-        <v>9</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H188" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I188" s="4"/>
+      <c r="J188" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K188" s="4"/>
       <c r="L188" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="M188" s="12">
-        <v>9</v>
-      </c>
-      <c r="O188" s="55"/>
-      <c r="P188" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P188" s="52"/>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B189" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="C189" s="4">
-        <v>8</v>
-      </c>
-      <c r="D189" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="E189" s="4">
-        <v>8</v>
-      </c>
+      <c r="B189" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C189" s="4"/>
+      <c r="D189" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E189" s="4"/>
       <c r="F189" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G189" s="4">
         <v>7</v>
       </c>
-      <c r="H189" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I189" s="4">
-        <v>8</v>
-      </c>
-      <c r="J189" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="K189" s="4">
-        <v>8</v>
-      </c>
+      <c r="H189" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I189" s="4"/>
+      <c r="J189" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K189" s="4"/>
       <c r="L189" s="4" t="s">
         <v>12</v>
       </c>
       <c r="M189" s="12">
         <v>8</v>
       </c>
-      <c r="O189" s="55"/>
-      <c r="P189" s="56"/>
+      <c r="P189" s="52"/>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B190" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C190" s="4">
-        <v>6</v>
-      </c>
-      <c r="D190" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E190" s="4">
-        <v>4</v>
-      </c>
-      <c r="F190" s="3" t="s">
-        <v>21</v>
+      <c r="B190" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C190" s="4"/>
+      <c r="D190" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E190" s="4"/>
+      <c r="F190" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="G190" s="4">
-        <v>5</v>
-      </c>
-      <c r="H190" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I190" s="4">
-        <v>8</v>
-      </c>
-      <c r="J190" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="K190" s="4">
-        <v>8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H190" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I190" s="4"/>
+      <c r="J190" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K190" s="4"/>
       <c r="L190" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M190" s="12">
-        <v>7</v>
-      </c>
-      <c r="O190" s="55"/>
-      <c r="P190" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P190" s="52"/>
     </row>
     <row r="191" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B191" s="53" t="s">
+      <c r="B191" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C191" s="23"/>
+      <c r="D191" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E191" s="23"/>
+      <c r="F191" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C191" s="23">
-        <v>7</v>
-      </c>
-      <c r="D191" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E191" s="23">
-        <v>8</v>
-      </c>
-      <c r="F191" s="23" t="s">
-        <v>21</v>
-      </c>
       <c r="G191" s="23">
-        <v>5</v>
-      </c>
-      <c r="H191" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="I191" s="23">
-        <v>8</v>
-      </c>
-      <c r="J191" s="53" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="H191" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I191" s="23"/>
+      <c r="J191" s="23" t="s">
+        <v>52</v>
       </c>
       <c r="K191" s="23"/>
-      <c r="L191" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="M191" s="24"/>
-      <c r="O191" s="55"/>
-      <c r="P191" s="56"/>
+      <c r="L191" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M191" s="24">
+        <v>8</v>
+      </c>
+      <c r="P191" s="52"/>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A192" s="49" t="s">
-        <v>41</v>
+      <c r="A192" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B192" s="44"/>
       <c r="C192" s="44">
         <f>SUM(C187:C191)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D192" s="44"/>
       <c r="E192" s="44">
         <f>SUM(E187:E191)</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F192" s="44"/>
       <c r="G192" s="44">
         <f>SUM(G187:G191)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H192" s="44"/>
       <c r="I192" s="44">
         <f>SUM(I187:I191)</f>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J192" s="44"/>
       <c r="K192" s="44">
         <f>SUM(K187:K191)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L192" s="44"/>
       <c r="M192" s="45">
         <f>SUM(M187:M191)</f>
-        <v>34</v>
-      </c>
-      <c r="O192" s="55"/>
-      <c r="P192" s="56"/>
+        <v>40</v>
+      </c>
+      <c r="P192" s="52"/>
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B193" s="39"/>
       <c r="C193" s="39">
@@ -7592,66 +7422,63 @@
       </c>
       <c r="D193" s="39"/>
       <c r="E193" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F193" s="39"/>
       <c r="G193" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H193" s="39"/>
       <c r="I193" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J193" s="39"/>
       <c r="K193" s="39">
-        <v>3</v>
+        <v>-16</v>
       </c>
       <c r="L193" s="39"/>
       <c r="M193" s="40">
-        <v>-6</v>
-      </c>
-      <c r="O193" s="55"/>
-      <c r="P193" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="P193" s="52"/>
     </row>
     <row r="194" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B194" s="42"/>
       <c r="C194" s="42">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D194" s="42"/>
       <c r="E194" s="42">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F194" s="42"/>
       <c r="G194" s="42">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H194" s="42"/>
       <c r="I194" s="42">
-        <v>28</v>
+        <v>-6</v>
       </c>
       <c r="J194" s="42"/>
       <c r="K194" s="42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L194" s="42"/>
       <c r="M194" s="43">
-        <v>3</v>
-      </c>
-      <c r="N194" s="51"/>
-      <c r="O194" s="55"/>
-      <c r="P194" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="N194" s="46"/>
+      <c r="P194" s="52"/>
     </row>
     <row r="195" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O195" s="55"/>
-      <c r="P195" s="56"/>
+      <c r="P195" s="52"/>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>2</v>
@@ -7689,94 +7516,79 @@
       <c r="M196" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O196" s="55"/>
-      <c r="P196" s="56"/>
+      <c r="P196" s="52"/>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B197" s="4" t="s">
-        <v>30</v>
+      <c r="B197" s="23" t="s">
+        <v>28</v>
       </c>
       <c r="C197" s="4">
-        <v>10</v>
-      </c>
-      <c r="D197" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="E197" s="4">
-        <v>10</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D197" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E197" s="4"/>
       <c r="F197" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G197" s="4">
-        <v>9</v>
-      </c>
-      <c r="H197" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="I197" s="4">
-        <v>10</v>
-      </c>
-      <c r="J197" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="K197" s="4">
-        <v>10</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H197" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I197" s="4"/>
+      <c r="J197" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K197" s="4"/>
       <c r="L197" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M197" s="12">
-        <v>10</v>
-      </c>
-      <c r="O197" s="55"/>
-      <c r="P197" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P197" s="52"/>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B198" s="4" t="s">
-        <v>31</v>
+      <c r="B198" s="23" t="s">
+        <v>28</v>
       </c>
       <c r="C198" s="4">
-        <v>9</v>
-      </c>
-      <c r="D198" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="E198" s="4">
-        <v>9</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D198" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E198" s="4"/>
       <c r="F198" s="4" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G198" s="4">
-        <v>8</v>
-      </c>
-      <c r="H198" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="I198" s="4">
-        <v>9</v>
-      </c>
-      <c r="J198" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="K198" s="4">
-        <v>9</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H198" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I198" s="4"/>
+      <c r="J198" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K198" s="4"/>
       <c r="L198" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="M198" s="12">
-        <v>9</v>
-      </c>
-      <c r="O198" s="55"/>
-      <c r="P198" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="P198" s="52"/>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
@@ -7788,228 +7600,201 @@
       <c r="C199" s="4">
         <v>8</v>
       </c>
-      <c r="D199" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="E199" s="4">
-        <v>8</v>
-      </c>
+      <c r="D199" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E199" s="4"/>
       <c r="F199" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G199" s="4">
         <v>7</v>
       </c>
-      <c r="H199" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I199" s="4">
-        <v>8</v>
-      </c>
-      <c r="J199" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="K199" s="4">
-        <v>8</v>
-      </c>
-      <c r="L199" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="M199" s="12">
-        <v>8</v>
-      </c>
-      <c r="O199" s="55"/>
-      <c r="P199" s="56"/>
+      <c r="H199" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I199" s="4"/>
+      <c r="J199" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K199" s="4"/>
+      <c r="L199" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M199" s="12"/>
+      <c r="P199" s="52"/>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B200" s="23" t="s">
-        <v>29</v>
+      <c r="B200" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C200" s="4">
-        <v>6</v>
-      </c>
-      <c r="D200" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E200" s="4">
-        <v>4</v>
-      </c>
-      <c r="F200" s="3" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="D200" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E200" s="4"/>
+      <c r="F200" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="G200" s="4">
-        <v>5</v>
-      </c>
-      <c r="H200" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="I200" s="4">
-        <v>8</v>
-      </c>
-      <c r="J200" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="K200" s="4">
-        <v>8</v>
-      </c>
-      <c r="L200" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="M200" s="12">
-        <v>7</v>
-      </c>
-      <c r="O200" s="55"/>
-      <c r="P200" s="56"/>
+        <v>7</v>
+      </c>
+      <c r="H200" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I200" s="4"/>
+      <c r="J200" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K200" s="4"/>
+      <c r="L200" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M200" s="12"/>
+      <c r="P200" s="52"/>
     </row>
     <row r="201" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C201" s="23">
-        <v>7</v>
-      </c>
-      <c r="D201" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E201" s="23">
-        <v>8</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D201" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E201" s="23"/>
       <c r="F201" s="23" t="s">
         <v>16</v>
       </c>
       <c r="G201" s="23">
         <v>7</v>
       </c>
-      <c r="H201" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="I201" s="23">
-        <v>8</v>
-      </c>
-      <c r="J201" s="53" t="s">
-        <v>13</v>
+      <c r="H201" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="I201" s="23"/>
+      <c r="J201" s="23" t="s">
+        <v>52</v>
       </c>
       <c r="K201" s="23"/>
-      <c r="L201" s="53" t="s">
-        <v>54</v>
+      <c r="L201" s="50" t="s">
+        <v>72</v>
       </c>
       <c r="M201" s="24"/>
-      <c r="O201" s="55"/>
-      <c r="P201" s="56"/>
+      <c r="P201" s="52"/>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A202" s="49" t="s">
-        <v>41</v>
+      <c r="A202" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B202" s="44"/>
       <c r="C202" s="44">
         <f>SUM(C197:C201)</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D202" s="44"/>
       <c r="E202" s="44">
         <f>SUM(E197:E201)</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F202" s="44"/>
       <c r="G202" s="44">
         <f>SUM(G197:G201)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H202" s="44"/>
       <c r="I202" s="44">
         <f>SUM(I197:I201)</f>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J202" s="44"/>
       <c r="K202" s="44">
         <f>SUM(K197:K201)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L202" s="44"/>
       <c r="M202" s="45">
         <f>SUM(M197:M201)</f>
-        <v>34</v>
-      </c>
-      <c r="O202" s="55"/>
-      <c r="P202" s="56"/>
+        <v>16</v>
+      </c>
+      <c r="P202" s="52"/>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B203" s="39"/>
       <c r="C203" s="39">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="D203" s="39"/>
       <c r="E203" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F203" s="39"/>
       <c r="G203" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H203" s="39"/>
       <c r="I203" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J203" s="39"/>
       <c r="K203" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L203" s="39"/>
       <c r="M203" s="40">
-        <v>-6</v>
-      </c>
-      <c r="O203" s="55"/>
-      <c r="P203" s="56"/>
+        <v>-8</v>
+      </c>
+      <c r="P203" s="52"/>
     </row>
     <row r="204" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B204" s="42"/>
       <c r="C204" s="42">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D204" s="42"/>
       <c r="E204" s="42">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F204" s="42"/>
       <c r="G204" s="42">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H204" s="42"/>
       <c r="I204" s="42">
-        <v>28</v>
+        <v>-6</v>
       </c>
       <c r="J204" s="42"/>
       <c r="K204" s="42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L204" s="42"/>
       <c r="M204" s="43">
-        <v>3</v>
-      </c>
-      <c r="N204" s="51"/>
-      <c r="O204" s="55"/>
-      <c r="P204" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="N204" s="46"/>
+      <c r="P204" s="52"/>
     </row>
     <row r="205" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O205" s="55"/>
-      <c r="P205" s="56"/>
+      <c r="P205" s="52"/>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>2</v>
@@ -8047,94 +7832,79 @@
       <c r="M206" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O206" s="55"/>
-      <c r="P206" s="56"/>
+      <c r="P206" s="52"/>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C207" s="4">
-        <v>10</v>
-      </c>
-      <c r="D207" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="E207" s="4">
-        <v>10</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D207" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G207" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I207" s="4">
-        <v>10</v>
-      </c>
-      <c r="J207" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="K207" s="4">
-        <v>10</v>
-      </c>
-      <c r="L207" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="M207" s="12">
-        <v>10</v>
-      </c>
-      <c r="O207" s="55"/>
-      <c r="P207" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="J207" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K207" s="4"/>
+      <c r="L207" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M207" s="12"/>
+      <c r="P207" s="52"/>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C208" s="4">
-        <v>9</v>
-      </c>
-      <c r="D208" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="E208" s="4">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D208" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G208" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="I208" s="4">
-        <v>9</v>
-      </c>
-      <c r="J208" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="K208" s="4">
-        <v>9</v>
-      </c>
-      <c r="L208" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="M208" s="12">
-        <v>9</v>
-      </c>
-      <c r="O208" s="55"/>
-      <c r="P208" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="J208" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K208" s="4"/>
+      <c r="L208" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M208" s="12"/>
+      <c r="P208" s="52"/>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
@@ -8146,12 +7916,10 @@
       <c r="C209" s="4">
         <v>8</v>
       </c>
-      <c r="D209" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="E209" s="4">
-        <v>8</v>
-      </c>
+      <c r="D209" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
         <v>16</v>
       </c>
@@ -8164,42 +7932,35 @@
       <c r="I209" s="4">
         <v>8</v>
       </c>
-      <c r="J209" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="K209" s="4">
-        <v>8</v>
-      </c>
-      <c r="L209" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="M209" s="12">
-        <v>8</v>
-      </c>
-      <c r="O209" s="55"/>
-      <c r="P209" s="56"/>
+      <c r="J209" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K209" s="4"/>
+      <c r="L209" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M209" s="12"/>
+      <c r="P209" s="52"/>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C210" s="4">
-        <v>6</v>
-      </c>
-      <c r="D210" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E210" s="4">
-        <v>4</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="D210" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E210" s="4"/>
+      <c r="F210" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="G210" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H210" s="4" t="s">
         <v>12</v>
@@ -8207,42 +7968,35 @@
       <c r="I210" s="4">
         <v>8</v>
       </c>
-      <c r="J210" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="K210" s="4">
-        <v>8</v>
-      </c>
-      <c r="L210" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="M210" s="12">
-        <v>7</v>
-      </c>
-      <c r="O210" s="55"/>
-      <c r="P210" s="56"/>
+      <c r="J210" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K210" s="4"/>
+      <c r="L210" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M210" s="12"/>
+      <c r="P210" s="52"/>
     </row>
     <row r="211" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B211" s="23" t="s">
+      <c r="B211" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C211" s="23">
         <v>7</v>
       </c>
-      <c r="D211" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E211" s="23">
-        <v>8</v>
-      </c>
+      <c r="D211" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="E211" s="23"/>
       <c r="F211" s="23" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G211" s="23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H211" s="23" t="s">
         <v>12</v>
@@ -8250,124 +8004,119 @@
       <c r="I211" s="23">
         <v>8</v>
       </c>
-      <c r="J211" s="53" t="s">
-        <v>13</v>
+      <c r="J211" s="23" t="s">
+        <v>52</v>
       </c>
       <c r="K211" s="23"/>
-      <c r="L211" s="53" t="s">
-        <v>54</v>
+      <c r="L211" s="50" t="s">
+        <v>72</v>
       </c>
       <c r="M211" s="24"/>
-      <c r="O211" s="55"/>
-      <c r="P211" s="56"/>
+      <c r="P211" s="52"/>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A212" s="49" t="s">
-        <v>41</v>
+      <c r="A212" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B212" s="44"/>
       <c r="C212" s="44">
         <f>SUM(C207:C211)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D212" s="44"/>
       <c r="E212" s="44">
         <f>SUM(E207:E211)</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F212" s="44"/>
       <c r="G212" s="44">
         <f>SUM(G207:G211)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H212" s="44"/>
       <c r="I212" s="44">
         <f>SUM(I207:I211)</f>
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J212" s="44"/>
       <c r="K212" s="44">
         <f>SUM(K207:K211)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L212" s="44"/>
       <c r="M212" s="45">
         <f>SUM(M207:M211)</f>
-        <v>34</v>
-      </c>
-      <c r="O212" s="55"/>
-      <c r="P212" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="P212" s="52"/>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B213" s="39"/>
       <c r="C213" s="39">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D213" s="39"/>
       <c r="E213" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F213" s="39"/>
       <c r="G213" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H213" s="39"/>
       <c r="I213" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J213" s="39"/>
       <c r="K213" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L213" s="39"/>
       <c r="M213" s="40">
-        <v>-6</v>
-      </c>
-      <c r="O213" s="55"/>
-      <c r="P213" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="P213" s="52"/>
     </row>
     <row r="214" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B214" s="42"/>
       <c r="C214" s="42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D214" s="42"/>
       <c r="E214" s="42">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F214" s="42"/>
       <c r="G214" s="42">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H214" s="42"/>
       <c r="I214" s="42">
-        <v>28</v>
+        <v>-6</v>
       </c>
       <c r="J214" s="42"/>
       <c r="K214" s="42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L214" s="42"/>
       <c r="M214" s="43">
-        <v>3</v>
-      </c>
-      <c r="N214" s="51"/>
-      <c r="O214" s="55"/>
-      <c r="P214" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="N214" s="46"/>
+      <c r="P214" s="52"/>
     </row>
     <row r="215" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O215" s="55"/>
-      <c r="P215" s="56"/>
+      <c r="P215" s="52"/>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B216" s="8" t="s">
         <v>2</v>
@@ -8405,94 +8154,83 @@
       <c r="M216" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O216" s="55"/>
-      <c r="P216" s="56"/>
+      <c r="P216" s="52"/>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C217" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E217" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G217" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I217" s="4">
-        <v>10</v>
-      </c>
-      <c r="J217" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="K217" s="4">
-        <v>10</v>
-      </c>
-      <c r="L217" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="M217" s="12">
-        <v>10</v>
-      </c>
-      <c r="O217" s="55"/>
-      <c r="P217" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="J217" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K217" s="4"/>
+      <c r="L217" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M217" s="12"/>
+      <c r="P217" s="52"/>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C218" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E218" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G218" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="I218" s="4">
-        <v>9</v>
-      </c>
-      <c r="J218" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="K218" s="4">
-        <v>9</v>
-      </c>
-      <c r="L218" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="M218" s="12">
-        <v>9</v>
-      </c>
-      <c r="O218" s="55"/>
-      <c r="P218" s="56"/>
+        <v>8</v>
+      </c>
+      <c r="J218" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K218" s="4"/>
+      <c r="L218" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M218" s="12"/>
+      <c r="P218" s="52"/>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
@@ -8510,7 +8248,7 @@
       <c r="E219" s="4">
         <v>8</v>
       </c>
-      <c r="F219" s="52" t="s">
+      <c r="F219" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G219" s="4">
@@ -8522,42 +8260,37 @@
       <c r="I219" s="4">
         <v>8</v>
       </c>
-      <c r="J219" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="K219" s="4">
-        <v>8</v>
-      </c>
-      <c r="L219" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="M219" s="12">
-        <v>8</v>
-      </c>
-      <c r="O219" s="55"/>
-      <c r="P219" s="56"/>
+      <c r="J219" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K219" s="4"/>
+      <c r="L219" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M219" s="12"/>
+      <c r="P219" s="52"/>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C220" s="4">
-        <v>6</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E220" s="4">
-        <v>4</v>
-      </c>
-      <c r="F220" s="52" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="F220" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="G220" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H220" s="4" t="s">
         <v>12</v>
@@ -8565,38 +8298,33 @@
       <c r="I220" s="4">
         <v>8</v>
       </c>
-      <c r="J220" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="K220" s="4">
-        <v>8</v>
-      </c>
-      <c r="L220" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="M220" s="12">
-        <v>7</v>
-      </c>
-      <c r="O220" s="55"/>
-      <c r="P220" s="56"/>
+      <c r="J220" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K220" s="4"/>
+      <c r="L220" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M220" s="12"/>
+      <c r="P220" s="52"/>
     </row>
     <row r="221" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B221" s="23" t="s">
+      <c r="B221" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C221" s="23">
         <v>7</v>
       </c>
-      <c r="D221" s="23" t="s">
+      <c r="D221" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E221" s="23">
         <v>8</v>
       </c>
-      <c r="F221" s="53" t="s">
+      <c r="F221" s="23" t="s">
         <v>16</v>
       </c>
       <c r="G221" s="23">
@@ -8608,124 +8336,119 @@
       <c r="I221" s="23">
         <v>8</v>
       </c>
-      <c r="J221" s="53" t="s">
-        <v>13</v>
+      <c r="J221" s="23" t="s">
+        <v>52</v>
       </c>
       <c r="K221" s="23"/>
-      <c r="L221" s="53" t="s">
-        <v>54</v>
+      <c r="L221" s="50" t="s">
+        <v>72</v>
       </c>
       <c r="M221" s="24"/>
-      <c r="O221" s="55"/>
-      <c r="P221" s="56"/>
+      <c r="P221" s="52"/>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A222" s="49" t="s">
-        <v>41</v>
+      <c r="A222" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B222" s="44"/>
       <c r="C222" s="44">
         <f>SUM(C217:C221)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D222" s="44"/>
       <c r="E222" s="44">
         <f>SUM(E217:E221)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F222" s="44"/>
       <c r="G222" s="44">
         <f>SUM(G217:G221)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H222" s="44"/>
       <c r="I222" s="44">
         <f>SUM(I217:I221)</f>
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J222" s="44"/>
       <c r="K222" s="44">
         <f>SUM(K217:K221)</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L222" s="44"/>
       <c r="M222" s="45">
         <f>SUM(M217:M221)</f>
-        <v>34</v>
-      </c>
-      <c r="O222" s="55"/>
-      <c r="P222" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="P222" s="52"/>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B223" s="39"/>
       <c r="C223" s="39">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D223" s="39"/>
       <c r="E223" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F223" s="39"/>
       <c r="G223" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H223" s="39"/>
       <c r="I223" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J223" s="39"/>
       <c r="K223" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L223" s="39"/>
       <c r="M223" s="40">
-        <v>-6</v>
-      </c>
-      <c r="O223" s="55"/>
-      <c r="P223" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="P223" s="52"/>
     </row>
     <row r="224" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B224" s="42"/>
       <c r="C224" s="42">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="D224" s="42"/>
       <c r="E224" s="42">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F224" s="42"/>
       <c r="G224" s="42">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H224" s="42"/>
       <c r="I224" s="42">
-        <v>28</v>
+        <v>-6</v>
       </c>
       <c r="J224" s="42"/>
       <c r="K224" s="42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L224" s="42"/>
       <c r="M224" s="43">
-        <v>3</v>
-      </c>
-      <c r="N224" s="51"/>
-      <c r="O224" s="55"/>
-      <c r="P224" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="N224" s="46"/>
+      <c r="P224" s="52"/>
     </row>
     <row r="225" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O225" s="55"/>
-      <c r="P225" s="56"/>
+      <c r="P225" s="52"/>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B226" s="8" t="s">
         <v>2</v>
@@ -8763,94 +8486,87 @@
       <c r="M226" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O226" s="55"/>
-      <c r="P226" s="56"/>
+      <c r="P226" s="52"/>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C227" s="4">
         <v>10</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E227" s="4">
         <v>10</v>
       </c>
-      <c r="F227" s="52" t="s">
-        <v>32</v>
+      <c r="F227" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="G227" s="4">
         <v>9</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I227" s="4">
         <v>10</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K227" s="4">
         <v>10</v>
       </c>
-      <c r="L227" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="M227" s="12">
-        <v>10</v>
-      </c>
-      <c r="O227" s="55"/>
-      <c r="P227" s="56"/>
+      <c r="L227" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M227" s="12"/>
+      <c r="P227" s="52"/>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C228" s="4">
         <v>9</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E228" s="4">
         <v>9</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G228" s="4">
         <v>8</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I228" s="4">
         <v>9</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K228" s="4">
         <v>9</v>
       </c>
-      <c r="L228" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="M228" s="12">
-        <v>9</v>
-      </c>
-      <c r="O228" s="55"/>
-      <c r="P228" s="56"/>
+      <c r="L228" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M228" s="12"/>
+      <c r="P228" s="52"/>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
@@ -8886,21 +8602,18 @@
       <c r="K229" s="4">
         <v>8</v>
       </c>
-      <c r="L229" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="M229" s="12">
-        <v>8</v>
-      </c>
-      <c r="O229" s="55"/>
-      <c r="P229" s="56"/>
+      <c r="L229" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M229" s="12"/>
+      <c r="P229" s="52"/>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C230" s="4">
         <v>6</v>
@@ -8911,11 +8624,11 @@
       <c r="E230" s="4">
         <v>4</v>
       </c>
-      <c r="F230" s="3" t="s">
-        <v>21</v>
+      <c r="F230" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="G230" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>12</v>
@@ -8929,14 +8642,11 @@
       <c r="K230" s="4">
         <v>8</v>
       </c>
-      <c r="L230" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="M230" s="12">
-        <v>7</v>
-      </c>
-      <c r="O230" s="55"/>
-      <c r="P230" s="56"/>
+      <c r="L230" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="M230" s="12"/>
+      <c r="P230" s="52"/>
     </row>
     <row r="231" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="22" t="s">
@@ -8970,16 +8680,15 @@
         <v>13</v>
       </c>
       <c r="K231" s="23"/>
-      <c r="L231" s="53" t="s">
-        <v>54</v>
+      <c r="L231" s="50" t="s">
+        <v>72</v>
       </c>
       <c r="M231" s="24"/>
-      <c r="O231" s="55"/>
-      <c r="P231" s="56"/>
+      <c r="P231" s="52"/>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A232" s="49" t="s">
-        <v>41</v>
+      <c r="A232" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B232" s="44"/>
       <c r="C232" s="44">
@@ -8994,7 +8703,7 @@
       <c r="F232" s="44"/>
       <c r="G232" s="44">
         <f>SUM(G227:G231)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H232" s="44"/>
       <c r="I232" s="44">
@@ -9009,14 +8718,13 @@
       <c r="L232" s="44"/>
       <c r="M232" s="45">
         <f>SUM(M227:M231)</f>
-        <v>34</v>
-      </c>
-      <c r="O232" s="55"/>
-      <c r="P232" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="P232" s="52"/>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B233" s="39"/>
       <c r="C233" s="39">
@@ -9028,7 +8736,7 @@
       </c>
       <c r="F233" s="39"/>
       <c r="G233" s="39">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H233" s="39"/>
       <c r="I233" s="39">
@@ -9040,49 +8748,45 @@
       </c>
       <c r="L233" s="39"/>
       <c r="M233" s="40">
-        <v>-6</v>
-      </c>
-      <c r="O233" s="55"/>
-      <c r="P233" s="56"/>
+        <v>0</v>
+      </c>
+      <c r="P233" s="52"/>
     </row>
     <row r="234" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B234" s="42"/>
       <c r="C234" s="42">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="D234" s="42"/>
       <c r="E234" s="42">
-        <v>24</v>
+        <v>-1</v>
       </c>
       <c r="F234" s="42"/>
       <c r="G234" s="42">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H234" s="42"/>
       <c r="I234" s="42">
-        <v>28</v>
+        <v>-3</v>
       </c>
       <c r="J234" s="42"/>
       <c r="K234" s="42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L234" s="42"/>
       <c r="M234" s="43">
-        <v>3</v>
-      </c>
-      <c r="N234" s="51"/>
-      <c r="O234" s="55"/>
-      <c r="P234" s="56"/>
-    </row>
-    <row r="235" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O235" s="55"/>
-    </row>
+        <v>0</v>
+      </c>
+      <c r="N234" s="46"/>
+      <c r="P234" s="52"/>
+    </row>
+    <row r="235" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B236" s="8" t="s">
         <v>2</v>
@@ -9120,91 +8824,88 @@
       <c r="M236" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O236" s="55"/>
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C237" s="4">
         <v>10</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E237" s="4">
         <v>10</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G237" s="4">
         <v>9</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I237" s="4">
         <v>10</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K237" s="4">
         <v>10</v>
       </c>
       <c r="L237" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M237" s="12">
         <v>10</v>
       </c>
-      <c r="O237" s="55"/>
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C238" s="4">
         <v>9</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E238" s="4">
         <v>9</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G238" s="4">
         <v>8</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I238" s="4">
         <v>9</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K238" s="4">
         <v>9</v>
       </c>
       <c r="L238" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M238" s="12">
         <v>9</v>
       </c>
-      <c r="O238" s="55"/>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
@@ -9246,14 +8947,13 @@
       <c r="M239" s="12">
         <v>8</v>
       </c>
-      <c r="O239" s="55"/>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C240" s="4">
         <v>6</v>
@@ -9288,9 +8988,8 @@
       <c r="M240" s="12">
         <v>7</v>
       </c>
-      <c r="O240" s="55"/>
-    </row>
-    <row r="241" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="241" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="22" t="s">
         <v>11</v>
       </c>
@@ -9323,14 +9022,13 @@
       </c>
       <c r="K241" s="23"/>
       <c r="L241" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M241" s="24"/>
-      <c r="O241" s="55"/>
-    </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A242" s="49" t="s">
-        <v>41</v>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A242" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B242" s="44"/>
       <c r="C242" s="44">
@@ -9362,11 +9060,10 @@
         <f>SUM(M237:M241)</f>
         <v>34</v>
       </c>
-      <c r="O242" s="55"/>
-    </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B243" s="39"/>
       <c r="C243" s="39">
@@ -9392,11 +9089,10 @@
       <c r="M243" s="40">
         <v>-6</v>
       </c>
-      <c r="O243" s="55"/>
-    </row>
-    <row r="244" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="244" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B244" s="42"/>
       <c r="C244" s="42">
@@ -9422,15 +9118,12 @@
       <c r="M244" s="43">
         <v>3</v>
       </c>
-      <c r="N244" s="51"/>
-      <c r="O244" s="55"/>
-    </row>
-    <row r="245" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O245" s="55"/>
-    </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N244" s="49"/>
+    </row>
+    <row r="245" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B246" s="8" t="s">
         <v>2</v>
@@ -9468,93 +9161,90 @@
       <c r="M246" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O246" s="55"/>
-    </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C247" s="4">
+        <v>10</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E247" s="4">
+        <v>10</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G247" s="4">
+        <v>9</v>
+      </c>
+      <c r="H247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I247" s="4">
+        <v>10</v>
+      </c>
+      <c r="J247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K247" s="4">
+        <v>10</v>
+      </c>
+      <c r="L247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M247" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A248" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B248" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C247" s="4">
-        <v>10</v>
-      </c>
-      <c r="D247" s="4" t="s">
+      <c r="C248" s="4">
+        <v>9</v>
+      </c>
+      <c r="D248" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E247" s="4">
-        <v>10</v>
-      </c>
-      <c r="F247" s="4" t="s">
+      <c r="E248" s="4">
+        <v>9</v>
+      </c>
+      <c r="F248" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G247" s="4">
-        <v>9</v>
-      </c>
-      <c r="H247" s="4" t="s">
+      <c r="G248" s="4">
+        <v>8</v>
+      </c>
+      <c r="H248" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I247" s="4">
-        <v>10</v>
-      </c>
-      <c r="J247" s="4" t="s">
+      <c r="I248" s="4">
+        <v>9</v>
+      </c>
+      <c r="J248" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K247" s="4">
-        <v>10</v>
-      </c>
-      <c r="L247" s="4" t="s">
+      <c r="K248" s="4">
+        <v>9</v>
+      </c>
+      <c r="L248" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M247" s="12">
-        <v>10</v>
-      </c>
-      <c r="O247" s="55"/>
-    </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A248" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B248" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C248" s="4">
-        <v>9</v>
-      </c>
-      <c r="D248" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E248" s="4">
-        <v>9</v>
-      </c>
-      <c r="F248" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G248" s="4">
-        <v>8</v>
-      </c>
-      <c r="H248" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I248" s="4">
-        <v>9</v>
-      </c>
-      <c r="J248" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K248" s="4">
-        <v>9</v>
-      </c>
-      <c r="L248" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="M248" s="12">
         <v>9</v>
       </c>
-      <c r="O248" s="55"/>
-    </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
         <v>9</v>
       </c>
@@ -9594,14 +9284,13 @@
       <c r="M249" s="12">
         <v>8</v>
       </c>
-      <c r="O249" s="55"/>
-    </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C250" s="4">
         <v>6</v>
@@ -9636,9 +9325,8 @@
       <c r="M250" s="12">
         <v>7</v>
       </c>
-      <c r="O250" s="55"/>
-    </row>
-    <row r="251" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="251" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="22" t="s">
         <v>11</v>
       </c>
@@ -9671,14 +9359,13 @@
       </c>
       <c r="K251" s="23"/>
       <c r="L251" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M251" s="24"/>
-      <c r="O251" s="55"/>
-    </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A252" s="49" t="s">
-        <v>41</v>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A252" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B252" s="44"/>
       <c r="C252" s="44">
@@ -9710,11 +9397,10 @@
         <f>SUM(M247:M251)</f>
         <v>34</v>
       </c>
-      <c r="O252" s="55"/>
-    </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B253" s="39"/>
       <c r="C253" s="39">
@@ -9740,11 +9426,10 @@
       <c r="M253" s="40">
         <v>-6</v>
       </c>
-      <c r="O253" s="55"/>
-    </row>
-    <row r="254" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="254" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B254" s="42"/>
       <c r="C254" s="42">
@@ -9770,15 +9455,12 @@
       <c r="M254" s="43">
         <v>3</v>
       </c>
-      <c r="N254" s="51"/>
-      <c r="O254" s="55"/>
-    </row>
-    <row r="255" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O255" s="55"/>
-    </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N254" s="49"/>
+    </row>
+    <row r="255" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B256" s="8" t="s">
         <v>2</v>
@@ -9816,93 +9498,90 @@
       <c r="M256" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O256" s="55"/>
-    </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B257" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C257" s="4">
+        <v>10</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E257" s="4">
+        <v>10</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G257" s="4">
+        <v>9</v>
+      </c>
+      <c r="H257" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I257" s="4">
+        <v>10</v>
+      </c>
+      <c r="J257" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K257" s="4">
+        <v>10</v>
+      </c>
+      <c r="L257" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M257" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A258" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B258" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C257" s="4">
-        <v>10</v>
-      </c>
-      <c r="D257" s="4" t="s">
+      <c r="C258" s="4">
+        <v>9</v>
+      </c>
+      <c r="D258" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E257" s="4">
-        <v>10</v>
-      </c>
-      <c r="F257" s="4" t="s">
+      <c r="E258" s="4">
+        <v>9</v>
+      </c>
+      <c r="F258" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G257" s="4">
-        <v>9</v>
-      </c>
-      <c r="H257" s="4" t="s">
+      <c r="G258" s="4">
+        <v>8</v>
+      </c>
+      <c r="H258" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I257" s="4">
-        <v>10</v>
-      </c>
-      <c r="J257" s="4" t="s">
+      <c r="I258" s="4">
+        <v>9</v>
+      </c>
+      <c r="J258" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K257" s="4">
-        <v>10</v>
-      </c>
-      <c r="L257" s="4" t="s">
+      <c r="K258" s="4">
+        <v>9</v>
+      </c>
+      <c r="L258" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M257" s="12">
-        <v>10</v>
-      </c>
-      <c r="O257" s="55"/>
-    </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A258" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B258" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C258" s="4">
-        <v>9</v>
-      </c>
-      <c r="D258" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E258" s="4">
-        <v>9</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G258" s="4">
-        <v>8</v>
-      </c>
-      <c r="H258" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I258" s="4">
-        <v>9</v>
-      </c>
-      <c r="J258" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K258" s="4">
-        <v>9</v>
-      </c>
-      <c r="L258" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="M258" s="12">
         <v>9</v>
       </c>
-      <c r="O258" s="55"/>
-    </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" s="11" t="s">
         <v>9</v>
       </c>
@@ -9942,14 +9621,13 @@
       <c r="M259" s="12">
         <v>8</v>
       </c>
-      <c r="O259" s="55"/>
-    </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C260" s="4">
         <v>6</v>
@@ -9984,9 +9662,8 @@
       <c r="M260" s="12">
         <v>7</v>
       </c>
-      <c r="O260" s="55"/>
-    </row>
-    <row r="261" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="261" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="22" t="s">
         <v>11</v>
       </c>
@@ -10019,14 +9696,13 @@
       </c>
       <c r="K261" s="23"/>
       <c r="L261" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M261" s="24"/>
-      <c r="O261" s="55"/>
-    </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A262" s="49" t="s">
-        <v>41</v>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A262" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B262" s="44"/>
       <c r="C262" s="44">
@@ -10058,11 +9734,10 @@
         <f>SUM(M257:M261)</f>
         <v>34</v>
       </c>
-      <c r="O262" s="55"/>
-    </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B263" s="39"/>
       <c r="C263" s="39">
@@ -10088,11 +9763,10 @@
       <c r="M263" s="40">
         <v>-6</v>
       </c>
-      <c r="O263" s="55"/>
-    </row>
-    <row r="264" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="264" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B264" s="42"/>
       <c r="C264" s="42">
@@ -10118,15 +9792,12 @@
       <c r="M264" s="43">
         <v>3</v>
       </c>
-      <c r="N264" s="51"/>
-      <c r="O264" s="55"/>
-    </row>
-    <row r="265" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O265" s="55"/>
-    </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N264" s="49"/>
+    </row>
+    <row r="265" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B266" s="8" t="s">
         <v>2</v>
@@ -10164,93 +9835,90 @@
       <c r="M266" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O266" s="55"/>
-    </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B267" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C267" s="4">
+        <v>10</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E267" s="4">
+        <v>10</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G267" s="4">
+        <v>9</v>
+      </c>
+      <c r="H267" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I267" s="4">
+        <v>10</v>
+      </c>
+      <c r="J267" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K267" s="4">
+        <v>10</v>
+      </c>
+      <c r="L267" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M267" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A268" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B268" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C267" s="4">
-        <v>10</v>
-      </c>
-      <c r="D267" s="4" t="s">
+      <c r="C268" s="4">
+        <v>9</v>
+      </c>
+      <c r="D268" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E267" s="4">
-        <v>10</v>
-      </c>
-      <c r="F267" s="4" t="s">
+      <c r="E268" s="4">
+        <v>9</v>
+      </c>
+      <c r="F268" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G267" s="4">
-        <v>9</v>
-      </c>
-      <c r="H267" s="4" t="s">
+      <c r="G268" s="4">
+        <v>8</v>
+      </c>
+      <c r="H268" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I267" s="4">
-        <v>10</v>
-      </c>
-      <c r="J267" s="4" t="s">
+      <c r="I268" s="4">
+        <v>9</v>
+      </c>
+      <c r="J268" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K267" s="4">
-        <v>10</v>
-      </c>
-      <c r="L267" s="4" t="s">
+      <c r="K268" s="4">
+        <v>9</v>
+      </c>
+      <c r="L268" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M267" s="12">
-        <v>10</v>
-      </c>
-      <c r="O267" s="55"/>
-    </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A268" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B268" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C268" s="4">
-        <v>9</v>
-      </c>
-      <c r="D268" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E268" s="4">
-        <v>9</v>
-      </c>
-      <c r="F268" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G268" s="4">
-        <v>8</v>
-      </c>
-      <c r="H268" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I268" s="4">
-        <v>9</v>
-      </c>
-      <c r="J268" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K268" s="4">
-        <v>9</v>
-      </c>
-      <c r="L268" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="M268" s="12">
         <v>9</v>
       </c>
-      <c r="O268" s="55"/>
-    </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" s="11" t="s">
         <v>9</v>
       </c>
@@ -10290,14 +9958,13 @@
       <c r="M269" s="12">
         <v>8</v>
       </c>
-      <c r="O269" s="55"/>
-    </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C270" s="4">
         <v>6</v>
@@ -10332,9 +9999,8 @@
       <c r="M270" s="12">
         <v>7</v>
       </c>
-      <c r="O270" s="55"/>
-    </row>
-    <row r="271" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="271" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="22" t="s">
         <v>11</v>
       </c>
@@ -10367,14 +10033,13 @@
       </c>
       <c r="K271" s="23"/>
       <c r="L271" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M271" s="24"/>
-      <c r="O271" s="55"/>
-    </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A272" s="49" t="s">
-        <v>41</v>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A272" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="B272" s="44"/>
       <c r="C272" s="44">
@@ -10406,11 +10071,10 @@
         <f>SUM(M267:M271)</f>
         <v>34</v>
       </c>
-      <c r="O272" s="55"/>
-    </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B273" s="39"/>
       <c r="C273" s="39">
@@ -10436,11 +10100,10 @@
       <c r="M273" s="40">
         <v>-6</v>
       </c>
-      <c r="O273" s="55"/>
-    </row>
-    <row r="274" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="274" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B274" s="42"/>
       <c r="C274" s="42">
@@ -10466,8 +10129,7 @@
       <c r="M274" s="43">
         <v>3</v>
       </c>
-      <c r="N274" s="51"/>
-      <c r="O274" s="55"/>
+      <c r="N274" s="49"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="798" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC756A4-3334-4006-8A84-F538883D8EA0}"/>
+  <xr:revisionPtr revIDLastSave="800" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44BA3C20-6AA8-4B2C-8332-5A026191232D}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="30" windowWidth="36255" windowHeight="20550" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="1950" yWindow="1035" windowWidth="32460" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="74">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -179,9 +179,6 @@
     <t>Vecka 18 (20 april-1 maj)</t>
   </si>
   <si>
-    <t>Vecka 19 (4-8 maj</t>
-  </si>
-  <si>
     <t>Vecka 20 (11-15 maj)</t>
   </si>
   <si>
@@ -254,9 +251,6 @@
     <t>07:00-14:45 (Prod)</t>
   </si>
   <si>
-    <t>Ledog</t>
-  </si>
-  <si>
     <t>Semester</t>
   </si>
   <si>
@@ -264,6 +258,9 @@
   </si>
   <si>
     <t>Sommarjobb</t>
+  </si>
+  <si>
+    <t>Vecka 19 (4-8 maj)</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +1460,7 @@
       </c>
       <c r="N10" s="46"/>
       <c r="O10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2857,7 +2854,7 @@
         <v>26</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53" s="20">
         <v>7</v>
@@ -3120,7 +3117,7 @@
         <v>42</v>
       </c>
       <c r="B60" s="54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C60" s="55">
         <v>15</v>
@@ -3134,19 +3131,19 @@
         <v>-3</v>
       </c>
       <c r="H60" s="54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I60" s="55">
         <v>14</v>
       </c>
       <c r="J60" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="K60" s="55">
+        <v>9</v>
+      </c>
+      <c r="L60" s="54" t="s">
         <v>67</v>
-      </c>
-      <c r="K60" s="55">
-        <v>9</v>
-      </c>
-      <c r="L60" s="54" t="s">
-        <v>68</v>
       </c>
       <c r="M60" s="56">
         <v>12</v>
@@ -4059,7 +4056,7 @@
       </c>
       <c r="K88" s="4"/>
       <c r="L88" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M88" s="12">
         <v>7</v>
@@ -4191,7 +4188,7 @@
     <row r="93" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>2</v>
@@ -4530,7 +4527,7 @@
     <row r="103" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>2</v>
@@ -4611,7 +4608,7 @@
         <v>10</v>
       </c>
       <c r="N105" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
@@ -4701,7 +4698,7 @@
         <v>35</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="C108" s="20"/>
       <c r="D108" s="16" t="s">
@@ -4861,7 +4858,7 @@
     <row r="113" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>2</v>
@@ -4917,7 +4914,7 @@
         <v>10</v>
       </c>
       <c r="F115" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
@@ -4956,7 +4953,7 @@
         <v>9</v>
       </c>
       <c r="F116" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
@@ -4995,7 +4992,7 @@
         <v>8</v>
       </c>
       <c r="F117" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
@@ -5034,7 +5031,7 @@
         <v>8</v>
       </c>
       <c r="F118" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="5" t="s">
@@ -5073,7 +5070,7 @@
         <v>8</v>
       </c>
       <c r="F119" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G119" s="23"/>
       <c r="H119" s="23" t="s">
@@ -5220,7 +5217,7 @@
     <row r="125" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B126" s="8" t="s">
         <v>2</v>
@@ -5276,7 +5273,7 @@
         <v>10</v>
       </c>
       <c r="F127" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4" t="s">
@@ -5315,7 +5312,7 @@
         <v>9</v>
       </c>
       <c r="F128" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4" t="s">
@@ -5354,7 +5351,7 @@
         <v>8</v>
       </c>
       <c r="F129" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
@@ -5393,7 +5390,7 @@
         <v>4</v>
       </c>
       <c r="F130" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
@@ -5432,7 +5429,7 @@
         <v>8</v>
       </c>
       <c r="F131" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G131" s="23"/>
       <c r="H131" s="23" t="s">
@@ -5446,7 +5443,7 @@
       </c>
       <c r="K131" s="23"/>
       <c r="L131" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M131" s="24"/>
     </row>
@@ -5547,7 +5544,7 @@
     <row r="135" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B136" s="8" t="s">
         <v>2</v>
@@ -5603,7 +5600,7 @@
         <v>10</v>
       </c>
       <c r="F137" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
@@ -5642,7 +5639,7 @@
         <v>9</v>
       </c>
       <c r="F138" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
@@ -5681,7 +5678,7 @@
         <v>4</v>
       </c>
       <c r="F139" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
@@ -5708,7 +5705,7 @@
         <v>10</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C140" s="4">
         <v>5</v>
@@ -5720,7 +5717,7 @@
         <v>8</v>
       </c>
       <c r="F140" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="5" t="s">
@@ -5743,7 +5740,7 @@
         <v>11</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C141" s="23">
         <v>5</v>
@@ -5753,7 +5750,7 @@
       </c>
       <c r="E141" s="23"/>
       <c r="F141" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G141" s="23"/>
       <c r="H141" s="23" t="s">
@@ -5810,7 +5807,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B143" s="39"/>
       <c r="C143" s="39">
@@ -5926,7 +5923,7 @@
         <v>8</v>
       </c>
       <c r="F147" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G147" s="4"/>
       <c r="H147" s="4" t="s">
@@ -5965,7 +5962,7 @@
         <v>8</v>
       </c>
       <c r="F148" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4" t="s">
@@ -6004,7 +6001,7 @@
         <v>8</v>
       </c>
       <c r="F149" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G149" s="4"/>
       <c r="H149" s="4" t="s">
@@ -6041,7 +6038,7 @@
         <v>8</v>
       </c>
       <c r="F150" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4" t="s">
@@ -6076,7 +6073,7 @@
         <v>8</v>
       </c>
       <c r="F151" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G151" s="23"/>
       <c r="H151" s="23" t="s">
@@ -6238,7 +6235,7 @@
         <v>7</v>
       </c>
       <c r="B157" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4" t="s">
@@ -6276,7 +6273,7 @@
         <v>8</v>
       </c>
       <c r="B158" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4" t="s">
@@ -6314,7 +6311,7 @@
         <v>9</v>
       </c>
       <c r="B159" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4" t="s">
@@ -6352,7 +6349,7 @@
         <v>10</v>
       </c>
       <c r="B160" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4" t="s">
@@ -6515,7 +6512,7 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B166" s="8" t="s">
         <v>2</v>
@@ -6560,7 +6557,7 @@
         <v>7</v>
       </c>
       <c r="B167" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C167" s="4"/>
       <c r="D167" s="4" t="s">
@@ -6576,7 +6573,7 @@
         <v>7</v>
       </c>
       <c r="H167" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I167" s="4"/>
       <c r="J167" s="4" t="s">
@@ -6598,7 +6595,7 @@
         <v>8</v>
       </c>
       <c r="B168" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C168" s="4"/>
       <c r="D168" s="4" t="s">
@@ -6614,7 +6611,7 @@
         <v>7</v>
       </c>
       <c r="H168" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I168" s="4"/>
       <c r="J168" s="4" t="s">
@@ -6636,7 +6633,7 @@
         <v>9</v>
       </c>
       <c r="B169" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4" t="s">
@@ -6652,7 +6649,7 @@
         <v>7</v>
       </c>
       <c r="H169" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I169" s="4"/>
       <c r="J169" s="4" t="s">
@@ -6674,7 +6671,7 @@
         <v>10</v>
       </c>
       <c r="B170" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C170" s="4"/>
       <c r="D170" s="3" t="s">
@@ -6690,7 +6687,7 @@
         <v>5</v>
       </c>
       <c r="H170" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I170" s="4"/>
       <c r="J170" s="4" t="s">
@@ -6712,7 +6709,7 @@
         <v>11</v>
       </c>
       <c r="B171" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C171" s="23"/>
       <c r="D171" s="3" t="s">
@@ -6728,7 +6725,7 @@
         <v>5</v>
       </c>
       <c r="H171" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I171" s="23"/>
       <c r="J171" s="23" t="s">
@@ -6846,7 +6843,7 @@
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B176" s="8" t="s">
         <v>2</v>
@@ -6891,11 +6888,11 @@
         <v>7</v>
       </c>
       <c r="B177" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E177" s="4"/>
       <c r="F177" s="4" t="s">
@@ -6905,7 +6902,7 @@
         <v>7</v>
       </c>
       <c r="H177" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4" t="s">
@@ -6927,11 +6924,11 @@
         <v>8</v>
       </c>
       <c r="B178" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C178" s="4"/>
       <c r="D178" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="4" t="s">
@@ -6941,7 +6938,7 @@
         <v>7</v>
       </c>
       <c r="H178" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I178" s="4"/>
       <c r="J178" s="4" t="s">
@@ -6963,11 +6960,11 @@
         <v>9</v>
       </c>
       <c r="B179" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C179" s="4"/>
       <c r="D179" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="4" t="s">
@@ -6977,7 +6974,7 @@
         <v>7</v>
       </c>
       <c r="H179" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4" t="s">
@@ -6999,11 +6996,11 @@
         <v>10</v>
       </c>
       <c r="B180" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C180" s="4"/>
       <c r="D180" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="23" t="s">
@@ -7013,7 +7010,7 @@
         <v>7</v>
       </c>
       <c r="H180" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I180" s="4"/>
       <c r="J180" s="4" t="s">
@@ -7035,11 +7032,11 @@
         <v>11</v>
       </c>
       <c r="B181" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C181" s="23"/>
       <c r="D181" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E181" s="23"/>
       <c r="F181" s="23" t="s">
@@ -7049,7 +7046,7 @@
         <v>7</v>
       </c>
       <c r="H181" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I181" s="23"/>
       <c r="J181" s="23" t="s">
@@ -7166,7 +7163,7 @@
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>2</v>
@@ -7211,11 +7208,11 @@
         <v>7</v>
       </c>
       <c r="B187" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C187" s="4"/>
       <c r="D187" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E187" s="4"/>
       <c r="F187" s="4" t="s">
@@ -7225,7 +7222,7 @@
         <v>7</v>
       </c>
       <c r="H187" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I187" s="4"/>
       <c r="J187" s="5" t="s">
@@ -7245,11 +7242,11 @@
         <v>8</v>
       </c>
       <c r="B188" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C188" s="4"/>
       <c r="D188" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="4" t="s">
@@ -7259,7 +7256,7 @@
         <v>7</v>
       </c>
       <c r="H188" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I188" s="4"/>
       <c r="J188" s="5" t="s">
@@ -7279,11 +7276,11 @@
         <v>9</v>
       </c>
       <c r="B189" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C189" s="4"/>
       <c r="D189" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="4" t="s">
@@ -7293,11 +7290,11 @@
         <v>7</v>
       </c>
       <c r="H189" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I189" s="4"/>
       <c r="J189" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K189" s="4"/>
       <c r="L189" s="4" t="s">
@@ -7313,11 +7310,11 @@
         <v>10</v>
       </c>
       <c r="B190" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C190" s="4"/>
       <c r="D190" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="23" t="s">
@@ -7327,11 +7324,11 @@
         <v>7</v>
       </c>
       <c r="H190" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I190" s="4"/>
       <c r="J190" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K190" s="4"/>
       <c r="L190" s="4" t="s">
@@ -7347,11 +7344,11 @@
         <v>11</v>
       </c>
       <c r="B191" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C191" s="23"/>
       <c r="D191" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E191" s="23"/>
       <c r="F191" s="23" t="s">
@@ -7361,11 +7358,11 @@
         <v>7</v>
       </c>
       <c r="H191" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I191" s="23"/>
       <c r="J191" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K191" s="23"/>
       <c r="L191" s="4" t="s">
@@ -7478,7 +7475,7 @@
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>2</v>
@@ -7529,7 +7526,7 @@
         <v>6</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="4" t="s">
@@ -7539,11 +7536,11 @@
         <v>7</v>
       </c>
       <c r="H197" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I197" s="4"/>
       <c r="J197" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K197" s="4"/>
       <c r="L197" s="4" t="s">
@@ -7565,7 +7562,7 @@
         <v>6</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="4" t="s">
@@ -7575,11 +7572,11 @@
         <v>7</v>
       </c>
       <c r="H198" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I198" s="4"/>
       <c r="J198" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K198" s="4"/>
       <c r="L198" s="4" t="s">
@@ -7601,7 +7598,7 @@
         <v>8</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="4" t="s">
@@ -7611,11 +7608,11 @@
         <v>7</v>
       </c>
       <c r="H199" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I199" s="4"/>
       <c r="J199" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K199" s="4"/>
       <c r="L199" s="5" t="s">
@@ -7635,7 +7632,7 @@
         <v>8</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="23" t="s">
@@ -7645,15 +7642,15 @@
         <v>7</v>
       </c>
       <c r="H200" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I200" s="4"/>
       <c r="J200" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K200" s="4"/>
       <c r="L200" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M200" s="12"/>
       <c r="P200" s="52"/>
@@ -7669,7 +7666,7 @@
         <v>8</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E201" s="23"/>
       <c r="F201" s="23" t="s">
@@ -7679,15 +7676,15 @@
         <v>7</v>
       </c>
       <c r="H201" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I201" s="23"/>
       <c r="J201" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K201" s="23"/>
       <c r="L201" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M201" s="24"/>
       <c r="P201" s="52"/>
@@ -7794,7 +7791,7 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>2</v>
@@ -7845,7 +7842,7 @@
         <v>8</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
@@ -7861,11 +7858,11 @@
         <v>8</v>
       </c>
       <c r="J207" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K207" s="4"/>
       <c r="L207" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M207" s="12"/>
       <c r="P207" s="52"/>
@@ -7881,7 +7878,7 @@
         <v>8</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
@@ -7897,11 +7894,11 @@
         <v>8</v>
       </c>
       <c r="J208" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K208" s="4"/>
       <c r="L208" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M208" s="12"/>
       <c r="P208" s="52"/>
@@ -7917,7 +7914,7 @@
         <v>8</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
@@ -7933,11 +7930,11 @@
         <v>8</v>
       </c>
       <c r="J209" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K209" s="4"/>
       <c r="L209" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M209" s="12"/>
       <c r="P209" s="52"/>
@@ -7953,7 +7950,7 @@
         <v>8</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="23" t="s">
@@ -7969,11 +7966,11 @@
         <v>8</v>
       </c>
       <c r="J210" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K210" s="4"/>
       <c r="L210" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M210" s="12"/>
       <c r="P210" s="52"/>
@@ -7989,7 +7986,7 @@
         <v>7</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E211" s="23"/>
       <c r="F211" s="23" t="s">
@@ -8005,11 +8002,11 @@
         <v>8</v>
       </c>
       <c r="J211" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K211" s="23"/>
       <c r="L211" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M211" s="24"/>
       <c r="P211" s="52"/>
@@ -8116,7 +8113,7 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B216" s="8" t="s">
         <v>2</v>
@@ -8185,11 +8182,11 @@
         <v>8</v>
       </c>
       <c r="J217" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K217" s="4"/>
       <c r="L217" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M217" s="12"/>
       <c r="P217" s="52"/>
@@ -8223,11 +8220,11 @@
         <v>8</v>
       </c>
       <c r="J218" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K218" s="4"/>
       <c r="L218" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M218" s="12"/>
       <c r="P218" s="52"/>
@@ -8261,11 +8258,11 @@
         <v>8</v>
       </c>
       <c r="J219" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K219" s="4"/>
       <c r="L219" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M219" s="12"/>
       <c r="P219" s="52"/>
@@ -8299,11 +8296,11 @@
         <v>8</v>
       </c>
       <c r="J220" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K220" s="4"/>
       <c r="L220" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M220" s="12"/>
       <c r="P220" s="52"/>
@@ -8337,11 +8334,11 @@
         <v>8</v>
       </c>
       <c r="J221" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K221" s="23"/>
       <c r="L221" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M221" s="24"/>
       <c r="P221" s="52"/>
@@ -8448,7 +8445,7 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B226" s="8" t="s">
         <v>2</v>
@@ -8523,7 +8520,7 @@
         <v>10</v>
       </c>
       <c r="L227" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M227" s="12"/>
       <c r="P227" s="52"/>
@@ -8563,7 +8560,7 @@
         <v>9</v>
       </c>
       <c r="L228" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M228" s="12"/>
       <c r="P228" s="52"/>
@@ -8603,7 +8600,7 @@
         <v>8</v>
       </c>
       <c r="L229" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M229" s="12"/>
       <c r="P229" s="52"/>
@@ -8643,7 +8640,7 @@
         <v>8</v>
       </c>
       <c r="L230" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M230" s="12"/>
       <c r="P230" s="52"/>
@@ -8681,7 +8678,7 @@
       </c>
       <c r="K231" s="23"/>
       <c r="L231" s="50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M231" s="24"/>
       <c r="P231" s="52"/>
@@ -8786,7 +8783,7 @@
     <row r="235" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B236" s="8" t="s">
         <v>2</v>
@@ -9022,7 +9019,7 @@
       </c>
       <c r="K241" s="23"/>
       <c r="L241" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M241" s="24"/>
     </row>
@@ -9123,7 +9120,7 @@
     <row r="245" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B246" s="8" t="s">
         <v>2</v>
@@ -9359,7 +9356,7 @@
       </c>
       <c r="K251" s="23"/>
       <c r="L251" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M251" s="24"/>
     </row>
@@ -9460,7 +9457,7 @@
     <row r="255" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B256" s="8" t="s">
         <v>2</v>
@@ -9696,7 +9693,7 @@
       </c>
       <c r="K261" s="23"/>
       <c r="L261" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M261" s="24"/>
     </row>
@@ -9797,7 +9794,7 @@
     <row r="265" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B266" s="8" t="s">
         <v>2</v>
@@ -10033,7 +10030,7 @@
       </c>
       <c r="K271" s="23"/>
       <c r="L271" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M271" s="24"/>
     </row>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="800" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44BA3C20-6AA8-4B2C-8332-5A026191232D}"/>
+  <xr:revisionPtr revIDLastSave="801" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{399064FA-A289-48D7-9CE9-0E1DCCAC933E}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1035" windowWidth="32460" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="2340" yWindow="1035" windowWidth="32460" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -176,9 +176,6 @@
     <t>Vecka 17 (20-24 april)</t>
   </si>
   <si>
-    <t>Vecka 18 (20 april-1 maj)</t>
-  </si>
-  <si>
     <t>Vecka 20 (11-15 maj)</t>
   </si>
   <si>
@@ -261,6 +258,9 @@
   </si>
   <si>
     <t>Vecka 19 (4-8 maj)</t>
+  </si>
+  <si>
+    <t>Vecka 18 (27 april-1 maj)</t>
   </si>
 </sst>
 </file>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="N10" s="46"/>
       <c r="O10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2854,7 +2854,7 @@
         <v>26</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C53" s="20">
         <v>7</v>
@@ -3117,7 +3117,7 @@
         <v>42</v>
       </c>
       <c r="B60" s="54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" s="55">
         <v>15</v>
@@ -3131,19 +3131,19 @@
         <v>-3</v>
       </c>
       <c r="H60" s="54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I60" s="55">
         <v>14</v>
       </c>
       <c r="J60" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="K60" s="55">
+        <v>9</v>
+      </c>
+      <c r="L60" s="54" t="s">
         <v>66</v>
-      </c>
-      <c r="K60" s="55">
-        <v>9</v>
-      </c>
-      <c r="L60" s="54" t="s">
-        <v>67</v>
       </c>
       <c r="M60" s="56">
         <v>12</v>
@@ -3861,7 +3861,7 @@
     <row r="83" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>2</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="K88" s="4"/>
       <c r="L88" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M88" s="12">
         <v>7</v>
@@ -4188,7 +4188,7 @@
     <row r="93" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>2</v>
@@ -4527,7 +4527,7 @@
     <row r="103" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>2</v>
@@ -4608,7 +4608,7 @@
         <v>10</v>
       </c>
       <c r="N105" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
@@ -4858,7 +4858,7 @@
     <row r="113" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>2</v>
@@ -4914,7 +4914,7 @@
         <v>10</v>
       </c>
       <c r="F115" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4" t="s">
@@ -4953,7 +4953,7 @@
         <v>9</v>
       </c>
       <c r="F116" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="s">
@@ -4992,7 +4992,7 @@
         <v>8</v>
       </c>
       <c r="F117" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4" t="s">
@@ -5031,7 +5031,7 @@
         <v>8</v>
       </c>
       <c r="F118" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="5" t="s">
@@ -5070,7 +5070,7 @@
         <v>8</v>
       </c>
       <c r="F119" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G119" s="23"/>
       <c r="H119" s="23" t="s">
@@ -5217,7 +5217,7 @@
     <row r="125" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B126" s="8" t="s">
         <v>2</v>
@@ -5273,7 +5273,7 @@
         <v>10</v>
       </c>
       <c r="F127" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4" t="s">
@@ -5312,7 +5312,7 @@
         <v>9</v>
       </c>
       <c r="F128" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4" t="s">
@@ -5351,7 +5351,7 @@
         <v>8</v>
       </c>
       <c r="F129" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4" t="s">
@@ -5390,7 +5390,7 @@
         <v>4</v>
       </c>
       <c r="F130" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
@@ -5429,7 +5429,7 @@
         <v>8</v>
       </c>
       <c r="F131" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G131" s="23"/>
       <c r="H131" s="23" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="K131" s="23"/>
       <c r="L131" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M131" s="24"/>
     </row>
@@ -5544,7 +5544,7 @@
     <row r="135" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B136" s="8" t="s">
         <v>2</v>
@@ -5600,7 +5600,7 @@
         <v>10</v>
       </c>
       <c r="F137" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
@@ -5639,7 +5639,7 @@
         <v>9</v>
       </c>
       <c r="F138" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
@@ -5678,7 +5678,7 @@
         <v>4</v>
       </c>
       <c r="F139" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
@@ -5705,7 +5705,7 @@
         <v>10</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C140" s="4">
         <v>5</v>
@@ -5717,7 +5717,7 @@
         <v>8</v>
       </c>
       <c r="F140" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="5" t="s">
@@ -5740,7 +5740,7 @@
         <v>11</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C141" s="23">
         <v>5</v>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="E141" s="23"/>
       <c r="F141" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G141" s="23"/>
       <c r="H141" s="23" t="s">
@@ -5807,7 +5807,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B143" s="39"/>
       <c r="C143" s="39">
@@ -5923,7 +5923,7 @@
         <v>8</v>
       </c>
       <c r="F147" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G147" s="4"/>
       <c r="H147" s="4" t="s">
@@ -5962,7 +5962,7 @@
         <v>8</v>
       </c>
       <c r="F148" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4" t="s">
@@ -6001,7 +6001,7 @@
         <v>8</v>
       </c>
       <c r="F149" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G149" s="4"/>
       <c r="H149" s="4" t="s">
@@ -6038,7 +6038,7 @@
         <v>8</v>
       </c>
       <c r="F150" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4" t="s">
@@ -6073,7 +6073,7 @@
         <v>8</v>
       </c>
       <c r="F151" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G151" s="23"/>
       <c r="H151" s="23" t="s">
@@ -6235,7 +6235,7 @@
         <v>7</v>
       </c>
       <c r="B157" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4" t="s">
@@ -6273,7 +6273,7 @@
         <v>8</v>
       </c>
       <c r="B158" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4" t="s">
@@ -6311,7 +6311,7 @@
         <v>9</v>
       </c>
       <c r="B159" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4" t="s">
@@ -6349,7 +6349,7 @@
         <v>10</v>
       </c>
       <c r="B160" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4" t="s">
@@ -6512,7 +6512,7 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B166" s="8" t="s">
         <v>2</v>
@@ -6557,7 +6557,7 @@
         <v>7</v>
       </c>
       <c r="B167" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C167" s="4"/>
       <c r="D167" s="4" t="s">
@@ -6573,7 +6573,7 @@
         <v>7</v>
       </c>
       <c r="H167" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I167" s="4"/>
       <c r="J167" s="4" t="s">
@@ -6595,7 +6595,7 @@
         <v>8</v>
       </c>
       <c r="B168" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C168" s="4"/>
       <c r="D168" s="4" t="s">
@@ -6611,7 +6611,7 @@
         <v>7</v>
       </c>
       <c r="H168" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I168" s="4"/>
       <c r="J168" s="4" t="s">
@@ -6633,7 +6633,7 @@
         <v>9</v>
       </c>
       <c r="B169" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4" t="s">
@@ -6649,7 +6649,7 @@
         <v>7</v>
       </c>
       <c r="H169" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I169" s="4"/>
       <c r="J169" s="4" t="s">
@@ -6671,7 +6671,7 @@
         <v>10</v>
       </c>
       <c r="B170" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C170" s="4"/>
       <c r="D170" s="3" t="s">
@@ -6687,7 +6687,7 @@
         <v>5</v>
       </c>
       <c r="H170" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I170" s="4"/>
       <c r="J170" s="4" t="s">
@@ -6709,7 +6709,7 @@
         <v>11</v>
       </c>
       <c r="B171" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C171" s="23"/>
       <c r="D171" s="3" t="s">
@@ -6725,7 +6725,7 @@
         <v>5</v>
       </c>
       <c r="H171" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I171" s="23"/>
       <c r="J171" s="23" t="s">
@@ -6843,7 +6843,7 @@
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B176" s="8" t="s">
         <v>2</v>
@@ -6888,11 +6888,11 @@
         <v>7</v>
       </c>
       <c r="B177" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E177" s="4"/>
       <c r="F177" s="4" t="s">
@@ -6902,7 +6902,7 @@
         <v>7</v>
       </c>
       <c r="H177" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4" t="s">
@@ -6924,11 +6924,11 @@
         <v>8</v>
       </c>
       <c r="B178" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C178" s="4"/>
       <c r="D178" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="4" t="s">
@@ -6938,7 +6938,7 @@
         <v>7</v>
       </c>
       <c r="H178" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I178" s="4"/>
       <c r="J178" s="4" t="s">
@@ -6960,11 +6960,11 @@
         <v>9</v>
       </c>
       <c r="B179" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C179" s="4"/>
       <c r="D179" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="4" t="s">
@@ -6974,7 +6974,7 @@
         <v>7</v>
       </c>
       <c r="H179" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4" t="s">
@@ -6996,11 +6996,11 @@
         <v>10</v>
       </c>
       <c r="B180" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C180" s="4"/>
       <c r="D180" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="23" t="s">
@@ -7010,7 +7010,7 @@
         <v>7</v>
       </c>
       <c r="H180" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I180" s="4"/>
       <c r="J180" s="4" t="s">
@@ -7032,11 +7032,11 @@
         <v>11</v>
       </c>
       <c r="B181" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C181" s="23"/>
       <c r="D181" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E181" s="23"/>
       <c r="F181" s="23" t="s">
@@ -7046,7 +7046,7 @@
         <v>7</v>
       </c>
       <c r="H181" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I181" s="23"/>
       <c r="J181" s="23" t="s">
@@ -7163,7 +7163,7 @@
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>2</v>
@@ -7208,11 +7208,11 @@
         <v>7</v>
       </c>
       <c r="B187" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C187" s="4"/>
       <c r="D187" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E187" s="4"/>
       <c r="F187" s="4" t="s">
@@ -7222,7 +7222,7 @@
         <v>7</v>
       </c>
       <c r="H187" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I187" s="4"/>
       <c r="J187" s="5" t="s">
@@ -7242,11 +7242,11 @@
         <v>8</v>
       </c>
       <c r="B188" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C188" s="4"/>
       <c r="D188" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="4" t="s">
@@ -7256,7 +7256,7 @@
         <v>7</v>
       </c>
       <c r="H188" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I188" s="4"/>
       <c r="J188" s="5" t="s">
@@ -7276,11 +7276,11 @@
         <v>9</v>
       </c>
       <c r="B189" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C189" s="4"/>
       <c r="D189" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="4" t="s">
@@ -7290,11 +7290,11 @@
         <v>7</v>
       </c>
       <c r="H189" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I189" s="4"/>
       <c r="J189" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K189" s="4"/>
       <c r="L189" s="4" t="s">
@@ -7310,11 +7310,11 @@
         <v>10</v>
       </c>
       <c r="B190" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C190" s="4"/>
       <c r="D190" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="23" t="s">
@@ -7324,11 +7324,11 @@
         <v>7</v>
       </c>
       <c r="H190" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I190" s="4"/>
       <c r="J190" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K190" s="4"/>
       <c r="L190" s="4" t="s">
@@ -7344,11 +7344,11 @@
         <v>11</v>
       </c>
       <c r="B191" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C191" s="23"/>
       <c r="D191" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E191" s="23"/>
       <c r="F191" s="23" t="s">
@@ -7358,11 +7358,11 @@
         <v>7</v>
       </c>
       <c r="H191" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I191" s="23"/>
       <c r="J191" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K191" s="23"/>
       <c r="L191" s="4" t="s">
@@ -7475,7 +7475,7 @@
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>2</v>
@@ -7526,7 +7526,7 @@
         <v>6</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="4" t="s">
@@ -7536,11 +7536,11 @@
         <v>7</v>
       </c>
       <c r="H197" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I197" s="4"/>
       <c r="J197" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K197" s="4"/>
       <c r="L197" s="4" t="s">
@@ -7562,7 +7562,7 @@
         <v>6</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="4" t="s">
@@ -7572,11 +7572,11 @@
         <v>7</v>
       </c>
       <c r="H198" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I198" s="4"/>
       <c r="J198" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K198" s="4"/>
       <c r="L198" s="4" t="s">
@@ -7598,7 +7598,7 @@
         <v>8</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="4" t="s">
@@ -7608,11 +7608,11 @@
         <v>7</v>
       </c>
       <c r="H199" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I199" s="4"/>
       <c r="J199" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K199" s="4"/>
       <c r="L199" s="5" t="s">
@@ -7632,7 +7632,7 @@
         <v>8</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="23" t="s">
@@ -7642,15 +7642,15 @@
         <v>7</v>
       </c>
       <c r="H200" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I200" s="4"/>
       <c r="J200" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K200" s="4"/>
       <c r="L200" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M200" s="12"/>
       <c r="P200" s="52"/>
@@ -7666,7 +7666,7 @@
         <v>8</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E201" s="23"/>
       <c r="F201" s="23" t="s">
@@ -7676,15 +7676,15 @@
         <v>7</v>
       </c>
       <c r="H201" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I201" s="23"/>
       <c r="J201" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K201" s="23"/>
       <c r="L201" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M201" s="24"/>
       <c r="P201" s="52"/>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>2</v>
@@ -7842,7 +7842,7 @@
         <v>8</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
@@ -7858,11 +7858,11 @@
         <v>8</v>
       </c>
       <c r="J207" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K207" s="4"/>
       <c r="L207" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M207" s="12"/>
       <c r="P207" s="52"/>
@@ -7878,7 +7878,7 @@
         <v>8</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
@@ -7894,11 +7894,11 @@
         <v>8</v>
       </c>
       <c r="J208" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K208" s="4"/>
       <c r="L208" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M208" s="12"/>
       <c r="P208" s="52"/>
@@ -7914,7 +7914,7 @@
         <v>8</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
@@ -7930,11 +7930,11 @@
         <v>8</v>
       </c>
       <c r="J209" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K209" s="4"/>
       <c r="L209" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M209" s="12"/>
       <c r="P209" s="52"/>
@@ -7950,7 +7950,7 @@
         <v>8</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="23" t="s">
@@ -7966,11 +7966,11 @@
         <v>8</v>
       </c>
       <c r="J210" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K210" s="4"/>
       <c r="L210" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M210" s="12"/>
       <c r="P210" s="52"/>
@@ -7986,7 +7986,7 @@
         <v>7</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E211" s="23"/>
       <c r="F211" s="23" t="s">
@@ -8002,11 +8002,11 @@
         <v>8</v>
       </c>
       <c r="J211" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K211" s="23"/>
       <c r="L211" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M211" s="24"/>
       <c r="P211" s="52"/>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B216" s="8" t="s">
         <v>2</v>
@@ -8182,11 +8182,11 @@
         <v>8</v>
       </c>
       <c r="J217" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K217" s="4"/>
       <c r="L217" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M217" s="12"/>
       <c r="P217" s="52"/>
@@ -8220,11 +8220,11 @@
         <v>8</v>
       </c>
       <c r="J218" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K218" s="4"/>
       <c r="L218" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M218" s="12"/>
       <c r="P218" s="52"/>
@@ -8258,11 +8258,11 @@
         <v>8</v>
       </c>
       <c r="J219" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K219" s="4"/>
       <c r="L219" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M219" s="12"/>
       <c r="P219" s="52"/>
@@ -8296,11 +8296,11 @@
         <v>8</v>
       </c>
       <c r="J220" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K220" s="4"/>
       <c r="L220" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M220" s="12"/>
       <c r="P220" s="52"/>
@@ -8334,11 +8334,11 @@
         <v>8</v>
       </c>
       <c r="J221" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K221" s="23"/>
       <c r="L221" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M221" s="24"/>
       <c r="P221" s="52"/>
@@ -8445,7 +8445,7 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B226" s="8" t="s">
         <v>2</v>
@@ -8520,7 +8520,7 @@
         <v>10</v>
       </c>
       <c r="L227" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M227" s="12"/>
       <c r="P227" s="52"/>
@@ -8560,7 +8560,7 @@
         <v>9</v>
       </c>
       <c r="L228" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M228" s="12"/>
       <c r="P228" s="52"/>
@@ -8600,7 +8600,7 @@
         <v>8</v>
       </c>
       <c r="L229" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M229" s="12"/>
       <c r="P229" s="52"/>
@@ -8640,7 +8640,7 @@
         <v>8</v>
       </c>
       <c r="L230" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M230" s="12"/>
       <c r="P230" s="52"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K231" s="23"/>
       <c r="L231" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M231" s="24"/>
       <c r="P231" s="52"/>
@@ -8783,7 +8783,7 @@
     <row r="235" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B236" s="8" t="s">
         <v>2</v>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="K241" s="23"/>
       <c r="L241" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M241" s="24"/>
     </row>
@@ -9120,7 +9120,7 @@
     <row r="245" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B246" s="8" t="s">
         <v>2</v>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="K251" s="23"/>
       <c r="L251" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M251" s="24"/>
     </row>
@@ -9457,7 +9457,7 @@
     <row r="255" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B256" s="8" t="s">
         <v>2</v>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="K261" s="23"/>
       <c r="L261" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M261" s="24"/>
     </row>
@@ -9794,7 +9794,7 @@
     <row r="265" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B266" s="8" t="s">
         <v>2</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="K271" s="23"/>
       <c r="L271" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M271" s="24"/>
     </row>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="801" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{399064FA-A289-48D7-9CE9-0E1DCCAC933E}"/>
+  <xr:revisionPtr revIDLastSave="805" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44870784-8025-4260-ADD5-025E7247D4CD}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1035" windowWidth="32460" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="3120" yWindow="1035" windowWidth="32460" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -604,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -735,7 +735,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3116,36 +3115,36 @@
       <c r="A60" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="54" t="s">
+      <c r="B60" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="55">
+      <c r="C60" s="54">
         <v>15</v>
       </c>
       <c r="D60" s="42"/>
-      <c r="E60" s="55">
+      <c r="E60" s="54">
         <v>8</v>
       </c>
       <c r="F60" s="42"/>
-      <c r="G60" s="55">
+      <c r="G60" s="54">
         <v>-3</v>
       </c>
-      <c r="H60" s="54" t="s">
+      <c r="H60" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="I60" s="55">
+      <c r="I60" s="54">
         <v>14</v>
       </c>
-      <c r="J60" s="54" t="s">
+      <c r="J60" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="K60" s="55">
-        <v>9</v>
-      </c>
-      <c r="L60" s="54" t="s">
+      <c r="K60" s="54">
+        <v>9</v>
+      </c>
+      <c r="L60" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="M60" s="56">
+      <c r="M60" s="55">
         <v>12</v>
       </c>
       <c r="N60" s="46"/>
@@ -3360,12 +3359,10 @@
       <c r="A67" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B67" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" s="23">
-        <v>7</v>
-      </c>
+      <c r="B67" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="23"/>
       <c r="D67" s="23" t="s">
         <v>12</v>
       </c>
@@ -3402,7 +3399,7 @@
       <c r="B68" s="44"/>
       <c r="C68" s="44">
         <f>SUM(C63:C67)</f>
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D68" s="44"/>
       <c r="E68" s="44">
@@ -5864,8 +5861,8 @@
       </c>
       <c r="N144" s="46"/>
     </row>
-    <row r="145" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>36</v>
       </c>
@@ -5906,7 +5903,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>7</v>
       </c>
@@ -5945,7 +5942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>8</v>
       </c>
@@ -5984,7 +5981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>9</v>
       </c>
@@ -6023,7 +6020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
         <v>10</v>
       </c>
@@ -6058,7 +6055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="22" t="s">
         <v>11</v>
       </c>
@@ -6093,7 +6090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="35" t="s">
         <v>40</v>
       </c>
@@ -6128,7 +6125,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="38" t="s">
         <v>41</v>
       </c>
@@ -6157,7 +6154,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="154" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="41" t="s">
         <v>42</v>
       </c>
@@ -6187,8 +6184,8 @@
       </c>
       <c r="N154" s="46"/>
     </row>
-    <row r="155" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>37</v>
       </c>
@@ -6228,9 +6225,8 @@
       <c r="M156" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P156" s="52"/>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
         <v>7</v>
       </c>
@@ -6266,9 +6262,8 @@
       <c r="M157" s="12">
         <v>8</v>
       </c>
-      <c r="P157" s="52"/>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>8</v>
       </c>
@@ -6304,9 +6299,8 @@
       <c r="M158" s="12">
         <v>8</v>
       </c>
-      <c r="P158" s="52"/>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>9</v>
       </c>
@@ -6342,9 +6336,8 @@
       <c r="M159" s="12">
         <v>8</v>
       </c>
-      <c r="P159" s="52"/>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
         <v>10</v>
       </c>
@@ -6378,7 +6371,6 @@
       <c r="M160" s="12">
         <v>8</v>
       </c>
-      <c r="P160" s="52"/>
     </row>
     <row r="161" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="29" t="s">
@@ -6408,7 +6400,6 @@
         <v>13</v>
       </c>
       <c r="M161" s="31"/>
-      <c r="P161" s="52"/>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" s="35" t="s">
@@ -6444,7 +6435,6 @@
         <f>SUM(M157:M161)</f>
         <v>32</v>
       </c>
-      <c r="P162" s="52"/>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" s="38" t="s">
@@ -6474,7 +6464,6 @@
       <c r="M163" s="40">
         <v>0</v>
       </c>
-      <c r="P163" s="52"/>
     </row>
     <row r="164" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="41" t="s">
@@ -6505,11 +6494,8 @@
         <v>8</v>
       </c>
       <c r="N164" s="46"/>
-      <c r="P164" s="52"/>
-    </row>
-    <row r="165" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P165" s="52"/>
-    </row>
+    </row>
+    <row r="165" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>51</v>
@@ -6550,7 +6536,6 @@
       <c r="M166" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P166" s="52"/>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
@@ -6588,7 +6573,6 @@
       <c r="M167" s="12">
         <v>8</v>
       </c>
-      <c r="P167" s="52"/>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
@@ -6626,7 +6610,6 @@
       <c r="M168" s="12">
         <v>8</v>
       </c>
-      <c r="P168" s="52"/>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
@@ -6664,7 +6647,6 @@
       <c r="M169" s="12">
         <v>8</v>
       </c>
-      <c r="P169" s="52"/>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
@@ -6702,7 +6684,6 @@
       <c r="M170" s="12">
         <v>8</v>
       </c>
-      <c r="P170" s="52"/>
     </row>
     <row r="171" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="22" t="s">
@@ -6738,8 +6719,7 @@
       <c r="M171" s="24">
         <v>8</v>
       </c>
-      <c r="P171" s="52"/>
-      <c r="Q171" s="53"/>
+      <c r="Q171" s="52"/>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" s="47" t="s">
@@ -6775,7 +6755,6 @@
         <f>SUM(M167:M171)</f>
         <v>40</v>
       </c>
-      <c r="P172" s="52"/>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="38" t="s">
@@ -6805,7 +6784,6 @@
       <c r="M173" s="40">
         <v>0</v>
       </c>
-      <c r="P173" s="52"/>
     </row>
     <row r="174" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="41" t="s">
@@ -6836,11 +6814,8 @@
         <v>8</v>
       </c>
       <c r="N174" s="46"/>
-      <c r="P174" s="52"/>
-    </row>
-    <row r="175" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P175" s="52"/>
-    </row>
+    </row>
+    <row r="175" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>52</v>
@@ -6881,9 +6856,8 @@
       <c r="M176" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P176" s="52"/>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
         <v>7</v>
       </c>
@@ -6917,9 +6891,8 @@
       <c r="M177" s="12">
         <v>8</v>
       </c>
-      <c r="P177" s="52"/>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>8</v>
       </c>
@@ -6953,9 +6926,8 @@
       <c r="M178" s="12">
         <v>8</v>
       </c>
-      <c r="P178" s="52"/>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>9</v>
       </c>
@@ -6989,9 +6961,8 @@
       <c r="M179" s="12">
         <v>8</v>
       </c>
-      <c r="P179" s="52"/>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>10</v>
       </c>
@@ -7025,9 +6996,8 @@
       <c r="M180" s="12">
         <v>8</v>
       </c>
-      <c r="P180" s="52"/>
-    </row>
-    <row r="181" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="22" t="s">
         <v>11</v>
       </c>
@@ -7059,9 +7029,8 @@
       <c r="M181" s="24">
         <v>8</v>
       </c>
-      <c r="P181" s="52"/>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="47" t="s">
         <v>40</v>
       </c>
@@ -7095,9 +7064,8 @@
         <f>SUM(M177:M181)</f>
         <v>40</v>
       </c>
-      <c r="P182" s="52"/>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="38" t="s">
         <v>41</v>
       </c>
@@ -7125,9 +7093,8 @@
       <c r="M183" s="40">
         <v>0</v>
       </c>
-      <c r="P183" s="52"/>
-    </row>
-    <row r="184" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="41" t="s">
         <v>42</v>
       </c>
@@ -7156,12 +7123,9 @@
         <v>8</v>
       </c>
       <c r="N184" s="46"/>
-      <c r="P184" s="52"/>
-    </row>
-    <row r="185" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P185" s="52"/>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>53</v>
       </c>
@@ -7201,9 +7165,8 @@
       <c r="M186" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P186" s="52"/>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>7</v>
       </c>
@@ -7235,9 +7198,8 @@
       <c r="M187" s="12">
         <v>8</v>
       </c>
-      <c r="P187" s="52"/>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
         <v>8</v>
       </c>
@@ -7269,9 +7231,8 @@
       <c r="M188" s="12">
         <v>8</v>
       </c>
-      <c r="P188" s="52"/>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>9</v>
       </c>
@@ -7303,9 +7264,8 @@
       <c r="M189" s="12">
         <v>8</v>
       </c>
-      <c r="P189" s="52"/>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
         <v>10</v>
       </c>
@@ -7337,9 +7297,8 @@
       <c r="M190" s="12">
         <v>8</v>
       </c>
-      <c r="P190" s="52"/>
-    </row>
-    <row r="191" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="22" t="s">
         <v>11</v>
       </c>
@@ -7371,9 +7330,8 @@
       <c r="M191" s="24">
         <v>8</v>
       </c>
-      <c r="P191" s="52"/>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="47" t="s">
         <v>40</v>
       </c>
@@ -7407,9 +7365,8 @@
         <f>SUM(M187:M191)</f>
         <v>40</v>
       </c>
-      <c r="P192" s="52"/>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="38" t="s">
         <v>41</v>
       </c>
@@ -7437,9 +7394,8 @@
       <c r="M193" s="40">
         <v>0</v>
       </c>
-      <c r="P193" s="52"/>
-    </row>
-    <row r="194" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="41" t="s">
         <v>42</v>
       </c>
@@ -7468,12 +7424,9 @@
         <v>8</v>
       </c>
       <c r="N194" s="46"/>
-      <c r="P194" s="52"/>
-    </row>
-    <row r="195" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P195" s="52"/>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>54</v>
       </c>
@@ -7513,9 +7466,8 @@
       <c r="M196" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P196" s="52"/>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
         <v>7</v>
       </c>
@@ -7549,9 +7501,8 @@
       <c r="M197" s="12">
         <v>8</v>
       </c>
-      <c r="P197" s="52"/>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
         <v>8</v>
       </c>
@@ -7585,9 +7536,8 @@
       <c r="M198" s="12">
         <v>8</v>
       </c>
-      <c r="P198" s="52"/>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
         <v>9</v>
       </c>
@@ -7619,9 +7569,8 @@
         <v>13</v>
       </c>
       <c r="M199" s="12"/>
-      <c r="P199" s="52"/>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
         <v>10</v>
       </c>
@@ -7653,9 +7602,8 @@
         <v>69</v>
       </c>
       <c r="M200" s="12"/>
-      <c r="P200" s="52"/>
-    </row>
-    <row r="201" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="201" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="22" t="s">
         <v>11</v>
       </c>
@@ -7687,9 +7635,8 @@
         <v>69</v>
       </c>
       <c r="M201" s="24"/>
-      <c r="P201" s="52"/>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="47" t="s">
         <v>40</v>
       </c>
@@ -7723,9 +7670,8 @@
         <f>SUM(M197:M201)</f>
         <v>16</v>
       </c>
-      <c r="P202" s="52"/>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="38" t="s">
         <v>41</v>
       </c>
@@ -7753,9 +7699,8 @@
       <c r="M203" s="40">
         <v>-8</v>
       </c>
-      <c r="P203" s="52"/>
-    </row>
-    <row r="204" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="204" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="41" t="s">
         <v>42</v>
       </c>
@@ -7784,12 +7729,9 @@
         <v>0</v>
       </c>
       <c r="N204" s="46"/>
-      <c r="P204" s="52"/>
-    </row>
-    <row r="205" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P205" s="52"/>
-    </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
         <v>55</v>
       </c>
@@ -7829,9 +7771,8 @@
       <c r="M206" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P206" s="52"/>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
         <v>7</v>
       </c>
@@ -7865,9 +7806,8 @@
         <v>69</v>
       </c>
       <c r="M207" s="12"/>
-      <c r="P207" s="52"/>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>8</v>
       </c>
@@ -7901,9 +7841,8 @@
         <v>69</v>
       </c>
       <c r="M208" s="12"/>
-      <c r="P208" s="52"/>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>9</v>
       </c>
@@ -7937,9 +7876,8 @@
         <v>69</v>
       </c>
       <c r="M209" s="12"/>
-      <c r="P209" s="52"/>
-    </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
         <v>10</v>
       </c>
@@ -7973,9 +7911,8 @@
         <v>69</v>
       </c>
       <c r="M210" s="12"/>
-      <c r="P210" s="52"/>
-    </row>
-    <row r="211" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="22" t="s">
         <v>11</v>
       </c>
@@ -8009,9 +7946,8 @@
         <v>69</v>
       </c>
       <c r="M211" s="24"/>
-      <c r="P211" s="52"/>
-    </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" s="47" t="s">
         <v>40</v>
       </c>
@@ -8045,9 +7981,8 @@
         <f>SUM(M207:M211)</f>
         <v>0</v>
       </c>
-      <c r="P212" s="52"/>
-    </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" s="38" t="s">
         <v>41</v>
       </c>
@@ -8075,9 +8010,8 @@
       <c r="M213" s="40">
         <v>0</v>
       </c>
-      <c r="P213" s="52"/>
-    </row>
-    <row r="214" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="41" t="s">
         <v>42</v>
       </c>
@@ -8106,12 +8040,9 @@
         <v>0</v>
       </c>
       <c r="N214" s="46"/>
-      <c r="P214" s="52"/>
-    </row>
-    <row r="215" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P215" s="52"/>
-    </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>56</v>
       </c>
@@ -8151,9 +8082,8 @@
       <c r="M216" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P216" s="52"/>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
         <v>7</v>
       </c>
@@ -8189,9 +8119,8 @@
         <v>69</v>
       </c>
       <c r="M217" s="12"/>
-      <c r="P217" s="52"/>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
         <v>8</v>
       </c>
@@ -8227,9 +8156,8 @@
         <v>69</v>
       </c>
       <c r="M218" s="12"/>
-      <c r="P218" s="52"/>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>9</v>
       </c>
@@ -8265,9 +8193,8 @@
         <v>69</v>
       </c>
       <c r="M219" s="12"/>
-      <c r="P219" s="52"/>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>10</v>
       </c>
@@ -8303,9 +8230,8 @@
         <v>69</v>
       </c>
       <c r="M220" s="12"/>
-      <c r="P220" s="52"/>
-    </row>
-    <row r="221" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="221" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="22" t="s">
         <v>11</v>
       </c>
@@ -8341,9 +8267,8 @@
         <v>69</v>
       </c>
       <c r="M221" s="24"/>
-      <c r="P221" s="52"/>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="47" t="s">
         <v>40</v>
       </c>
@@ -8377,9 +8302,8 @@
         <f>SUM(M217:M221)</f>
         <v>0</v>
       </c>
-      <c r="P222" s="52"/>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" s="38" t="s">
         <v>41</v>
       </c>
@@ -8407,9 +8331,8 @@
       <c r="M223" s="40">
         <v>0</v>
       </c>
-      <c r="P223" s="52"/>
-    </row>
-    <row r="224" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="224" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="41" t="s">
         <v>42</v>
       </c>
@@ -8438,12 +8361,9 @@
         <v>0</v>
       </c>
       <c r="N224" s="46"/>
-      <c r="P224" s="52"/>
-    </row>
-    <row r="225" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P225" s="52"/>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>57</v>
       </c>
@@ -8483,9 +8403,8 @@
       <c r="M226" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P226" s="52"/>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>7</v>
       </c>
@@ -8523,9 +8442,8 @@
         <v>69</v>
       </c>
       <c r="M227" s="12"/>
-      <c r="P227" s="52"/>
-    </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
         <v>8</v>
       </c>
@@ -8563,9 +8481,8 @@
         <v>69</v>
       </c>
       <c r="M228" s="12"/>
-      <c r="P228" s="52"/>
-    </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
         <v>9</v>
       </c>
@@ -8603,9 +8520,8 @@
         <v>69</v>
       </c>
       <c r="M229" s="12"/>
-      <c r="P229" s="52"/>
-    </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
         <v>10</v>
       </c>
@@ -8643,9 +8559,8 @@
         <v>69</v>
       </c>
       <c r="M230" s="12"/>
-      <c r="P230" s="52"/>
-    </row>
-    <row r="231" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="231" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="22" t="s">
         <v>11</v>
       </c>
@@ -8681,9 +8596,8 @@
         <v>69</v>
       </c>
       <c r="M231" s="24"/>
-      <c r="P231" s="52"/>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" s="47" t="s">
         <v>40</v>
       </c>
@@ -8717,9 +8631,8 @@
         <f>SUM(M227:M231)</f>
         <v>0</v>
       </c>
-      <c r="P232" s="52"/>
-    </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" s="38" t="s">
         <v>41</v>
       </c>
@@ -8747,9 +8660,8 @@
       <c r="M233" s="40">
         <v>0</v>
       </c>
-      <c r="P233" s="52"/>
-    </row>
-    <row r="234" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="234" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="41" t="s">
         <v>42</v>
       </c>
@@ -8778,10 +8690,9 @@
         <v>0</v>
       </c>
       <c r="N234" s="46"/>
-      <c r="P234" s="52"/>
-    </row>
-    <row r="235" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
         <v>58</v>
       </c>
@@ -8822,7 +8733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="11" t="s">
         <v>7</v>
       </c>
@@ -8863,7 +8774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
         <v>8</v>
       </c>
@@ -8904,7 +8815,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
         <v>9</v>
       </c>
@@ -8945,7 +8856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
         <v>10</v>
       </c>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="805" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44870784-8025-4260-ADD5-025E7247D4CD}"/>
+  <xr:revisionPtr revIDLastSave="972" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB32F0D0-DA4C-486A-8912-02212F0E8F9F}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1035" windowWidth="32460" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="1965" yWindow="315" windowWidth="37680" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="74">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -254,13 +254,13 @@
     <t>10:15-15:45</t>
   </si>
   <si>
-    <t>Sommarjobb</t>
-  </si>
-  <si>
     <t>Vecka 19 (4-8 maj)</t>
   </si>
   <si>
     <t>Vecka 18 (27 april-1 maj)</t>
+  </si>
+  <si>
+    <t>08:00-15:45 (Prod)</t>
   </si>
 </sst>
 </file>
@@ -3858,7 +3858,7 @@
     <row r="83" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>2</v>
@@ -4185,7 +4185,7 @@
     <row r="93" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>2</v>
@@ -4604,9 +4604,6 @@
       <c r="M105" s="12">
         <v>10</v>
       </c>
-      <c r="N105" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
@@ -4654,37 +4651,37 @@
         <v>9</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C107" s="4">
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E107" s="4">
         <v>8</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G107" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I107" s="4">
         <v>8</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K107" s="4">
         <v>8</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M107" s="12">
         <v>8</v>
@@ -4724,10 +4721,10 @@
         <v>11</v>
       </c>
       <c r="B109" s="23" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C109" s="23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D109" s="32" t="s">
         <v>13</v>
@@ -4765,7 +4762,7 @@
       <c r="B110" s="44"/>
       <c r="C110" s="44">
         <f>SUM(C105:C109)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D110" s="44"/>
       <c r="E110" s="44">
@@ -4775,7 +4772,7 @@
       <c r="F110" s="44"/>
       <c r="G110" s="44">
         <f>SUM(G105:G109)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H110" s="44"/>
       <c r="I110" s="44">
@@ -4799,7 +4796,7 @@
       </c>
       <c r="B111" s="39"/>
       <c r="C111" s="39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" s="39"/>
       <c r="E111" s="39">
@@ -4828,7 +4825,7 @@
       </c>
       <c r="B112" s="42"/>
       <c r="C112" s="42">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D112" s="42"/>
       <c r="E112" s="42">
@@ -4910,10 +4907,12 @@
       <c r="E115" s="4">
         <v>10</v>
       </c>
-      <c r="F115" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G115" s="4"/>
+      <c r="F115" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G115" s="4">
+        <v>9</v>
+      </c>
       <c r="H115" s="4" t="s">
         <v>29</v>
       </c>
@@ -4949,10 +4948,12 @@
       <c r="E116" s="4">
         <v>9</v>
       </c>
-      <c r="F116" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G116" s="4"/>
+      <c r="F116" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G116" s="4">
+        <v>8</v>
+      </c>
       <c r="H116" s="4" t="s">
         <v>30</v>
       </c>
@@ -4988,10 +4989,12 @@
       <c r="E117" s="4">
         <v>8</v>
       </c>
-      <c r="F117" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G117" s="4"/>
+      <c r="F117" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G117" s="4">
+        <v>7</v>
+      </c>
       <c r="H117" s="4" t="s">
         <v>12</v>
       </c>
@@ -5027,10 +5030,12 @@
       <c r="E118" s="4">
         <v>8</v>
       </c>
-      <c r="F118" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G118" s="4"/>
+      <c r="F118" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" s="4">
+        <v>7</v>
+      </c>
       <c r="H118" s="5" t="s">
         <v>19</v>
       </c>
@@ -5066,10 +5071,12 @@
       <c r="E119" s="23">
         <v>8</v>
       </c>
-      <c r="F119" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G119" s="23"/>
+      <c r="F119" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G119" s="23">
+        <v>5</v>
+      </c>
       <c r="H119" s="23" t="s">
         <v>12</v>
       </c>
@@ -5104,7 +5111,7 @@
       <c r="F120" s="44"/>
       <c r="G120" s="44">
         <f>SUM(G115:G119)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H120" s="44"/>
       <c r="I120" s="44">
@@ -5136,7 +5143,7 @@
       </c>
       <c r="F121" s="39"/>
       <c r="G121" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" s="39"/>
       <c r="I121" s="39">
@@ -5157,7 +5164,7 @@
       </c>
       <c r="B122" s="42"/>
       <c r="C122" s="42">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D122" s="42"/>
       <c r="E122" s="42">
@@ -5165,7 +5172,7 @@
       </c>
       <c r="F122" s="42"/>
       <c r="G122" s="42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122" s="42"/>
       <c r="I122" s="42">
@@ -5269,10 +5276,12 @@
       <c r="E127" s="4">
         <v>10</v>
       </c>
-      <c r="F127" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G127" s="4"/>
+      <c r="F127" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G127" s="4">
+        <v>9</v>
+      </c>
       <c r="H127" s="4" t="s">
         <v>29</v>
       </c>
@@ -5308,10 +5317,12 @@
       <c r="E128" s="4">
         <v>9</v>
       </c>
-      <c r="F128" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G128" s="4"/>
+      <c r="F128" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G128" s="4">
+        <v>8</v>
+      </c>
       <c r="H128" s="4" t="s">
         <v>30</v>
       </c>
@@ -5347,10 +5358,12 @@
       <c r="E129" s="4">
         <v>8</v>
       </c>
-      <c r="F129" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G129" s="4"/>
+      <c r="F129" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" s="4">
+        <v>7</v>
+      </c>
       <c r="H129" s="4" t="s">
         <v>12</v>
       </c>
@@ -5386,10 +5399,12 @@
       <c r="E130" s="4">
         <v>4</v>
       </c>
-      <c r="F130" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G130" s="4"/>
+      <c r="F130" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G130" s="4">
+        <v>5</v>
+      </c>
       <c r="H130" s="4" t="s">
         <v>12</v>
       </c>
@@ -5425,10 +5440,12 @@
       <c r="E131" s="23">
         <v>8</v>
       </c>
-      <c r="F131" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G131" s="23"/>
+      <c r="F131" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G131" s="23">
+        <v>5</v>
+      </c>
       <c r="H131" s="23" t="s">
         <v>12</v>
       </c>
@@ -5461,7 +5478,7 @@
       <c r="F132" s="44"/>
       <c r="G132" s="44">
         <f>SUM(G127:G131)</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H132" s="44"/>
       <c r="I132" s="44">
@@ -5493,7 +5510,7 @@
       </c>
       <c r="F133" s="39"/>
       <c r="G133" s="39">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H133" s="39"/>
       <c r="I133" s="39">
@@ -5514,7 +5531,7 @@
       </c>
       <c r="B134" s="42"/>
       <c r="C134" s="42">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D134" s="42"/>
       <c r="E134" s="42">
@@ -5824,7 +5841,7 @@
       </c>
       <c r="J143" s="39"/>
       <c r="K143" s="39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L143" s="39"/>
       <c r="M143" s="40">
@@ -5837,7 +5854,7 @@
       </c>
       <c r="B144" s="42"/>
       <c r="C144" s="42">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D144" s="42"/>
       <c r="E144" s="42">
@@ -5853,7 +5870,7 @@
       </c>
       <c r="J144" s="42"/>
       <c r="K144" s="42">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L144" s="42"/>
       <c r="M144" s="43">
@@ -6049,7 +6066,7 @@
       </c>
       <c r="K150" s="4"/>
       <c r="L150" s="21" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="M150" s="12">
         <v>7</v>
@@ -6084,7 +6101,7 @@
       </c>
       <c r="K151" s="23"/>
       <c r="L151" s="48" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="M151" s="24">
         <v>7</v>
@@ -6160,7 +6177,7 @@
       </c>
       <c r="B154" s="42"/>
       <c r="C154" s="42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D154" s="42"/>
       <c r="E154" s="42">
@@ -6176,7 +6193,7 @@
       </c>
       <c r="J154" s="42"/>
       <c r="K154" s="42">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L154" s="42"/>
       <c r="M154" s="43">
@@ -6471,7 +6488,7 @@
       </c>
       <c r="B164" s="42"/>
       <c r="C164" s="42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D164" s="42"/>
       <c r="E164" s="42">
@@ -6791,7 +6808,7 @@
       </c>
       <c r="B174" s="42"/>
       <c r="C174" s="42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D174" s="42"/>
       <c r="E174" s="42">
@@ -7100,7 +7117,7 @@
       </c>
       <c r="B184" s="42"/>
       <c r="C184" s="42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D184" s="42"/>
       <c r="E184" s="42">
@@ -7401,7 +7418,7 @@
       </c>
       <c r="B194" s="42"/>
       <c r="C194" s="42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D194" s="42"/>
       <c r="E194" s="42">
@@ -7706,7 +7723,7 @@
       </c>
       <c r="B204" s="42"/>
       <c r="C204" s="42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D204" s="42"/>
       <c r="E204" s="42">
@@ -8017,7 +8034,7 @@
       </c>
       <c r="B214" s="42"/>
       <c r="C214" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D214" s="42"/>
       <c r="E214" s="42">
@@ -8338,7 +8355,7 @@
       </c>
       <c r="B224" s="42"/>
       <c r="C224" s="42">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D224" s="42"/>
       <c r="E224" s="42">
@@ -8667,7 +8684,7 @@
       </c>
       <c r="B234" s="42"/>
       <c r="C234" s="42">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D234" s="42"/>
       <c r="E234" s="42">
@@ -9004,7 +9021,7 @@
       </c>
       <c r="B244" s="42"/>
       <c r="C244" s="42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D244" s="42"/>
       <c r="E244" s="42">

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="972" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB32F0D0-DA4C-486A-8912-02212F0E8F9F}"/>
+  <xr:revisionPtr revIDLastSave="1059" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82814B07-FE41-4B2B-8F9B-AEBCD632EA2C}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="315" windowWidth="37680" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="3090" yWindow="195" windowWidth="44205" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="75">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>08:00-15:45 (Prod)</t>
+  </si>
+  <si>
+    <t>Emil</t>
   </si>
 </sst>
 </file>
@@ -604,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -743,6 +746,36 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1092,7 +1125,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q274"/>
+  <dimension ref="A1:S274"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1108,9 +1141,11 @@
     <col min="11" max="11" width="6.85546875" customWidth="1"/>
     <col min="12" max="12" width="18.7109375" style="2" customWidth="1"/>
     <col min="13" max="13" width="6.7109375" customWidth="1"/>
+    <col min="14" max="14" width="19.7109375" customWidth="1"/>
+    <col min="15" max="15" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1121,7 +1156,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1161,8 +1196,10 @@
       <c r="M2" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N2" s="8"/>
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>7</v>
       </c>
@@ -1202,8 +1239,10 @@
       <c r="M3" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N3" s="4"/>
+      <c r="O3" s="12"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>8</v>
       </c>
@@ -1243,8 +1282,10 @@
       <c r="M4" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N4" s="4"/>
+      <c r="O4" s="12"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>9</v>
       </c>
@@ -1284,8 +1325,10 @@
       <c r="M5" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N5" s="4"/>
+      <c r="O5" s="12"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
@@ -1325,8 +1368,10 @@
       <c r="M6" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="4"/>
+      <c r="O6" s="12"/>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>11</v>
       </c>
@@ -1364,8 +1409,10 @@
       <c r="M7" s="15">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N7" s="14"/>
+      <c r="O7" s="15"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
         <v>40</v>
       </c>
@@ -1399,8 +1446,10 @@
         <f>SUM(M3:M7)</f>
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N8" s="36"/>
+      <c r="O8" s="37"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
         <v>41</v>
       </c>
@@ -1428,8 +1477,10 @@
       <c r="M9" s="40">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N9" s="39"/>
+      <c r="O9" s="40"/>
+    </row>
+    <row r="10" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>42</v>
       </c>
@@ -1457,18 +1508,22 @@
       <c r="M10" s="43">
         <v>1</v>
       </c>
-      <c r="N10" s="46"/>
-      <c r="O10" t="s">
+      <c r="N10" s="42"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G11" s="2"/>
       <c r="I11" s="2"/>
       <c r="K11" s="2"/>
       <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>17</v>
       </c>
@@ -1508,8 +1563,10 @@
       <c r="M12" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N12" s="56"/>
+      <c r="O12" s="56"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>7</v>
       </c>
@@ -1549,8 +1606,10 @@
       <c r="M13" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>8</v>
       </c>
@@ -1590,8 +1649,10 @@
       <c r="M14" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N14" s="56"/>
+      <c r="O14" s="56"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>9</v>
       </c>
@@ -1631,8 +1692,10 @@
       <c r="M15" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N15" s="56"/>
+      <c r="O15" s="56"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>10</v>
       </c>
@@ -1672,8 +1735,10 @@
       <c r="M16" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
+    </row>
+    <row r="17" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>11</v>
       </c>
@@ -1711,8 +1776,10 @@
       <c r="M17" s="15">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N17" s="56"/>
+      <c r="O17" s="56"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
         <v>40</v>
       </c>
@@ -1746,8 +1813,10 @@
         <f>SUM(M13:M17)</f>
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
         <v>41</v>
       </c>
@@ -1775,8 +1844,10 @@
       <c r="M19" s="40">
         <v>-1</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+    </row>
+    <row r="20" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>42</v>
       </c>
@@ -1804,15 +1875,19 @@
       <c r="M20" s="43">
         <v>0</v>
       </c>
-      <c r="N20" s="46"/>
-    </row>
-    <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="59"/>
+      <c r="O20" s="59"/>
+      <c r="P20" s="46"/>
+    </row>
+    <row r="21" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G21" s="2"/>
       <c r="I21" s="2"/>
       <c r="K21" s="2"/>
       <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
@@ -1852,8 +1927,10 @@
       <c r="M22" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N22" s="56"/>
+      <c r="O22" s="56"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>7</v>
       </c>
@@ -1893,8 +1970,10 @@
       <c r="M23" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>8</v>
       </c>
@@ -1934,8 +2013,10 @@
       <c r="M24" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N24" s="56"/>
+      <c r="O24" s="56"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>9</v>
       </c>
@@ -1975,8 +2056,10 @@
       <c r="M25" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
+    </row>
+    <row r="26" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>10</v>
       </c>
@@ -2014,8 +2097,10 @@
       <c r="M26" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N26" s="56"/>
+      <c r="O26" s="56"/>
+    </row>
+    <row r="27" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>11</v>
       </c>
@@ -2051,8 +2136,10 @@
         <v>13</v>
       </c>
       <c r="M27" s="15"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="35" t="s">
         <v>40</v>
       </c>
@@ -2086,8 +2173,10 @@
         <f>SUM(M23:M27)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N28" s="57"/>
+      <c r="O28" s="57"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
         <v>41</v>
       </c>
@@ -2115,8 +2204,10 @@
       <c r="M29" s="40">
         <v>-6</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N29" s="58"/>
+      <c r="O29" s="58"/>
+    </row>
+    <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
         <v>42</v>
       </c>
@@ -2144,10 +2235,12 @@
       <c r="M30" s="43">
         <v>-6</v>
       </c>
-      <c r="N30" s="46"/>
-    </row>
-    <row r="31" spans="1:14" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N30" s="59"/>
+      <c r="O30" s="59"/>
+      <c r="P30" s="46"/>
+    </row>
+    <row r="31" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>20</v>
       </c>
@@ -2187,8 +2280,10 @@
       <c r="M32" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>7</v>
       </c>
@@ -2228,8 +2323,10 @@
       <c r="M33" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N33" s="56"/>
+      <c r="O33" s="56"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>8</v>
       </c>
@@ -2269,8 +2366,10 @@
       <c r="M34" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N34" s="56"/>
+      <c r="O34" s="56"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>9</v>
       </c>
@@ -2310,8 +2409,10 @@
       <c r="M35" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N35" s="56"/>
+      <c r="O35" s="56"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>10</v>
       </c>
@@ -2349,8 +2450,10 @@
       <c r="M36" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N36" s="56"/>
+      <c r="O36" s="56"/>
+    </row>
+    <row r="37" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>11</v>
       </c>
@@ -2388,8 +2491,10 @@
       <c r="M37" s="15">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N37" s="56"/>
+      <c r="O37" s="56"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
         <v>40</v>
       </c>
@@ -2423,8 +2528,10 @@
         <f>SUM(M33:M37)</f>
         <v>39</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
         <v>41</v>
       </c>
@@ -2452,8 +2559,10 @@
       <c r="M39" s="40">
         <v>-1</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
+    </row>
+    <row r="40" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="41" t="s">
         <v>42</v>
       </c>
@@ -2481,10 +2590,12 @@
       <c r="M40" s="43">
         <v>-7</v>
       </c>
-      <c r="N40" s="46"/>
-    </row>
-    <row r="41" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N40" s="59"/>
+      <c r="O40" s="59"/>
+      <c r="P40" s="46"/>
+    </row>
+    <row r="41" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>23</v>
       </c>
@@ -2524,8 +2635,10 @@
       <c r="M42" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N42" s="56"/>
+      <c r="O42" s="56"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>7</v>
       </c>
@@ -2565,8 +2678,10 @@
       <c r="M43" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N43" s="56"/>
+      <c r="O43" s="56"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>8</v>
       </c>
@@ -2606,8 +2721,10 @@
       <c r="M44" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N44" s="56"/>
+      <c r="O44" s="56"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>9</v>
       </c>
@@ -2645,8 +2762,10 @@
       <c r="M45" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N45" s="56"/>
+      <c r="O45" s="56"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>10</v>
       </c>
@@ -2682,8 +2801,10 @@
       <c r="M46" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N46" s="56"/>
+      <c r="O46" s="56"/>
+    </row>
+    <row r="47" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
         <v>25</v>
       </c>
@@ -2711,8 +2832,10 @@
         <v>13</v>
       </c>
       <c r="M47" s="27"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N47" s="60"/>
+      <c r="O47" s="60"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="35" t="s">
         <v>40</v>
       </c>
@@ -2746,8 +2869,10 @@
         <f>SUM(M43:M47)</f>
         <v>32</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N48" s="57"/>
+      <c r="O48" s="57"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
         <v>41</v>
       </c>
@@ -2775,8 +2900,10 @@
       <c r="M49" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
+    </row>
+    <row r="50" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="41" t="s">
         <v>42</v>
       </c>
@@ -2804,10 +2931,12 @@
       <c r="M50" s="43">
         <v>-7</v>
       </c>
-      <c r="N50" s="46"/>
-    </row>
-    <row r="51" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N50" s="59"/>
+      <c r="O50" s="59"/>
+      <c r="P50" s="46"/>
+    </row>
+    <row r="51" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>24</v>
       </c>
@@ -2847,8 +2976,10 @@
       <c r="M52" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N52" s="56"/>
+      <c r="O52" s="56"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
         <v>26</v>
       </c>
@@ -2886,8 +3017,10 @@
       <c r="M53" s="28">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N53" s="61"/>
+      <c r="O53" s="61"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>8</v>
       </c>
@@ -2927,8 +3060,10 @@
       <c r="M54" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N54" s="56"/>
+      <c r="O54" s="56"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>9</v>
       </c>
@@ -2968,8 +3103,10 @@
       <c r="M55" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N55" s="56"/>
+      <c r="O55" s="56"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>10</v>
       </c>
@@ -3007,8 +3144,10 @@
       <c r="M56" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N56" s="56"/>
+      <c r="O56" s="56"/>
+    </row>
+    <row r="57" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>11</v>
       </c>
@@ -3046,8 +3185,10 @@
       <c r="M57" s="15">
         <v>7</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N57" s="56"/>
+      <c r="O57" s="56"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="35" t="s">
         <v>40</v>
       </c>
@@ -3081,8 +3222,10 @@
         <f>SUM(M53:M57)</f>
         <v>39</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N58" s="57"/>
+      <c r="O58" s="57"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
         <v>41</v>
       </c>
@@ -3110,8 +3253,10 @@
       <c r="M59" s="40">
         <v>7</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N59" s="58"/>
+      <c r="O59" s="58"/>
+    </row>
+    <row r="60" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="41" t="s">
         <v>42</v>
       </c>
@@ -3147,10 +3292,12 @@
       <c r="M60" s="55">
         <v>12</v>
       </c>
-      <c r="N60" s="46"/>
-    </row>
-    <row r="61" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N60" s="62"/>
+      <c r="O60" s="62"/>
+      <c r="P60" s="46"/>
+    </row>
+    <row r="61" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>43</v>
       </c>
@@ -3190,8 +3337,10 @@
       <c r="M62" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N62" s="56"/>
+      <c r="O62" s="56"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>7</v>
       </c>
@@ -3231,8 +3380,10 @@
       <c r="M63" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N63" s="56"/>
+      <c r="O63" s="56"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
         <v>8</v>
       </c>
@@ -3272,8 +3423,10 @@
       <c r="M64" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N64" s="56"/>
+      <c r="O64" s="56"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>9</v>
       </c>
@@ -3313,8 +3466,10 @@
       <c r="M65" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N65" s="56"/>
+      <c r="O65" s="56"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>10</v>
       </c>
@@ -3354,8 +3509,10 @@
       <c r="M66" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N66" s="56"/>
+      <c r="O66" s="56"/>
+    </row>
+    <row r="67" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="22" t="s">
         <v>11</v>
       </c>
@@ -3391,8 +3548,10 @@
       <c r="M67" s="24">
         <v>7</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N67" s="56"/>
+      <c r="O67" s="56"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="47" t="s">
         <v>40</v>
       </c>
@@ -3426,8 +3585,10 @@
         <f>SUM(M63:M67)</f>
         <v>41</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N68" s="57"/>
+      <c r="O68" s="57"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
         <v>41</v>
       </c>
@@ -3455,8 +3616,10 @@
       <c r="M69" s="40">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N69" s="58"/>
+      <c r="O69" s="58"/>
+    </row>
+    <row r="70" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41" t="s">
         <v>42</v>
       </c>
@@ -3484,10 +3647,12 @@
       <c r="M70" s="43">
         <v>13</v>
       </c>
-      <c r="N70" s="46"/>
-    </row>
-    <row r="71" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N70" s="59"/>
+      <c r="O70" s="59"/>
+      <c r="P70" s="46"/>
+    </row>
+    <row r="71" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>44</v>
       </c>
@@ -3527,8 +3692,10 @@
       <c r="M72" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N72" s="56"/>
+      <c r="O72" s="56"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
         <v>7</v>
       </c>
@@ -3568,8 +3735,10 @@
       <c r="M73" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N73" s="56"/>
+      <c r="O73" s="56"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
         <v>8</v>
       </c>
@@ -3609,8 +3778,10 @@
       <c r="M74" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N74" s="56"/>
+      <c r="O74" s="56"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>9</v>
       </c>
@@ -3650,8 +3821,10 @@
       <c r="M75" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N75" s="56"/>
+      <c r="O75" s="56"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
         <v>10</v>
       </c>
@@ -3691,8 +3864,10 @@
       <c r="M76" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N76" s="56"/>
+      <c r="O76" s="56"/>
+    </row>
+    <row r="77" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>11</v>
       </c>
@@ -3730,8 +3905,10 @@
       <c r="M77" s="15">
         <v>7</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N77" s="56"/>
+      <c r="O77" s="56"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
         <v>40</v>
       </c>
@@ -3765,8 +3942,10 @@
         <f>SUM(M73:M77)</f>
         <v>39</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N78" s="57"/>
+      <c r="O78" s="57"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
         <v>41</v>
       </c>
@@ -3794,8 +3973,10 @@
       <c r="M79" s="40">
         <v>-1</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N79" s="58"/>
+      <c r="O79" s="58"/>
+    </row>
+    <row r="80" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="41" t="s">
         <v>42</v>
       </c>
@@ -3823,9 +4004,11 @@
       <c r="M80" s="43">
         <v>12</v>
       </c>
-      <c r="N80" s="46"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N80" s="59"/>
+      <c r="O80" s="59"/>
+      <c r="P80" s="46"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="33"/>
       <c r="B81" s="34"/>
       <c r="C81" s="34"/>
@@ -3839,8 +4022,10 @@
       <c r="K81" s="34"/>
       <c r="L81" s="34"/>
       <c r="M81" s="34"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N81" s="34"/>
+      <c r="O81" s="34"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="33"/>
       <c r="B82" s="34"/>
       <c r="C82" s="34"/>
@@ -3854,9 +4039,11 @@
       <c r="K82" s="34"/>
       <c r="L82" s="34"/>
       <c r="M82" s="34"/>
-    </row>
-    <row r="83" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N82" s="34"/>
+      <c r="O82" s="34"/>
+    </row>
+    <row r="83" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>72</v>
       </c>
@@ -3896,8 +4083,10 @@
       <c r="M84" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N84" s="56"/>
+      <c r="O84" s="56"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>7</v>
       </c>
@@ -3937,8 +4126,10 @@
       <c r="M85" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N85" s="56"/>
+      <c r="O85" s="56"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
         <v>8</v>
       </c>
@@ -3978,8 +4169,10 @@
       <c r="M86" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N86" s="56"/>
+      <c r="O86" s="56"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>9</v>
       </c>
@@ -4019,8 +4212,10 @@
       <c r="M87" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N87" s="56"/>
+      <c r="O87" s="56"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>10</v>
       </c>
@@ -4058,8 +4253,10 @@
       <c r="M88" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N88" s="56"/>
+      <c r="O88" s="56"/>
+    </row>
+    <row r="89" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="29" t="s">
         <v>27</v>
       </c>
@@ -4087,8 +4284,10 @@
         <v>13</v>
       </c>
       <c r="M89" s="31"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N89" s="60"/>
+      <c r="O89" s="60"/>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="47" t="s">
         <v>40</v>
       </c>
@@ -4122,8 +4321,10 @@
         <f>SUM(M85:M89)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N90" s="57"/>
+      <c r="O90" s="57"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="38" t="s">
         <v>41</v>
       </c>
@@ -4151,8 +4352,10 @@
       <c r="M91" s="40">
         <v>2</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N91" s="58"/>
+      <c r="O91" s="58"/>
+    </row>
+    <row r="92" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="41" t="s">
         <v>42</v>
       </c>
@@ -4180,10 +4383,12 @@
       <c r="M92" s="43">
         <v>14</v>
       </c>
-      <c r="N92" s="46"/>
-    </row>
-    <row r="93" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N92" s="59"/>
+      <c r="O92" s="59"/>
+      <c r="P92" s="46"/>
+    </row>
+    <row r="93" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>71</v>
       </c>
@@ -4223,8 +4428,10 @@
       <c r="M94" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N94" s="56"/>
+      <c r="O94" s="56"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>7</v>
       </c>
@@ -4264,8 +4471,10 @@
       <c r="M95" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N95" s="56"/>
+      <c r="O95" s="56"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>8</v>
       </c>
@@ -4305,8 +4514,10 @@
       <c r="M96" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N96" s="56"/>
+      <c r="O96" s="56"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>9</v>
       </c>
@@ -4346,8 +4557,10 @@
       <c r="M97" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N97" s="56"/>
+      <c r="O97" s="56"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
         <v>10</v>
       </c>
@@ -4387,8 +4600,10 @@
       <c r="M98" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N98" s="56"/>
+      <c r="O98" s="56"/>
+    </row>
+    <row r="99" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
         <v>11</v>
       </c>
@@ -4426,8 +4641,10 @@
       <c r="M99" s="24">
         <v>7</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N99" s="56"/>
+      <c r="O99" s="56"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="47" t="s">
         <v>40</v>
       </c>
@@ -4461,8 +4678,10 @@
         <f>SUM(M95:M99)</f>
         <v>39</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N100" s="57"/>
+      <c r="O100" s="57"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="38" t="s">
         <v>41</v>
       </c>
@@ -4490,8 +4709,10 @@
       <c r="M101" s="40">
         <v>-1</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N101" s="58"/>
+      <c r="O101" s="58"/>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="41" t="s">
         <v>42</v>
       </c>
@@ -4519,10 +4740,12 @@
       <c r="M102" s="43">
         <v>13</v>
       </c>
-      <c r="N102" s="46"/>
-    </row>
-    <row r="103" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N102" s="59"/>
+      <c r="O102" s="59"/>
+      <c r="P102" s="46"/>
+    </row>
+    <row r="103" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>45</v>
       </c>
@@ -4562,9 +4785,11 @@
       <c r="M104" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O104" s="2"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N104" s="56"/>
+      <c r="O104" s="56"/>
+      <c r="Q104" s="2"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>7</v>
       </c>
@@ -4604,8 +4829,10 @@
       <c r="M105" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N105" s="56"/>
+      <c r="O105" s="56"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
         <v>8</v>
       </c>
@@ -4645,8 +4872,10 @@
       <c r="M106" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N106" s="56"/>
+      <c r="O106" s="56"/>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
         <v>9</v>
       </c>
@@ -4686,8 +4915,10 @@
       <c r="M107" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N107" s="56"/>
+      <c r="O107" s="56"/>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
         <v>35</v>
       </c>
@@ -4715,8 +4946,10 @@
         <v>13</v>
       </c>
       <c r="M108" s="19"/>
-    </row>
-    <row r="109" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N108" s="60"/>
+      <c r="O108" s="60"/>
+    </row>
+    <row r="109" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
         <v>11</v>
       </c>
@@ -4754,8 +4987,10 @@
       <c r="M109" s="24">
         <v>7</v>
       </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N109" s="56"/>
+      <c r="O109" s="56"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="47" t="s">
         <v>40</v>
       </c>
@@ -4789,8 +5024,10 @@
         <f>SUM(M105:M109)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N110" s="57"/>
+      <c r="O110" s="57"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="38" t="s">
         <v>41</v>
       </c>
@@ -4818,8 +5055,10 @@
       <c r="M111" s="40">
         <v>2</v>
       </c>
-    </row>
-    <row r="112" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N111" s="58"/>
+      <c r="O111" s="58"/>
+    </row>
+    <row r="112" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="41" t="s">
         <v>42</v>
       </c>
@@ -4847,10 +5086,12 @@
       <c r="M112" s="43">
         <v>15</v>
       </c>
-      <c r="N112" s="46"/>
-    </row>
-    <row r="113" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N112" s="59"/>
+      <c r="O112" s="59"/>
+      <c r="P112" s="46"/>
+    </row>
+    <row r="113" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>46</v>
       </c>
@@ -4890,8 +5131,10 @@
       <c r="M114" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N114" s="56"/>
+      <c r="O114" s="56"/>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
         <v>7</v>
       </c>
@@ -4931,8 +5174,10 @@
       <c r="M115" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N115" s="56"/>
+      <c r="O115" s="56"/>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>8</v>
       </c>
@@ -4972,8 +5217,10 @@
       <c r="M116" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N116" s="56"/>
+      <c r="O116" s="56"/>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>9</v>
       </c>
@@ -5013,8 +5260,10 @@
       <c r="M117" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N117" s="56"/>
+      <c r="O117" s="56"/>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>10</v>
       </c>
@@ -5031,10 +5280,10 @@
         <v>8</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G118" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H118" s="5" t="s">
         <v>19</v>
@@ -5054,8 +5303,10 @@
       <c r="M118" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N118" s="56"/>
+      <c r="O118" s="56"/>
+    </row>
+    <row r="119" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
         <v>11</v>
       </c>
@@ -5072,10 +5323,10 @@
         <v>8</v>
       </c>
       <c r="F119" s="23" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G119" s="23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H119" s="23" t="s">
         <v>12</v>
@@ -5093,8 +5344,10 @@
       <c r="M119" s="24">
         <v>7</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N119" s="56"/>
+      <c r="O119" s="56"/>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="47" t="s">
         <v>40</v>
       </c>
@@ -5128,8 +5381,10 @@
         <f>SUM(M115:M119)</f>
         <v>39</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N120" s="57"/>
+      <c r="O120" s="57"/>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="38" t="s">
         <v>41</v>
       </c>
@@ -5157,8 +5412,10 @@
       <c r="M121" s="40">
         <v>-1</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N121" s="58"/>
+      <c r="O121" s="58"/>
+    </row>
+    <row r="122" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="41" t="s">
         <v>42</v>
       </c>
@@ -5186,9 +5443,11 @@
       <c r="M122" s="43">
         <v>14</v>
       </c>
-      <c r="N122" s="46"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N122" s="59"/>
+      <c r="O122" s="59"/>
+      <c r="P122" s="46"/>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="33"/>
       <c r="B123" s="34"/>
       <c r="C123" s="34"/>
@@ -5202,8 +5461,10 @@
       <c r="K123" s="34"/>
       <c r="L123" s="34"/>
       <c r="M123" s="34"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N123" s="34"/>
+      <c r="O123" s="34"/>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="33"/>
       <c r="B124" s="34"/>
       <c r="C124" s="34"/>
@@ -5217,9 +5478,11 @@
       <c r="K124" s="34"/>
       <c r="L124" s="34"/>
       <c r="M124" s="34"/>
-    </row>
-    <row r="125" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N124" s="34"/>
+      <c r="O124" s="34"/>
+    </row>
+    <row r="125" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>47</v>
       </c>
@@ -5259,8 +5522,14 @@
       <c r="M126" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N126" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O126" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
         <v>7</v>
       </c>
@@ -5300,8 +5569,14 @@
       <c r="M127" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N127" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O127" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>8</v>
       </c>
@@ -5341,8 +5616,14 @@
       <c r="M128" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N128" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O128" s="12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>9</v>
       </c>
@@ -5382,8 +5663,12 @@
       <c r="M129" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N129" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O129" s="12"/>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>10</v>
       </c>
@@ -5423,8 +5708,12 @@
       <c r="M130" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N130" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O130" s="12"/>
+    </row>
+    <row r="131" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>11</v>
       </c>
@@ -5460,8 +5749,12 @@
         <v>50</v>
       </c>
       <c r="M131" s="24"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N131" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O131" s="24"/>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="47" t="s">
         <v>40</v>
       </c>
@@ -5495,8 +5788,13 @@
         <f>SUM(M127:M131)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N132" s="63"/>
+      <c r="O132" s="45">
+        <f>SUM(O127:O131)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="38" t="s">
         <v>41</v>
       </c>
@@ -5524,8 +5822,12 @@
       <c r="M133" s="40">
         <v>-6</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N133" s="64"/>
+      <c r="O133" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="41" t="s">
         <v>42</v>
       </c>
@@ -5553,10 +5855,14 @@
       <c r="M134" s="43">
         <v>8</v>
       </c>
-      <c r="N134" s="46"/>
-    </row>
-    <row r="135" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N134" s="65"/>
+      <c r="O134" s="43">
+        <v>0</v>
+      </c>
+      <c r="P134" s="46"/>
+    </row>
+    <row r="135" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>48</v>
       </c>
@@ -5596,8 +5902,14 @@
       <c r="M136" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N136" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O136" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
         <v>7</v>
       </c>
@@ -5635,8 +5947,14 @@
       <c r="M137" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N137" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O137" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
         <v>8</v>
       </c>
@@ -5674,8 +5992,14 @@
       <c r="M138" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N138" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O138" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>9</v>
       </c>
@@ -5713,8 +6037,14 @@
       <c r="M139" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N139" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O139" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>10</v>
       </c>
@@ -5748,8 +6078,14 @@
         <v>13</v>
       </c>
       <c r="M140" s="12"/>
-    </row>
-    <row r="141" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N140" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O140" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
         <v>11</v>
       </c>
@@ -5783,8 +6119,14 @@
       <c r="M141" s="24">
         <v>7</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N141" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="O141" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="47" t="s">
         <v>40</v>
       </c>
@@ -5818,8 +6160,13 @@
         <f>SUM(M137:M141)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N142" s="63"/>
+      <c r="O142" s="45">
+        <f>SUM(O137:O141)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="38" t="s">
         <v>49</v>
       </c>
@@ -5847,8 +6194,12 @@
       <c r="M143" s="40">
         <v>2</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N143" s="64"/>
+      <c r="O143" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="41" t="s">
         <v>42</v>
       </c>
@@ -5876,10 +6227,14 @@
       <c r="M144" s="43">
         <v>10</v>
       </c>
-      <c r="N144" s="46"/>
-    </row>
-    <row r="145" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N144" s="65"/>
+      <c r="O144" s="43">
+        <v>0</v>
+      </c>
+      <c r="P144" s="46"/>
+    </row>
+    <row r="145" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>36</v>
       </c>
@@ -5919,8 +6274,14 @@
       <c r="M146" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N146" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O146" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>7</v>
       </c>
@@ -5958,8 +6319,14 @@
       <c r="M147" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N147" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O147" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>8</v>
       </c>
@@ -5997,8 +6364,14 @@
       <c r="M148" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N148" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O148" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>9</v>
       </c>
@@ -6036,8 +6409,14 @@
       <c r="M149" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N149" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O149" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
         <v>10</v>
       </c>
@@ -6071,8 +6450,14 @@
       <c r="M150" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N150" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O150" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="22" t="s">
         <v>11</v>
       </c>
@@ -6106,8 +6491,14 @@
       <c r="M151" s="24">
         <v>7</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N151" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="O151" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="35" t="s">
         <v>40</v>
       </c>
@@ -6141,8 +6532,13 @@
         <f>SUM(M147:M151)</f>
         <v>38</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N152" s="63"/>
+      <c r="O152" s="45">
+        <f>SUM(O147:O151)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="38" t="s">
         <v>41</v>
       </c>
@@ -6170,8 +6566,12 @@
       <c r="M153" s="40">
         <v>-2</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N153" s="64"/>
+      <c r="O153" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="41" t="s">
         <v>42</v>
       </c>
@@ -6199,10 +6599,14 @@
       <c r="M154" s="43">
         <v>8</v>
       </c>
-      <c r="N154" s="46"/>
-    </row>
-    <row r="155" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N154" s="65"/>
+      <c r="O154" s="43">
+        <v>0</v>
+      </c>
+      <c r="P154" s="46"/>
+    </row>
+    <row r="155" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>37</v>
       </c>
@@ -6242,8 +6646,14 @@
       <c r="M156" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N156" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O156" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
         <v>7</v>
       </c>
@@ -6279,8 +6689,14 @@
       <c r="M157" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N157" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O157" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>8</v>
       </c>
@@ -6316,8 +6732,14 @@
       <c r="M158" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N158" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O158" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>9</v>
       </c>
@@ -6353,8 +6775,14 @@
       <c r="M159" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N159" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O159" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
         <v>10</v>
       </c>
@@ -6388,8 +6816,14 @@
       <c r="M160" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="161" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N160" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O160" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="29" t="s">
         <v>38</v>
       </c>
@@ -6417,8 +6851,12 @@
         <v>13</v>
       </c>
       <c r="M161" s="31"/>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N161" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="O161" s="31"/>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" s="35" t="s">
         <v>40</v>
       </c>
@@ -6452,8 +6890,13 @@
         <f>SUM(M157:M161)</f>
         <v>32</v>
       </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N162" s="63"/>
+      <c r="O162" s="45">
+        <f>SUM(O157:O161)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" s="38" t="s">
         <v>41</v>
       </c>
@@ -6481,8 +6924,12 @@
       <c r="M163" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N163" s="64"/>
+      <c r="O163" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="41" t="s">
         <v>42</v>
       </c>
@@ -6510,10 +6957,14 @@
       <c r="M164" s="43">
         <v>8</v>
       </c>
-      <c r="N164" s="46"/>
-    </row>
-    <row r="165" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N164" s="65"/>
+      <c r="O164" s="43">
+        <v>0</v>
+      </c>
+      <c r="P164" s="46"/>
+    </row>
+    <row r="165" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>51</v>
       </c>
@@ -6553,8 +7004,14 @@
       <c r="M166" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N166" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O166" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
         <v>7</v>
       </c>
@@ -6590,8 +7047,14 @@
       <c r="M167" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N167" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O167" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
         <v>8</v>
       </c>
@@ -6627,8 +7090,14 @@
       <c r="M168" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N168" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O168" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
         <v>9</v>
       </c>
@@ -6664,8 +7133,14 @@
       <c r="M169" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N169" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O169" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
         <v>10</v>
       </c>
@@ -6701,8 +7176,14 @@
       <c r="M170" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="171" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N170" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O170" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="22" t="s">
         <v>11</v>
       </c>
@@ -6736,9 +7217,15 @@
       <c r="M171" s="24">
         <v>8</v>
       </c>
-      <c r="Q171" s="52"/>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N171" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="O171" s="24">
+        <v>8</v>
+      </c>
+      <c r="S171" s="52"/>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" s="47" t="s">
         <v>40</v>
       </c>
@@ -6772,8 +7259,13 @@
         <f>SUM(M167:M171)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N172" s="63"/>
+      <c r="O172" s="45">
+        <f>SUM(O167:O171)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" s="38" t="s">
         <v>41</v>
       </c>
@@ -6801,8 +7293,12 @@
       <c r="M173" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N173" s="64"/>
+      <c r="O173" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="41" t="s">
         <v>42</v>
       </c>
@@ -6830,10 +7326,14 @@
       <c r="M174" s="43">
         <v>8</v>
       </c>
-      <c r="N174" s="46"/>
-    </row>
-    <row r="175" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N174" s="65"/>
+      <c r="O174" s="43">
+        <v>0</v>
+      </c>
+      <c r="P174" s="46"/>
+    </row>
+    <row r="175" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>52</v>
       </c>
@@ -6873,8 +7373,14 @@
       <c r="M176" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N176" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O176" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
         <v>7</v>
       </c>
@@ -6908,8 +7414,14 @@
       <c r="M177" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N177" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O177" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>8</v>
       </c>
@@ -6943,8 +7455,14 @@
       <c r="M178" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N178" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O178" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>9</v>
       </c>
@@ -6978,8 +7496,14 @@
       <c r="M179" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N179" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O179" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>10</v>
       </c>
@@ -7013,8 +7537,14 @@
       <c r="M180" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N180" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O180" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="22" t="s">
         <v>11</v>
       </c>
@@ -7046,8 +7576,14 @@
       <c r="M181" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N181" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="O181" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="47" t="s">
         <v>40</v>
       </c>
@@ -7081,8 +7617,13 @@
         <f>SUM(M177:M181)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N182" s="63"/>
+      <c r="O182" s="45">
+        <f>SUM(O177:O181)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="38" t="s">
         <v>41</v>
       </c>
@@ -7110,8 +7651,12 @@
       <c r="M183" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N183" s="64"/>
+      <c r="O183" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="41" t="s">
         <v>42</v>
       </c>
@@ -7139,10 +7684,14 @@
       <c r="M184" s="43">
         <v>8</v>
       </c>
-      <c r="N184" s="46"/>
-    </row>
-    <row r="185" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N184" s="65"/>
+      <c r="O184" s="43">
+        <v>0</v>
+      </c>
+      <c r="P184" s="46"/>
+    </row>
+    <row r="185" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>53</v>
       </c>
@@ -7182,8 +7731,14 @@
       <c r="M186" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N186" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O186" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>7</v>
       </c>
@@ -7215,8 +7770,14 @@
       <c r="M187" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N187" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O187" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
         <v>8</v>
       </c>
@@ -7248,8 +7809,14 @@
       <c r="M188" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N188" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O188" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>9</v>
       </c>
@@ -7281,8 +7848,14 @@
       <c r="M189" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N189" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O189" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
         <v>10</v>
       </c>
@@ -7314,8 +7887,14 @@
       <c r="M190" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N190" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O190" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="22" t="s">
         <v>11</v>
       </c>
@@ -7347,8 +7926,14 @@
       <c r="M191" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N191" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="O191" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="47" t="s">
         <v>40</v>
       </c>
@@ -7382,8 +7967,13 @@
         <f>SUM(M187:M191)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N192" s="63"/>
+      <c r="O192" s="45">
+        <f>SUM(O187:O191)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="38" t="s">
         <v>41</v>
       </c>
@@ -7411,8 +8001,12 @@
       <c r="M193" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N193" s="64"/>
+      <c r="O193" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="41" t="s">
         <v>42</v>
       </c>
@@ -7440,10 +8034,14 @@
       <c r="M194" s="43">
         <v>8</v>
       </c>
-      <c r="N194" s="46"/>
-    </row>
-    <row r="195" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N194" s="65"/>
+      <c r="O194" s="43">
+        <v>0</v>
+      </c>
+      <c r="P194" s="46"/>
+    </row>
+    <row r="195" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>54</v>
       </c>
@@ -7483,8 +8081,14 @@
       <c r="M196" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N196" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O196" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
         <v>7</v>
       </c>
@@ -7518,8 +8122,14 @@
       <c r="M197" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N197" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O197" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
         <v>8</v>
       </c>
@@ -7553,8 +8163,14 @@
       <c r="M198" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N198" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O198" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
         <v>9</v>
       </c>
@@ -7586,8 +8202,14 @@
         <v>13</v>
       </c>
       <c r="M199" s="12"/>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N199" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O199" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
         <v>10</v>
       </c>
@@ -7619,8 +8241,14 @@
         <v>69</v>
       </c>
       <c r="M200" s="12"/>
-    </row>
-    <row r="201" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N200" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O200" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="22" t="s">
         <v>11</v>
       </c>
@@ -7652,8 +8280,14 @@
         <v>69</v>
       </c>
       <c r="M201" s="24"/>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N201" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="O201" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="47" t="s">
         <v>40</v>
       </c>
@@ -7687,8 +8321,13 @@
         <f>SUM(M197:M201)</f>
         <v>16</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N202" s="63"/>
+      <c r="O202" s="45">
+        <f>SUM(O197:O201)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="38" t="s">
         <v>41</v>
       </c>
@@ -7716,8 +8355,12 @@
       <c r="M203" s="40">
         <v>-8</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N203" s="64"/>
+      <c r="O203" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="41" t="s">
         <v>42</v>
       </c>
@@ -7745,10 +8388,14 @@
       <c r="M204" s="43">
         <v>0</v>
       </c>
-      <c r="N204" s="46"/>
-    </row>
-    <row r="205" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N204" s="65"/>
+      <c r="O204" s="43">
+        <v>0</v>
+      </c>
+      <c r="P204" s="46"/>
+    </row>
+    <row r="205" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
         <v>55</v>
       </c>
@@ -7788,8 +8435,14 @@
       <c r="M206" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N206" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O206" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
         <v>7</v>
       </c>
@@ -7823,8 +8476,14 @@
         <v>69</v>
       </c>
       <c r="M207" s="12"/>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N207" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O207" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>8</v>
       </c>
@@ -7858,8 +8517,14 @@
         <v>69</v>
       </c>
       <c r="M208" s="12"/>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N208" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O208" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>9</v>
       </c>
@@ -7893,8 +8558,14 @@
         <v>69</v>
       </c>
       <c r="M209" s="12"/>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N209" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O209" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
         <v>10</v>
       </c>
@@ -7928,8 +8599,14 @@
         <v>69</v>
       </c>
       <c r="M210" s="12"/>
-    </row>
-    <row r="211" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N210" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O210" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="22" t="s">
         <v>11</v>
       </c>
@@ -7963,8 +8640,14 @@
         <v>69</v>
       </c>
       <c r="M211" s="24"/>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N211" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O211" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" s="47" t="s">
         <v>40</v>
       </c>
@@ -7998,8 +8681,13 @@
         <f>SUM(M207:M211)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N212" s="36"/>
+      <c r="O212" s="37">
+        <f>SUM(O207:O211)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" s="38" t="s">
         <v>41</v>
       </c>
@@ -8027,8 +8715,12 @@
       <c r="M213" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N213" s="39"/>
+      <c r="O213" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="41" t="s">
         <v>42</v>
       </c>
@@ -8056,10 +8748,14 @@
       <c r="M214" s="43">
         <v>0</v>
       </c>
-      <c r="N214" s="46"/>
-    </row>
-    <row r="215" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N214" s="42"/>
+      <c r="O214" s="43">
+        <v>0</v>
+      </c>
+      <c r="P214" s="46"/>
+    </row>
+    <row r="215" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>56</v>
       </c>
@@ -8099,8 +8795,14 @@
       <c r="M216" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N216" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O216" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
         <v>7</v>
       </c>
@@ -8136,8 +8838,14 @@
         <v>69</v>
       </c>
       <c r="M217" s="12"/>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N217" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O217" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
         <v>8</v>
       </c>
@@ -8173,8 +8881,14 @@
         <v>69</v>
       </c>
       <c r="M218" s="12"/>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N218" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O218" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>9</v>
       </c>
@@ -8210,8 +8924,14 @@
         <v>69</v>
       </c>
       <c r="M219" s="12"/>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N219" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O219" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>10</v>
       </c>
@@ -8247,8 +8967,14 @@
         <v>69</v>
       </c>
       <c r="M220" s="12"/>
-    </row>
-    <row r="221" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N220" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O220" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="22" t="s">
         <v>11</v>
       </c>
@@ -8284,8 +9010,14 @@
         <v>69</v>
       </c>
       <c r="M221" s="24"/>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N221" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="O221" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" s="47" t="s">
         <v>40</v>
       </c>
@@ -8319,8 +9051,13 @@
         <f>SUM(M217:M221)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N222" s="63"/>
+      <c r="O222" s="45">
+        <f>SUM(O217:O221)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" s="38" t="s">
         <v>41</v>
       </c>
@@ -8348,8 +9085,12 @@
       <c r="M223" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N223" s="64"/>
+      <c r="O223" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="41" t="s">
         <v>42</v>
       </c>
@@ -8377,10 +9118,14 @@
       <c r="M224" s="43">
         <v>0</v>
       </c>
-      <c r="N224" s="46"/>
-    </row>
-    <row r="225" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N224" s="65"/>
+      <c r="O224" s="43">
+        <v>0</v>
+      </c>
+      <c r="P224" s="46"/>
+    </row>
+    <row r="225" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>57</v>
       </c>
@@ -8420,8 +9165,14 @@
       <c r="M226" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N226" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O226" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>7</v>
       </c>
@@ -8459,8 +9210,14 @@
         <v>69</v>
       </c>
       <c r="M227" s="12"/>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N227" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O227" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
         <v>8</v>
       </c>
@@ -8498,8 +9255,14 @@
         <v>69</v>
       </c>
       <c r="M228" s="12"/>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N228" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O228" s="12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
         <v>9</v>
       </c>
@@ -8537,8 +9300,12 @@
         <v>69</v>
       </c>
       <c r="M229" s="12"/>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N229" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O229" s="12"/>
+    </row>
+    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
         <v>10</v>
       </c>
@@ -8576,8 +9343,12 @@
         <v>69</v>
       </c>
       <c r="M230" s="12"/>
-    </row>
-    <row r="231" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N230" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O230" s="12"/>
+    </row>
+    <row r="231" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="22" t="s">
         <v>11</v>
       </c>
@@ -8613,8 +9384,12 @@
         <v>69</v>
       </c>
       <c r="M231" s="24"/>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N231" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O231" s="24"/>
+    </row>
+    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" s="47" t="s">
         <v>40</v>
       </c>
@@ -8648,8 +9423,13 @@
         <f>SUM(M227:M231)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N232" s="63"/>
+      <c r="O232" s="45">
+        <f>SUM(O227:O231)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" s="38" t="s">
         <v>41</v>
       </c>
@@ -8677,8 +9457,12 @@
       <c r="M233" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N233" s="64"/>
+      <c r="O233" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="41" t="s">
         <v>42</v>
       </c>
@@ -8706,10 +9490,14 @@
       <c r="M234" s="43">
         <v>0</v>
       </c>
-      <c r="N234" s="46"/>
-    </row>
-    <row r="235" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N234" s="65"/>
+      <c r="O234" s="43">
+        <v>0</v>
+      </c>
+      <c r="P234" s="46"/>
+    </row>
+    <row r="235" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
         <v>58</v>
       </c>
@@ -8749,8 +9537,14 @@
       <c r="M236" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N236" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O236" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" s="11" t="s">
         <v>7</v>
       </c>
@@ -8790,8 +9584,14 @@
       <c r="M237" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N237" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O237" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
         <v>8</v>
       </c>
@@ -8831,8 +9631,14 @@
       <c r="M238" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N238" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O238" s="12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
         <v>9</v>
       </c>
@@ -8872,8 +9678,12 @@
       <c r="M239" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N239" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O239" s="12"/>
+    </row>
+    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
         <v>10</v>
       </c>
@@ -8913,8 +9723,12 @@
       <c r="M240" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="241" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N240" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O240" s="12"/>
+    </row>
+    <row r="241" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="22" t="s">
         <v>11</v>
       </c>
@@ -8950,8 +9764,12 @@
         <v>50</v>
       </c>
       <c r="M241" s="24"/>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N241" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O241" s="24"/>
+    </row>
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" s="47" t="s">
         <v>40</v>
       </c>
@@ -8985,8 +9803,13 @@
         <f>SUM(M237:M241)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N242" s="63"/>
+      <c r="O242" s="45">
+        <f>SUM(O237:O241)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" s="38" t="s">
         <v>41</v>
       </c>
@@ -9014,8 +9837,12 @@
       <c r="M243" s="40">
         <v>-6</v>
       </c>
-    </row>
-    <row r="244" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N243" s="64"/>
+      <c r="O243" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="41" t="s">
         <v>42</v>
       </c>
@@ -9043,10 +9870,14 @@
       <c r="M244" s="43">
         <v>3</v>
       </c>
-      <c r="N244" s="49"/>
-    </row>
-    <row r="245" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N244" s="65"/>
+      <c r="O244" s="43">
+        <v>0</v>
+      </c>
+      <c r="P244" s="49"/>
+    </row>
+    <row r="245" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
         <v>59</v>
       </c>
@@ -9086,8 +9917,14 @@
       <c r="M246" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N246" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O246" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" s="11" t="s">
         <v>7</v>
       </c>
@@ -9127,8 +9964,14 @@
       <c r="M247" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O247" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
         <v>8</v>
       </c>
@@ -9168,8 +10011,14 @@
       <c r="M248" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N248" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O248" s="12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
         <v>9</v>
       </c>
@@ -9209,8 +10058,12 @@
       <c r="M249" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N249" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O249" s="12"/>
+    </row>
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
         <v>10</v>
       </c>
@@ -9250,8 +10103,12 @@
       <c r="M250" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N250" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O250" s="12"/>
+    </row>
+    <row r="251" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="22" t="s">
         <v>11</v>
       </c>
@@ -9287,8 +10144,12 @@
         <v>50</v>
       </c>
       <c r="M251" s="24"/>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N251" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O251" s="24"/>
+    </row>
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" s="47" t="s">
         <v>40</v>
       </c>
@@ -9322,8 +10183,13 @@
         <f>SUM(M247:M251)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N252" s="63"/>
+      <c r="O252" s="45">
+        <f>SUM(O247:O251)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" s="38" t="s">
         <v>41</v>
       </c>
@@ -9351,8 +10217,12 @@
       <c r="M253" s="40">
         <v>-6</v>
       </c>
-    </row>
-    <row r="254" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N253" s="64"/>
+      <c r="O253" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="41" t="s">
         <v>42</v>
       </c>
@@ -9380,10 +10250,14 @@
       <c r="M254" s="43">
         <v>3</v>
       </c>
-      <c r="N254" s="49"/>
-    </row>
-    <row r="255" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N254" s="65"/>
+      <c r="O254" s="43">
+        <v>0</v>
+      </c>
+      <c r="P254" s="49"/>
+    </row>
+    <row r="255" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
         <v>60</v>
       </c>
@@ -9423,8 +10297,14 @@
       <c r="M256" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N256" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O256" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>7</v>
       </c>
@@ -9464,8 +10344,14 @@
       <c r="M257" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N257" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O257" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
         <v>8</v>
       </c>
@@ -9505,8 +10391,14 @@
       <c r="M258" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N258" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O258" s="12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" s="11" t="s">
         <v>9</v>
       </c>
@@ -9546,8 +10438,12 @@
       <c r="M259" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N259" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O259" s="12"/>
+    </row>
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
         <v>10</v>
       </c>
@@ -9587,8 +10483,12 @@
       <c r="M260" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="261" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N260" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O260" s="12"/>
+    </row>
+    <row r="261" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="22" t="s">
         <v>11</v>
       </c>
@@ -9624,8 +10524,12 @@
         <v>50</v>
       </c>
       <c r="M261" s="24"/>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N261" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O261" s="24"/>
+    </row>
+    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262" s="47" t="s">
         <v>40</v>
       </c>
@@ -9659,8 +10563,13 @@
         <f>SUM(M257:M261)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N262" s="63"/>
+      <c r="O262" s="45">
+        <f>SUM(O257:O261)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263" s="38" t="s">
         <v>41</v>
       </c>
@@ -9688,8 +10597,12 @@
       <c r="M263" s="40">
         <v>-6</v>
       </c>
-    </row>
-    <row r="264" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N263" s="64"/>
+      <c r="O263" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="41" t="s">
         <v>42</v>
       </c>
@@ -9717,10 +10630,14 @@
       <c r="M264" s="43">
         <v>3</v>
       </c>
-      <c r="N264" s="49"/>
-    </row>
-    <row r="265" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N264" s="65"/>
+      <c r="O264" s="43">
+        <v>0</v>
+      </c>
+      <c r="P264" s="49"/>
+    </row>
+    <row r="265" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
         <v>61</v>
       </c>
@@ -9760,8 +10677,14 @@
       <c r="M266" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N266" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="O266" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
         <v>7</v>
       </c>
@@ -9801,8 +10724,14 @@
       <c r="M267" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N267" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O267" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
         <v>8</v>
       </c>
@@ -9842,8 +10771,14 @@
       <c r="M268" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N268" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O268" s="12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269" s="11" t="s">
         <v>9</v>
       </c>
@@ -9883,8 +10818,12 @@
       <c r="M269" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N269" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O269" s="12"/>
+    </row>
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
         <v>10</v>
       </c>
@@ -9924,8 +10863,12 @@
       <c r="M270" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="271" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N270" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O270" s="12"/>
+    </row>
+    <row r="271" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="22" t="s">
         <v>11</v>
       </c>
@@ -9961,8 +10904,12 @@
         <v>50</v>
       </c>
       <c r="M271" s="24"/>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N271" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O271" s="24"/>
+    </row>
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272" s="47" t="s">
         <v>40</v>
       </c>
@@ -9996,8 +10943,13 @@
         <f>SUM(M267:M271)</f>
         <v>34</v>
       </c>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N272" s="63"/>
+      <c r="O272" s="45">
+        <f>SUM(O267:O271)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273" s="38" t="s">
         <v>41</v>
       </c>
@@ -10025,8 +10977,12 @@
       <c r="M273" s="40">
         <v>-6</v>
       </c>
-    </row>
-    <row r="274" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N273" s="64"/>
+      <c r="O273" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="41" t="s">
         <v>42</v>
       </c>
@@ -10054,7 +11010,11 @@
       <c r="M274" s="43">
         <v>3</v>
       </c>
-      <c r="N274" s="49"/>
+      <c r="N274" s="65"/>
+      <c r="O274" s="43">
+        <v>0</v>
+      </c>
+      <c r="P274" s="49"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1059" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82814B07-FE41-4B2B-8F9B-AEBCD632EA2C}"/>
+  <xr:revisionPtr revIDLastSave="1062" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7281135B-EEE4-4D08-AFA1-CBF166197A53}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="195" windowWidth="44205" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="2070" yWindow="240" windowWidth="38385" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="74">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -189,9 +189,6 @@
   </si>
   <si>
     <t>Veckans saldo (Nationadag lörd)</t>
-  </si>
-  <si>
-    <t>Ledigt</t>
   </si>
   <si>
     <t>Vecka 26 (22-26 juni)</t>
@@ -607,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -748,25 +745,22 @@
     <xf numFmtId="164" fontId="1" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1512,7 +1506,7 @@
       <c r="O10" s="43"/>
       <c r="P10" s="46"/>
       <c r="Q10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1563,8 +1557,8 @@
       <c r="M12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N12" s="56"/>
-      <c r="O12" s="56"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
@@ -1606,8 +1600,8 @@
       <c r="M13" s="12">
         <v>10</v>
       </c>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
@@ -1649,8 +1643,8 @@
       <c r="M14" s="12">
         <v>9</v>
       </c>
-      <c r="N14" s="56"/>
-      <c r="O14" s="56"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
@@ -1692,8 +1686,8 @@
       <c r="M15" s="12">
         <v>8</v>
       </c>
-      <c r="N15" s="56"/>
-      <c r="O15" s="56"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
@@ -1735,8 +1729,8 @@
       <c r="M16" s="12">
         <v>5</v>
       </c>
-      <c r="N16" s="56"/>
-      <c r="O16" s="56"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
@@ -1776,8 +1770,8 @@
       <c r="M17" s="15">
         <v>7</v>
       </c>
-      <c r="N17" s="56"/>
-      <c r="O17" s="56"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
@@ -1813,8 +1807,8 @@
         <f>SUM(M13:M17)</f>
         <v>39</v>
       </c>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="56"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
@@ -1844,8 +1838,8 @@
       <c r="M19" s="40">
         <v>-1</v>
       </c>
-      <c r="N19" s="58"/>
-      <c r="O19" s="58"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
     </row>
     <row r="20" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
@@ -1875,8 +1869,8 @@
       <c r="M20" s="43">
         <v>0</v>
       </c>
-      <c r="N20" s="59"/>
-      <c r="O20" s="59"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
       <c r="P20" s="46"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1927,8 +1921,8 @@
       <c r="M22" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N22" s="56"/>
-      <c r="O22" s="56"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
@@ -1970,8 +1964,8 @@
       <c r="M23" s="12">
         <v>10</v>
       </c>
-      <c r="N23" s="56"/>
-      <c r="O23" s="56"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
@@ -2013,8 +2007,8 @@
       <c r="M24" s="12">
         <v>9</v>
       </c>
-      <c r="N24" s="56"/>
-      <c r="O24" s="56"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
@@ -2056,8 +2050,8 @@
       <c r="M25" s="12">
         <v>8</v>
       </c>
-      <c r="N25" s="56"/>
-      <c r="O25" s="56"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
     </row>
     <row r="26" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
@@ -2097,8 +2091,8 @@
       <c r="M26" s="12">
         <v>7</v>
       </c>
-      <c r="N26" s="56"/>
-      <c r="O26" s="56"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
@@ -2136,8 +2130,8 @@
         <v>13</v>
       </c>
       <c r="M27" s="15"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="35" t="s">
@@ -2173,8 +2167,8 @@
         <f>SUM(M23:M27)</f>
         <v>34</v>
       </c>
-      <c r="N28" s="57"/>
-      <c r="O28" s="57"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="56"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
@@ -2204,8 +2198,8 @@
       <c r="M29" s="40">
         <v>-6</v>
       </c>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
     </row>
     <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
@@ -2235,8 +2229,8 @@
       <c r="M30" s="43">
         <v>-6</v>
       </c>
-      <c r="N30" s="59"/>
-      <c r="O30" s="59"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="58"/>
       <c r="P30" s="46"/>
     </row>
     <row r="31" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2280,8 +2274,8 @@
       <c r="M32" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N32" s="56"/>
-      <c r="O32" s="56"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
@@ -2323,8 +2317,8 @@
       <c r="M33" s="12">
         <v>10</v>
       </c>
-      <c r="N33" s="56"/>
-      <c r="O33" s="56"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
@@ -2366,8 +2360,8 @@
       <c r="M34" s="12">
         <v>9</v>
       </c>
-      <c r="N34" s="56"/>
-      <c r="O34" s="56"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
@@ -2409,8 +2403,8 @@
       <c r="M35" s="12">
         <v>8</v>
       </c>
-      <c r="N35" s="56"/>
-      <c r="O35" s="56"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
@@ -2450,8 +2444,8 @@
       <c r="M36" s="12">
         <v>5</v>
       </c>
-      <c r="N36" s="56"/>
-      <c r="O36" s="56"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
     </row>
     <row r="37" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
@@ -2491,8 +2485,8 @@
       <c r="M37" s="15">
         <v>7</v>
       </c>
-      <c r="N37" s="56"/>
-      <c r="O37" s="56"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
@@ -2528,8 +2522,8 @@
         <f>SUM(M33:M37)</f>
         <v>39</v>
       </c>
-      <c r="N38" s="57"/>
-      <c r="O38" s="57"/>
+      <c r="N38" s="56"/>
+      <c r="O38" s="56"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
@@ -2559,8 +2553,8 @@
       <c r="M39" s="40">
         <v>-1</v>
       </c>
-      <c r="N39" s="58"/>
-      <c r="O39" s="58"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="41" t="s">
@@ -2590,8 +2584,8 @@
       <c r="M40" s="43">
         <v>-7</v>
       </c>
-      <c r="N40" s="59"/>
-      <c r="O40" s="59"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
       <c r="P40" s="46"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2635,8 +2629,8 @@
       <c r="M42" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N42" s="56"/>
-      <c r="O42" s="56"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
@@ -2678,8 +2672,8 @@
       <c r="M43" s="12">
         <v>10</v>
       </c>
-      <c r="N43" s="56"/>
-      <c r="O43" s="56"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
@@ -2721,8 +2715,8 @@
       <c r="M44" s="12">
         <v>9</v>
       </c>
-      <c r="N44" s="56"/>
-      <c r="O44" s="56"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
@@ -2762,8 +2756,8 @@
       <c r="M45" s="12">
         <v>8</v>
       </c>
-      <c r="N45" s="56"/>
-      <c r="O45" s="56"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
@@ -2801,8 +2795,8 @@
       <c r="M46" s="12">
         <v>5</v>
       </c>
-      <c r="N46" s="56"/>
-      <c r="O46" s="56"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
     </row>
     <row r="47" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
@@ -2832,8 +2826,8 @@
         <v>13</v>
       </c>
       <c r="M47" s="27"/>
-      <c r="N47" s="60"/>
-      <c r="O47" s="60"/>
+      <c r="N47" s="59"/>
+      <c r="O47" s="59"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="35" t="s">
@@ -2869,8 +2863,8 @@
         <f>SUM(M43:M47)</f>
         <v>32</v>
       </c>
-      <c r="N48" s="57"/>
-      <c r="O48" s="57"/>
+      <c r="N48" s="56"/>
+      <c r="O48" s="56"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
@@ -2900,8 +2894,8 @@
       <c r="M49" s="40">
         <v>0</v>
       </c>
-      <c r="N49" s="58"/>
-      <c r="O49" s="58"/>
+      <c r="N49" s="57"/>
+      <c r="O49" s="57"/>
     </row>
     <row r="50" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="41" t="s">
@@ -2931,8 +2925,8 @@
       <c r="M50" s="43">
         <v>-7</v>
       </c>
-      <c r="N50" s="59"/>
-      <c r="O50" s="59"/>
+      <c r="N50" s="58"/>
+      <c r="O50" s="58"/>
       <c r="P50" s="46"/>
     </row>
     <row r="51" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2976,15 +2970,15 @@
       <c r="M52" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N52" s="56"/>
-      <c r="O52" s="56"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
         <v>26</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" s="20">
         <v>7</v>
@@ -3017,8 +3011,8 @@
       <c r="M53" s="28">
         <v>10</v>
       </c>
-      <c r="N53" s="61"/>
-      <c r="O53" s="61"/>
+      <c r="N53" s="60"/>
+      <c r="O53" s="60"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
@@ -3060,8 +3054,8 @@
       <c r="M54" s="12">
         <v>9</v>
       </c>
-      <c r="N54" s="56"/>
-      <c r="O54" s="56"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
@@ -3103,8 +3097,8 @@
       <c r="M55" s="12">
         <v>8</v>
       </c>
-      <c r="N55" s="56"/>
-      <c r="O55" s="56"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
@@ -3144,8 +3138,8 @@
       <c r="M56" s="12">
         <v>5</v>
       </c>
-      <c r="N56" s="56"/>
-      <c r="O56" s="56"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
     </row>
     <row r="57" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
@@ -3185,8 +3179,8 @@
       <c r="M57" s="15">
         <v>7</v>
       </c>
-      <c r="N57" s="56"/>
-      <c r="O57" s="56"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="35" t="s">
@@ -3222,8 +3216,8 @@
         <f>SUM(M53:M57)</f>
         <v>39</v>
       </c>
-      <c r="N58" s="57"/>
-      <c r="O58" s="57"/>
+      <c r="N58" s="56"/>
+      <c r="O58" s="56"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
@@ -3253,15 +3247,15 @@
       <c r="M59" s="40">
         <v>7</v>
       </c>
-      <c r="N59" s="58"/>
-      <c r="O59" s="58"/>
+      <c r="N59" s="57"/>
+      <c r="O59" s="57"/>
     </row>
     <row r="60" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B60" s="53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C60" s="54">
         <v>15</v>
@@ -3275,25 +3269,25 @@
         <v>-3</v>
       </c>
       <c r="H60" s="53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I60" s="54">
         <v>14</v>
       </c>
       <c r="J60" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="K60" s="54">
+        <v>9</v>
+      </c>
+      <c r="L60" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="K60" s="54">
-        <v>9</v>
-      </c>
-      <c r="L60" s="53" t="s">
-        <v>66</v>
-      </c>
       <c r="M60" s="55">
         <v>12</v>
       </c>
-      <c r="N60" s="62"/>
-      <c r="O60" s="62"/>
+      <c r="N60" s="61"/>
+      <c r="O60" s="61"/>
       <c r="P60" s="46"/>
     </row>
     <row r="61" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3337,8 +3331,8 @@
       <c r="M62" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N62" s="56"/>
-      <c r="O62" s="56"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
@@ -3380,8 +3374,8 @@
       <c r="M63" s="12">
         <v>10</v>
       </c>
-      <c r="N63" s="56"/>
-      <c r="O63" s="56"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
@@ -3423,8 +3417,8 @@
       <c r="M64" s="12">
         <v>9</v>
       </c>
-      <c r="N64" s="56"/>
-      <c r="O64" s="56"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
@@ -3466,8 +3460,8 @@
       <c r="M65" s="12">
         <v>8</v>
       </c>
-      <c r="N65" s="56"/>
-      <c r="O65" s="56"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
@@ -3509,15 +3503,15 @@
       <c r="M66" s="12">
         <v>7</v>
       </c>
-      <c r="N66" s="56"/>
-      <c r="O66" s="56"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
     </row>
     <row r="67" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B67" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C67" s="23"/>
       <c r="D67" s="23" t="s">
@@ -3548,8 +3542,8 @@
       <c r="M67" s="24">
         <v>7</v>
       </c>
-      <c r="N67" s="56"/>
-      <c r="O67" s="56"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="47" t="s">
@@ -3585,8 +3579,8 @@
         <f>SUM(M63:M67)</f>
         <v>41</v>
       </c>
-      <c r="N68" s="57"/>
-      <c r="O68" s="57"/>
+      <c r="N68" s="56"/>
+      <c r="O68" s="56"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
@@ -3616,8 +3610,8 @@
       <c r="M69" s="40">
         <v>1</v>
       </c>
-      <c r="N69" s="58"/>
-      <c r="O69" s="58"/>
+      <c r="N69" s="57"/>
+      <c r="O69" s="57"/>
     </row>
     <row r="70" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41" t="s">
@@ -3647,8 +3641,8 @@
       <c r="M70" s="43">
         <v>13</v>
       </c>
-      <c r="N70" s="59"/>
-      <c r="O70" s="59"/>
+      <c r="N70" s="58"/>
+      <c r="O70" s="58"/>
       <c r="P70" s="46"/>
     </row>
     <row r="71" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3692,8 +3686,8 @@
       <c r="M72" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N72" s="56"/>
-      <c r="O72" s="56"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
@@ -3735,8 +3729,8 @@
       <c r="M73" s="12">
         <v>10</v>
       </c>
-      <c r="N73" s="56"/>
-      <c r="O73" s="56"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
@@ -3778,8 +3772,8 @@
       <c r="M74" s="12">
         <v>9</v>
       </c>
-      <c r="N74" s="56"/>
-      <c r="O74" s="56"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
@@ -3821,8 +3815,8 @@
       <c r="M75" s="12">
         <v>8</v>
       </c>
-      <c r="N75" s="56"/>
-      <c r="O75" s="56"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
@@ -3864,8 +3858,8 @@
       <c r="M76" s="12">
         <v>5</v>
       </c>
-      <c r="N76" s="56"/>
-      <c r="O76" s="56"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
     </row>
     <row r="77" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
@@ -3905,8 +3899,8 @@
       <c r="M77" s="15">
         <v>7</v>
       </c>
-      <c r="N77" s="56"/>
-      <c r="O77" s="56"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
@@ -3942,8 +3936,8 @@
         <f>SUM(M73:M77)</f>
         <v>39</v>
       </c>
-      <c r="N78" s="57"/>
-      <c r="O78" s="57"/>
+      <c r="N78" s="56"/>
+      <c r="O78" s="56"/>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
@@ -3973,8 +3967,8 @@
       <c r="M79" s="40">
         <v>-1</v>
       </c>
-      <c r="N79" s="58"/>
-      <c r="O79" s="58"/>
+      <c r="N79" s="57"/>
+      <c r="O79" s="57"/>
     </row>
     <row r="80" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="41" t="s">
@@ -4004,8 +3998,8 @@
       <c r="M80" s="43">
         <v>12</v>
       </c>
-      <c r="N80" s="59"/>
-      <c r="O80" s="59"/>
+      <c r="N80" s="58"/>
+      <c r="O80" s="58"/>
       <c r="P80" s="46"/>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
@@ -4045,7 +4039,7 @@
     <row r="83" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>2</v>
@@ -4083,8 +4077,8 @@
       <c r="M84" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N84" s="56"/>
-      <c r="O84" s="56"/>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
@@ -4126,8 +4120,8 @@
       <c r="M85" s="12">
         <v>10</v>
       </c>
-      <c r="N85" s="56"/>
-      <c r="O85" s="56"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
@@ -4169,8 +4163,8 @@
       <c r="M86" s="12">
         <v>9</v>
       </c>
-      <c r="N86" s="56"/>
-      <c r="O86" s="56"/>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
@@ -4212,8 +4206,8 @@
       <c r="M87" s="12">
         <v>8</v>
       </c>
-      <c r="N87" s="56"/>
-      <c r="O87" s="56"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
@@ -4248,13 +4242,13 @@
       </c>
       <c r="K88" s="4"/>
       <c r="L88" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M88" s="12">
         <v>7</v>
       </c>
-      <c r="N88" s="56"/>
-      <c r="O88" s="56"/>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
     </row>
     <row r="89" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="29" t="s">
@@ -4284,8 +4278,8 @@
         <v>13</v>
       </c>
       <c r="M89" s="31"/>
-      <c r="N89" s="60"/>
-      <c r="O89" s="60"/>
+      <c r="N89" s="59"/>
+      <c r="O89" s="59"/>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="47" t="s">
@@ -4321,8 +4315,8 @@
         <f>SUM(M85:M89)</f>
         <v>34</v>
       </c>
-      <c r="N90" s="57"/>
-      <c r="O90" s="57"/>
+      <c r="N90" s="56"/>
+      <c r="O90" s="56"/>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="38" t="s">
@@ -4352,8 +4346,8 @@
       <c r="M91" s="40">
         <v>2</v>
       </c>
-      <c r="N91" s="58"/>
-      <c r="O91" s="58"/>
+      <c r="N91" s="57"/>
+      <c r="O91" s="57"/>
     </row>
     <row r="92" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="41" t="s">
@@ -4383,14 +4377,14 @@
       <c r="M92" s="43">
         <v>14</v>
       </c>
-      <c r="N92" s="59"/>
-      <c r="O92" s="59"/>
+      <c r="N92" s="58"/>
+      <c r="O92" s="58"/>
       <c r="P92" s="46"/>
     </row>
     <row r="93" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>2</v>
@@ -4428,8 +4422,8 @@
       <c r="M94" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N94" s="56"/>
-      <c r="O94" s="56"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
@@ -4471,8 +4465,8 @@
       <c r="M95" s="12">
         <v>10</v>
       </c>
-      <c r="N95" s="56"/>
-      <c r="O95" s="56"/>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
@@ -4514,8 +4508,8 @@
       <c r="M96" s="12">
         <v>9</v>
       </c>
-      <c r="N96" s="56"/>
-      <c r="O96" s="56"/>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
@@ -4557,8 +4551,8 @@
       <c r="M97" s="12">
         <v>8</v>
       </c>
-      <c r="N97" s="56"/>
-      <c r="O97" s="56"/>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
@@ -4600,8 +4594,8 @@
       <c r="M98" s="12">
         <v>5</v>
       </c>
-      <c r="N98" s="56"/>
-      <c r="O98" s="56"/>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
     </row>
     <row r="99" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
@@ -4641,8 +4635,8 @@
       <c r="M99" s="24">
         <v>7</v>
       </c>
-      <c r="N99" s="56"/>
-      <c r="O99" s="56"/>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="47" t="s">
@@ -4678,8 +4672,8 @@
         <f>SUM(M95:M99)</f>
         <v>39</v>
       </c>
-      <c r="N100" s="57"/>
-      <c r="O100" s="57"/>
+      <c r="N100" s="56"/>
+      <c r="O100" s="56"/>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="38" t="s">
@@ -4709,8 +4703,8 @@
       <c r="M101" s="40">
         <v>-1</v>
       </c>
-      <c r="N101" s="58"/>
-      <c r="O101" s="58"/>
+      <c r="N101" s="57"/>
+      <c r="O101" s="57"/>
     </row>
     <row r="102" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="41" t="s">
@@ -4740,8 +4734,8 @@
       <c r="M102" s="43">
         <v>13</v>
       </c>
-      <c r="N102" s="59"/>
-      <c r="O102" s="59"/>
+      <c r="N102" s="58"/>
+      <c r="O102" s="58"/>
       <c r="P102" s="46"/>
     </row>
     <row r="103" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -4785,8 +4779,8 @@
       <c r="M104" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N104" s="56"/>
-      <c r="O104" s="56"/>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
       <c r="Q104" s="2"/>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -4829,8 +4823,8 @@
       <c r="M105" s="12">
         <v>10</v>
       </c>
-      <c r="N105" s="56"/>
-      <c r="O105" s="56"/>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
@@ -4872,8 +4866,8 @@
       <c r="M106" s="12">
         <v>9</v>
       </c>
-      <c r="N106" s="56"/>
-      <c r="O106" s="56"/>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
@@ -4915,8 +4909,8 @@
       <c r="M107" s="12">
         <v>8</v>
       </c>
-      <c r="N107" s="56"/>
-      <c r="O107" s="56"/>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
@@ -4946,8 +4940,8 @@
         <v>13</v>
       </c>
       <c r="M108" s="19"/>
-      <c r="N108" s="60"/>
-      <c r="O108" s="60"/>
+      <c r="N108" s="59"/>
+      <c r="O108" s="59"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
@@ -4987,8 +4981,8 @@
       <c r="M109" s="24">
         <v>7</v>
       </c>
-      <c r="N109" s="56"/>
-      <c r="O109" s="56"/>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="47" t="s">
@@ -5024,8 +5018,8 @@
         <f>SUM(M105:M109)</f>
         <v>34</v>
       </c>
-      <c r="N110" s="57"/>
-      <c r="O110" s="57"/>
+      <c r="N110" s="56"/>
+      <c r="O110" s="56"/>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="38" t="s">
@@ -5055,8 +5049,8 @@
       <c r="M111" s="40">
         <v>2</v>
       </c>
-      <c r="N111" s="58"/>
-      <c r="O111" s="58"/>
+      <c r="N111" s="57"/>
+      <c r="O111" s="57"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="41" t="s">
@@ -5086,8 +5080,8 @@
       <c r="M112" s="43">
         <v>15</v>
       </c>
-      <c r="N112" s="59"/>
-      <c r="O112" s="59"/>
+      <c r="N112" s="58"/>
+      <c r="O112" s="58"/>
       <c r="P112" s="46"/>
     </row>
     <row r="113" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -5131,8 +5125,8 @@
       <c r="M114" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N114" s="56"/>
-      <c r="O114" s="56"/>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
@@ -5174,8 +5168,8 @@
       <c r="M115" s="12">
         <v>10</v>
       </c>
-      <c r="N115" s="56"/>
-      <c r="O115" s="56"/>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
@@ -5217,8 +5211,8 @@
       <c r="M116" s="12">
         <v>9</v>
       </c>
-      <c r="N116" s="56"/>
-      <c r="O116" s="56"/>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
@@ -5260,8 +5254,8 @@
       <c r="M117" s="12">
         <v>8</v>
       </c>
-      <c r="N117" s="56"/>
-      <c r="O117" s="56"/>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
@@ -5303,8 +5297,8 @@
       <c r="M118" s="12">
         <v>5</v>
       </c>
-      <c r="N118" s="56"/>
-      <c r="O118" s="56"/>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
     </row>
     <row r="119" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
@@ -5344,8 +5338,8 @@
       <c r="M119" s="24">
         <v>7</v>
       </c>
-      <c r="N119" s="56"/>
-      <c r="O119" s="56"/>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="47" t="s">
@@ -5381,8 +5375,8 @@
         <f>SUM(M115:M119)</f>
         <v>39</v>
       </c>
-      <c r="N120" s="57"/>
-      <c r="O120" s="57"/>
+      <c r="N120" s="56"/>
+      <c r="O120" s="56"/>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="38" t="s">
@@ -5412,8 +5406,8 @@
       <c r="M121" s="40">
         <v>-1</v>
       </c>
-      <c r="N121" s="58"/>
-      <c r="O121" s="58"/>
+      <c r="N121" s="57"/>
+      <c r="O121" s="57"/>
     </row>
     <row r="122" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="41" t="s">
@@ -5443,8 +5437,8 @@
       <c r="M122" s="43">
         <v>14</v>
       </c>
-      <c r="N122" s="59"/>
-      <c r="O122" s="59"/>
+      <c r="N122" s="58"/>
+      <c r="O122" s="58"/>
       <c r="P122" s="46"/>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
@@ -5523,7 +5517,7 @@
         <v>18</v>
       </c>
       <c r="N126" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O126" s="10" t="s">
         <v>18</v>
@@ -5664,7 +5658,7 @@
         <v>8</v>
       </c>
       <c r="N129" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O129" s="12"/>
     </row>
@@ -5709,7 +5703,7 @@
         <v>7</v>
       </c>
       <c r="N130" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O130" s="12"/>
     </row>
@@ -5746,11 +5740,11 @@
       </c>
       <c r="K131" s="23"/>
       <c r="L131" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="M131" s="24"/>
       <c r="N131" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O131" s="24"/>
     </row>
@@ -5788,7 +5782,7 @@
         <f>SUM(M127:M131)</f>
         <v>34</v>
       </c>
-      <c r="N132" s="63"/>
+      <c r="N132" s="62"/>
       <c r="O132" s="45">
         <f>SUM(O127:O131)</f>
         <v>19</v>
@@ -5822,7 +5816,7 @@
       <c r="M133" s="40">
         <v>-6</v>
       </c>
-      <c r="N133" s="64"/>
+      <c r="N133" s="63"/>
       <c r="O133" s="40">
         <v>0</v>
       </c>
@@ -5855,7 +5849,7 @@
       <c r="M134" s="43">
         <v>8</v>
       </c>
-      <c r="N134" s="65"/>
+      <c r="N134" s="64"/>
       <c r="O134" s="43">
         <v>0</v>
       </c>
@@ -5903,7 +5897,7 @@
         <v>18</v>
       </c>
       <c r="N136" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O136" s="10" t="s">
         <v>18</v>
@@ -5926,7 +5920,7 @@
         <v>10</v>
       </c>
       <c r="F137" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
@@ -5971,7 +5965,7 @@
         <v>9</v>
       </c>
       <c r="F138" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
@@ -6016,7 +6010,7 @@
         <v>4</v>
       </c>
       <c r="F139" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
@@ -6049,7 +6043,7 @@
         <v>10</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C140" s="4">
         <v>5</v>
@@ -6061,7 +6055,7 @@
         <v>8</v>
       </c>
       <c r="F140" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="5" t="s">
@@ -6090,7 +6084,7 @@
         <v>11</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C141" s="23">
         <v>5</v>
@@ -6100,7 +6094,7 @@
       </c>
       <c r="E141" s="23"/>
       <c r="F141" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G141" s="23"/>
       <c r="H141" s="23" t="s">
@@ -6160,7 +6154,7 @@
         <f>SUM(M137:M141)</f>
         <v>34</v>
       </c>
-      <c r="N142" s="63"/>
+      <c r="N142" s="62"/>
       <c r="O142" s="45">
         <f>SUM(O137:O141)</f>
         <v>40</v>
@@ -6194,7 +6188,7 @@
       <c r="M143" s="40">
         <v>2</v>
       </c>
-      <c r="N143" s="64"/>
+      <c r="N143" s="63"/>
       <c r="O143" s="40">
         <v>0</v>
       </c>
@@ -6227,7 +6221,7 @@
       <c r="M144" s="43">
         <v>10</v>
       </c>
-      <c r="N144" s="65"/>
+      <c r="N144" s="64"/>
       <c r="O144" s="43">
         <v>0</v>
       </c>
@@ -6275,7 +6269,7 @@
         <v>18</v>
       </c>
       <c r="N146" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O146" s="10" t="s">
         <v>18</v>
@@ -6298,7 +6292,7 @@
         <v>8</v>
       </c>
       <c r="F147" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G147" s="4"/>
       <c r="H147" s="4" t="s">
@@ -6343,7 +6337,7 @@
         <v>8</v>
       </c>
       <c r="F148" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4" t="s">
@@ -6388,7 +6382,7 @@
         <v>8</v>
       </c>
       <c r="F149" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G149" s="4"/>
       <c r="H149" s="4" t="s">
@@ -6431,7 +6425,7 @@
         <v>8</v>
       </c>
       <c r="F150" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4" t="s">
@@ -6445,7 +6439,7 @@
       </c>
       <c r="K150" s="4"/>
       <c r="L150" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M150" s="12">
         <v>7</v>
@@ -6472,7 +6466,7 @@
         <v>8</v>
       </c>
       <c r="F151" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G151" s="23"/>
       <c r="H151" s="23" t="s">
@@ -6486,7 +6480,7 @@
       </c>
       <c r="K151" s="23"/>
       <c r="L151" s="48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M151" s="24">
         <v>7</v>
@@ -6532,7 +6526,7 @@
         <f>SUM(M147:M151)</f>
         <v>38</v>
       </c>
-      <c r="N152" s="63"/>
+      <c r="N152" s="62"/>
       <c r="O152" s="45">
         <f>SUM(O147:O151)</f>
         <v>40</v>
@@ -6566,7 +6560,7 @@
       <c r="M153" s="40">
         <v>-2</v>
       </c>
-      <c r="N153" s="64"/>
+      <c r="N153" s="63"/>
       <c r="O153" s="40">
         <v>0</v>
       </c>
@@ -6599,7 +6593,7 @@
       <c r="M154" s="43">
         <v>8</v>
       </c>
-      <c r="N154" s="65"/>
+      <c r="N154" s="64"/>
       <c r="O154" s="43">
         <v>0</v>
       </c>
@@ -6647,7 +6641,7 @@
         <v>18</v>
       </c>
       <c r="N156" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O156" s="10" t="s">
         <v>18</v>
@@ -6658,7 +6652,7 @@
         <v>7</v>
       </c>
       <c r="B157" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4" t="s">
@@ -6701,7 +6695,7 @@
         <v>8</v>
       </c>
       <c r="B158" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4" t="s">
@@ -6744,7 +6738,7 @@
         <v>9</v>
       </c>
       <c r="B159" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4" t="s">
@@ -6787,7 +6781,7 @@
         <v>10</v>
       </c>
       <c r="B160" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4" t="s">
@@ -6890,7 +6884,7 @@
         <f>SUM(M157:M161)</f>
         <v>32</v>
       </c>
-      <c r="N162" s="63"/>
+      <c r="N162" s="62"/>
       <c r="O162" s="45">
         <f>SUM(O157:O161)</f>
         <v>32</v>
@@ -6924,7 +6918,7 @@
       <c r="M163" s="40">
         <v>0</v>
       </c>
-      <c r="N163" s="64"/>
+      <c r="N163" s="63"/>
       <c r="O163" s="40">
         <v>0</v>
       </c>
@@ -6957,7 +6951,7 @@
       <c r="M164" s="43">
         <v>8</v>
       </c>
-      <c r="N164" s="65"/>
+      <c r="N164" s="64"/>
       <c r="O164" s="43">
         <v>0</v>
       </c>
@@ -6966,7 +6960,7 @@
     <row r="165" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B166" s="8" t="s">
         <v>2</v>
@@ -7005,7 +6999,7 @@
         <v>18</v>
       </c>
       <c r="N166" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O166" s="10" t="s">
         <v>18</v>
@@ -7016,7 +7010,7 @@
         <v>7</v>
       </c>
       <c r="B167" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C167" s="4"/>
       <c r="D167" s="4" t="s">
@@ -7032,7 +7026,7 @@
         <v>7</v>
       </c>
       <c r="H167" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I167" s="4"/>
       <c r="J167" s="4" t="s">
@@ -7059,7 +7053,7 @@
         <v>8</v>
       </c>
       <c r="B168" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C168" s="4"/>
       <c r="D168" s="4" t="s">
@@ -7075,7 +7069,7 @@
         <v>7</v>
       </c>
       <c r="H168" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I168" s="4"/>
       <c r="J168" s="4" t="s">
@@ -7102,7 +7096,7 @@
         <v>9</v>
       </c>
       <c r="B169" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4" t="s">
@@ -7118,7 +7112,7 @@
         <v>7</v>
       </c>
       <c r="H169" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I169" s="4"/>
       <c r="J169" s="4" t="s">
@@ -7145,7 +7139,7 @@
         <v>10</v>
       </c>
       <c r="B170" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C170" s="4"/>
       <c r="D170" s="3" t="s">
@@ -7161,7 +7155,7 @@
         <v>5</v>
       </c>
       <c r="H170" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I170" s="4"/>
       <c r="J170" s="4" t="s">
@@ -7188,7 +7182,7 @@
         <v>11</v>
       </c>
       <c r="B171" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C171" s="23"/>
       <c r="D171" s="3" t="s">
@@ -7204,7 +7198,7 @@
         <v>5</v>
       </c>
       <c r="H171" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I171" s="23"/>
       <c r="J171" s="23" t="s">
@@ -7259,7 +7253,7 @@
         <f>SUM(M167:M171)</f>
         <v>40</v>
       </c>
-      <c r="N172" s="63"/>
+      <c r="N172" s="62"/>
       <c r="O172" s="45">
         <f>SUM(O167:O171)</f>
         <v>40</v>
@@ -7293,7 +7287,7 @@
       <c r="M173" s="40">
         <v>0</v>
       </c>
-      <c r="N173" s="64"/>
+      <c r="N173" s="63"/>
       <c r="O173" s="40">
         <v>0</v>
       </c>
@@ -7326,7 +7320,7 @@
       <c r="M174" s="43">
         <v>8</v>
       </c>
-      <c r="N174" s="65"/>
+      <c r="N174" s="64"/>
       <c r="O174" s="43">
         <v>0</v>
       </c>
@@ -7335,7 +7329,7 @@
     <row r="175" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B176" s="8" t="s">
         <v>2</v>
@@ -7374,7 +7368,7 @@
         <v>18</v>
       </c>
       <c r="N176" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O176" s="10" t="s">
         <v>18</v>
@@ -7385,11 +7379,11 @@
         <v>7</v>
       </c>
       <c r="B177" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E177" s="4"/>
       <c r="F177" s="4" t="s">
@@ -7399,7 +7393,7 @@
         <v>7</v>
       </c>
       <c r="H177" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4" t="s">
@@ -7426,11 +7420,11 @@
         <v>8</v>
       </c>
       <c r="B178" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C178" s="4"/>
       <c r="D178" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="4" t="s">
@@ -7440,7 +7434,7 @@
         <v>7</v>
       </c>
       <c r="H178" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I178" s="4"/>
       <c r="J178" s="4" t="s">
@@ -7467,11 +7461,11 @@
         <v>9</v>
       </c>
       <c r="B179" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C179" s="4"/>
       <c r="D179" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="4" t="s">
@@ -7481,7 +7475,7 @@
         <v>7</v>
       </c>
       <c r="H179" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4" t="s">
@@ -7508,11 +7502,11 @@
         <v>10</v>
       </c>
       <c r="B180" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C180" s="4"/>
       <c r="D180" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="23" t="s">
@@ -7522,7 +7516,7 @@
         <v>7</v>
       </c>
       <c r="H180" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I180" s="4"/>
       <c r="J180" s="4" t="s">
@@ -7549,11 +7543,11 @@
         <v>11</v>
       </c>
       <c r="B181" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C181" s="23"/>
       <c r="D181" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E181" s="23"/>
       <c r="F181" s="23" t="s">
@@ -7563,7 +7557,7 @@
         <v>7</v>
       </c>
       <c r="H181" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I181" s="23"/>
       <c r="J181" s="23" t="s">
@@ -7617,7 +7611,7 @@
         <f>SUM(M177:M181)</f>
         <v>40</v>
       </c>
-      <c r="N182" s="63"/>
+      <c r="N182" s="62"/>
       <c r="O182" s="45">
         <f>SUM(O177:O181)</f>
         <v>40</v>
@@ -7651,7 +7645,7 @@
       <c r="M183" s="40">
         <v>0</v>
       </c>
-      <c r="N183" s="64"/>
+      <c r="N183" s="63"/>
       <c r="O183" s="40">
         <v>0</v>
       </c>
@@ -7684,7 +7678,7 @@
       <c r="M184" s="43">
         <v>8</v>
       </c>
-      <c r="N184" s="65"/>
+      <c r="N184" s="64"/>
       <c r="O184" s="43">
         <v>0</v>
       </c>
@@ -7693,7 +7687,7 @@
     <row r="185" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>2</v>
@@ -7732,7 +7726,7 @@
         <v>18</v>
       </c>
       <c r="N186" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O186" s="10" t="s">
         <v>18</v>
@@ -7743,11 +7737,11 @@
         <v>7</v>
       </c>
       <c r="B187" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C187" s="4"/>
       <c r="D187" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E187" s="4"/>
       <c r="F187" s="4" t="s">
@@ -7757,7 +7751,7 @@
         <v>7</v>
       </c>
       <c r="H187" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I187" s="4"/>
       <c r="J187" s="5" t="s">
@@ -7782,11 +7776,11 @@
         <v>8</v>
       </c>
       <c r="B188" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C188" s="4"/>
       <c r="D188" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="4" t="s">
@@ -7796,7 +7790,7 @@
         <v>7</v>
       </c>
       <c r="H188" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I188" s="4"/>
       <c r="J188" s="5" t="s">
@@ -7821,11 +7815,11 @@
         <v>9</v>
       </c>
       <c r="B189" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C189" s="4"/>
       <c r="D189" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="4" t="s">
@@ -7835,11 +7829,11 @@
         <v>7</v>
       </c>
       <c r="H189" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I189" s="4"/>
       <c r="J189" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K189" s="4"/>
       <c r="L189" s="4" t="s">
@@ -7860,11 +7854,11 @@
         <v>10</v>
       </c>
       <c r="B190" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C190" s="4"/>
       <c r="D190" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="23" t="s">
@@ -7874,11 +7868,11 @@
         <v>7</v>
       </c>
       <c r="H190" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I190" s="4"/>
       <c r="J190" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K190" s="4"/>
       <c r="L190" s="4" t="s">
@@ -7899,11 +7893,11 @@
         <v>11</v>
       </c>
       <c r="B191" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C191" s="23"/>
       <c r="D191" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E191" s="23"/>
       <c r="F191" s="23" t="s">
@@ -7913,11 +7907,11 @@
         <v>7</v>
       </c>
       <c r="H191" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I191" s="23"/>
       <c r="J191" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K191" s="23"/>
       <c r="L191" s="4" t="s">
@@ -7967,7 +7961,7 @@
         <f>SUM(M187:M191)</f>
         <v>40</v>
       </c>
-      <c r="N192" s="63"/>
+      <c r="N192" s="62"/>
       <c r="O192" s="45">
         <f>SUM(O187:O191)</f>
         <v>40</v>
@@ -8001,7 +7995,7 @@
       <c r="M193" s="40">
         <v>0</v>
       </c>
-      <c r="N193" s="64"/>
+      <c r="N193" s="63"/>
       <c r="O193" s="40">
         <v>0</v>
       </c>
@@ -8034,7 +8028,7 @@
       <c r="M194" s="43">
         <v>8</v>
       </c>
-      <c r="N194" s="65"/>
+      <c r="N194" s="64"/>
       <c r="O194" s="43">
         <v>0</v>
       </c>
@@ -8043,7 +8037,7 @@
     <row r="195" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>2</v>
@@ -8082,7 +8076,7 @@
         <v>18</v>
       </c>
       <c r="N196" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O196" s="10" t="s">
         <v>18</v>
@@ -8099,7 +8093,7 @@
         <v>6</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="4" t="s">
@@ -8109,11 +8103,11 @@
         <v>7</v>
       </c>
       <c r="H197" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I197" s="4"/>
       <c r="J197" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K197" s="4"/>
       <c r="L197" s="4" t="s">
@@ -8140,7 +8134,7 @@
         <v>6</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="4" t="s">
@@ -8150,11 +8144,11 @@
         <v>7</v>
       </c>
       <c r="H198" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I198" s="4"/>
       <c r="J198" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K198" s="4"/>
       <c r="L198" s="4" t="s">
@@ -8181,7 +8175,7 @@
         <v>8</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="4" t="s">
@@ -8191,11 +8185,11 @@
         <v>7</v>
       </c>
       <c r="H199" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I199" s="4"/>
       <c r="J199" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K199" s="4"/>
       <c r="L199" s="5" t="s">
@@ -8220,7 +8214,7 @@
         <v>8</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="23" t="s">
@@ -8230,15 +8224,15 @@
         <v>7</v>
       </c>
       <c r="H200" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I200" s="4"/>
       <c r="J200" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K200" s="4"/>
       <c r="L200" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M200" s="12"/>
       <c r="N200" s="4" t="s">
@@ -8259,7 +8253,7 @@
         <v>8</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E201" s="23"/>
       <c r="F201" s="23" t="s">
@@ -8269,15 +8263,15 @@
         <v>7</v>
       </c>
       <c r="H201" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I201" s="23"/>
       <c r="J201" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K201" s="23"/>
       <c r="L201" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M201" s="24"/>
       <c r="N201" s="23" t="s">
@@ -8321,7 +8315,7 @@
         <f>SUM(M197:M201)</f>
         <v>16</v>
       </c>
-      <c r="N202" s="63"/>
+      <c r="N202" s="62"/>
       <c r="O202" s="45">
         <f>SUM(O197:O201)</f>
         <v>40</v>
@@ -8355,7 +8349,7 @@
       <c r="M203" s="40">
         <v>-8</v>
       </c>
-      <c r="N203" s="64"/>
+      <c r="N203" s="63"/>
       <c r="O203" s="40">
         <v>0</v>
       </c>
@@ -8388,7 +8382,7 @@
       <c r="M204" s="43">
         <v>0</v>
       </c>
-      <c r="N204" s="65"/>
+      <c r="N204" s="64"/>
       <c r="O204" s="43">
         <v>0</v>
       </c>
@@ -8397,7 +8391,7 @@
     <row r="205" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>2</v>
@@ -8436,7 +8430,7 @@
         <v>18</v>
       </c>
       <c r="N206" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O206" s="10" t="s">
         <v>18</v>
@@ -8453,7 +8447,7 @@
         <v>8</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
@@ -8469,11 +8463,11 @@
         <v>8</v>
       </c>
       <c r="J207" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K207" s="4"/>
       <c r="L207" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M207" s="12"/>
       <c r="N207" s="4" t="s">
@@ -8494,7 +8488,7 @@
         <v>8</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
@@ -8510,11 +8504,11 @@
         <v>8</v>
       </c>
       <c r="J208" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K208" s="4"/>
       <c r="L208" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M208" s="12"/>
       <c r="N208" s="4" t="s">
@@ -8535,7 +8529,7 @@
         <v>8</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
@@ -8551,11 +8545,11 @@
         <v>8</v>
       </c>
       <c r="J209" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K209" s="4"/>
       <c r="L209" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M209" s="12"/>
       <c r="N209" s="4" t="s">
@@ -8576,7 +8570,7 @@
         <v>8</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="23" t="s">
@@ -8592,11 +8586,11 @@
         <v>8</v>
       </c>
       <c r="J210" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K210" s="4"/>
       <c r="L210" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M210" s="12"/>
       <c r="N210" s="4" t="s">
@@ -8617,7 +8611,7 @@
         <v>7</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E211" s="23"/>
       <c r="F211" s="23" t="s">
@@ -8633,11 +8627,11 @@
         <v>8</v>
       </c>
       <c r="J211" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K211" s="23"/>
       <c r="L211" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M211" s="24"/>
       <c r="N211" s="4" t="s">
@@ -8757,7 +8751,7 @@
     <row r="215" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B216" s="8" t="s">
         <v>2</v>
@@ -8796,7 +8790,7 @@
         <v>18</v>
       </c>
       <c r="N216" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O216" s="10" t="s">
         <v>18</v>
@@ -8831,11 +8825,11 @@
         <v>8</v>
       </c>
       <c r="J217" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K217" s="4"/>
       <c r="L217" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M217" s="12"/>
       <c r="N217" s="4" t="s">
@@ -8874,11 +8868,11 @@
         <v>8</v>
       </c>
       <c r="J218" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K218" s="4"/>
       <c r="L218" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M218" s="12"/>
       <c r="N218" s="4" t="s">
@@ -8917,11 +8911,11 @@
         <v>8</v>
       </c>
       <c r="J219" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K219" s="4"/>
       <c r="L219" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M219" s="12"/>
       <c r="N219" s="4" t="s">
@@ -8960,11 +8954,11 @@
         <v>8</v>
       </c>
       <c r="J220" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K220" s="4"/>
       <c r="L220" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M220" s="12"/>
       <c r="N220" s="4" t="s">
@@ -9003,11 +8997,11 @@
         <v>8</v>
       </c>
       <c r="J221" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K221" s="23"/>
       <c r="L221" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M221" s="24"/>
       <c r="N221" s="23" t="s">
@@ -9051,7 +9045,7 @@
         <f>SUM(M217:M221)</f>
         <v>0</v>
       </c>
-      <c r="N222" s="63"/>
+      <c r="N222" s="62"/>
       <c r="O222" s="45">
         <f>SUM(O217:O221)</f>
         <v>40</v>
@@ -9085,7 +9079,7 @@
       <c r="M223" s="40">
         <v>0</v>
       </c>
-      <c r="N223" s="64"/>
+      <c r="N223" s="63"/>
       <c r="O223" s="40">
         <v>0</v>
       </c>
@@ -9118,7 +9112,7 @@
       <c r="M224" s="43">
         <v>0</v>
       </c>
-      <c r="N224" s="65"/>
+      <c r="N224" s="64"/>
       <c r="O224" s="43">
         <v>0</v>
       </c>
@@ -9127,7 +9121,7 @@
     <row r="225" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B226" s="8" t="s">
         <v>2</v>
@@ -9166,7 +9160,7 @@
         <v>18</v>
       </c>
       <c r="N226" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O226" s="10" t="s">
         <v>18</v>
@@ -9207,7 +9201,7 @@
         <v>10</v>
       </c>
       <c r="L227" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M227" s="12"/>
       <c r="N227" s="4" t="s">
@@ -9252,7 +9246,7 @@
         <v>9</v>
       </c>
       <c r="L228" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M228" s="12"/>
       <c r="N228" s="4" t="s">
@@ -9297,11 +9291,11 @@
         <v>8</v>
       </c>
       <c r="L229" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M229" s="12"/>
       <c r="N229" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O229" s="12"/>
     </row>
@@ -9340,11 +9334,11 @@
         <v>8</v>
       </c>
       <c r="L230" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M230" s="12"/>
       <c r="N230" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O230" s="12"/>
     </row>
@@ -9381,11 +9375,11 @@
       </c>
       <c r="K231" s="23"/>
       <c r="L231" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M231" s="24"/>
       <c r="N231" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O231" s="24"/>
     </row>
@@ -9423,7 +9417,7 @@
         <f>SUM(M227:M231)</f>
         <v>0</v>
       </c>
-      <c r="N232" s="63"/>
+      <c r="N232" s="62"/>
       <c r="O232" s="45">
         <f>SUM(O227:O231)</f>
         <v>19</v>
@@ -9457,7 +9451,7 @@
       <c r="M233" s="40">
         <v>0</v>
       </c>
-      <c r="N233" s="64"/>
+      <c r="N233" s="63"/>
       <c r="O233" s="40">
         <v>0</v>
       </c>
@@ -9490,7 +9484,7 @@
       <c r="M234" s="43">
         <v>0</v>
       </c>
-      <c r="N234" s="65"/>
+      <c r="N234" s="64"/>
       <c r="O234" s="43">
         <v>0</v>
       </c>
@@ -9499,7 +9493,7 @@
     <row r="235" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B236" s="8" t="s">
         <v>2</v>
@@ -9538,7 +9532,7 @@
         <v>18</v>
       </c>
       <c r="N236" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O236" s="10" t="s">
         <v>18</v>
@@ -9679,7 +9673,7 @@
         <v>8</v>
       </c>
       <c r="N239" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O239" s="12"/>
     </row>
@@ -9724,7 +9718,7 @@
         <v>7</v>
       </c>
       <c r="N240" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O240" s="12"/>
     </row>
@@ -9761,11 +9755,11 @@
       </c>
       <c r="K241" s="23"/>
       <c r="L241" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="M241" s="24"/>
       <c r="N241" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O241" s="24"/>
     </row>
@@ -9803,7 +9797,7 @@
         <f>SUM(M237:M241)</f>
         <v>34</v>
       </c>
-      <c r="N242" s="63"/>
+      <c r="N242" s="62"/>
       <c r="O242" s="45">
         <f>SUM(O237:O241)</f>
         <v>19</v>
@@ -9837,7 +9831,7 @@
       <c r="M243" s="40">
         <v>-6</v>
       </c>
-      <c r="N243" s="64"/>
+      <c r="N243" s="63"/>
       <c r="O243" s="40">
         <v>0</v>
       </c>
@@ -9870,7 +9864,7 @@
       <c r="M244" s="43">
         <v>3</v>
       </c>
-      <c r="N244" s="65"/>
+      <c r="N244" s="64"/>
       <c r="O244" s="43">
         <v>0</v>
       </c>
@@ -9879,7 +9873,7 @@
     <row r="245" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B246" s="8" t="s">
         <v>2</v>
@@ -9918,7 +9912,7 @@
         <v>18</v>
       </c>
       <c r="N246" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O246" s="10" t="s">
         <v>18</v>
@@ -10059,7 +10053,7 @@
         <v>8</v>
       </c>
       <c r="N249" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O249" s="12"/>
     </row>
@@ -10104,7 +10098,7 @@
         <v>7</v>
       </c>
       <c r="N250" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O250" s="12"/>
     </row>
@@ -10141,11 +10135,11 @@
       </c>
       <c r="K251" s="23"/>
       <c r="L251" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="M251" s="24"/>
       <c r="N251" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O251" s="24"/>
     </row>
@@ -10183,7 +10177,7 @@
         <f>SUM(M247:M251)</f>
         <v>34</v>
       </c>
-      <c r="N252" s="63"/>
+      <c r="N252" s="62"/>
       <c r="O252" s="45">
         <f>SUM(O247:O251)</f>
         <v>19</v>
@@ -10217,7 +10211,7 @@
       <c r="M253" s="40">
         <v>-6</v>
       </c>
-      <c r="N253" s="64"/>
+      <c r="N253" s="63"/>
       <c r="O253" s="40">
         <v>0</v>
       </c>
@@ -10250,7 +10244,7 @@
       <c r="M254" s="43">
         <v>3</v>
       </c>
-      <c r="N254" s="65"/>
+      <c r="N254" s="64"/>
       <c r="O254" s="43">
         <v>0</v>
       </c>
@@ -10259,7 +10253,7 @@
     <row r="255" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B256" s="8" t="s">
         <v>2</v>
@@ -10298,7 +10292,7 @@
         <v>18</v>
       </c>
       <c r="N256" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O256" s="10" t="s">
         <v>18</v>
@@ -10439,7 +10433,7 @@
         <v>8</v>
       </c>
       <c r="N259" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O259" s="12"/>
     </row>
@@ -10484,7 +10478,7 @@
         <v>7</v>
       </c>
       <c r="N260" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O260" s="12"/>
     </row>
@@ -10521,11 +10515,11 @@
       </c>
       <c r="K261" s="23"/>
       <c r="L261" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="M261" s="24"/>
       <c r="N261" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O261" s="24"/>
     </row>
@@ -10563,7 +10557,7 @@
         <f>SUM(M257:M261)</f>
         <v>34</v>
       </c>
-      <c r="N262" s="63"/>
+      <c r="N262" s="62"/>
       <c r="O262" s="45">
         <f>SUM(O257:O261)</f>
         <v>19</v>
@@ -10597,7 +10591,7 @@
       <c r="M263" s="40">
         <v>-6</v>
       </c>
-      <c r="N263" s="64"/>
+      <c r="N263" s="63"/>
       <c r="O263" s="40">
         <v>0</v>
       </c>
@@ -10630,7 +10624,7 @@
       <c r="M264" s="43">
         <v>3</v>
       </c>
-      <c r="N264" s="65"/>
+      <c r="N264" s="64"/>
       <c r="O264" s="43">
         <v>0</v>
       </c>
@@ -10639,7 +10633,7 @@
     <row r="265" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B266" s="8" t="s">
         <v>2</v>
@@ -10678,7 +10672,7 @@
         <v>18</v>
       </c>
       <c r="N266" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O266" s="10" t="s">
         <v>18</v>
@@ -10819,7 +10813,7 @@
         <v>8</v>
       </c>
       <c r="N269" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O269" s="12"/>
     </row>
@@ -10864,7 +10858,7 @@
         <v>7</v>
       </c>
       <c r="N270" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O270" s="12"/>
     </row>
@@ -10901,11 +10895,11 @@
       </c>
       <c r="K271" s="23"/>
       <c r="L271" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="M271" s="24"/>
       <c r="N271" s="23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O271" s="24"/>
     </row>
@@ -10943,7 +10937,7 @@
         <f>SUM(M267:M271)</f>
         <v>34</v>
       </c>
-      <c r="N272" s="63"/>
+      <c r="N272" s="62"/>
       <c r="O272" s="45">
         <f>SUM(O267:O271)</f>
         <v>19</v>
@@ -10977,7 +10971,7 @@
       <c r="M273" s="40">
         <v>-6</v>
       </c>
-      <c r="N273" s="64"/>
+      <c r="N273" s="63"/>
       <c r="O273" s="40">
         <v>0</v>
       </c>
@@ -11010,7 +11004,7 @@
       <c r="M274" s="43">
         <v>3</v>
       </c>
-      <c r="N274" s="65"/>
+      <c r="N274" s="64"/>
       <c r="O274" s="43">
         <v>0</v>
       </c>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1062" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7281135B-EEE4-4D08-AFA1-CBF166197A53}"/>
+  <xr:revisionPtr revIDLastSave="1141" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A72C749F-DD5E-4685-B7CF-FDE8ACDE4401}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="240" windowWidth="38385" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="2985" yWindow="315" windowWidth="42900" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="75">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -262,6 +262,9 @@
   <si>
     <t>Emil</t>
   </si>
+  <si>
+    <t>07:00-13:45</t>
+  </si>
 </sst>
 </file>
 
@@ -323,7 +326,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,6 +378,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -772,6 +781,7 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6280,44 +6290,44 @@
         <v>7</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C147" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E147" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F147" s="50" t="s">
         <v>68</v>
       </c>
       <c r="G147" s="4"/>
       <c r="H147" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="I147" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K147" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M147" s="12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N147" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="O147" s="12">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.25">
@@ -6325,44 +6335,44 @@
         <v>8</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C148" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E148" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F148" s="50" t="s">
         <v>68</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I148" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K148" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M148" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N148" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="O148" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.25">
@@ -6419,20 +6429,20 @@
       </c>
       <c r="C150" s="4"/>
       <c r="D150" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E150" s="4">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="E150" s="12">
+        <v>7</v>
       </c>
       <c r="F150" s="50" t="s">
         <v>68</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I150" s="4">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="I150" s="12">
+        <v>7</v>
       </c>
       <c r="J150" s="5" t="s">
         <v>13</v>
@@ -6445,10 +6455,10 @@
         <v>7</v>
       </c>
       <c r="N150" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O150" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6460,20 +6470,20 @@
       </c>
       <c r="C151" s="23"/>
       <c r="D151" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E151" s="23">
-        <v>8</v>
+        <v>74</v>
+      </c>
+      <c r="E151" s="24">
+        <v>6</v>
       </c>
       <c r="F151" s="50" t="s">
         <v>68</v>
       </c>
       <c r="G151" s="23"/>
       <c r="H151" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="I151" s="23">
-        <v>8</v>
+        <v>74</v>
+      </c>
+      <c r="I151" s="24">
+        <v>6</v>
       </c>
       <c r="J151" s="23" t="s">
         <v>13</v>
@@ -6486,10 +6496,10 @@
         <v>7</v>
       </c>
       <c r="N151" s="23" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="O151" s="24">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.25">
@@ -6499,7 +6509,7 @@
       <c r="B152" s="44"/>
       <c r="C152" s="44">
         <f>SUM(C147:C151)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D152" s="44"/>
       <c r="E152" s="44">
@@ -6519,12 +6529,12 @@
       <c r="J152" s="44"/>
       <c r="K152" s="44">
         <f>SUM(K147:K151)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L152" s="44"/>
       <c r="M152" s="45">
         <f>SUM(M147:M151)</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N152" s="62"/>
       <c r="O152" s="45">
@@ -6538,7 +6548,7 @@
       </c>
       <c r="B153" s="39"/>
       <c r="C153" s="39">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="D153" s="39"/>
       <c r="E153" s="39">
@@ -6554,11 +6564,11 @@
       </c>
       <c r="J153" s="39"/>
       <c r="K153" s="39">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L153" s="39"/>
       <c r="M153" s="40">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="N153" s="63"/>
       <c r="O153" s="40">
@@ -6571,7 +6581,7 @@
       </c>
       <c r="B154" s="42"/>
       <c r="C154" s="42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D154" s="42"/>
       <c r="E154" s="42">
@@ -6587,11 +6597,11 @@
       </c>
       <c r="J154" s="42"/>
       <c r="K154" s="42">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L154" s="42"/>
       <c r="M154" s="43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N154" s="64"/>
       <c r="O154" s="43">
@@ -6656,38 +6666,38 @@
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E157" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G157" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H157" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I157" s="4"/>
       <c r="J157" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K157" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M157" s="12">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="M157" s="4">
+        <v>9</v>
       </c>
       <c r="N157" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="O157" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.25">
@@ -6699,38 +6709,38 @@
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E158" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G158" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H158" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I158" s="4"/>
       <c r="J158" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K158" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M158" s="12">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="M158" s="4">
+        <v>9</v>
       </c>
       <c r="N158" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="O158" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.25">
@@ -6811,10 +6821,10 @@
         <v>8</v>
       </c>
       <c r="N160" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O160" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6862,12 +6872,12 @@
       <c r="D162" s="44"/>
       <c r="E162" s="44">
         <f>SUM(E157:E161)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F162" s="44"/>
       <c r="G162" s="44">
         <f>SUM(G157:G161)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H162" s="44"/>
       <c r="I162" s="44">
@@ -6877,17 +6887,17 @@
       <c r="J162" s="44"/>
       <c r="K162" s="44">
         <f>SUM(K157:K161)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L162" s="44"/>
       <c r="M162" s="45">
         <f>SUM(M157:M161)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N162" s="62"/>
       <c r="O162" s="45">
         <f>SUM(O157:O161)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.25">
@@ -6912,11 +6922,11 @@
       </c>
       <c r="J163" s="39"/>
       <c r="K163" s="39">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L163" s="39"/>
       <c r="M163" s="40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N163" s="63"/>
       <c r="O163" s="40">
@@ -6929,15 +6939,15 @@
       </c>
       <c r="B164" s="42"/>
       <c r="C164" s="42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D164" s="42"/>
       <c r="E164" s="42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F164" s="42"/>
       <c r="G164" s="42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H164" s="42"/>
       <c r="I164" s="42">
@@ -6945,11 +6955,11 @@
       </c>
       <c r="J164" s="42"/>
       <c r="K164" s="42">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L164" s="42"/>
       <c r="M164" s="43">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N164" s="64"/>
       <c r="O164" s="43">
@@ -7298,7 +7308,7 @@
       </c>
       <c r="B174" s="42"/>
       <c r="C174" s="42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D174" s="42"/>
       <c r="E174" s="42">
@@ -7324,7 +7334,7 @@
       <c r="O174" s="43">
         <v>0</v>
       </c>
-      <c r="P174" s="46"/>
+      <c r="P174" s="65"/>
     </row>
     <row r="175" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="176" spans="1:19" x14ac:dyDescent="0.25">
@@ -7656,7 +7666,7 @@
       </c>
       <c r="B184" s="42"/>
       <c r="C184" s="42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D184" s="42"/>
       <c r="E184" s="42">
@@ -7682,7 +7692,7 @@
       <c r="O184" s="43">
         <v>0</v>
       </c>
-      <c r="P184" s="46"/>
+      <c r="P184" s="65"/>
     </row>
     <row r="185" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="186" spans="1:16" x14ac:dyDescent="0.25">
@@ -8006,7 +8016,7 @@
       </c>
       <c r="B194" s="42"/>
       <c r="C194" s="42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D194" s="42"/>
       <c r="E194" s="42">
@@ -8032,7 +8042,7 @@
       <c r="O194" s="43">
         <v>0</v>
       </c>
-      <c r="P194" s="46"/>
+      <c r="P194" s="65"/>
     </row>
     <row r="195" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1141" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A72C749F-DD5E-4685-B7CF-FDE8ACDE4401}"/>
+  <xr:revisionPtr revIDLastSave="1199" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E759F7D8-F814-4E9B-97A9-0D5F10402589}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="315" windowWidth="42900" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="2580" yWindow="315" windowWidth="42900" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="76">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>07:00-13:45</t>
+  </si>
+  <si>
+    <t>Behöver lägga in</t>
   </si>
 </sst>
 </file>
@@ -737,7 +740,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -782,6 +784,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1817,8 +1822,8 @@
         <f>SUM(M13:M17)</f>
         <v>39</v>
       </c>
-      <c r="N18" s="56"/>
-      <c r="O18" s="56"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="55"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
@@ -1848,8 +1853,8 @@
       <c r="M19" s="40">
         <v>-1</v>
       </c>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="56"/>
     </row>
     <row r="20" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
@@ -1879,8 +1884,8 @@
       <c r="M20" s="43">
         <v>0</v>
       </c>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="57"/>
       <c r="P20" s="46"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2091,7 +2096,7 @@
       <c r="I26" s="4">
         <v>8</v>
       </c>
-      <c r="J26" s="51" t="s">
+      <c r="J26" s="50" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="4"/>
@@ -2136,7 +2141,7 @@
         <v>13</v>
       </c>
       <c r="K27" s="14"/>
-      <c r="L27" s="51" t="s">
+      <c r="L27" s="50" t="s">
         <v>13</v>
       </c>
       <c r="M27" s="15"/>
@@ -2177,8 +2182,8 @@
         <f>SUM(M23:M27)</f>
         <v>34</v>
       </c>
-      <c r="N28" s="56"/>
-      <c r="O28" s="56"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="55"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
@@ -2208,8 +2213,8 @@
       <c r="M29" s="40">
         <v>-6</v>
       </c>
-      <c r="N29" s="57"/>
-      <c r="O29" s="57"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="56"/>
     </row>
     <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
@@ -2239,8 +2244,8 @@
       <c r="M30" s="43">
         <v>-6</v>
       </c>
-      <c r="N30" s="58"/>
-      <c r="O30" s="58"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
       <c r="P30" s="46"/>
     </row>
     <row r="31" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2532,8 +2537,8 @@
         <f>SUM(M33:M37)</f>
         <v>39</v>
       </c>
-      <c r="N38" s="56"/>
-      <c r="O38" s="56"/>
+      <c r="N38" s="55"/>
+      <c r="O38" s="55"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
@@ -2563,8 +2568,8 @@
       <c r="M39" s="40">
         <v>-1</v>
       </c>
-      <c r="N39" s="57"/>
-      <c r="O39" s="57"/>
+      <c r="N39" s="56"/>
+      <c r="O39" s="56"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="41" t="s">
@@ -2594,8 +2599,8 @@
       <c r="M40" s="43">
         <v>-7</v>
       </c>
-      <c r="N40" s="58"/>
-      <c r="O40" s="58"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
       <c r="P40" s="46"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2836,8 +2841,8 @@
         <v>13</v>
       </c>
       <c r="M47" s="27"/>
-      <c r="N47" s="59"/>
-      <c r="O47" s="59"/>
+      <c r="N47" s="58"/>
+      <c r="O47" s="58"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="35" t="s">
@@ -2873,8 +2878,8 @@
         <f>SUM(M43:M47)</f>
         <v>32</v>
       </c>
-      <c r="N48" s="56"/>
-      <c r="O48" s="56"/>
+      <c r="N48" s="55"/>
+      <c r="O48" s="55"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
@@ -2904,8 +2909,8 @@
       <c r="M49" s="40">
         <v>0</v>
       </c>
-      <c r="N49" s="57"/>
-      <c r="O49" s="57"/>
+      <c r="N49" s="56"/>
+      <c r="O49" s="56"/>
     </row>
     <row r="50" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="41" t="s">
@@ -2935,8 +2940,8 @@
       <c r="M50" s="43">
         <v>-7</v>
       </c>
-      <c r="N50" s="58"/>
-      <c r="O50" s="58"/>
+      <c r="N50" s="57"/>
+      <c r="O50" s="57"/>
       <c r="P50" s="46"/>
     </row>
     <row r="51" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3021,8 +3026,8 @@
       <c r="M53" s="28">
         <v>10</v>
       </c>
-      <c r="N53" s="60"/>
-      <c r="O53" s="60"/>
+      <c r="N53" s="59"/>
+      <c r="O53" s="59"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
@@ -3173,7 +3178,7 @@
       <c r="G57" s="14">
         <v>7</v>
       </c>
-      <c r="H57" s="51" t="s">
+      <c r="H57" s="50" t="s">
         <v>19</v>
       </c>
       <c r="I57" s="14">
@@ -3226,8 +3231,8 @@
         <f>SUM(M53:M57)</f>
         <v>39</v>
       </c>
-      <c r="N58" s="56"/>
-      <c r="O58" s="56"/>
+      <c r="N58" s="55"/>
+      <c r="O58" s="55"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
@@ -3257,47 +3262,47 @@
       <c r="M59" s="40">
         <v>7</v>
       </c>
-      <c r="N59" s="57"/>
-      <c r="O59" s="57"/>
+      <c r="N59" s="56"/>
+      <c r="O59" s="56"/>
     </row>
     <row r="60" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="53" t="s">
+      <c r="B60" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="54">
+      <c r="C60" s="53">
         <v>15</v>
       </c>
       <c r="D60" s="42"/>
-      <c r="E60" s="54">
+      <c r="E60" s="53">
         <v>8</v>
       </c>
       <c r="F60" s="42"/>
-      <c r="G60" s="54">
+      <c r="G60" s="53">
         <v>-3</v>
       </c>
-      <c r="H60" s="53" t="s">
+      <c r="H60" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="I60" s="54">
+      <c r="I60" s="53">
         <v>14</v>
       </c>
-      <c r="J60" s="53" t="s">
+      <c r="J60" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="K60" s="54">
-        <v>9</v>
-      </c>
-      <c r="L60" s="53" t="s">
+      <c r="K60" s="53">
+        <v>9</v>
+      </c>
+      <c r="L60" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="M60" s="55">
-        <v>12</v>
-      </c>
-      <c r="N60" s="61"/>
-      <c r="O60" s="61"/>
+      <c r="M60" s="54">
+        <v>12</v>
+      </c>
+      <c r="N60" s="60"/>
+      <c r="O60" s="60"/>
       <c r="P60" s="46"/>
     </row>
     <row r="61" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3520,7 +3525,7 @@
       <c r="A67" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B67" s="50" t="s">
+      <c r="B67" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C67" s="23"/>
@@ -3589,8 +3594,8 @@
         <f>SUM(M63:M67)</f>
         <v>41</v>
       </c>
-      <c r="N68" s="56"/>
-      <c r="O68" s="56"/>
+      <c r="N68" s="55"/>
+      <c r="O68" s="55"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
@@ -3620,8 +3625,8 @@
       <c r="M69" s="40">
         <v>1</v>
       </c>
-      <c r="N69" s="57"/>
-      <c r="O69" s="57"/>
+      <c r="N69" s="56"/>
+      <c r="O69" s="56"/>
     </row>
     <row r="70" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41" t="s">
@@ -3651,8 +3656,8 @@
       <c r="M70" s="43">
         <v>13</v>
       </c>
-      <c r="N70" s="58"/>
-      <c r="O70" s="58"/>
+      <c r="N70" s="57"/>
+      <c r="O70" s="57"/>
       <c r="P70" s="46"/>
     </row>
     <row r="71" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3946,8 +3951,8 @@
         <f>SUM(M73:M77)</f>
         <v>39</v>
       </c>
-      <c r="N78" s="56"/>
-      <c r="O78" s="56"/>
+      <c r="N78" s="55"/>
+      <c r="O78" s="55"/>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
@@ -3977,8 +3982,8 @@
       <c r="M79" s="40">
         <v>-1</v>
       </c>
-      <c r="N79" s="57"/>
-      <c r="O79" s="57"/>
+      <c r="N79" s="56"/>
+      <c r="O79" s="56"/>
     </row>
     <row r="80" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="41" t="s">
@@ -4008,8 +4013,8 @@
       <c r="M80" s="43">
         <v>12</v>
       </c>
-      <c r="N80" s="58"/>
-      <c r="O80" s="58"/>
+      <c r="N80" s="57"/>
+      <c r="O80" s="57"/>
       <c r="P80" s="46"/>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
@@ -4288,8 +4293,8 @@
         <v>13</v>
       </c>
       <c r="M89" s="31"/>
-      <c r="N89" s="59"/>
-      <c r="O89" s="59"/>
+      <c r="N89" s="58"/>
+      <c r="O89" s="58"/>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="47" t="s">
@@ -4325,8 +4330,8 @@
         <f>SUM(M85:M89)</f>
         <v>34</v>
       </c>
-      <c r="N90" s="56"/>
-      <c r="O90" s="56"/>
+      <c r="N90" s="55"/>
+      <c r="O90" s="55"/>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="38" t="s">
@@ -4356,8 +4361,8 @@
       <c r="M91" s="40">
         <v>2</v>
       </c>
-      <c r="N91" s="57"/>
-      <c r="O91" s="57"/>
+      <c r="N91" s="56"/>
+      <c r="O91" s="56"/>
     </row>
     <row r="92" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="41" t="s">
@@ -4387,8 +4392,8 @@
       <c r="M92" s="43">
         <v>14</v>
       </c>
-      <c r="N92" s="58"/>
-      <c r="O92" s="58"/>
+      <c r="N92" s="57"/>
+      <c r="O92" s="57"/>
       <c r="P92" s="46"/>
     </row>
     <row r="93" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -4682,8 +4687,8 @@
         <f>SUM(M95:M99)</f>
         <v>39</v>
       </c>
-      <c r="N100" s="56"/>
-      <c r="O100" s="56"/>
+      <c r="N100" s="55"/>
+      <c r="O100" s="55"/>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="38" t="s">
@@ -4713,8 +4718,8 @@
       <c r="M101" s="40">
         <v>-1</v>
       </c>
-      <c r="N101" s="57"/>
-      <c r="O101" s="57"/>
+      <c r="N101" s="56"/>
+      <c r="O101" s="56"/>
     </row>
     <row r="102" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="41" t="s">
@@ -4744,8 +4749,8 @@
       <c r="M102" s="43">
         <v>13</v>
       </c>
-      <c r="N102" s="58"/>
-      <c r="O102" s="58"/>
+      <c r="N102" s="57"/>
+      <c r="O102" s="57"/>
       <c r="P102" s="46"/>
     </row>
     <row r="103" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -4950,8 +4955,8 @@
         <v>13</v>
       </c>
       <c r="M108" s="19"/>
-      <c r="N108" s="59"/>
-      <c r="O108" s="59"/>
+      <c r="N108" s="58"/>
+      <c r="O108" s="58"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
@@ -5028,8 +5033,8 @@
         <f>SUM(M105:M109)</f>
         <v>34</v>
       </c>
-      <c r="N110" s="56"/>
-      <c r="O110" s="56"/>
+      <c r="N110" s="55"/>
+      <c r="O110" s="55"/>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="38" t="s">
@@ -5059,8 +5064,8 @@
       <c r="M111" s="40">
         <v>2</v>
       </c>
-      <c r="N111" s="57"/>
-      <c r="O111" s="57"/>
+      <c r="N111" s="56"/>
+      <c r="O111" s="56"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="41" t="s">
@@ -5090,8 +5095,8 @@
       <c r="M112" s="43">
         <v>15</v>
       </c>
-      <c r="N112" s="58"/>
-      <c r="O112" s="58"/>
+      <c r="N112" s="57"/>
+      <c r="O112" s="57"/>
       <c r="P112" s="46"/>
     </row>
     <row r="113" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -5385,8 +5390,8 @@
         <f>SUM(M115:M119)</f>
         <v>39</v>
       </c>
-      <c r="N120" s="56"/>
-      <c r="O120" s="56"/>
+      <c r="N120" s="55"/>
+      <c r="O120" s="55"/>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="38" t="s">
@@ -5416,8 +5421,8 @@
       <c r="M121" s="40">
         <v>-1</v>
       </c>
-      <c r="N121" s="57"/>
-      <c r="O121" s="57"/>
+      <c r="N121" s="56"/>
+      <c r="O121" s="56"/>
     </row>
     <row r="122" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="41" t="s">
@@ -5447,8 +5452,8 @@
       <c r="M122" s="43">
         <v>14</v>
       </c>
-      <c r="N122" s="58"/>
-      <c r="O122" s="58"/>
+      <c r="N122" s="57"/>
+      <c r="O122" s="57"/>
       <c r="P122" s="46"/>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
@@ -5792,7 +5797,7 @@
         <f>SUM(M127:M131)</f>
         <v>34</v>
       </c>
-      <c r="N132" s="62"/>
+      <c r="N132" s="61"/>
       <c r="O132" s="45">
         <f>SUM(O127:O131)</f>
         <v>19</v>
@@ -5826,7 +5831,7 @@
       <c r="M133" s="40">
         <v>-6</v>
       </c>
-      <c r="N133" s="63"/>
+      <c r="N133" s="62"/>
       <c r="O133" s="40">
         <v>0</v>
       </c>
@@ -5859,7 +5864,7 @@
       <c r="M134" s="43">
         <v>8</v>
       </c>
-      <c r="N134" s="64"/>
+      <c r="N134" s="63"/>
       <c r="O134" s="43">
         <v>0</v>
       </c>
@@ -5929,7 +5934,7 @@
       <c r="E137" s="4">
         <v>10</v>
       </c>
-      <c r="F137" s="50" t="s">
+      <c r="F137" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G137" s="4"/>
@@ -5974,7 +5979,7 @@
       <c r="E138" s="4">
         <v>9</v>
       </c>
-      <c r="F138" s="50" t="s">
+      <c r="F138" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G138" s="4"/>
@@ -6019,7 +6024,7 @@
       <c r="E139" s="4">
         <v>4</v>
       </c>
-      <c r="F139" s="50" t="s">
+      <c r="F139" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G139" s="4"/>
@@ -6064,7 +6069,7 @@
       <c r="E140" s="4">
         <v>8</v>
       </c>
-      <c r="F140" s="50" t="s">
+      <c r="F140" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G140" s="4"/>
@@ -6099,11 +6104,11 @@
       <c r="C141" s="23">
         <v>5</v>
       </c>
-      <c r="D141" s="32" t="s">
+      <c r="D141" s="65" t="s">
         <v>13</v>
       </c>
       <c r="E141" s="23"/>
-      <c r="F141" s="50" t="s">
+      <c r="F141" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G141" s="23"/>
@@ -6128,6 +6133,9 @@
       </c>
       <c r="O141" s="24">
         <v>8</v>
+      </c>
+      <c r="P141" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
@@ -6164,7 +6172,7 @@
         <f>SUM(M137:M141)</f>
         <v>34</v>
       </c>
-      <c r="N142" s="62"/>
+      <c r="N142" s="61"/>
       <c r="O142" s="45">
         <f>SUM(O137:O141)</f>
         <v>40</v>
@@ -6198,7 +6206,7 @@
       <c r="M143" s="40">
         <v>2</v>
       </c>
-      <c r="N143" s="63"/>
+      <c r="N143" s="62"/>
       <c r="O143" s="40">
         <v>0</v>
       </c>
@@ -6231,7 +6239,7 @@
       <c r="M144" s="43">
         <v>10</v>
       </c>
-      <c r="N144" s="64"/>
+      <c r="N144" s="63"/>
       <c r="O144" s="43">
         <v>0</v>
       </c>
@@ -6301,7 +6309,7 @@
       <c r="E147" s="4">
         <v>10</v>
       </c>
-      <c r="F147" s="50" t="s">
+      <c r="F147" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G147" s="4"/>
@@ -6346,7 +6354,7 @@
       <c r="E148" s="4">
         <v>9</v>
       </c>
-      <c r="F148" s="50" t="s">
+      <c r="F148" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G148" s="4"/>
@@ -6391,7 +6399,7 @@
       <c r="E149" s="4">
         <v>8</v>
       </c>
-      <c r="F149" s="50" t="s">
+      <c r="F149" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G149" s="4"/>
@@ -6434,7 +6442,7 @@
       <c r="E150" s="12">
         <v>7</v>
       </c>
-      <c r="F150" s="50" t="s">
+      <c r="F150" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G150" s="4"/>
@@ -6475,7 +6483,7 @@
       <c r="E151" s="24">
         <v>6</v>
       </c>
-      <c r="F151" s="50" t="s">
+      <c r="F151" s="49" t="s">
         <v>68</v>
       </c>
       <c r="G151" s="23"/>
@@ -6536,7 +6544,7 @@
         <f>SUM(M147:M151)</f>
         <v>41</v>
       </c>
-      <c r="N152" s="62"/>
+      <c r="N152" s="61"/>
       <c r="O152" s="45">
         <f>SUM(O147:O151)</f>
         <v>40</v>
@@ -6570,7 +6578,7 @@
       <c r="M153" s="40">
         <v>4</v>
       </c>
-      <c r="N153" s="63"/>
+      <c r="N153" s="62"/>
       <c r="O153" s="40">
         <v>0</v>
       </c>
@@ -6603,7 +6611,7 @@
       <c r="M154" s="43">
         <v>9</v>
       </c>
-      <c r="N154" s="64"/>
+      <c r="N154" s="63"/>
       <c r="O154" s="43">
         <v>0</v>
       </c>
@@ -6661,7 +6669,7 @@
       <c r="A157" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B157" s="50" t="s">
+      <c r="B157" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C157" s="4"/>
@@ -6682,7 +6690,7 @@
       </c>
       <c r="I157" s="4"/>
       <c r="J157" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K157" s="4">
         <v>9</v>
@@ -6704,50 +6712,50 @@
       <c r="A158" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B158" s="50" t="s">
+      <c r="B158" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E158" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G158" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H158" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I158" s="4"/>
       <c r="J158" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K158" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M158" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N158" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O158" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B159" s="50" t="s">
+      <c r="B159" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C159" s="4"/>
@@ -6790,15 +6798,15 @@
       <c r="A160" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B160" s="50" t="s">
+      <c r="B160" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E160" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>16</v>
@@ -6872,12 +6880,12 @@
       <c r="D162" s="44"/>
       <c r="E162" s="44">
         <f>SUM(E157:E161)</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F162" s="44"/>
       <c r="G162" s="44">
         <f>SUM(G157:G161)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H162" s="44"/>
       <c r="I162" s="44">
@@ -6887,17 +6895,17 @@
       <c r="J162" s="44"/>
       <c r="K162" s="44">
         <f>SUM(K157:K161)</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L162" s="44"/>
       <c r="M162" s="45">
         <f>SUM(M157:M161)</f>
-        <v>34</v>
-      </c>
-      <c r="N162" s="62"/>
+        <v>33</v>
+      </c>
+      <c r="N162" s="61"/>
       <c r="O162" s="45">
         <f>SUM(O157:O161)</f>
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.25">
@@ -6914,7 +6922,7 @@
       </c>
       <c r="F163" s="39"/>
       <c r="G163" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" s="39"/>
       <c r="I163" s="39">
@@ -6922,13 +6930,13 @@
       </c>
       <c r="J163" s="39"/>
       <c r="K163" s="39">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="L163" s="39"/>
       <c r="M163" s="40">
-        <v>2</v>
-      </c>
-      <c r="N163" s="63"/>
+        <v>1</v>
+      </c>
+      <c r="N163" s="62"/>
       <c r="O163" s="40">
         <v>0</v>
       </c>
@@ -6943,11 +6951,11 @@
       </c>
       <c r="D164" s="42"/>
       <c r="E164" s="42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F164" s="42"/>
       <c r="G164" s="42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H164" s="42"/>
       <c r="I164" s="42">
@@ -6961,7 +6969,7 @@
       <c r="M164" s="43">
         <v>10</v>
       </c>
-      <c r="N164" s="64"/>
+      <c r="N164" s="63"/>
       <c r="O164" s="43">
         <v>0</v>
       </c>
@@ -7019,7 +7027,7 @@
       <c r="A167" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B167" s="50" t="s">
+      <c r="B167" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C167" s="4"/>
@@ -7035,7 +7043,7 @@
       <c r="G167" s="4">
         <v>7</v>
       </c>
-      <c r="H167" s="50" t="s">
+      <c r="H167" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I167" s="4"/>
@@ -7062,7 +7070,7 @@
       <c r="A168" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B168" s="50" t="s">
+      <c r="B168" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C168" s="4"/>
@@ -7078,7 +7086,7 @@
       <c r="G168" s="4">
         <v>7</v>
       </c>
-      <c r="H168" s="50" t="s">
+      <c r="H168" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I168" s="4"/>
@@ -7105,7 +7113,7 @@
       <c r="A169" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B169" s="50" t="s">
+      <c r="B169" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C169" s="4"/>
@@ -7121,7 +7129,7 @@
       <c r="G169" s="4">
         <v>7</v>
       </c>
-      <c r="H169" s="50" t="s">
+      <c r="H169" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I169" s="4"/>
@@ -7148,7 +7156,7 @@
       <c r="A170" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B170" s="50" t="s">
+      <c r="B170" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C170" s="4"/>
@@ -7164,7 +7172,7 @@
       <c r="G170" s="4">
         <v>5</v>
       </c>
-      <c r="H170" s="50" t="s">
+      <c r="H170" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I170" s="4"/>
@@ -7191,7 +7199,7 @@
       <c r="A171" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B171" s="50" t="s">
+      <c r="B171" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C171" s="23"/>
@@ -7207,7 +7215,7 @@
       <c r="G171" s="23">
         <v>5</v>
       </c>
-      <c r="H171" s="50" t="s">
+      <c r="H171" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I171" s="23"/>
@@ -7227,7 +7235,7 @@
       <c r="O171" s="24">
         <v>8</v>
       </c>
-      <c r="S171" s="52"/>
+      <c r="S171" s="51"/>
     </row>
     <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" s="47" t="s">
@@ -7263,7 +7271,7 @@
         <f>SUM(M167:M171)</f>
         <v>40</v>
       </c>
-      <c r="N172" s="62"/>
+      <c r="N172" s="61"/>
       <c r="O172" s="45">
         <f>SUM(O167:O171)</f>
         <v>40</v>
@@ -7297,7 +7305,7 @@
       <c r="M173" s="40">
         <v>0</v>
       </c>
-      <c r="N173" s="63"/>
+      <c r="N173" s="62"/>
       <c r="O173" s="40">
         <v>0</v>
       </c>
@@ -7316,7 +7324,7 @@
       </c>
       <c r="F174" s="42"/>
       <c r="G174" s="42">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H174" s="42"/>
       <c r="I174" s="42">
@@ -7324,17 +7332,17 @@
       </c>
       <c r="J174" s="42"/>
       <c r="K174" s="42">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L174" s="42"/>
       <c r="M174" s="43">
-        <v>8</v>
-      </c>
-      <c r="N174" s="64"/>
+        <v>10</v>
+      </c>
+      <c r="N174" s="63"/>
       <c r="O174" s="43">
         <v>0</v>
       </c>
-      <c r="P174" s="65"/>
+      <c r="P174" s="46"/>
     </row>
     <row r="175" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="176" spans="1:19" x14ac:dyDescent="0.25">
@@ -7388,11 +7396,11 @@
       <c r="A177" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B177" s="50" t="s">
+      <c r="B177" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C177" s="4"/>
-      <c r="D177" s="50" t="s">
+      <c r="D177" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E177" s="4"/>
@@ -7402,7 +7410,7 @@
       <c r="G177" s="4">
         <v>7</v>
       </c>
-      <c r="H177" s="50" t="s">
+      <c r="H177" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I177" s="4"/>
@@ -7429,11 +7437,11 @@
       <c r="A178" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B178" s="50" t="s">
+      <c r="B178" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C178" s="4"/>
-      <c r="D178" s="50" t="s">
+      <c r="D178" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E178" s="4"/>
@@ -7443,7 +7451,7 @@
       <c r="G178" s="4">
         <v>7</v>
       </c>
-      <c r="H178" s="50" t="s">
+      <c r="H178" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I178" s="4"/>
@@ -7470,11 +7478,11 @@
       <c r="A179" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B179" s="50" t="s">
+      <c r="B179" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C179" s="4"/>
-      <c r="D179" s="50" t="s">
+      <c r="D179" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E179" s="4"/>
@@ -7484,7 +7492,7 @@
       <c r="G179" s="4">
         <v>7</v>
       </c>
-      <c r="H179" s="50" t="s">
+      <c r="H179" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I179" s="4"/>
@@ -7511,11 +7519,11 @@
       <c r="A180" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B180" s="50" t="s">
+      <c r="B180" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C180" s="4"/>
-      <c r="D180" s="50" t="s">
+      <c r="D180" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E180" s="4"/>
@@ -7525,7 +7533,7 @@
       <c r="G180" s="4">
         <v>7</v>
       </c>
-      <c r="H180" s="50" t="s">
+      <c r="H180" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I180" s="4"/>
@@ -7552,11 +7560,11 @@
       <c r="A181" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B181" s="50" t="s">
+      <c r="B181" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C181" s="23"/>
-      <c r="D181" s="50" t="s">
+      <c r="D181" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E181" s="23"/>
@@ -7566,7 +7574,7 @@
       <c r="G181" s="23">
         <v>7</v>
       </c>
-      <c r="H181" s="50" t="s">
+      <c r="H181" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I181" s="23"/>
@@ -7621,7 +7629,7 @@
         <f>SUM(M177:M181)</f>
         <v>40</v>
       </c>
-      <c r="N182" s="62"/>
+      <c r="N182" s="61"/>
       <c r="O182" s="45">
         <f>SUM(O177:O181)</f>
         <v>40</v>
@@ -7655,7 +7663,7 @@
       <c r="M183" s="40">
         <v>0</v>
       </c>
-      <c r="N183" s="63"/>
+      <c r="N183" s="62"/>
       <c r="O183" s="40">
         <v>0</v>
       </c>
@@ -7674,7 +7682,7 @@
       </c>
       <c r="F184" s="42"/>
       <c r="G184" s="42">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H184" s="42"/>
       <c r="I184" s="42">
@@ -7682,17 +7690,17 @@
       </c>
       <c r="J184" s="42"/>
       <c r="K184" s="42">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L184" s="42"/>
       <c r="M184" s="43">
-        <v>8</v>
-      </c>
-      <c r="N184" s="64"/>
+        <v>10</v>
+      </c>
+      <c r="N184" s="63"/>
       <c r="O184" s="43">
         <v>0</v>
       </c>
-      <c r="P184" s="65"/>
+      <c r="P184" s="46"/>
     </row>
     <row r="185" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="186" spans="1:16" x14ac:dyDescent="0.25">
@@ -7746,11 +7754,11 @@
       <c r="A187" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B187" s="50" t="s">
+      <c r="B187" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C187" s="4"/>
-      <c r="D187" s="50" t="s">
+      <c r="D187" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E187" s="4"/>
@@ -7760,7 +7768,7 @@
       <c r="G187" s="4">
         <v>7</v>
       </c>
-      <c r="H187" s="50" t="s">
+      <c r="H187" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I187" s="4"/>
@@ -7785,11 +7793,11 @@
       <c r="A188" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B188" s="50" t="s">
+      <c r="B188" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C188" s="4"/>
-      <c r="D188" s="50" t="s">
+      <c r="D188" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E188" s="4"/>
@@ -7799,7 +7807,7 @@
       <c r="G188" s="4">
         <v>7</v>
       </c>
-      <c r="H188" s="50" t="s">
+      <c r="H188" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I188" s="4"/>
@@ -7824,11 +7832,11 @@
       <c r="A189" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B189" s="50" t="s">
+      <c r="B189" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C189" s="4"/>
-      <c r="D189" s="50" t="s">
+      <c r="D189" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E189" s="4"/>
@@ -7838,11 +7846,11 @@
       <c r="G189" s="4">
         <v>7</v>
       </c>
-      <c r="H189" s="50" t="s">
+      <c r="H189" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I189" s="4"/>
-      <c r="J189" s="50" t="s">
+      <c r="J189" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K189" s="4"/>
@@ -7863,11 +7871,11 @@
       <c r="A190" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B190" s="50" t="s">
+      <c r="B190" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C190" s="4"/>
-      <c r="D190" s="50" t="s">
+      <c r="D190" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E190" s="4"/>
@@ -7877,11 +7885,11 @@
       <c r="G190" s="4">
         <v>7</v>
       </c>
-      <c r="H190" s="50" t="s">
+      <c r="H190" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I190" s="4"/>
-      <c r="J190" s="50" t="s">
+      <c r="J190" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K190" s="4"/>
@@ -7902,11 +7910,11 @@
       <c r="A191" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B191" s="50" t="s">
+      <c r="B191" s="49" t="s">
         <v>68</v>
       </c>
       <c r="C191" s="23"/>
-      <c r="D191" s="50" t="s">
+      <c r="D191" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E191" s="23"/>
@@ -7916,7 +7924,7 @@
       <c r="G191" s="23">
         <v>7</v>
       </c>
-      <c r="H191" s="50" t="s">
+      <c r="H191" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I191" s="23"/>
@@ -7971,7 +7979,7 @@
         <f>SUM(M187:M191)</f>
         <v>40</v>
       </c>
-      <c r="N192" s="62"/>
+      <c r="N192" s="61"/>
       <c r="O192" s="45">
         <f>SUM(O187:O191)</f>
         <v>40</v>
@@ -8005,7 +8013,7 @@
       <c r="M193" s="40">
         <v>0</v>
       </c>
-      <c r="N193" s="63"/>
+      <c r="N193" s="62"/>
       <c r="O193" s="40">
         <v>0</v>
       </c>
@@ -8024,7 +8032,7 @@
       </c>
       <c r="F194" s="42"/>
       <c r="G194" s="42">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H194" s="42"/>
       <c r="I194" s="42">
@@ -8032,17 +8040,17 @@
       </c>
       <c r="J194" s="42"/>
       <c r="K194" s="42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L194" s="42"/>
       <c r="M194" s="43">
-        <v>8</v>
-      </c>
-      <c r="N194" s="64"/>
+        <v>10</v>
+      </c>
+      <c r="N194" s="63"/>
       <c r="O194" s="43">
         <v>0</v>
       </c>
-      <c r="P194" s="65"/>
+      <c r="P194" s="46"/>
     </row>
     <row r="195" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="196" spans="1:16" x14ac:dyDescent="0.25">
@@ -8097,12 +8105,12 @@
         <v>7</v>
       </c>
       <c r="B197" s="23" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C197" s="4">
-        <v>6</v>
-      </c>
-      <c r="D197" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D197" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E197" s="4"/>
@@ -8112,11 +8120,11 @@
       <c r="G197" s="4">
         <v>7</v>
       </c>
-      <c r="H197" s="50" t="s">
+      <c r="H197" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I197" s="4"/>
-      <c r="J197" s="50" t="s">
+      <c r="J197" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K197" s="4"/>
@@ -8138,12 +8146,12 @@
         <v>8</v>
       </c>
       <c r="B198" s="23" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C198" s="4">
-        <v>6</v>
-      </c>
-      <c r="D198" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E198" s="4"/>
@@ -8153,11 +8161,11 @@
       <c r="G198" s="4">
         <v>7</v>
       </c>
-      <c r="H198" s="50" t="s">
+      <c r="H198" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I198" s="4"/>
-      <c r="J198" s="50" t="s">
+      <c r="J198" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K198" s="4"/>
@@ -8184,7 +8192,7 @@
       <c r="C199" s="4">
         <v>8</v>
       </c>
-      <c r="D199" s="50" t="s">
+      <c r="D199" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E199" s="4"/>
@@ -8194,11 +8202,11 @@
       <c r="G199" s="4">
         <v>7</v>
       </c>
-      <c r="H199" s="50" t="s">
+      <c r="H199" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I199" s="4"/>
-      <c r="J199" s="50" t="s">
+      <c r="J199" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K199" s="4"/>
@@ -8223,7 +8231,7 @@
       <c r="C200" s="4">
         <v>8</v>
       </c>
-      <c r="D200" s="50" t="s">
+      <c r="D200" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E200" s="4"/>
@@ -8233,15 +8241,15 @@
       <c r="G200" s="4">
         <v>7</v>
       </c>
-      <c r="H200" s="50" t="s">
+      <c r="H200" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I200" s="4"/>
-      <c r="J200" s="50" t="s">
+      <c r="J200" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K200" s="4"/>
-      <c r="L200" s="50" t="s">
+      <c r="L200" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M200" s="12"/>
@@ -8262,7 +8270,7 @@
       <c r="C201" s="23">
         <v>8</v>
       </c>
-      <c r="D201" s="50" t="s">
+      <c r="D201" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E201" s="23"/>
@@ -8272,7 +8280,7 @@
       <c r="G201" s="23">
         <v>7</v>
       </c>
-      <c r="H201" s="50" t="s">
+      <c r="H201" s="49" t="s">
         <v>68</v>
       </c>
       <c r="I201" s="23"/>
@@ -8280,7 +8288,7 @@
         <v>13</v>
       </c>
       <c r="K201" s="23"/>
-      <c r="L201" s="50" t="s">
+      <c r="L201" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M201" s="24"/>
@@ -8298,7 +8306,7 @@
       <c r="B202" s="44"/>
       <c r="C202" s="44">
         <f>SUM(C197:C201)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D202" s="44"/>
       <c r="E202" s="44">
@@ -8325,7 +8333,7 @@
         <f>SUM(M197:M201)</f>
         <v>16</v>
       </c>
-      <c r="N202" s="62"/>
+      <c r="N202" s="61"/>
       <c r="O202" s="45">
         <f>SUM(O197:O201)</f>
         <v>40</v>
@@ -8337,7 +8345,7 @@
       </c>
       <c r="B203" s="39"/>
       <c r="C203" s="39">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="D203" s="39"/>
       <c r="E203" s="39">
@@ -8359,7 +8367,7 @@
       <c r="M203" s="40">
         <v>-8</v>
       </c>
-      <c r="N203" s="63"/>
+      <c r="N203" s="62"/>
       <c r="O203" s="40">
         <v>0</v>
       </c>
@@ -8370,7 +8378,7 @@
       </c>
       <c r="B204" s="42"/>
       <c r="C204" s="42">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D204" s="42"/>
       <c r="E204" s="42">
@@ -8378,7 +8386,7 @@
       </c>
       <c r="F204" s="42"/>
       <c r="G204" s="42">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H204" s="42"/>
       <c r="I204" s="42">
@@ -8386,13 +8394,13 @@
       </c>
       <c r="J204" s="42"/>
       <c r="K204" s="42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L204" s="42"/>
       <c r="M204" s="43">
-        <v>0</v>
-      </c>
-      <c r="N204" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="N204" s="63"/>
       <c r="O204" s="43">
         <v>0</v>
       </c>
@@ -8456,7 +8464,7 @@
       <c r="C207" s="4">
         <v>8</v>
       </c>
-      <c r="D207" s="50" t="s">
+      <c r="D207" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E207" s="4"/>
@@ -8472,11 +8480,11 @@
       <c r="I207" s="4">
         <v>8</v>
       </c>
-      <c r="J207" s="50" t="s">
+      <c r="J207" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K207" s="4"/>
-      <c r="L207" s="50" t="s">
+      <c r="L207" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M207" s="12"/>
@@ -8497,7 +8505,7 @@
       <c r="C208" s="4">
         <v>8</v>
       </c>
-      <c r="D208" s="50" t="s">
+      <c r="D208" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E208" s="4"/>
@@ -8513,11 +8521,11 @@
       <c r="I208" s="4">
         <v>8</v>
       </c>
-      <c r="J208" s="50" t="s">
+      <c r="J208" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K208" s="4"/>
-      <c r="L208" s="50" t="s">
+      <c r="L208" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M208" s="12"/>
@@ -8538,7 +8546,7 @@
       <c r="C209" s="4">
         <v>8</v>
       </c>
-      <c r="D209" s="50" t="s">
+      <c r="D209" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E209" s="4"/>
@@ -8554,11 +8562,11 @@
       <c r="I209" s="4">
         <v>8</v>
       </c>
-      <c r="J209" s="50" t="s">
+      <c r="J209" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K209" s="4"/>
-      <c r="L209" s="50" t="s">
+      <c r="L209" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M209" s="12"/>
@@ -8579,7 +8587,7 @@
       <c r="C210" s="4">
         <v>8</v>
       </c>
-      <c r="D210" s="50" t="s">
+      <c r="D210" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E210" s="4"/>
@@ -8595,11 +8603,11 @@
       <c r="I210" s="4">
         <v>8</v>
       </c>
-      <c r="J210" s="50" t="s">
+      <c r="J210" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K210" s="4"/>
-      <c r="L210" s="50" t="s">
+      <c r="L210" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M210" s="12"/>
@@ -8620,7 +8628,7 @@
       <c r="C211" s="23">
         <v>7</v>
       </c>
-      <c r="D211" s="50" t="s">
+      <c r="D211" s="49" t="s">
         <v>68</v>
       </c>
       <c r="E211" s="23"/>
@@ -8640,7 +8648,7 @@
         <v>13</v>
       </c>
       <c r="K211" s="23"/>
-      <c r="L211" s="50" t="s">
+      <c r="L211" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M211" s="24"/>
@@ -8756,7 +8764,7 @@
       <c r="O214" s="43">
         <v>0</v>
       </c>
-      <c r="P214" s="46"/>
+      <c r="P214" s="64"/>
     </row>
     <row r="215" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
@@ -8834,11 +8842,11 @@
       <c r="I217" s="4">
         <v>8</v>
       </c>
-      <c r="J217" s="50" t="s">
+      <c r="J217" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K217" s="4"/>
-      <c r="L217" s="50" t="s">
+      <c r="L217" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M217" s="12"/>
@@ -8877,11 +8885,11 @@
       <c r="I218" s="4">
         <v>8</v>
       </c>
-      <c r="J218" s="50" t="s">
+      <c r="J218" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K218" s="4"/>
-      <c r="L218" s="50" t="s">
+      <c r="L218" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M218" s="12"/>
@@ -8920,11 +8928,11 @@
       <c r="I219" s="4">
         <v>8</v>
       </c>
-      <c r="J219" s="50" t="s">
+      <c r="J219" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K219" s="4"/>
-      <c r="L219" s="50" t="s">
+      <c r="L219" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M219" s="12"/>
@@ -8963,11 +8971,11 @@
       <c r="I220" s="4">
         <v>8</v>
       </c>
-      <c r="J220" s="50" t="s">
+      <c r="J220" s="49" t="s">
         <v>68</v>
       </c>
       <c r="K220" s="4"/>
-      <c r="L220" s="50" t="s">
+      <c r="L220" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M220" s="12"/>
@@ -9010,7 +9018,7 @@
         <v>13</v>
       </c>
       <c r="K221" s="23"/>
-      <c r="L221" s="50" t="s">
+      <c r="L221" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M221" s="24"/>
@@ -9055,7 +9063,7 @@
         <f>SUM(M217:M221)</f>
         <v>0</v>
       </c>
-      <c r="N222" s="62"/>
+      <c r="N222" s="61"/>
       <c r="O222" s="45">
         <f>SUM(O217:O221)</f>
         <v>40</v>
@@ -9089,7 +9097,7 @@
       <c r="M223" s="40">
         <v>0</v>
       </c>
-      <c r="N223" s="63"/>
+      <c r="N223" s="62"/>
       <c r="O223" s="40">
         <v>0</v>
       </c>
@@ -9122,11 +9130,11 @@
       <c r="M224" s="43">
         <v>0</v>
       </c>
-      <c r="N224" s="64"/>
+      <c r="N224" s="63"/>
       <c r="O224" s="43">
         <v>0</v>
       </c>
-      <c r="P224" s="46"/>
+      <c r="P224" s="64"/>
     </row>
     <row r="225" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="226" spans="1:16" x14ac:dyDescent="0.25">
@@ -9210,7 +9218,7 @@
       <c r="K227" s="4">
         <v>10</v>
       </c>
-      <c r="L227" s="50" t="s">
+      <c r="L227" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M227" s="12"/>
@@ -9255,7 +9263,7 @@
       <c r="K228" s="4">
         <v>9</v>
       </c>
-      <c r="L228" s="50" t="s">
+      <c r="L228" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M228" s="12"/>
@@ -9300,7 +9308,7 @@
       <c r="K229" s="4">
         <v>8</v>
       </c>
-      <c r="L229" s="50" t="s">
+      <c r="L229" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M229" s="12"/>
@@ -9343,7 +9351,7 @@
       <c r="K230" s="4">
         <v>8</v>
       </c>
-      <c r="L230" s="50" t="s">
+      <c r="L230" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M230" s="12"/>
@@ -9384,7 +9392,7 @@
         <v>13</v>
       </c>
       <c r="K231" s="23"/>
-      <c r="L231" s="50" t="s">
+      <c r="L231" s="49" t="s">
         <v>68</v>
       </c>
       <c r="M231" s="24"/>
@@ -9427,7 +9435,7 @@
         <f>SUM(M227:M231)</f>
         <v>0</v>
       </c>
-      <c r="N232" s="62"/>
+      <c r="N232" s="61"/>
       <c r="O232" s="45">
         <f>SUM(O227:O231)</f>
         <v>19</v>
@@ -9461,7 +9469,7 @@
       <c r="M233" s="40">
         <v>0</v>
       </c>
-      <c r="N233" s="63"/>
+      <c r="N233" s="62"/>
       <c r="O233" s="40">
         <v>0</v>
       </c>
@@ -9494,11 +9502,11 @@
       <c r="M234" s="43">
         <v>0</v>
       </c>
-      <c r="N234" s="64"/>
+      <c r="N234" s="63"/>
       <c r="O234" s="43">
         <v>0</v>
       </c>
-      <c r="P234" s="46"/>
+      <c r="P234" s="64"/>
     </row>
     <row r="235" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="236" spans="1:16" x14ac:dyDescent="0.25">
@@ -9807,7 +9815,7 @@
         <f>SUM(M237:M241)</f>
         <v>34</v>
       </c>
-      <c r="N242" s="62"/>
+      <c r="N242" s="61"/>
       <c r="O242" s="45">
         <f>SUM(O237:O241)</f>
         <v>19</v>
@@ -9841,7 +9849,7 @@
       <c r="M243" s="40">
         <v>-6</v>
       </c>
-      <c r="N243" s="63"/>
+      <c r="N243" s="62"/>
       <c r="O243" s="40">
         <v>0</v>
       </c>
@@ -9874,11 +9882,11 @@
       <c r="M244" s="43">
         <v>3</v>
       </c>
-      <c r="N244" s="64"/>
+      <c r="N244" s="63"/>
       <c r="O244" s="43">
         <v>0</v>
       </c>
-      <c r="P244" s="49"/>
+      <c r="P244" s="64"/>
     </row>
     <row r="245" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="246" spans="1:16" x14ac:dyDescent="0.25">
@@ -10187,7 +10195,7 @@
         <f>SUM(M247:M251)</f>
         <v>34</v>
       </c>
-      <c r="N252" s="62"/>
+      <c r="N252" s="61"/>
       <c r="O252" s="45">
         <f>SUM(O247:O251)</f>
         <v>19</v>
@@ -10221,7 +10229,7 @@
       <c r="M253" s="40">
         <v>-6</v>
       </c>
-      <c r="N253" s="63"/>
+      <c r="N253" s="62"/>
       <c r="O253" s="40">
         <v>0</v>
       </c>
@@ -10254,11 +10262,11 @@
       <c r="M254" s="43">
         <v>3</v>
       </c>
-      <c r="N254" s="64"/>
+      <c r="N254" s="63"/>
       <c r="O254" s="43">
         <v>0</v>
       </c>
-      <c r="P254" s="49"/>
+      <c r="P254" s="64"/>
     </row>
     <row r="255" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
@@ -10567,7 +10575,7 @@
         <f>SUM(M257:M261)</f>
         <v>34</v>
       </c>
-      <c r="N262" s="62"/>
+      <c r="N262" s="61"/>
       <c r="O262" s="45">
         <f>SUM(O257:O261)</f>
         <v>19</v>
@@ -10601,7 +10609,7 @@
       <c r="M263" s="40">
         <v>-6</v>
       </c>
-      <c r="N263" s="63"/>
+      <c r="N263" s="62"/>
       <c r="O263" s="40">
         <v>0</v>
       </c>
@@ -10634,11 +10642,11 @@
       <c r="M264" s="43">
         <v>3</v>
       </c>
-      <c r="N264" s="64"/>
+      <c r="N264" s="63"/>
       <c r="O264" s="43">
         <v>0</v>
       </c>
-      <c r="P264" s="49"/>
+      <c r="P264" s="64"/>
     </row>
     <row r="265" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="266" spans="1:16" x14ac:dyDescent="0.25">
@@ -10947,7 +10955,7 @@
         <f>SUM(M267:M271)</f>
         <v>34</v>
       </c>
-      <c r="N272" s="62"/>
+      <c r="N272" s="61"/>
       <c r="O272" s="45">
         <f>SUM(O267:O271)</f>
         <v>19</v>
@@ -10981,7 +10989,7 @@
       <c r="M273" s="40">
         <v>-6</v>
       </c>
-      <c r="N273" s="63"/>
+      <c r="N273" s="62"/>
       <c r="O273" s="40">
         <v>0</v>
       </c>
@@ -11014,11 +11022,11 @@
       <c r="M274" s="43">
         <v>3</v>
       </c>
-      <c r="N274" s="64"/>
+      <c r="N274" s="63"/>
       <c r="O274" s="43">
         <v>0</v>
       </c>
-      <c r="P274" s="49"/>
+      <c r="P274" s="64"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1199" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E759F7D8-F814-4E9B-97A9-0D5F10402589}"/>
+  <xr:revisionPtr revIDLastSave="1823" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12E2B44C-A5E5-4570-A212-CC3A6D07A3E9}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="315" windowWidth="42900" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="-90" yWindow="30" windowWidth="54180" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="84">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -221,9 +221,6 @@
     <t>Vecka 35 (24-28 aug)</t>
   </si>
   <si>
-    <t>Vecka 34 (31 aug-4 sep)</t>
-  </si>
-  <si>
     <t>Betyder att schemat är låst och utdelat</t>
   </si>
   <si>
@@ -266,7 +263,34 @@
     <t>07:00-13:45</t>
   </si>
   <si>
-    <t>Behöver lägga in</t>
+    <t>Vakans</t>
+  </si>
+  <si>
+    <t>Vecka 36 (31 aug-4 sep)</t>
+  </si>
+  <si>
+    <t>Vecka 37 (7sep-11 sep)</t>
+  </si>
+  <si>
+    <t>Vecka 38 (14 sep-18 sep)</t>
+  </si>
+  <si>
+    <t>Vecka 39 (21 sep-25 sep)</t>
+  </si>
+  <si>
+    <t>Vecka 40 (28 sep-2 okt)</t>
+  </si>
+  <si>
+    <t>Vecka 41 (5 okt-9 okt)</t>
+  </si>
+  <si>
+    <t>Vecka 42 (12 okt-16 okt)</t>
+  </si>
+  <si>
+    <t>Emilia</t>
+  </si>
+  <si>
+    <t>07:00-15:45 (NO)</t>
   </si>
 </sst>
 </file>
@@ -276,7 +300,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\+0;\-0;0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,13 +333,6 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -746,8 +763,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -787,6 +803,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -795,9 +814,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFDF5D3"/>
       <color rgb="FFB2F0FC"/>
       <color rgb="FFE3F7A3"/>
-      <color rgb="FFFDF5D3"/>
       <color rgb="FFF9E7F7"/>
       <color rgb="FFFCCDC4"/>
       <color rgb="FFF0CDC2"/>
@@ -1134,7 +1153,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S274"/>
+  <dimension ref="A1:T334"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1151,7 +1170,10 @@
     <col min="12" max="12" width="18.7109375" style="2" customWidth="1"/>
     <col min="13" max="13" width="6.7109375" customWidth="1"/>
     <col min="14" max="14" width="19.7109375" customWidth="1"/>
-    <col min="15" max="15" width="7.7109375" customWidth="1"/>
+    <col min="15" max="15" width="7" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" customWidth="1"/>
+    <col min="17" max="17" width="5.7109375" customWidth="1"/>
+    <col min="18" max="18" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
@@ -1521,7 +1543,7 @@
       <c r="O10" s="43"/>
       <c r="P10" s="46"/>
       <c r="Q10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1822,8 +1844,8 @@
         <f>SUM(M13:M17)</f>
         <v>39</v>
       </c>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
@@ -1853,8 +1875,8 @@
       <c r="M19" s="40">
         <v>-1</v>
       </c>
-      <c r="N19" s="56"/>
-      <c r="O19" s="56"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="55"/>
     </row>
     <row r="20" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
@@ -1884,8 +1906,8 @@
       <c r="M20" s="43">
         <v>0</v>
       </c>
-      <c r="N20" s="57"/>
-      <c r="O20" s="57"/>
+      <c r="N20" s="56"/>
+      <c r="O20" s="56"/>
       <c r="P20" s="46"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2182,8 +2204,8 @@
         <f>SUM(M23:M27)</f>
         <v>34</v>
       </c>
-      <c r="N28" s="55"/>
-      <c r="O28" s="55"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="54"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
@@ -2213,8 +2235,8 @@
       <c r="M29" s="40">
         <v>-6</v>
       </c>
-      <c r="N29" s="56"/>
-      <c r="O29" s="56"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="55"/>
     </row>
     <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
@@ -2244,8 +2266,8 @@
       <c r="M30" s="43">
         <v>-6</v>
       </c>
-      <c r="N30" s="57"/>
-      <c r="O30" s="57"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
       <c r="P30" s="46"/>
     </row>
     <row r="31" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2537,8 +2559,8 @@
         <f>SUM(M33:M37)</f>
         <v>39</v>
       </c>
-      <c r="N38" s="55"/>
-      <c r="O38" s="55"/>
+      <c r="N38" s="54"/>
+      <c r="O38" s="54"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
@@ -2568,8 +2590,8 @@
       <c r="M39" s="40">
         <v>-1</v>
       </c>
-      <c r="N39" s="56"/>
-      <c r="O39" s="56"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="55"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="41" t="s">
@@ -2599,8 +2621,8 @@
       <c r="M40" s="43">
         <v>-7</v>
       </c>
-      <c r="N40" s="57"/>
-      <c r="O40" s="57"/>
+      <c r="N40" s="56"/>
+      <c r="O40" s="56"/>
       <c r="P40" s="46"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2841,8 +2863,8 @@
         <v>13</v>
       </c>
       <c r="M47" s="27"/>
-      <c r="N47" s="58"/>
-      <c r="O47" s="58"/>
+      <c r="N47" s="57"/>
+      <c r="O47" s="57"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="35" t="s">
@@ -2878,8 +2900,8 @@
         <f>SUM(M43:M47)</f>
         <v>32</v>
       </c>
-      <c r="N48" s="55"/>
-      <c r="O48" s="55"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
@@ -2909,8 +2931,8 @@
       <c r="M49" s="40">
         <v>0</v>
       </c>
-      <c r="N49" s="56"/>
-      <c r="O49" s="56"/>
+      <c r="N49" s="55"/>
+      <c r="O49" s="55"/>
     </row>
     <row r="50" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="41" t="s">
@@ -2940,8 +2962,8 @@
       <c r="M50" s="43">
         <v>-7</v>
       </c>
-      <c r="N50" s="57"/>
-      <c r="O50" s="57"/>
+      <c r="N50" s="56"/>
+      <c r="O50" s="56"/>
       <c r="P50" s="46"/>
     </row>
     <row r="51" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2993,7 +3015,7 @@
         <v>26</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C53" s="20">
         <v>7</v>
@@ -3026,8 +3048,8 @@
       <c r="M53" s="28">
         <v>10</v>
       </c>
-      <c r="N53" s="59"/>
-      <c r="O53" s="59"/>
+      <c r="N53" s="58"/>
+      <c r="O53" s="58"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
@@ -3231,8 +3253,8 @@
         <f>SUM(M53:M57)</f>
         <v>39</v>
       </c>
-      <c r="N58" s="55"/>
-      <c r="O58" s="55"/>
+      <c r="N58" s="54"/>
+      <c r="O58" s="54"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
@@ -3262,47 +3284,47 @@
       <c r="M59" s="40">
         <v>7</v>
       </c>
-      <c r="N59" s="56"/>
-      <c r="O59" s="56"/>
+      <c r="N59" s="55"/>
+      <c r="O59" s="55"/>
     </row>
     <row r="60" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="52" t="s">
+      <c r="B60" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="52">
+        <v>15</v>
+      </c>
+      <c r="D60" s="42"/>
+      <c r="E60" s="52">
+        <v>8</v>
+      </c>
+      <c r="F60" s="42"/>
+      <c r="G60" s="52">
+        <v>-3</v>
+      </c>
+      <c r="H60" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="53">
-        <v>15</v>
-      </c>
-      <c r="D60" s="42"/>
-      <c r="E60" s="53">
-        <v>8</v>
-      </c>
-      <c r="F60" s="42"/>
-      <c r="G60" s="53">
-        <v>-3</v>
-      </c>
-      <c r="H60" s="52" t="s">
+      <c r="I60" s="52">
+        <v>14</v>
+      </c>
+      <c r="J60" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="I60" s="53">
-        <v>14</v>
-      </c>
-      <c r="J60" s="52" t="s">
+      <c r="K60" s="52">
+        <v>9</v>
+      </c>
+      <c r="L60" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="K60" s="53">
-        <v>9</v>
-      </c>
-      <c r="L60" s="52" t="s">
-        <v>65</v>
-      </c>
-      <c r="M60" s="54">
-        <v>12</v>
-      </c>
-      <c r="N60" s="60"/>
-      <c r="O60" s="60"/>
+      <c r="M60" s="53">
+        <v>12</v>
+      </c>
+      <c r="N60" s="59"/>
+      <c r="O60" s="59"/>
       <c r="P60" s="46"/>
     </row>
     <row r="61" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3526,7 +3548,7 @@
         <v>11</v>
       </c>
       <c r="B67" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67" s="23"/>
       <c r="D67" s="23" t="s">
@@ -3594,8 +3616,8 @@
         <f>SUM(M63:M67)</f>
         <v>41</v>
       </c>
-      <c r="N68" s="55"/>
-      <c r="O68" s="55"/>
+      <c r="N68" s="54"/>
+      <c r="O68" s="54"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
@@ -3625,8 +3647,8 @@
       <c r="M69" s="40">
         <v>1</v>
       </c>
-      <c r="N69" s="56"/>
-      <c r="O69" s="56"/>
+      <c r="N69" s="55"/>
+      <c r="O69" s="55"/>
     </row>
     <row r="70" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41" t="s">
@@ -3656,8 +3678,8 @@
       <c r="M70" s="43">
         <v>13</v>
       </c>
-      <c r="N70" s="57"/>
-      <c r="O70" s="57"/>
+      <c r="N70" s="56"/>
+      <c r="O70" s="56"/>
       <c r="P70" s="46"/>
     </row>
     <row r="71" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3951,8 +3973,8 @@
         <f>SUM(M73:M77)</f>
         <v>39</v>
       </c>
-      <c r="N78" s="55"/>
-      <c r="O78" s="55"/>
+      <c r="N78" s="54"/>
+      <c r="O78" s="54"/>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
@@ -3982,8 +4004,8 @@
       <c r="M79" s="40">
         <v>-1</v>
       </c>
-      <c r="N79" s="56"/>
-      <c r="O79" s="56"/>
+      <c r="N79" s="55"/>
+      <c r="O79" s="55"/>
     </row>
     <row r="80" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="41" t="s">
@@ -4013,8 +4035,8 @@
       <c r="M80" s="43">
         <v>12</v>
       </c>
-      <c r="N80" s="57"/>
-      <c r="O80" s="57"/>
+      <c r="N80" s="56"/>
+      <c r="O80" s="56"/>
       <c r="P80" s="46"/>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
@@ -4054,7 +4076,7 @@
     <row r="83" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>2</v>
@@ -4257,7 +4279,7 @@
       </c>
       <c r="K88" s="4"/>
       <c r="L88" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M88" s="12">
         <v>7</v>
@@ -4293,8 +4315,8 @@
         <v>13</v>
       </c>
       <c r="M89" s="31"/>
-      <c r="N89" s="58"/>
-      <c r="O89" s="58"/>
+      <c r="N89" s="57"/>
+      <c r="O89" s="57"/>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="47" t="s">
@@ -4330,8 +4352,8 @@
         <f>SUM(M85:M89)</f>
         <v>34</v>
       </c>
-      <c r="N90" s="55"/>
-      <c r="O90" s="55"/>
+      <c r="N90" s="54"/>
+      <c r="O90" s="54"/>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="38" t="s">
@@ -4361,8 +4383,8 @@
       <c r="M91" s="40">
         <v>2</v>
       </c>
-      <c r="N91" s="56"/>
-      <c r="O91" s="56"/>
+      <c r="N91" s="55"/>
+      <c r="O91" s="55"/>
     </row>
     <row r="92" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="41" t="s">
@@ -4392,14 +4414,14 @@
       <c r="M92" s="43">
         <v>14</v>
       </c>
-      <c r="N92" s="57"/>
-      <c r="O92" s="57"/>
+      <c r="N92" s="56"/>
+      <c r="O92" s="56"/>
       <c r="P92" s="46"/>
     </row>
     <row r="93" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>2</v>
@@ -4687,8 +4709,8 @@
         <f>SUM(M95:M99)</f>
         <v>39</v>
       </c>
-      <c r="N100" s="55"/>
-      <c r="O100" s="55"/>
+      <c r="N100" s="54"/>
+      <c r="O100" s="54"/>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="38" t="s">
@@ -4718,8 +4740,8 @@
       <c r="M101" s="40">
         <v>-1</v>
       </c>
-      <c r="N101" s="56"/>
-      <c r="O101" s="56"/>
+      <c r="N101" s="55"/>
+      <c r="O101" s="55"/>
     </row>
     <row r="102" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="41" t="s">
@@ -4749,8 +4771,8 @@
       <c r="M102" s="43">
         <v>13</v>
       </c>
-      <c r="N102" s="57"/>
-      <c r="O102" s="57"/>
+      <c r="N102" s="56"/>
+      <c r="O102" s="56"/>
       <c r="P102" s="46"/>
     </row>
     <row r="103" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -4955,8 +4977,8 @@
         <v>13</v>
       </c>
       <c r="M108" s="19"/>
-      <c r="N108" s="58"/>
-      <c r="O108" s="58"/>
+      <c r="N108" s="57"/>
+      <c r="O108" s="57"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
@@ -5033,8 +5055,8 @@
         <f>SUM(M105:M109)</f>
         <v>34</v>
       </c>
-      <c r="N110" s="55"/>
-      <c r="O110" s="55"/>
+      <c r="N110" s="54"/>
+      <c r="O110" s="54"/>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="38" t="s">
@@ -5064,8 +5086,8 @@
       <c r="M111" s="40">
         <v>2</v>
       </c>
-      <c r="N111" s="56"/>
-      <c r="O111" s="56"/>
+      <c r="N111" s="55"/>
+      <c r="O111" s="55"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="41" t="s">
@@ -5095,12 +5117,12 @@
       <c r="M112" s="43">
         <v>15</v>
       </c>
-      <c r="N112" s="57"/>
-      <c r="O112" s="57"/>
+      <c r="N112" s="56"/>
+      <c r="O112" s="56"/>
       <c r="P112" s="46"/>
     </row>
-    <row r="113" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>46</v>
       </c>
@@ -5143,7 +5165,7 @@
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
         <v>7</v>
       </c>
@@ -5186,7 +5208,7 @@
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>8</v>
       </c>
@@ -5229,7 +5251,7 @@
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>9</v>
       </c>
@@ -5272,7 +5294,7 @@
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>10</v>
       </c>
@@ -5315,7 +5337,7 @@
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
     </row>
-    <row r="119" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
         <v>11</v>
       </c>
@@ -5356,7 +5378,7 @@
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="47" t="s">
         <v>40</v>
       </c>
@@ -5390,10 +5412,10 @@
         <f>SUM(M115:M119)</f>
         <v>39</v>
       </c>
-      <c r="N120" s="55"/>
-      <c r="O120" s="55"/>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N120" s="54"/>
+      <c r="O120" s="54"/>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="38" t="s">
         <v>41</v>
       </c>
@@ -5421,10 +5443,10 @@
       <c r="M121" s="40">
         <v>-1</v>
       </c>
-      <c r="N121" s="56"/>
-      <c r="O121" s="56"/>
-    </row>
-    <row r="122" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N121" s="55"/>
+      <c r="O121" s="55"/>
+    </row>
+    <row r="122" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="41" t="s">
         <v>42</v>
       </c>
@@ -5452,11 +5474,11 @@
       <c r="M122" s="43">
         <v>14</v>
       </c>
-      <c r="N122" s="57"/>
-      <c r="O122" s="57"/>
+      <c r="N122" s="56"/>
+      <c r="O122" s="56"/>
       <c r="P122" s="46"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="33"/>
       <c r="B123" s="34"/>
       <c r="C123" s="34"/>
@@ -5473,7 +5495,7 @@
       <c r="N123" s="34"/>
       <c r="O123" s="34"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="33"/>
       <c r="B124" s="34"/>
       <c r="C124" s="34"/>
@@ -5490,8 +5512,8 @@
       <c r="N124" s="34"/>
       <c r="O124" s="34"/>
     </row>
-    <row r="125" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>47</v>
       </c>
@@ -5532,13 +5554,25 @@
         <v>18</v>
       </c>
       <c r="N126" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O126" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P126" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q126" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R126" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S126" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
         <v>7</v>
       </c>
@@ -5584,8 +5618,16 @@
       <c r="O127" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P127" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q127" s="12"/>
+      <c r="R127" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S127" s="12"/>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>8</v>
       </c>
@@ -5631,8 +5673,16 @@
       <c r="O128" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P128" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q128" s="12"/>
+      <c r="R128" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S128" s="12"/>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>9</v>
       </c>
@@ -5676,8 +5726,16 @@
         <v>13</v>
       </c>
       <c r="O129" s="12"/>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P129" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q129" s="12"/>
+      <c r="R129" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S129" s="12"/>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>10</v>
       </c>
@@ -5721,8 +5779,16 @@
         <v>13</v>
       </c>
       <c r="O130" s="12"/>
-    </row>
-    <row r="131" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P130" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q130" s="12"/>
+      <c r="R130" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S130" s="12"/>
+    </row>
+    <row r="131" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>11</v>
       </c>
@@ -5762,8 +5828,16 @@
         <v>13</v>
       </c>
       <c r="O131" s="24"/>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P131" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q131" s="24"/>
+      <c r="R131" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S131" s="24"/>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="47" t="s">
         <v>40</v>
       </c>
@@ -5797,13 +5871,23 @@
         <f>SUM(M127:M131)</f>
         <v>34</v>
       </c>
-      <c r="N132" s="61"/>
+      <c r="N132" s="60"/>
       <c r="O132" s="45">
         <f>SUM(O127:O131)</f>
         <v>19</v>
       </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P132" s="60"/>
+      <c r="Q132" s="45">
+        <f>SUM(Q127:Q131)</f>
+        <v>0</v>
+      </c>
+      <c r="R132" s="60"/>
+      <c r="S132" s="45">
+        <f>SUM(S127:S131)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="38" t="s">
         <v>41</v>
       </c>
@@ -5831,12 +5915,20 @@
       <c r="M133" s="40">
         <v>-6</v>
       </c>
-      <c r="N133" s="62"/>
+      <c r="N133" s="61"/>
       <c r="O133" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P133" s="61"/>
+      <c r="Q133" s="40">
+        <v>0</v>
+      </c>
+      <c r="R133" s="61"/>
+      <c r="S133" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="41" t="s">
         <v>42</v>
       </c>
@@ -5864,14 +5956,22 @@
       <c r="M134" s="43">
         <v>8</v>
       </c>
-      <c r="N134" s="63"/>
+      <c r="N134" s="62"/>
       <c r="O134" s="43">
         <v>0</v>
       </c>
-      <c r="P134" s="46"/>
-    </row>
-    <row r="135" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P134" s="62"/>
+      <c r="Q134" s="43">
+        <v>0</v>
+      </c>
+      <c r="R134" s="62"/>
+      <c r="S134" s="43">
+        <v>0</v>
+      </c>
+      <c r="T134" s="46"/>
+    </row>
+    <row r="135" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>48</v>
       </c>
@@ -5912,13 +6012,25 @@
         <v>18</v>
       </c>
       <c r="N136" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O136" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P136" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q136" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R136" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S136" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
         <v>7</v>
       </c>
@@ -5935,7 +6047,7 @@
         <v>10</v>
       </c>
       <c r="F137" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4" t="s">
@@ -5962,8 +6074,16 @@
       <c r="O137" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P137" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q137" s="12"/>
+      <c r="R137" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S137" s="12"/>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
         <v>8</v>
       </c>
@@ -5980,7 +6100,7 @@
         <v>9</v>
       </c>
       <c r="F138" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4" t="s">
@@ -6007,8 +6127,16 @@
       <c r="O138" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P138" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q138" s="12"/>
+      <c r="R138" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S138" s="12"/>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>9</v>
       </c>
@@ -6025,7 +6153,7 @@
         <v>4</v>
       </c>
       <c r="F139" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4" t="s">
@@ -6052,13 +6180,21 @@
       <c r="O139" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P139" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q139" s="12"/>
+      <c r="R139" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S139" s="12"/>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C140" s="4">
         <v>5</v>
@@ -6070,7 +6206,7 @@
         <v>8</v>
       </c>
       <c r="F140" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="5" t="s">
@@ -6093,23 +6229,31 @@
       <c r="O140" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="141" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P140" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q140" s="12"/>
+      <c r="R140" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S140" s="12"/>
+    </row>
+    <row r="141" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C141" s="23">
         <v>5</v>
       </c>
-      <c r="D141" s="65" t="s">
+      <c r="D141" s="64" t="s">
         <v>13</v>
       </c>
       <c r="E141" s="23"/>
       <c r="F141" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G141" s="23"/>
       <c r="H141" s="23" t="s">
@@ -6134,11 +6278,16 @@
       <c r="O141" s="24">
         <v>8</v>
       </c>
-      <c r="P141" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P141" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q141" s="24"/>
+      <c r="R141" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S141" s="24"/>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="47" t="s">
         <v>40</v>
       </c>
@@ -6172,13 +6321,23 @@
         <f>SUM(M137:M141)</f>
         <v>34</v>
       </c>
-      <c r="N142" s="61"/>
+      <c r="N142" s="60"/>
       <c r="O142" s="45">
         <f>SUM(O137:O141)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P142" s="60"/>
+      <c r="Q142" s="45">
+        <f>SUM(Q137:Q141)</f>
+        <v>0</v>
+      </c>
+      <c r="R142" s="60"/>
+      <c r="S142" s="45">
+        <f>SUM(S137:S141)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="38" t="s">
         <v>49</v>
       </c>
@@ -6206,12 +6365,20 @@
       <c r="M143" s="40">
         <v>2</v>
       </c>
-      <c r="N143" s="62"/>
+      <c r="N143" s="61"/>
       <c r="O143" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P143" s="61"/>
+      <c r="Q143" s="40">
+        <v>0</v>
+      </c>
+      <c r="R143" s="61"/>
+      <c r="S143" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="41" t="s">
         <v>42</v>
       </c>
@@ -6239,14 +6406,22 @@
       <c r="M144" s="43">
         <v>10</v>
       </c>
-      <c r="N144" s="63"/>
+      <c r="N144" s="62"/>
       <c r="O144" s="43">
         <v>0</v>
       </c>
-      <c r="P144" s="46"/>
-    </row>
-    <row r="145" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P144" s="62"/>
+      <c r="Q144" s="43">
+        <v>0</v>
+      </c>
+      <c r="R144" s="62"/>
+      <c r="S144" s="43">
+        <v>0</v>
+      </c>
+      <c r="T144" s="46"/>
+    </row>
+    <row r="145" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>36</v>
       </c>
@@ -6287,13 +6462,25 @@
         <v>18</v>
       </c>
       <c r="N146" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O146" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P146" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q146" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R146" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S146" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>7</v>
       </c>
@@ -6310,7 +6497,7 @@
         <v>10</v>
       </c>
       <c r="F147" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G147" s="4"/>
       <c r="H147" s="4" t="s">
@@ -6337,8 +6524,16 @@
       <c r="O147" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P147" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q147" s="12"/>
+      <c r="R147" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S147" s="12"/>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>8</v>
       </c>
@@ -6355,7 +6550,7 @@
         <v>9</v>
       </c>
       <c r="F148" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4" t="s">
@@ -6382,8 +6577,16 @@
       <c r="O148" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P148" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q148" s="12"/>
+      <c r="R148" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S148" s="12"/>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>9</v>
       </c>
@@ -6400,7 +6603,7 @@
         <v>8</v>
       </c>
       <c r="F149" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G149" s="4"/>
       <c r="H149" s="4" t="s">
@@ -6427,8 +6630,16 @@
       <c r="O149" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P149" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q149" s="12"/>
+      <c r="R149" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S149" s="12"/>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
         <v>10</v>
       </c>
@@ -6443,7 +6654,7 @@
         <v>7</v>
       </c>
       <c r="F150" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4" t="s">
@@ -6457,7 +6668,7 @@
       </c>
       <c r="K150" s="4"/>
       <c r="L150" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M150" s="12">
         <v>7</v>
@@ -6468,8 +6679,16 @@
       <c r="O150" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="151" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P150" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q150" s="12"/>
+      <c r="R150" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S150" s="12"/>
+    </row>
+    <row r="151" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="22" t="s">
         <v>11</v>
       </c>
@@ -6478,17 +6697,17 @@
       </c>
       <c r="C151" s="23"/>
       <c r="D151" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E151" s="24">
         <v>6</v>
       </c>
       <c r="F151" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G151" s="23"/>
       <c r="H151" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I151" s="24">
         <v>6</v>
@@ -6498,19 +6717,27 @@
       </c>
       <c r="K151" s="23"/>
       <c r="L151" s="48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M151" s="24">
         <v>7</v>
       </c>
       <c r="N151" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O151" s="24">
         <v>6</v>
       </c>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P151" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q151" s="24"/>
+      <c r="R151" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S151" s="24"/>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="35" t="s">
         <v>40</v>
       </c>
@@ -6544,13 +6771,23 @@
         <f>SUM(M147:M151)</f>
         <v>41</v>
       </c>
-      <c r="N152" s="61"/>
+      <c r="N152" s="60"/>
       <c r="O152" s="45">
         <f>SUM(O147:O151)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P152" s="60"/>
+      <c r="Q152" s="45">
+        <f>SUM(Q147:Q151)</f>
+        <v>0</v>
+      </c>
+      <c r="R152" s="60"/>
+      <c r="S152" s="45">
+        <f>SUM(S147:S151)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="38" t="s">
         <v>41</v>
       </c>
@@ -6578,12 +6815,20 @@
       <c r="M153" s="40">
         <v>4</v>
       </c>
-      <c r="N153" s="62"/>
+      <c r="N153" s="61"/>
       <c r="O153" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P153" s="61"/>
+      <c r="Q153" s="40">
+        <v>0</v>
+      </c>
+      <c r="R153" s="61"/>
+      <c r="S153" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="41" t="s">
         <v>42</v>
       </c>
@@ -6611,14 +6856,22 @@
       <c r="M154" s="43">
         <v>9</v>
       </c>
-      <c r="N154" s="63"/>
+      <c r="N154" s="62"/>
       <c r="O154" s="43">
         <v>0</v>
       </c>
-      <c r="P154" s="46"/>
-    </row>
-    <row r="155" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P154" s="62"/>
+      <c r="Q154" s="43">
+        <v>0</v>
+      </c>
+      <c r="R154" s="62"/>
+      <c r="S154" s="43">
+        <v>0</v>
+      </c>
+      <c r="T154" s="46"/>
+    </row>
+    <row r="155" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>37</v>
       </c>
@@ -6659,18 +6912,30 @@
         <v>18</v>
       </c>
       <c r="N156" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O156" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P156" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q156" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R156" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S156" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B157" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4" t="s">
@@ -6707,13 +6972,21 @@
       <c r="O157" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P157" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q157" s="12"/>
+      <c r="R157" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S157" s="12"/>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B158" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4" t="s">
@@ -6750,13 +7023,21 @@
       <c r="O158" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P158" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q158" s="12"/>
+      <c r="R158" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S158" s="12"/>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B159" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4" t="s">
@@ -6793,13 +7074,21 @@
       <c r="O159" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P159" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q159" s="12"/>
+      <c r="R159" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S159" s="12"/>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B160" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4" t="s">
@@ -6834,8 +7123,16 @@
       <c r="O160" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="161" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P160" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q160" s="12"/>
+      <c r="R160" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S160" s="12"/>
+    </row>
+    <row r="161" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="29" t="s">
         <v>38</v>
       </c>
@@ -6867,8 +7164,16 @@
         <v>13</v>
       </c>
       <c r="O161" s="31"/>
-    </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P161" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q161" s="24"/>
+      <c r="R161" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S161" s="24"/>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" s="35" t="s">
         <v>40</v>
       </c>
@@ -6902,13 +7207,23 @@
         <f>SUM(M157:M161)</f>
         <v>33</v>
       </c>
-      <c r="N162" s="61"/>
+      <c r="N162" s="60"/>
       <c r="O162" s="45">
         <f>SUM(O157:O161)</f>
         <v>32</v>
       </c>
-    </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P162" s="60"/>
+      <c r="Q162" s="45">
+        <f>SUM(Q157:Q161)</f>
+        <v>0</v>
+      </c>
+      <c r="R162" s="60"/>
+      <c r="S162" s="45">
+        <f>SUM(S157:S161)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" s="38" t="s">
         <v>41</v>
       </c>
@@ -6936,12 +7251,20 @@
       <c r="M163" s="40">
         <v>1</v>
       </c>
-      <c r="N163" s="62"/>
+      <c r="N163" s="61"/>
       <c r="O163" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P163" s="61"/>
+      <c r="Q163" s="40">
+        <v>0</v>
+      </c>
+      <c r="R163" s="61"/>
+      <c r="S163" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="41" t="s">
         <v>42</v>
       </c>
@@ -6969,14 +7292,22 @@
       <c r="M164" s="43">
         <v>10</v>
       </c>
-      <c r="N164" s="63"/>
+      <c r="N164" s="62"/>
       <c r="O164" s="43">
         <v>0</v>
       </c>
-      <c r="P164" s="46"/>
-    </row>
-    <row r="165" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P164" s="62"/>
+      <c r="Q164" s="43">
+        <v>0</v>
+      </c>
+      <c r="R164" s="62"/>
+      <c r="S164" s="43">
+        <v>0</v>
+      </c>
+      <c r="T164" s="46"/>
+    </row>
+    <row r="165" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>50</v>
       </c>
@@ -7017,18 +7348,30 @@
         <v>18</v>
       </c>
       <c r="N166" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O166" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P166" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q166" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R166" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S166" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B167" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C167" s="4"/>
       <c r="D167" s="4" t="s">
@@ -7044,7 +7387,7 @@
         <v>7</v>
       </c>
       <c r="H167" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I167" s="4"/>
       <c r="J167" s="4" t="s">
@@ -7065,13 +7408,21 @@
       <c r="O167" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P167" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q167" s="12"/>
+      <c r="R167" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S167" s="12"/>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B168" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C168" s="4"/>
       <c r="D168" s="4" t="s">
@@ -7087,7 +7438,7 @@
         <v>7</v>
       </c>
       <c r="H168" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I168" s="4"/>
       <c r="J168" s="4" t="s">
@@ -7108,13 +7459,21 @@
       <c r="O168" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P168" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q168" s="12"/>
+      <c r="R168" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S168" s="12"/>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B169" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4" t="s">
@@ -7129,10 +7488,12 @@
       <c r="G169" s="4">
         <v>7</v>
       </c>
-      <c r="H169" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="I169" s="4"/>
+      <c r="H169" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I169" s="4">
+        <v>8</v>
+      </c>
       <c r="J169" s="4" t="s">
         <v>12</v>
       </c>
@@ -7151,29 +7512,37 @@
       <c r="O169" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P169" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q169" s="12"/>
+      <c r="R169" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S169" s="12"/>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B170" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C170" s="4"/>
-      <c r="D170" s="3" t="s">
-        <v>19</v>
+      <c r="D170" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E170" s="4">
-        <v>4</v>
-      </c>
-      <c r="F170" s="3" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="G170" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H170" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I170" s="4"/>
       <c r="J170" s="4" t="s">
@@ -7194,13 +7563,21 @@
       <c r="O170" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="171" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P170" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q170" s="12"/>
+      <c r="R170" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S170" s="12"/>
+    </row>
+    <row r="171" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B171" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C171" s="23"/>
       <c r="D171" s="3" t="s">
@@ -7216,7 +7593,7 @@
         <v>5</v>
       </c>
       <c r="H171" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I171" s="23"/>
       <c r="J171" s="23" t="s">
@@ -7235,9 +7612,16 @@
       <c r="O171" s="24">
         <v>8</v>
       </c>
-      <c r="S171" s="51"/>
-    </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P171" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q171" s="24"/>
+      <c r="R171" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S171" s="24"/>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" s="47" t="s">
         <v>40</v>
       </c>
@@ -7249,17 +7633,17 @@
       <c r="D172" s="44"/>
       <c r="E172" s="44">
         <f>SUM(E167:E171)</f>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F172" s="44"/>
       <c r="G172" s="44">
         <f>SUM(G167:G171)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H172" s="44"/>
       <c r="I172" s="44">
         <f>SUM(I167:I171)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J172" s="44"/>
       <c r="K172" s="44">
@@ -7271,13 +7655,23 @@
         <f>SUM(M167:M171)</f>
         <v>40</v>
       </c>
-      <c r="N172" s="61"/>
+      <c r="N172" s="60"/>
       <c r="O172" s="45">
         <f>SUM(O167:O171)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P172" s="60"/>
+      <c r="Q172" s="45">
+        <f>SUM(Q167:Q171)</f>
+        <v>0</v>
+      </c>
+      <c r="R172" s="60"/>
+      <c r="S172" s="45">
+        <f>SUM(S167:S171)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" s="38" t="s">
         <v>41</v>
       </c>
@@ -7287,11 +7681,11 @@
       </c>
       <c r="D173" s="39"/>
       <c r="E173" s="39">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="F173" s="39"/>
       <c r="G173" s="39">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H173" s="39"/>
       <c r="I173" s="39">
@@ -7305,12 +7699,20 @@
       <c r="M173" s="40">
         <v>0</v>
       </c>
-      <c r="N173" s="62"/>
+      <c r="N173" s="61"/>
       <c r="O173" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P173" s="61"/>
+      <c r="Q173" s="40">
+        <v>0</v>
+      </c>
+      <c r="R173" s="61"/>
+      <c r="S173" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="41" t="s">
         <v>42</v>
       </c>
@@ -7320,11 +7722,11 @@
       </c>
       <c r="D174" s="42"/>
       <c r="E174" s="42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F174" s="42"/>
       <c r="G174" s="42">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H174" s="42"/>
       <c r="I174" s="42">
@@ -7338,14 +7740,22 @@
       <c r="M174" s="43">
         <v>10</v>
       </c>
-      <c r="N174" s="63"/>
+      <c r="N174" s="62"/>
       <c r="O174" s="43">
         <v>0</v>
       </c>
-      <c r="P174" s="46"/>
-    </row>
-    <row r="175" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P174" s="62"/>
+      <c r="Q174" s="43">
+        <v>0</v>
+      </c>
+      <c r="R174" s="62"/>
+      <c r="S174" s="43">
+        <v>0</v>
+      </c>
+      <c r="T174" s="46"/>
+    </row>
+    <row r="175" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>51</v>
       </c>
@@ -7386,22 +7796,34 @@
         <v>18</v>
       </c>
       <c r="N176" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O176" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P176" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q176" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R176" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S176" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B177" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E177" s="4"/>
       <c r="F177" s="4" t="s">
@@ -7411,7 +7833,7 @@
         <v>7</v>
       </c>
       <c r="H177" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4" t="s">
@@ -7432,17 +7854,25 @@
       <c r="O177" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P177" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q177" s="12"/>
+      <c r="R177" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S177" s="12"/>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B178" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C178" s="4"/>
       <c r="D178" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="4" t="s">
@@ -7452,7 +7882,7 @@
         <v>7</v>
       </c>
       <c r="H178" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I178" s="4"/>
       <c r="J178" s="4" t="s">
@@ -7473,17 +7903,25 @@
       <c r="O178" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P178" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q178" s="12"/>
+      <c r="R178" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S178" s="12"/>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B179" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C179" s="4"/>
       <c r="D179" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="4" t="s">
@@ -7493,7 +7931,7 @@
         <v>7</v>
       </c>
       <c r="H179" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4" t="s">
@@ -7514,17 +7952,25 @@
       <c r="O179" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P179" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q179" s="12"/>
+      <c r="R179" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S179" s="12"/>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B180" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C180" s="4"/>
       <c r="D180" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="23" t="s">
@@ -7534,7 +7980,7 @@
         <v>7</v>
       </c>
       <c r="H180" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I180" s="4"/>
       <c r="J180" s="4" t="s">
@@ -7555,17 +8001,25 @@
       <c r="O180" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="181" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P180" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q180" s="12"/>
+      <c r="R180" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S180" s="12"/>
+    </row>
+    <row r="181" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B181" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C181" s="23"/>
       <c r="D181" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E181" s="23"/>
       <c r="F181" s="23" t="s">
@@ -7575,7 +8029,7 @@
         <v>7</v>
       </c>
       <c r="H181" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I181" s="23"/>
       <c r="J181" s="23" t="s">
@@ -7594,8 +8048,16 @@
       <c r="O181" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P181" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q181" s="24"/>
+      <c r="R181" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S181" s="24"/>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="47" t="s">
         <v>40</v>
       </c>
@@ -7629,13 +8091,23 @@
         <f>SUM(M177:M181)</f>
         <v>40</v>
       </c>
-      <c r="N182" s="61"/>
+      <c r="N182" s="60"/>
       <c r="O182" s="45">
         <f>SUM(O177:O181)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P182" s="60"/>
+      <c r="Q182" s="45">
+        <f>SUM(Q177:Q181)</f>
+        <v>0</v>
+      </c>
+      <c r="R182" s="60"/>
+      <c r="S182" s="45">
+        <f>SUM(S177:S181)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="38" t="s">
         <v>41</v>
       </c>
@@ -7663,12 +8135,20 @@
       <c r="M183" s="40">
         <v>0</v>
       </c>
-      <c r="N183" s="62"/>
+      <c r="N183" s="61"/>
       <c r="O183" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P183" s="61"/>
+      <c r="Q183" s="40">
+        <v>0</v>
+      </c>
+      <c r="R183" s="61"/>
+      <c r="S183" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="41" t="s">
         <v>42</v>
       </c>
@@ -7678,11 +8158,11 @@
       </c>
       <c r="D184" s="42"/>
       <c r="E184" s="42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F184" s="42"/>
       <c r="G184" s="42">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H184" s="42"/>
       <c r="I184" s="42">
@@ -7696,14 +8176,22 @@
       <c r="M184" s="43">
         <v>10</v>
       </c>
-      <c r="N184" s="63"/>
+      <c r="N184" s="62"/>
       <c r="O184" s="43">
         <v>0</v>
       </c>
-      <c r="P184" s="46"/>
-    </row>
-    <row r="185" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P184" s="62"/>
+      <c r="Q184" s="43">
+        <v>0</v>
+      </c>
+      <c r="R184" s="62"/>
+      <c r="S184" s="43">
+        <v>0</v>
+      </c>
+      <c r="T184" s="46"/>
+    </row>
+    <row r="185" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>52</v>
       </c>
@@ -7744,22 +8232,34 @@
         <v>18</v>
       </c>
       <c r="N186" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O186" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P186" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q186" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R186" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S186" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B187" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C187" s="4"/>
       <c r="D187" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E187" s="4"/>
       <c r="F187" s="4" t="s">
@@ -7769,7 +8269,7 @@
         <v>7</v>
       </c>
       <c r="H187" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I187" s="4"/>
       <c r="J187" s="5" t="s">
@@ -7788,17 +8288,27 @@
       <c r="O187" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P187" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q187" s="12">
+        <v>8</v>
+      </c>
+      <c r="R187" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S187" s="12"/>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B188" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C188" s="4"/>
       <c r="D188" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="4" t="s">
@@ -7808,7 +8318,7 @@
         <v>7</v>
       </c>
       <c r="H188" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I188" s="4"/>
       <c r="J188" s="5" t="s">
@@ -7827,17 +8337,27 @@
       <c r="O188" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P188" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q188" s="12">
+        <v>8</v>
+      </c>
+      <c r="R188" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S188" s="12"/>
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B189" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C189" s="4"/>
       <c r="D189" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="4" t="s">
@@ -7847,11 +8367,11 @@
         <v>7</v>
       </c>
       <c r="H189" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I189" s="4"/>
       <c r="J189" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K189" s="4"/>
       <c r="L189" s="4" t="s">
@@ -7866,17 +8386,25 @@
       <c r="O189" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P189" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q189" s="12"/>
+      <c r="R189" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S189" s="12"/>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B190" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C190" s="4"/>
       <c r="D190" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="23" t="s">
@@ -7886,11 +8414,11 @@
         <v>7</v>
       </c>
       <c r="H190" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I190" s="4"/>
       <c r="J190" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K190" s="4"/>
       <c r="L190" s="4" t="s">
@@ -7905,17 +8433,25 @@
       <c r="O190" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="191" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P190" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q190" s="12"/>
+      <c r="R190" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S190" s="12"/>
+    </row>
+    <row r="191" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B191" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C191" s="23"/>
       <c r="D191" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E191" s="23"/>
       <c r="F191" s="23" t="s">
@@ -7925,7 +8461,7 @@
         <v>7</v>
       </c>
       <c r="H191" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I191" s="23"/>
       <c r="J191" s="23" t="s">
@@ -7944,8 +8480,16 @@
       <c r="O191" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P191" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q191" s="24"/>
+      <c r="R191" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S191" s="24"/>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" s="47" t="s">
         <v>40</v>
       </c>
@@ -7979,13 +8523,23 @@
         <f>SUM(M187:M191)</f>
         <v>40</v>
       </c>
-      <c r="N192" s="61"/>
+      <c r="N192" s="60"/>
       <c r="O192" s="45">
         <f>SUM(O187:O191)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P192" s="60"/>
+      <c r="Q192" s="45">
+        <f>SUM(Q187:Q191)</f>
+        <v>16</v>
+      </c>
+      <c r="R192" s="60"/>
+      <c r="S192" s="45">
+        <f>SUM(S187:S191)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" s="38" t="s">
         <v>41</v>
       </c>
@@ -8013,12 +8567,20 @@
       <c r="M193" s="40">
         <v>0</v>
       </c>
-      <c r="N193" s="62"/>
+      <c r="N193" s="61"/>
       <c r="O193" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P193" s="61"/>
+      <c r="Q193" s="40">
+        <v>0</v>
+      </c>
+      <c r="R193" s="61"/>
+      <c r="S193" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="41" t="s">
         <v>42</v>
       </c>
@@ -8028,11 +8590,11 @@
       </c>
       <c r="D194" s="42"/>
       <c r="E194" s="42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F194" s="42"/>
       <c r="G194" s="42">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H194" s="42"/>
       <c r="I194" s="42">
@@ -8046,18 +8608,26 @@
       <c r="M194" s="43">
         <v>10</v>
       </c>
-      <c r="N194" s="63"/>
+      <c r="N194" s="62"/>
       <c r="O194" s="43">
         <v>0</v>
       </c>
-      <c r="P194" s="46"/>
-    </row>
-    <row r="195" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P194" s="62"/>
+      <c r="Q194" s="43">
+        <v>0</v>
+      </c>
+      <c r="R194" s="62"/>
+      <c r="S194" s="43">
+        <v>0</v>
+      </c>
+      <c r="T194" s="46"/>
+    </row>
+    <row r="195" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C196" s="8" t="s">
@@ -8094,24 +8664,34 @@
         <v>18</v>
       </c>
       <c r="N196" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O196" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P196" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q196" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R196" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S196" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B197" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C197" s="4">
-        <v>8</v>
-      </c>
+      <c r="B197" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C197" s="4"/>
       <c r="D197" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="4" t="s">
@@ -8121,11 +8701,11 @@
         <v>7</v>
       </c>
       <c r="H197" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I197" s="4"/>
       <c r="J197" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K197" s="4"/>
       <c r="L197" s="4" t="s">
@@ -8140,8 +8720,18 @@
       <c r="O197" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P197" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q197" s="12">
+        <v>8</v>
+      </c>
+      <c r="R197" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S197" s="12"/>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
         <v>8</v>
       </c>
@@ -8152,7 +8742,7 @@
         <v>8</v>
       </c>
       <c r="D198" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="4" t="s">
@@ -8162,18 +8752,18 @@
         <v>7</v>
       </c>
       <c r="H198" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I198" s="4"/>
       <c r="J198" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K198" s="4"/>
       <c r="L198" s="4" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="M198" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N198" s="4" t="s">
         <v>12</v>
@@ -8181,8 +8771,18 @@
       <c r="O198" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P198" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q198" s="12">
+        <v>8</v>
+      </c>
+      <c r="R198" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S198" s="12"/>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
         <v>9</v>
       </c>
@@ -8193,7 +8793,7 @@
         <v>8</v>
       </c>
       <c r="D199" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="4" t="s">
@@ -8203,11 +8803,11 @@
         <v>7</v>
       </c>
       <c r="H199" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I199" s="4"/>
       <c r="J199" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K199" s="4"/>
       <c r="L199" s="5" t="s">
@@ -8220,8 +8820,16 @@
       <c r="O199" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P199" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q199" s="12"/>
+      <c r="R199" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S199" s="12"/>
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
         <v>10</v>
       </c>
@@ -8232,7 +8840,7 @@
         <v>8</v>
       </c>
       <c r="D200" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="23" t="s">
@@ -8242,15 +8850,15 @@
         <v>7</v>
       </c>
       <c r="H200" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I200" s="4"/>
       <c r="J200" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K200" s="4"/>
       <c r="L200" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M200" s="12"/>
       <c r="N200" s="4" t="s">
@@ -8259,8 +8867,16 @@
       <c r="O200" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="201" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P200" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q200" s="12"/>
+      <c r="R200" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S200" s="12"/>
+    </row>
+    <row r="201" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="22" t="s">
         <v>11</v>
       </c>
@@ -8271,7 +8887,7 @@
         <v>8</v>
       </c>
       <c r="D201" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E201" s="23"/>
       <c r="F201" s="23" t="s">
@@ -8281,7 +8897,7 @@
         <v>7</v>
       </c>
       <c r="H201" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I201" s="23"/>
       <c r="J201" s="23" t="s">
@@ -8289,7 +8905,7 @@
       </c>
       <c r="K201" s="23"/>
       <c r="L201" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M201" s="24"/>
       <c r="N201" s="23" t="s">
@@ -8298,15 +8914,23 @@
       <c r="O201" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P201" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q201" s="24"/>
+      <c r="R201" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S201" s="24"/>
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202" s="47" t="s">
         <v>40</v>
       </c>
       <c r="B202" s="44"/>
       <c r="C202" s="44">
         <f>SUM(C197:C201)</f>
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D202" s="44"/>
       <c r="E202" s="44">
@@ -8331,21 +8955,31 @@
       <c r="L202" s="44"/>
       <c r="M202" s="45">
         <f>SUM(M197:M201)</f>
-        <v>16</v>
-      </c>
-      <c r="N202" s="61"/>
+        <v>14</v>
+      </c>
+      <c r="N202" s="60"/>
       <c r="O202" s="45">
         <f>SUM(O197:O201)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P202" s="60"/>
+      <c r="Q202" s="45">
+        <f>SUM(Q197:Q201)</f>
+        <v>16</v>
+      </c>
+      <c r="R202" s="60"/>
+      <c r="S202" s="45">
+        <f>SUM(S197:S201)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203" s="38" t="s">
         <v>41</v>
       </c>
       <c r="B203" s="39"/>
       <c r="C203" s="39">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="D203" s="39"/>
       <c r="E203" s="39">
@@ -8365,28 +8999,36 @@
       </c>
       <c r="L203" s="39"/>
       <c r="M203" s="40">
-        <v>-8</v>
-      </c>
-      <c r="N203" s="62"/>
+        <v>-10</v>
+      </c>
+      <c r="N203" s="61"/>
       <c r="O203" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P203" s="61"/>
+      <c r="Q203" s="40">
+        <v>0</v>
+      </c>
+      <c r="R203" s="61"/>
+      <c r="S203" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B204" s="42"/>
       <c r="C204" s="42">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D204" s="42"/>
       <c r="E204" s="42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F204" s="42"/>
       <c r="G204" s="42">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H204" s="42"/>
       <c r="I204" s="42">
@@ -8398,16 +9040,24 @@
       </c>
       <c r="L204" s="42"/>
       <c r="M204" s="43">
-        <v>2</v>
-      </c>
-      <c r="N204" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="N204" s="62"/>
       <c r="O204" s="43">
         <v>0</v>
       </c>
-      <c r="P204" s="46"/>
-    </row>
-    <row r="205" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P204" s="62"/>
+      <c r="Q204" s="43">
+        <v>0</v>
+      </c>
+      <c r="R204" s="62"/>
+      <c r="S204" s="43">
+        <v>0</v>
+      </c>
+      <c r="T204" s="46"/>
+    </row>
+    <row r="205" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
         <v>54</v>
       </c>
@@ -8448,13 +9098,25 @@
         <v>18</v>
       </c>
       <c r="N206" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O206" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P206" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q206" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R206" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S206" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
         <v>7</v>
       </c>
@@ -8465,7 +9127,7 @@
         <v>8</v>
       </c>
       <c r="D207" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
@@ -8481,11 +9143,11 @@
         <v>8</v>
       </c>
       <c r="J207" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K207" s="4"/>
       <c r="L207" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M207" s="12"/>
       <c r="N207" s="4" t="s">
@@ -8494,8 +9156,18 @@
       <c r="O207" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P207" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q207" s="12">
+        <v>8</v>
+      </c>
+      <c r="R207" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S207" s="12"/>
+    </row>
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>8</v>
       </c>
@@ -8506,7 +9178,7 @@
         <v>8</v>
       </c>
       <c r="D208" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
@@ -8522,11 +9194,11 @@
         <v>8</v>
       </c>
       <c r="J208" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K208" s="4"/>
       <c r="L208" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M208" s="12"/>
       <c r="N208" s="4" t="s">
@@ -8535,8 +9207,18 @@
       <c r="O208" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P208" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q208" s="12">
+        <v>8</v>
+      </c>
+      <c r="R208" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S208" s="12"/>
+    </row>
+    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>9</v>
       </c>
@@ -8547,7 +9229,7 @@
         <v>8</v>
       </c>
       <c r="D209" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
@@ -8563,11 +9245,11 @@
         <v>8</v>
       </c>
       <c r="J209" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K209" s="4"/>
       <c r="L209" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M209" s="12"/>
       <c r="N209" s="4" t="s">
@@ -8576,8 +9258,16 @@
       <c r="O209" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P209" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q209" s="12"/>
+      <c r="R209" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S209" s="12"/>
+    </row>
+    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
         <v>10</v>
       </c>
@@ -8588,7 +9278,7 @@
         <v>8</v>
       </c>
       <c r="D210" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="23" t="s">
@@ -8604,11 +9294,11 @@
         <v>8</v>
       </c>
       <c r="J210" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K210" s="4"/>
       <c r="L210" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M210" s="12"/>
       <c r="N210" s="4" t="s">
@@ -8617,19 +9307,27 @@
       <c r="O210" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="211" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P210" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q210" s="12"/>
+      <c r="R210" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S210" s="12"/>
+    </row>
+    <row r="211" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C211" s="23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D211" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E211" s="23"/>
       <c r="F211" s="23" t="s">
@@ -8649,7 +9347,7 @@
       </c>
       <c r="K211" s="23"/>
       <c r="L211" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M211" s="24"/>
       <c r="N211" s="4" t="s">
@@ -8658,15 +9356,23 @@
       <c r="O211" s="15">
         <v>8</v>
       </c>
-    </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P211" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q211" s="24"/>
+      <c r="R211" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S211" s="24"/>
+    </row>
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212" s="47" t="s">
         <v>40</v>
       </c>
       <c r="B212" s="44"/>
       <c r="C212" s="44">
         <f>SUM(C207:C211)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D212" s="44"/>
       <c r="E212" s="44">
@@ -8698,14 +9404,24 @@
         <f>SUM(O207:O211)</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P212" s="60"/>
+      <c r="Q212" s="45">
+        <f>SUM(Q207:Q211)</f>
+        <v>16</v>
+      </c>
+      <c r="R212" s="60"/>
+      <c r="S212" s="45">
+        <f>SUM(S207:S211)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213" s="38" t="s">
         <v>41</v>
       </c>
       <c r="B213" s="39"/>
       <c r="C213" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D213" s="39"/>
       <c r="E213" s="39">
@@ -8731,8 +9447,16 @@
       <c r="O213" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P213" s="61"/>
+      <c r="Q213" s="40">
+        <v>0</v>
+      </c>
+      <c r="R213" s="61"/>
+      <c r="S213" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="41" t="s">
         <v>42</v>
       </c>
@@ -8742,11 +9466,11 @@
       </c>
       <c r="D214" s="42"/>
       <c r="E214" s="42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F214" s="42"/>
       <c r="G214" s="42">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H214" s="42"/>
       <c r="I214" s="42">
@@ -8754,7 +9478,7 @@
       </c>
       <c r="J214" s="42"/>
       <c r="K214" s="42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L214" s="42"/>
       <c r="M214" s="43">
@@ -8764,10 +9488,18 @@
       <c r="O214" s="43">
         <v>0</v>
       </c>
-      <c r="P214" s="64"/>
-    </row>
-    <row r="215" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P214" s="62"/>
+      <c r="Q214" s="43">
+        <v>0</v>
+      </c>
+      <c r="R214" s="62"/>
+      <c r="S214" s="43">
+        <v>0</v>
+      </c>
+      <c r="T214" s="46"/>
+    </row>
+    <row r="215" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>55</v>
       </c>
@@ -8808,13 +9540,25 @@
         <v>18</v>
       </c>
       <c r="N216" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O216" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P216" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q216" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R216" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S216" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
         <v>7</v>
       </c>
@@ -8843,11 +9587,11 @@
         <v>8</v>
       </c>
       <c r="J217" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K217" s="4"/>
       <c r="L217" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M217" s="12"/>
       <c r="N217" s="4" t="s">
@@ -8856,8 +9600,20 @@
       <c r="O217" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P217" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q217" s="12">
+        <v>8</v>
+      </c>
+      <c r="R217" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="S217" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
         <v>8</v>
       </c>
@@ -8886,11 +9642,11 @@
         <v>8</v>
       </c>
       <c r="J218" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K218" s="4"/>
       <c r="L218" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M218" s="12"/>
       <c r="N218" s="4" t="s">
@@ -8899,8 +9655,18 @@
       <c r="O218" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P218" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q218" s="12">
+        <v>8</v>
+      </c>
+      <c r="R218" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S218" s="12"/>
+    </row>
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>9</v>
       </c>
@@ -8929,11 +9695,11 @@
         <v>8</v>
       </c>
       <c r="J219" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K219" s="4"/>
       <c r="L219" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M219" s="12"/>
       <c r="N219" s="4" t="s">
@@ -8942,8 +9708,16 @@
       <c r="O219" s="12">
         <v>8</v>
       </c>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P219" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q219" s="12"/>
+      <c r="R219" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S219" s="12"/>
+    </row>
+    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>10</v>
       </c>
@@ -8972,29 +9746,35 @@
         <v>8</v>
       </c>
       <c r="J220" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K220" s="4"/>
       <c r="L220" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M220" s="12"/>
       <c r="N220" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O220" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="221" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="O220" s="12"/>
+      <c r="P220" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q220" s="12"/>
+      <c r="R220" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S220" s="12"/>
+    </row>
+    <row r="221" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C221" s="23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>12</v>
@@ -9019,7 +9799,7 @@
       </c>
       <c r="K221" s="23"/>
       <c r="L221" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M221" s="24"/>
       <c r="N221" s="23" t="s">
@@ -9028,15 +9808,23 @@
       <c r="O221" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P221" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q221" s="24"/>
+      <c r="R221" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S221" s="24"/>
+    </row>
+    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222" s="47" t="s">
         <v>40</v>
       </c>
       <c r="B222" s="44"/>
       <c r="C222" s="44">
         <f>SUM(C217:C221)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D222" s="44"/>
       <c r="E222" s="44">
@@ -9063,19 +9851,29 @@
         <f>SUM(M217:M221)</f>
         <v>0</v>
       </c>
-      <c r="N222" s="61"/>
+      <c r="N222" s="60"/>
       <c r="O222" s="45">
         <f>SUM(O217:O221)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="P222" s="60"/>
+      <c r="Q222" s="45">
+        <f>SUM(Q217:Q221)</f>
+        <v>16</v>
+      </c>
+      <c r="R222" s="60"/>
+      <c r="S222" s="45">
+        <f>SUM(S217:S221)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A223" s="38" t="s">
         <v>41</v>
       </c>
       <c r="B223" s="39"/>
       <c r="C223" s="39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D223" s="39"/>
       <c r="E223" s="39">
@@ -9097,26 +9895,34 @@
       <c r="M223" s="40">
         <v>0</v>
       </c>
-      <c r="N223" s="62"/>
+      <c r="N223" s="61"/>
       <c r="O223" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P223" s="61"/>
+      <c r="Q223" s="40">
+        <v>0</v>
+      </c>
+      <c r="R223" s="61"/>
+      <c r="S223" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B224" s="42"/>
       <c r="C224" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D224" s="42"/>
       <c r="E224" s="42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F224" s="42"/>
       <c r="G224" s="42">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H224" s="42"/>
       <c r="I224" s="42">
@@ -9130,14 +9936,22 @@
       <c r="M224" s="43">
         <v>0</v>
       </c>
-      <c r="N224" s="63"/>
+      <c r="N224" s="62"/>
       <c r="O224" s="43">
         <v>0</v>
       </c>
-      <c r="P224" s="64"/>
-    </row>
-    <row r="225" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P224" s="62"/>
+      <c r="Q224" s="43">
+        <v>0</v>
+      </c>
+      <c r="R224" s="62"/>
+      <c r="S224" s="43">
+        <v>0</v>
+      </c>
+      <c r="T224" s="46"/>
+    </row>
+    <row r="225" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>56</v>
       </c>
@@ -9178,13 +9992,25 @@
         <v>18</v>
       </c>
       <c r="N226" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O226" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P226" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q226" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R226" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S226" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>7</v>
       </c>
@@ -9201,10 +10027,10 @@
         <v>10</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G227" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>29</v>
@@ -9219,7 +10045,7 @@
         <v>10</v>
       </c>
       <c r="L227" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M227" s="12"/>
       <c r="N227" s="4" t="s">
@@ -9228,8 +10054,20 @@
       <c r="O227" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P227" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q227" s="12">
+        <v>10</v>
+      </c>
+      <c r="R227" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S227" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
         <v>8</v>
       </c>
@@ -9246,10 +10084,10 @@
         <v>9</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G228" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H228" s="4" t="s">
         <v>30</v>
@@ -9264,7 +10102,7 @@
         <v>9</v>
       </c>
       <c r="L228" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M228" s="12"/>
       <c r="N228" s="4" t="s">
@@ -9273,8 +10111,18 @@
       <c r="O228" s="12">
         <v>9</v>
       </c>
-    </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P228" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q228" s="12">
+        <v>9</v>
+      </c>
+      <c r="R228" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S228" s="12"/>
+    </row>
+    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
         <v>9</v>
       </c>
@@ -9291,10 +10139,10 @@
         <v>8</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G229" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>12</v>
@@ -9309,35 +10157,43 @@
         <v>8</v>
       </c>
       <c r="L229" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M229" s="12"/>
       <c r="N229" s="23" t="s">
         <v>13</v>
       </c>
       <c r="O229" s="12"/>
-    </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P229" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q229" s="12"/>
+      <c r="R229" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S229" s="12"/>
+    </row>
+    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C230" s="4">
-        <v>6</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E230" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G230" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>12</v>
@@ -9352,36 +10208,42 @@
         <v>8</v>
       </c>
       <c r="L230" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M230" s="12"/>
       <c r="N230" s="23" t="s">
         <v>13</v>
       </c>
       <c r="O230" s="12"/>
-    </row>
-    <row r="231" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P230" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q230" s="12"/>
+      <c r="R230" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S230" s="12"/>
+    </row>
+    <row r="231" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B231" s="23" t="s">
-        <v>16</v>
+      <c r="B231" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C231" s="23">
-        <v>7</v>
-      </c>
-      <c r="D231" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D231" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E231" s="23">
         <v>8</v>
       </c>
-      <c r="F231" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G231" s="23">
-        <v>5</v>
-      </c>
+      <c r="F231" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G231" s="23"/>
       <c r="H231" s="23" t="s">
         <v>12</v>
       </c>
@@ -9393,32 +10255,40 @@
       </c>
       <c r="K231" s="23"/>
       <c r="L231" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M231" s="24"/>
       <c r="N231" s="23" t="s">
         <v>13</v>
       </c>
       <c r="O231" s="24"/>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P231" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q231" s="24"/>
+      <c r="R231" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S231" s="24"/>
+    </row>
+    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A232" s="47" t="s">
         <v>40</v>
       </c>
       <c r="B232" s="44"/>
       <c r="C232" s="44">
         <f>SUM(C227:C231)</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D232" s="44"/>
       <c r="E232" s="44">
         <f>SUM(E227:E231)</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F232" s="44"/>
       <c r="G232" s="44">
         <f>SUM(G227:G231)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H232" s="44"/>
       <c r="I232" s="44">
@@ -9435,27 +10305,37 @@
         <f>SUM(M227:M231)</f>
         <v>0</v>
       </c>
-      <c r="N232" s="61"/>
+      <c r="N232" s="60"/>
       <c r="O232" s="45">
         <f>SUM(O227:O231)</f>
         <v>19</v>
       </c>
-    </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P232" s="60"/>
+      <c r="Q232" s="45">
+        <f>SUM(Q227:Q231)</f>
+        <v>19</v>
+      </c>
+      <c r="R232" s="60"/>
+      <c r="S232" s="45">
+        <f>SUM(S227:S231)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A233" s="38" t="s">
         <v>41</v>
       </c>
       <c r="B233" s="39"/>
       <c r="C233" s="39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D233" s="39"/>
       <c r="E233" s="39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F233" s="39"/>
       <c r="G233" s="39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" s="39"/>
       <c r="I233" s="39">
@@ -9469,26 +10349,34 @@
       <c r="M233" s="40">
         <v>0</v>
       </c>
-      <c r="N233" s="62"/>
+      <c r="N233" s="61"/>
       <c r="O233" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P233" s="61"/>
+      <c r="Q233" s="40">
+        <v>0</v>
+      </c>
+      <c r="R233" s="61"/>
+      <c r="S233" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B234" s="42"/>
       <c r="C234" s="42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D234" s="42"/>
       <c r="E234" s="42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F234" s="42"/>
       <c r="G234" s="42">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H234" s="42"/>
       <c r="I234" s="42">
@@ -9502,14 +10390,22 @@
       <c r="M234" s="43">
         <v>0</v>
       </c>
-      <c r="N234" s="63"/>
+      <c r="N234" s="62"/>
       <c r="O234" s="43">
         <v>0</v>
       </c>
-      <c r="P234" s="64"/>
-    </row>
-    <row r="235" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P234" s="62"/>
+      <c r="Q234" s="43">
+        <v>0</v>
+      </c>
+      <c r="R234" s="62"/>
+      <c r="S234" s="43">
+        <v>0</v>
+      </c>
+      <c r="T234" s="46"/>
+    </row>
+    <row r="235" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
         <v>57</v>
       </c>
@@ -9550,13 +10446,25 @@
         <v>18</v>
       </c>
       <c r="N236" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O236" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P236" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q236" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R236" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S236" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A237" s="11" t="s">
         <v>7</v>
       </c>
@@ -9573,10 +10481,10 @@
         <v>10</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G237" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>29</v>
@@ -9602,70 +10510,90 @@
       <c r="O237" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P237" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q237" s="12">
+        <v>10</v>
+      </c>
+      <c r="R237" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S237" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C238" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E238" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G238" s="4">
         <v>8</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I238" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K238" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L238" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M238" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N238" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O238" s="12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="P238" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q238" s="12">
+        <v>8</v>
+      </c>
+      <c r="R238" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S238" s="12"/>
+    </row>
+    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C239" s="4">
-        <v>8</v>
-      </c>
-      <c r="D239" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E239" s="4">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E239" s="4"/>
       <c r="F239" s="4" t="s">
         <v>16</v>
       </c>
@@ -9685,7 +10613,7 @@
         <v>8</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="M239" s="12">
         <v>8</v>
@@ -9694,40 +10622,50 @@
         <v>13</v>
       </c>
       <c r="O239" s="12"/>
-    </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P239" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q239" s="12">
+        <v>8</v>
+      </c>
+      <c r="R239" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S239" s="12"/>
+    </row>
+    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C240" s="4">
+        <v>8</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E240" s="4">
+        <v>8</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G240" s="4">
+        <v>7</v>
+      </c>
+      <c r="H240" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I240" s="4">
+        <v>8</v>
+      </c>
+      <c r="J240" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K240" s="4">
         <v>6</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E240" s="4">
-        <v>4</v>
-      </c>
-      <c r="F240" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G240" s="4">
-        <v>5</v>
-      </c>
-      <c r="H240" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I240" s="4">
-        <v>8</v>
-      </c>
-      <c r="J240" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K240" s="4">
-        <v>8</v>
       </c>
       <c r="L240" s="4" t="s">
         <v>14</v>
@@ -9739,24 +10677,32 @@
         <v>13</v>
       </c>
       <c r="O240" s="12"/>
-    </row>
-    <row r="241" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P240" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q240" s="12"/>
+      <c r="R240" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S240" s="12"/>
+    </row>
+    <row r="241" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B241" s="23" t="s">
-        <v>16</v>
+      <c r="B241" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C241" s="23">
-        <v>7</v>
-      </c>
-      <c r="D241" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D241" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E241" s="23">
         <v>8</v>
       </c>
-      <c r="F241" s="23" t="s">
+      <c r="F241" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G241" s="23">
@@ -9773,15 +10719,25 @@
       </c>
       <c r="K241" s="23"/>
       <c r="L241" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="M241" s="24"/>
+        <v>14</v>
+      </c>
+      <c r="M241" s="24">
+        <v>7</v>
+      </c>
       <c r="N241" s="23" t="s">
         <v>13</v>
       </c>
       <c r="O241" s="24"/>
-    </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P241" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q241" s="24"/>
+      <c r="R241" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S241" s="24"/>
+    </row>
+    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A242" s="47" t="s">
         <v>40</v>
       </c>
@@ -9793,35 +10749,45 @@
       <c r="D242" s="44"/>
       <c r="E242" s="44">
         <f>SUM(E237:E241)</f>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F242" s="44"/>
       <c r="G242" s="44">
         <f>SUM(G237:G241)</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H242" s="44"/>
       <c r="I242" s="44">
         <f>SUM(I237:I241)</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J242" s="44"/>
       <c r="K242" s="44">
         <f>SUM(K237:K241)</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L242" s="44"/>
       <c r="M242" s="45">
         <f>SUM(M237:M241)</f>
-        <v>34</v>
-      </c>
-      <c r="N242" s="61"/>
+        <v>40</v>
+      </c>
+      <c r="N242" s="60"/>
       <c r="O242" s="45">
         <f>SUM(O237:O241)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="P242" s="60"/>
+      <c r="Q242" s="45">
+        <f>SUM(Q237:Q241)</f>
+        <v>26</v>
+      </c>
+      <c r="R242" s="60"/>
+      <c r="S242" s="45">
+        <f>SUM(S237:S241)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A243" s="38" t="s">
         <v>41</v>
       </c>
@@ -9831,65 +10797,81 @@
       </c>
       <c r="D243" s="39"/>
       <c r="E243" s="39">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="F243" s="39"/>
       <c r="G243" s="39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H243" s="39"/>
       <c r="I243" s="39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J243" s="39"/>
       <c r="K243" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L243" s="39"/>
       <c r="M243" s="40">
-        <v>-6</v>
-      </c>
-      <c r="N243" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="N243" s="61"/>
       <c r="O243" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P243" s="61"/>
+      <c r="Q243" s="40">
+        <v>0</v>
+      </c>
+      <c r="R243" s="61"/>
+      <c r="S243" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B244" s="42"/>
       <c r="C244" s="42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D244" s="42"/>
       <c r="E244" s="42">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F244" s="42"/>
       <c r="G244" s="42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H244" s="42"/>
       <c r="I244" s="42">
-        <v>28</v>
+        <v>-1</v>
       </c>
       <c r="J244" s="42"/>
       <c r="K244" s="42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L244" s="42"/>
       <c r="M244" s="43">
-        <v>3</v>
-      </c>
-      <c r="N244" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="N244" s="62"/>
       <c r="O244" s="43">
         <v>0</v>
       </c>
-      <c r="P244" s="64"/>
-    </row>
-    <row r="245" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P244" s="62"/>
+      <c r="Q244" s="43">
+        <v>0</v>
+      </c>
+      <c r="R244" s="62"/>
+      <c r="S244" s="43">
+        <v>0</v>
+      </c>
+      <c r="T244" s="46"/>
+    </row>
+    <row r="245" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
         <v>58</v>
       </c>
@@ -9930,13 +10912,25 @@
         <v>18</v>
       </c>
       <c r="N246" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O246" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P246" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q246" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R246" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S246" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A247" s="11" t="s">
         <v>7</v>
       </c>
@@ -9953,10 +10947,10 @@
         <v>10</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G247" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>29</v>
@@ -9982,63 +10976,85 @@
       <c r="O247" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q247" s="12">
+        <v>10</v>
+      </c>
+      <c r="R247" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S247" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C248" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E248" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G248" s="4">
         <v>8</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I248" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K248" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L248" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M248" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N248" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O248" s="12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="P248" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q248" s="12">
+        <v>8</v>
+      </c>
+      <c r="R248" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S248" s="12"/>
+    </row>
+    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C249" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D249" s="4" t="s">
         <v>12</v>
@@ -10065,7 +11081,7 @@
         <v>8</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="M249" s="12">
         <v>8</v>
@@ -10074,40 +11090,48 @@
         <v>13</v>
       </c>
       <c r="O249" s="12"/>
-    </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P249" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q249" s="12"/>
+      <c r="R249" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S249" s="12"/>
+    </row>
+    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C250" s="4">
+        <v>8</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E250" s="4">
+        <v>8</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G250" s="4">
+        <v>7</v>
+      </c>
+      <c r="H250" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I250" s="4">
+        <v>8</v>
+      </c>
+      <c r="J250" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K250" s="4">
         <v>6</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E250" s="4">
-        <v>4</v>
-      </c>
-      <c r="F250" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G250" s="4">
-        <v>5</v>
-      </c>
-      <c r="H250" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I250" s="4">
-        <v>8</v>
-      </c>
-      <c r="J250" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K250" s="4">
-        <v>8</v>
       </c>
       <c r="L250" s="4" t="s">
         <v>14</v>
@@ -10119,28 +11143,36 @@
         <v>13</v>
       </c>
       <c r="O250" s="12"/>
-    </row>
-    <row r="251" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P250" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q250" s="12"/>
+      <c r="R250" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S250" s="12"/>
+    </row>
+    <row r="251" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B251" s="23" t="s">
+      <c r="B251" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C251" s="23">
+        <v>8</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E251" s="23">
+        <v>8</v>
+      </c>
+      <c r="F251" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C251" s="23">
-        <v>7</v>
-      </c>
-      <c r="D251" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E251" s="23">
-        <v>8</v>
-      </c>
-      <c r="F251" s="23" t="s">
-        <v>21</v>
-      </c>
       <c r="G251" s="23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H251" s="23" t="s">
         <v>12</v>
@@ -10153,15 +11185,25 @@
       </c>
       <c r="K251" s="23"/>
       <c r="L251" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="M251" s="24"/>
+        <v>14</v>
+      </c>
+      <c r="M251" s="24">
+        <v>7</v>
+      </c>
       <c r="N251" s="23" t="s">
         <v>13</v>
       </c>
       <c r="O251" s="24"/>
-    </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P251" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q251" s="24"/>
+      <c r="R251" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S251" s="24"/>
+    </row>
+    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A252" s="47" t="s">
         <v>40</v>
       </c>
@@ -10173,35 +11215,45 @@
       <c r="D252" s="44"/>
       <c r="E252" s="44">
         <f>SUM(E247:E251)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F252" s="44"/>
       <c r="G252" s="44">
         <f>SUM(G247:G251)</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H252" s="44"/>
       <c r="I252" s="44">
         <f>SUM(I247:I251)</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J252" s="44"/>
       <c r="K252" s="44">
         <f>SUM(K247:K251)</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L252" s="44"/>
       <c r="M252" s="45">
         <f>SUM(M247:M251)</f>
-        <v>34</v>
-      </c>
-      <c r="N252" s="61"/>
+        <v>40</v>
+      </c>
+      <c r="N252" s="60"/>
       <c r="O252" s="45">
         <f>SUM(O247:O251)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="P252" s="60"/>
+      <c r="Q252" s="45">
+        <f>SUM(Q247:Q251)</f>
+        <v>18</v>
+      </c>
+      <c r="R252" s="60"/>
+      <c r="S252" s="45">
+        <f>SUM(S247:S251)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A253" s="38" t="s">
         <v>41</v>
       </c>
@@ -10211,65 +11263,81 @@
       </c>
       <c r="D253" s="39"/>
       <c r="E253" s="39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F253" s="39"/>
       <c r="G253" s="39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H253" s="39"/>
       <c r="I253" s="39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J253" s="39"/>
       <c r="K253" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L253" s="39"/>
       <c r="M253" s="40">
-        <v>-6</v>
-      </c>
-      <c r="N253" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="N253" s="61"/>
       <c r="O253" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="254" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P253" s="61"/>
+      <c r="Q253" s="40">
+        <v>0</v>
+      </c>
+      <c r="R253" s="61"/>
+      <c r="S253" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B254" s="42"/>
       <c r="C254" s="42">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D254" s="42"/>
       <c r="E254" s="42">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F254" s="42"/>
       <c r="G254" s="42">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H254" s="42"/>
       <c r="I254" s="42">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J254" s="42"/>
       <c r="K254" s="42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L254" s="42"/>
       <c r="M254" s="43">
-        <v>3</v>
-      </c>
-      <c r="N254" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="N254" s="62"/>
       <c r="O254" s="43">
         <v>0</v>
       </c>
-      <c r="P254" s="64"/>
-    </row>
-    <row r="255" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P254" s="62"/>
+      <c r="Q254" s="43">
+        <v>0</v>
+      </c>
+      <c r="R254" s="62"/>
+      <c r="S254" s="43">
+        <v>0</v>
+      </c>
+      <c r="T254" s="46"/>
+    </row>
+    <row r="255" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
         <v>59</v>
       </c>
@@ -10310,13 +11378,25 @@
         <v>18</v>
       </c>
       <c r="N256" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O256" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P256" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q256" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R256" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S256" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>7</v>
       </c>
@@ -10333,10 +11413,10 @@
         <v>10</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G257" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H257" s="4" t="s">
         <v>29</v>
@@ -10362,63 +11442,85 @@
       <c r="O257" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P257" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q257" s="12">
+        <v>10</v>
+      </c>
+      <c r="R257" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S257" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C258" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E258" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G258" s="4">
         <v>8</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I258" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J258" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K258" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L258" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M258" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N258" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O258" s="12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="P258" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q258" s="12">
+        <v>8</v>
+      </c>
+      <c r="R258" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S258" s="12"/>
+    </row>
+    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A259" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C259" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D259" s="4" t="s">
         <v>12</v>
@@ -10445,7 +11547,7 @@
         <v>8</v>
       </c>
       <c r="L259" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="M259" s="12">
         <v>8</v>
@@ -10454,40 +11556,46 @@
         <v>13</v>
       </c>
       <c r="O259" s="12"/>
-    </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P259" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q259" s="12"/>
+      <c r="R259" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S259" s="12"/>
+    </row>
+    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C260" s="4">
+        <v>8</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E260" s="4">
+        <v>8</v>
+      </c>
+      <c r="F260" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G260" s="4"/>
+      <c r="H260" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I260" s="4">
+        <v>8</v>
+      </c>
+      <c r="J260" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K260" s="4">
         <v>6</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E260" s="4">
-        <v>4</v>
-      </c>
-      <c r="F260" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G260" s="4">
-        <v>5</v>
-      </c>
-      <c r="H260" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I260" s="4">
-        <v>8</v>
-      </c>
-      <c r="J260" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K260" s="4">
-        <v>8</v>
       </c>
       <c r="L260" s="4" t="s">
         <v>14</v>
@@ -10496,30 +11604,40 @@
         <v>7</v>
       </c>
       <c r="N260" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="O260" s="12"/>
-    </row>
-    <row r="261" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="O260" s="12">
+        <v>8</v>
+      </c>
+      <c r="P260" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q260" s="12"/>
+      <c r="R260" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S260" s="12"/>
+    </row>
+    <row r="261" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B261" s="23" t="s">
+      <c r="B261" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C261" s="23">
+        <v>8</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E261" s="23">
+        <v>8</v>
+      </c>
+      <c r="F261" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C261" s="23">
-        <v>7</v>
-      </c>
-      <c r="D261" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E261" s="23">
-        <v>8</v>
-      </c>
-      <c r="F261" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="G261" s="23">
+      <c r="G261" s="4">
         <v>7</v>
       </c>
       <c r="H261" s="23" t="s">
@@ -10533,15 +11651,25 @@
       </c>
       <c r="K261" s="23"/>
       <c r="L261" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="M261" s="24"/>
+        <v>14</v>
+      </c>
+      <c r="M261" s="24">
+        <v>7</v>
+      </c>
       <c r="N261" s="23" t="s">
         <v>13</v>
       </c>
       <c r="O261" s="24"/>
-    </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P261" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q261" s="24"/>
+      <c r="R261" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S261" s="24"/>
+    </row>
+    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A262" s="47" t="s">
         <v>40</v>
       </c>
@@ -10553,35 +11681,45 @@
       <c r="D262" s="44"/>
       <c r="E262" s="44">
         <f>SUM(E257:E261)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F262" s="44"/>
       <c r="G262" s="44">
         <f>SUM(G257:G261)</f>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H262" s="44"/>
       <c r="I262" s="44">
         <f>SUM(I257:I261)</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J262" s="44"/>
       <c r="K262" s="44">
         <f>SUM(K257:K261)</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L262" s="44"/>
       <c r="M262" s="45">
         <f>SUM(M257:M261)</f>
-        <v>34</v>
-      </c>
-      <c r="N262" s="61"/>
+        <v>40</v>
+      </c>
+      <c r="N262" s="60"/>
       <c r="O262" s="45">
         <f>SUM(O257:O261)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="P262" s="60"/>
+      <c r="Q262" s="45">
+        <f>SUM(Q257:Q261)</f>
+        <v>18</v>
+      </c>
+      <c r="R262" s="60"/>
+      <c r="S262" s="45">
+        <f>SUM(S257:S261)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A263" s="38" t="s">
         <v>41</v>
       </c>
@@ -10591,67 +11729,83 @@
       </c>
       <c r="D263" s="39"/>
       <c r="E263" s="39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F263" s="39"/>
       <c r="G263" s="39">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H263" s="39"/>
       <c r="I263" s="39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J263" s="39"/>
       <c r="K263" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L263" s="39"/>
       <c r="M263" s="40">
-        <v>-6</v>
-      </c>
-      <c r="N263" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="N263" s="61"/>
       <c r="O263" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="264" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P263" s="61"/>
+      <c r="Q263" s="40">
+        <v>0</v>
+      </c>
+      <c r="R263" s="61"/>
+      <c r="S263" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B264" s="42"/>
       <c r="C264" s="42">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D264" s="42"/>
       <c r="E264" s="42">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F264" s="42"/>
       <c r="G264" s="42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H264" s="42"/>
       <c r="I264" s="42">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="J264" s="42"/>
       <c r="K264" s="42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L264" s="42"/>
       <c r="M264" s="43">
-        <v>3</v>
-      </c>
-      <c r="N264" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="N264" s="62"/>
       <c r="O264" s="43">
         <v>0</v>
       </c>
-      <c r="P264" s="64"/>
-    </row>
-    <row r="265" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P264" s="62"/>
+      <c r="Q264" s="43">
+        <v>0</v>
+      </c>
+      <c r="R264" s="62"/>
+      <c r="S264" s="43">
+        <v>0</v>
+      </c>
+      <c r="T264" s="63"/>
+    </row>
+    <row r="265" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B266" s="8" t="s">
         <v>2</v>
@@ -10690,13 +11844,25 @@
         <v>18</v>
       </c>
       <c r="N266" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O266" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P266" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q266" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R266" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S266" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
         <v>7</v>
       </c>
@@ -10713,10 +11879,10 @@
         <v>10</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G267" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H267" s="4" t="s">
         <v>29</v>
@@ -10742,63 +11908,85 @@
       <c r="O267" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P267" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q267" s="12">
+        <v>10</v>
+      </c>
+      <c r="R267" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S267" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C268" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E268" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G268" s="4">
         <v>8</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I268" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K268" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L268" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M268" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N268" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O268" s="12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="P268" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q268" s="12">
+        <v>8</v>
+      </c>
+      <c r="R268" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S268" s="12"/>
+    </row>
+    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A269" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C269" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>12</v>
@@ -10825,7 +12013,7 @@
         <v>8</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="M269" s="12">
         <v>8</v>
@@ -10834,40 +12022,46 @@
         <v>13</v>
       </c>
       <c r="O269" s="12"/>
-    </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P269" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q269" s="12"/>
+      <c r="R269" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S269" s="12"/>
+    </row>
+    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C270" s="4">
+        <v>8</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E270" s="4">
+        <v>8</v>
+      </c>
+      <c r="F270" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G270" s="4"/>
+      <c r="H270" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I270" s="4">
+        <v>8</v>
+      </c>
+      <c r="J270" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K270" s="4">
         <v>6</v>
-      </c>
-      <c r="D270" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E270" s="4">
-        <v>4</v>
-      </c>
-      <c r="F270" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G270" s="4">
-        <v>5</v>
-      </c>
-      <c r="H270" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I270" s="4">
-        <v>8</v>
-      </c>
-      <c r="J270" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K270" s="4">
-        <v>8</v>
       </c>
       <c r="L270" s="4" t="s">
         <v>14</v>
@@ -10879,28 +12073,38 @@
         <v>13</v>
       </c>
       <c r="O270" s="12"/>
-    </row>
-    <row r="271" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P270" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q270" s="12">
+        <v>8</v>
+      </c>
+      <c r="R270" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S270" s="12"/>
+    </row>
+    <row r="271" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B271" s="23" t="s">
+      <c r="B271" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C271" s="23">
+        <v>8</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E271" s="23">
+        <v>8</v>
+      </c>
+      <c r="F271" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C271" s="23">
-        <v>7</v>
-      </c>
-      <c r="D271" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E271" s="23">
-        <v>8</v>
-      </c>
-      <c r="F271" s="23" t="s">
-        <v>21</v>
-      </c>
       <c r="G271" s="23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H271" s="23" t="s">
         <v>12</v>
@@ -10913,15 +12117,25 @@
       </c>
       <c r="K271" s="23"/>
       <c r="L271" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="M271" s="24"/>
+        <v>14</v>
+      </c>
+      <c r="M271" s="24">
+        <v>7</v>
+      </c>
       <c r="N271" s="23" t="s">
         <v>13</v>
       </c>
       <c r="O271" s="24"/>
-    </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P271" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q271" s="24"/>
+      <c r="R271" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S271" s="24"/>
+    </row>
+    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A272" s="47" t="s">
         <v>40</v>
       </c>
@@ -10933,35 +12147,45 @@
       <c r="D272" s="44"/>
       <c r="E272" s="44">
         <f>SUM(E267:E271)</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F272" s="44"/>
       <c r="G272" s="44">
         <f>SUM(G267:G271)</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H272" s="44"/>
       <c r="I272" s="44">
         <f>SUM(I267:I271)</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J272" s="44"/>
       <c r="K272" s="44">
         <f>SUM(K267:K271)</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L272" s="44"/>
       <c r="M272" s="45">
         <f>SUM(M267:M271)</f>
-        <v>34</v>
-      </c>
-      <c r="N272" s="61"/>
+        <v>40</v>
+      </c>
+      <c r="N272" s="60"/>
       <c r="O272" s="45">
         <f>SUM(O267:O271)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="P272" s="60"/>
+      <c r="Q272" s="45">
+        <f>SUM(Q267:Q271)</f>
+        <v>26</v>
+      </c>
+      <c r="R272" s="60"/>
+      <c r="S272" s="45">
+        <f>SUM(S267:S271)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A273" s="38" t="s">
         <v>41</v>
       </c>
@@ -10971,62 +12195,2874 @@
       </c>
       <c r="D273" s="39"/>
       <c r="E273" s="39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F273" s="39"/>
       <c r="G273" s="39">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H273" s="39"/>
       <c r="I273" s="39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J273" s="39"/>
       <c r="K273" s="39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L273" s="39"/>
       <c r="M273" s="40">
-        <v>-6</v>
-      </c>
-      <c r="N273" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="N273" s="61"/>
       <c r="O273" s="40">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P273" s="61"/>
+      <c r="Q273" s="40">
+        <v>0</v>
+      </c>
+      <c r="R273" s="61"/>
+      <c r="S273" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B274" s="42"/>
       <c r="C274" s="42">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D274" s="42"/>
       <c r="E274" s="42">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F274" s="42"/>
       <c r="G274" s="42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H274" s="42"/>
       <c r="I274" s="42">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="J274" s="42"/>
       <c r="K274" s="42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L274" s="42"/>
       <c r="M274" s="43">
+        <v>0</v>
+      </c>
+      <c r="N274" s="62"/>
+      <c r="O274" s="43">
+        <v>0</v>
+      </c>
+      <c r="P274" s="62"/>
+      <c r="Q274" s="43">
+        <v>0</v>
+      </c>
+      <c r="R274" s="62"/>
+      <c r="S274" s="43">
+        <v>0</v>
+      </c>
+      <c r="T274" s="63"/>
+    </row>
+    <row r="275" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A276" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C276" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D276" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="N274" s="63"/>
-      <c r="O274" s="43">
-        <v>0</v>
-      </c>
-      <c r="P274" s="64"/>
+      <c r="E276" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F276" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H276" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I276" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J276" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K276" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L276" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M276" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N276" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O276" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P276" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q276" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R276" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S276" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A277" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C277" s="4">
+        <v>10</v>
+      </c>
+      <c r="D277" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E277" s="4">
+        <v>10</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G277" s="4">
+        <v>10</v>
+      </c>
+      <c r="H277" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I277" s="4">
+        <v>10</v>
+      </c>
+      <c r="J277" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K277" s="4">
+        <v>10</v>
+      </c>
+      <c r="L277" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M277" s="12">
+        <v>10</v>
+      </c>
+      <c r="N277" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O277" s="12">
+        <v>10</v>
+      </c>
+      <c r="P277" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q277" s="12">
+        <v>10</v>
+      </c>
+      <c r="R277" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S277" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A278" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C278" s="4">
+        <v>8</v>
+      </c>
+      <c r="D278" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E278" s="4">
+        <v>8</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G278" s="4">
+        <v>8</v>
+      </c>
+      <c r="H278" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I278" s="4">
+        <v>8</v>
+      </c>
+      <c r="J278" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K278" s="4">
+        <v>8</v>
+      </c>
+      <c r="L278" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M278" s="12">
+        <v>8</v>
+      </c>
+      <c r="N278" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O278" s="12">
+        <v>8</v>
+      </c>
+      <c r="P278" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q278" s="12">
+        <v>8</v>
+      </c>
+      <c r="R278" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S278" s="12"/>
+    </row>
+    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A279" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C279" s="4">
+        <v>6</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E279" s="4"/>
+      <c r="F279" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G279" s="4">
+        <v>7</v>
+      </c>
+      <c r="H279" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I279" s="4">
+        <v>8</v>
+      </c>
+      <c r="J279" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K279" s="4">
+        <v>8</v>
+      </c>
+      <c r="L279" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M279" s="12">
+        <v>8</v>
+      </c>
+      <c r="N279" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O279" s="12">
+        <v>8</v>
+      </c>
+      <c r="P279" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q279" s="12"/>
+      <c r="R279" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S279" s="12"/>
+    </row>
+    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A280" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C280" s="4">
+        <v>8</v>
+      </c>
+      <c r="D280" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E280" s="4">
+        <v>8</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G280" s="4">
+        <v>7</v>
+      </c>
+      <c r="H280" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I280" s="4">
+        <v>8</v>
+      </c>
+      <c r="J280" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K280" s="4">
+        <v>6</v>
+      </c>
+      <c r="L280" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M280" s="12">
+        <v>7</v>
+      </c>
+      <c r="N280" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O280" s="12"/>
+      <c r="P280" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q280" s="12"/>
+      <c r="R280" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S280" s="12"/>
+    </row>
+    <row r="281" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C281" s="23">
+        <v>8</v>
+      </c>
+      <c r="D281" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E281" s="23">
+        <v>8</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G281" s="23">
+        <v>7</v>
+      </c>
+      <c r="H281" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I281" s="23">
+        <v>8</v>
+      </c>
+      <c r="J281" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K281" s="23"/>
+      <c r="L281" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="M281" s="24">
+        <v>7</v>
+      </c>
+      <c r="N281" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O281" s="24"/>
+      <c r="P281" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q281" s="24"/>
+      <c r="R281" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S281" s="24"/>
+    </row>
+    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A282" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B282" s="44"/>
+      <c r="C282" s="44">
+        <f>SUM(C277:C281)</f>
+        <v>40</v>
+      </c>
+      <c r="D282" s="44"/>
+      <c r="E282" s="44">
+        <f>SUM(E277:E281)</f>
+        <v>34</v>
+      </c>
+      <c r="F282" s="44"/>
+      <c r="G282" s="44">
+        <f>SUM(G277:G281)</f>
+        <v>39</v>
+      </c>
+      <c r="H282" s="44"/>
+      <c r="I282" s="44">
+        <f>SUM(I277:I281)</f>
+        <v>42</v>
+      </c>
+      <c r="J282" s="44"/>
+      <c r="K282" s="44">
+        <f>SUM(K277:K281)</f>
+        <v>32</v>
+      </c>
+      <c r="L282" s="44"/>
+      <c r="M282" s="45">
+        <f>SUM(M277:M281)</f>
+        <v>40</v>
+      </c>
+      <c r="N282" s="60"/>
+      <c r="O282" s="45">
+        <f>SUM(O277:O281)</f>
+        <v>26</v>
+      </c>
+      <c r="P282" s="60"/>
+      <c r="Q282" s="45">
+        <f>SUM(Q277:Q281)</f>
+        <v>18</v>
+      </c>
+      <c r="R282" s="60"/>
+      <c r="S282" s="45">
+        <f>SUM(S277:S281)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A283" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B283" s="39"/>
+      <c r="C283" s="39">
+        <v>0</v>
+      </c>
+      <c r="D283" s="39"/>
+      <c r="E283" s="39">
+        <v>-6</v>
+      </c>
+      <c r="F283" s="39"/>
+      <c r="G283" s="39">
+        <v>4</v>
+      </c>
+      <c r="H283" s="39"/>
+      <c r="I283" s="39">
+        <v>2</v>
+      </c>
+      <c r="J283" s="39"/>
+      <c r="K283" s="39">
+        <v>0</v>
+      </c>
+      <c r="L283" s="39"/>
+      <c r="M283" s="40">
+        <v>0</v>
+      </c>
+      <c r="N283" s="61"/>
+      <c r="O283" s="40">
+        <v>0</v>
+      </c>
+      <c r="P283" s="61"/>
+      <c r="Q283" s="40">
+        <v>0</v>
+      </c>
+      <c r="R283" s="61"/>
+      <c r="S283" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B284" s="42"/>
+      <c r="C284" s="42">
+        <v>4</v>
+      </c>
+      <c r="D284" s="42"/>
+      <c r="E284" s="42">
+        <v>1</v>
+      </c>
+      <c r="F284" s="42"/>
+      <c r="G284" s="42">
+        <v>6</v>
+      </c>
+      <c r="H284" s="42"/>
+      <c r="I284" s="42">
+        <v>7</v>
+      </c>
+      <c r="J284" s="42"/>
+      <c r="K284" s="42">
+        <v>3</v>
+      </c>
+      <c r="L284" s="42"/>
+      <c r="M284" s="43">
+        <v>0</v>
+      </c>
+      <c r="N284" s="62"/>
+      <c r="O284" s="43">
+        <v>0</v>
+      </c>
+      <c r="P284" s="62"/>
+      <c r="Q284" s="43">
+        <v>0</v>
+      </c>
+      <c r="R284" s="62"/>
+      <c r="S284" s="43">
+        <v>0</v>
+      </c>
+      <c r="T284" s="63"/>
+    </row>
+    <row r="285" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A286" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C286" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E286" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H286" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I286" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J286" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K286" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L286" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M286" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N286" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O286" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P286" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q286" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R286" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S286" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A287" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C287" s="4">
+        <v>10</v>
+      </c>
+      <c r="D287" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E287" s="4">
+        <v>10</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G287" s="4">
+        <v>10</v>
+      </c>
+      <c r="H287" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I287" s="4">
+        <v>10</v>
+      </c>
+      <c r="J287" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K287" s="4">
+        <v>10</v>
+      </c>
+      <c r="L287" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M287" s="12">
+        <v>10</v>
+      </c>
+      <c r="N287" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O287" s="12">
+        <v>10</v>
+      </c>
+      <c r="P287" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q287" s="12">
+        <v>10</v>
+      </c>
+      <c r="R287" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S287" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A288" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C288" s="4">
+        <v>8</v>
+      </c>
+      <c r="D288" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E288" s="4">
+        <v>8</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G288" s="4">
+        <v>8</v>
+      </c>
+      <c r="H288" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I288" s="4">
+        <v>8</v>
+      </c>
+      <c r="J288" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K288" s="4">
+        <v>8</v>
+      </c>
+      <c r="L288" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M288" s="12">
+        <v>8</v>
+      </c>
+      <c r="N288" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O288" s="12">
+        <v>8</v>
+      </c>
+      <c r="P288" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q288" s="12">
+        <v>8</v>
+      </c>
+      <c r="R288" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S288" s="12"/>
+    </row>
+    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A289" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C289" s="4">
+        <v>6</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E289" s="4">
+        <v>8</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G289" s="4">
+        <v>7</v>
+      </c>
+      <c r="H289" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I289" s="4"/>
+      <c r="J289" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K289" s="4">
+        <v>8</v>
+      </c>
+      <c r="L289" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M289" s="12">
+        <v>8</v>
+      </c>
+      <c r="N289" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O289" s="12"/>
+      <c r="P289" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q289" s="4">
+        <v>8</v>
+      </c>
+      <c r="R289" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S289" s="12"/>
+    </row>
+    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A290" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C290" s="4">
+        <v>8</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E290" s="4">
+        <v>8</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G290" s="4"/>
+      <c r="H290" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I290" s="4">
+        <v>8</v>
+      </c>
+      <c r="J290" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K290" s="4">
+        <v>6</v>
+      </c>
+      <c r="L290" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M290" s="12">
+        <v>7</v>
+      </c>
+      <c r="N290" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O290" s="4"/>
+      <c r="P290" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q290" s="4">
+        <v>8</v>
+      </c>
+      <c r="R290" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S290" s="12"/>
+    </row>
+    <row r="291" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A291" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C291" s="23">
+        <v>8</v>
+      </c>
+      <c r="D291" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E291" s="23">
+        <v>8</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G291" s="23">
+        <v>7</v>
+      </c>
+      <c r="H291" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I291" s="23">
+        <v>8</v>
+      </c>
+      <c r="J291" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K291" s="23"/>
+      <c r="L291" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="M291" s="24">
+        <v>7</v>
+      </c>
+      <c r="N291" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O291" s="24"/>
+      <c r="P291" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q291" s="24"/>
+      <c r="R291" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S291" s="24"/>
+    </row>
+    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A292" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B292" s="44"/>
+      <c r="C292" s="44">
+        <f>SUM(C287:C291)</f>
+        <v>40</v>
+      </c>
+      <c r="D292" s="44"/>
+      <c r="E292" s="44">
+        <f>SUM(E287:E291)</f>
+        <v>42</v>
+      </c>
+      <c r="F292" s="44"/>
+      <c r="G292" s="44">
+        <f>SUM(G287:G291)</f>
+        <v>32</v>
+      </c>
+      <c r="H292" s="44"/>
+      <c r="I292" s="44">
+        <f>SUM(I287:I291)</f>
+        <v>34</v>
+      </c>
+      <c r="J292" s="44"/>
+      <c r="K292" s="44">
+        <f>SUM(K287:K291)</f>
+        <v>32</v>
+      </c>
+      <c r="L292" s="44"/>
+      <c r="M292" s="45">
+        <f>SUM(M287:M291)</f>
+        <v>40</v>
+      </c>
+      <c r="N292" s="60"/>
+      <c r="O292" s="45">
+        <f>SUM(O287:O291)</f>
+        <v>18</v>
+      </c>
+      <c r="P292" s="60"/>
+      <c r="Q292" s="45">
+        <f>SUM(Q287:Q291)</f>
+        <v>34</v>
+      </c>
+      <c r="R292" s="60"/>
+      <c r="S292" s="45">
+        <f>SUM(S287:S291)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A293" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B293" s="39"/>
+      <c r="C293" s="39">
+        <v>0</v>
+      </c>
+      <c r="D293" s="39"/>
+      <c r="E293" s="39">
+        <v>2</v>
+      </c>
+      <c r="F293" s="39"/>
+      <c r="G293" s="39">
+        <v>-3</v>
+      </c>
+      <c r="H293" s="39"/>
+      <c r="I293" s="39">
+        <v>-6</v>
+      </c>
+      <c r="J293" s="39"/>
+      <c r="K293" s="39">
+        <v>0</v>
+      </c>
+      <c r="L293" s="39"/>
+      <c r="M293" s="40">
+        <v>0</v>
+      </c>
+      <c r="N293" s="61"/>
+      <c r="O293" s="40">
+        <v>0</v>
+      </c>
+      <c r="P293" s="61"/>
+      <c r="Q293" s="40">
+        <v>0</v>
+      </c>
+      <c r="R293" s="61"/>
+      <c r="S293" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B294" s="42"/>
+      <c r="C294" s="42">
+        <v>4</v>
+      </c>
+      <c r="D294" s="42"/>
+      <c r="E294" s="42">
+        <v>3</v>
+      </c>
+      <c r="F294" s="42"/>
+      <c r="G294" s="42">
+        <v>3</v>
+      </c>
+      <c r="H294" s="42"/>
+      <c r="I294" s="42">
+        <v>1</v>
+      </c>
+      <c r="J294" s="42"/>
+      <c r="K294" s="42">
+        <v>3</v>
+      </c>
+      <c r="L294" s="42"/>
+      <c r="M294" s="43">
+        <v>0</v>
+      </c>
+      <c r="N294" s="62"/>
+      <c r="O294" s="43">
+        <v>0</v>
+      </c>
+      <c r="P294" s="62"/>
+      <c r="Q294" s="43">
+        <v>0</v>
+      </c>
+      <c r="R294" s="62"/>
+      <c r="S294" s="43">
+        <v>0</v>
+      </c>
+      <c r="T294" s="63"/>
+    </row>
+    <row r="295" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A296" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C296" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D296" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E296" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F296" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G296" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H296" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I296" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J296" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K296" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L296" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M296" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N296" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O296" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P296" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q296" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R296" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S296" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A297" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C297" s="4">
+        <v>10</v>
+      </c>
+      <c r="D297" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E297" s="4">
+        <v>10</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G297" s="4">
+        <v>10</v>
+      </c>
+      <c r="H297" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I297" s="4">
+        <v>10</v>
+      </c>
+      <c r="J297" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K297" s="4">
+        <v>10</v>
+      </c>
+      <c r="L297" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M297" s="12">
+        <v>10</v>
+      </c>
+      <c r="N297" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O297" s="12">
+        <v>10</v>
+      </c>
+      <c r="P297" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q297" s="12">
+        <v>10</v>
+      </c>
+      <c r="R297" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S297" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A298" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C298" s="4">
+        <v>8</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E298" s="4">
+        <v>8</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G298" s="4">
+        <v>8</v>
+      </c>
+      <c r="H298" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I298" s="4">
+        <v>8</v>
+      </c>
+      <c r="J298" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K298" s="4">
+        <v>8</v>
+      </c>
+      <c r="L298" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M298" s="12">
+        <v>8</v>
+      </c>
+      <c r="N298" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O298" s="12">
+        <v>8</v>
+      </c>
+      <c r="P298" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q298" s="12">
+        <v>8</v>
+      </c>
+      <c r="R298" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S298" s="12"/>
+    </row>
+    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A299" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C299" s="4">
+        <v>6</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E299" s="4">
+        <v>8</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G299" s="4">
+        <v>7</v>
+      </c>
+      <c r="H299" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I299" s="4">
+        <v>8</v>
+      </c>
+      <c r="J299" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K299" s="4">
+        <v>8</v>
+      </c>
+      <c r="L299" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M299" s="12">
+        <v>8</v>
+      </c>
+      <c r="N299" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O299" s="12"/>
+      <c r="P299" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q299" s="12"/>
+      <c r="R299" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S299" s="12"/>
+    </row>
+    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A300" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C300" s="4">
+        <v>8</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E300" s="4">
+        <v>8</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G300" s="4">
+        <v>7</v>
+      </c>
+      <c r="H300" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I300" s="4">
+        <v>8</v>
+      </c>
+      <c r="J300" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K300" s="4">
+        <v>6</v>
+      </c>
+      <c r="L300" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M300" s="12">
+        <v>7</v>
+      </c>
+      <c r="N300" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O300" s="12"/>
+      <c r="P300" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q300" s="12"/>
+      <c r="R300" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S300" s="12"/>
+    </row>
+    <row r="301" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A301" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C301" s="23">
+        <v>8</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E301" s="23">
+        <v>8</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G301" s="23">
+        <v>7</v>
+      </c>
+      <c r="H301" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I301" s="23">
+        <v>8</v>
+      </c>
+      <c r="J301" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K301" s="23"/>
+      <c r="L301" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="M301" s="24">
+        <v>7</v>
+      </c>
+      <c r="N301" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O301" s="24"/>
+      <c r="P301" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q301" s="24"/>
+      <c r="R301" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S301" s="24"/>
+    </row>
+    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A302" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B302" s="44"/>
+      <c r="C302" s="44">
+        <f>SUM(C297:C301)</f>
+        <v>40</v>
+      </c>
+      <c r="D302" s="44"/>
+      <c r="E302" s="44">
+        <f>SUM(E297:E301)</f>
+        <v>42</v>
+      </c>
+      <c r="F302" s="44"/>
+      <c r="G302" s="44">
+        <f>SUM(G297:G301)</f>
+        <v>39</v>
+      </c>
+      <c r="H302" s="44"/>
+      <c r="I302" s="44">
+        <f>SUM(I297:I301)</f>
+        <v>42</v>
+      </c>
+      <c r="J302" s="44"/>
+      <c r="K302" s="44">
+        <f>SUM(K297:K301)</f>
+        <v>32</v>
+      </c>
+      <c r="L302" s="44"/>
+      <c r="M302" s="45">
+        <f>SUM(M297:M301)</f>
+        <v>40</v>
+      </c>
+      <c r="N302" s="60"/>
+      <c r="O302" s="45">
+        <f>SUM(O297:O301)</f>
+        <v>18</v>
+      </c>
+      <c r="P302" s="60"/>
+      <c r="Q302" s="45">
+        <f>SUM(Q297:Q301)</f>
+        <v>18</v>
+      </c>
+      <c r="R302" s="60"/>
+      <c r="S302" s="45">
+        <f>SUM(S297:S301)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A303" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B303" s="39"/>
+      <c r="C303" s="39">
+        <v>0</v>
+      </c>
+      <c r="D303" s="39"/>
+      <c r="E303" s="39">
+        <v>2</v>
+      </c>
+      <c r="F303" s="39"/>
+      <c r="G303" s="39">
+        <v>4</v>
+      </c>
+      <c r="H303" s="39"/>
+      <c r="I303" s="39">
+        <v>2</v>
+      </c>
+      <c r="J303" s="39"/>
+      <c r="K303" s="39">
+        <v>0</v>
+      </c>
+      <c r="L303" s="39"/>
+      <c r="M303" s="40">
+        <v>0</v>
+      </c>
+      <c r="N303" s="61"/>
+      <c r="O303" s="40">
+        <v>0</v>
+      </c>
+      <c r="P303" s="61"/>
+      <c r="Q303" s="40">
+        <v>0</v>
+      </c>
+      <c r="R303" s="61"/>
+      <c r="S303" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A304" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B304" s="42"/>
+      <c r="C304" s="42">
+        <v>4</v>
+      </c>
+      <c r="D304" s="42"/>
+      <c r="E304" s="42">
+        <v>5</v>
+      </c>
+      <c r="F304" s="42"/>
+      <c r="G304" s="42">
+        <v>7</v>
+      </c>
+      <c r="H304" s="42"/>
+      <c r="I304" s="42">
+        <v>3</v>
+      </c>
+      <c r="J304" s="42"/>
+      <c r="K304" s="42">
+        <v>3</v>
+      </c>
+      <c r="L304" s="42"/>
+      <c r="M304" s="43">
+        <v>0</v>
+      </c>
+      <c r="N304" s="62"/>
+      <c r="O304" s="43">
+        <v>0</v>
+      </c>
+      <c r="P304" s="62"/>
+      <c r="Q304" s="43">
+        <v>0</v>
+      </c>
+      <c r="R304" s="62"/>
+      <c r="S304" s="43">
+        <v>0</v>
+      </c>
+      <c r="T304" s="63"/>
+    </row>
+    <row r="305" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A306" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C306" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D306" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E306" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F306" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H306" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I306" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J306" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K306" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L306" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M306" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N306" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O306" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P306" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q306" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R306" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S306" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A307" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C307" s="4">
+        <v>10</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E307" s="4">
+        <v>10</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G307" s="4">
+        <v>10</v>
+      </c>
+      <c r="H307" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I307" s="4">
+        <v>10</v>
+      </c>
+      <c r="J307" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K307" s="4">
+        <v>10</v>
+      </c>
+      <c r="L307" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M307" s="12">
+        <v>10</v>
+      </c>
+      <c r="N307" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O307" s="12">
+        <v>10</v>
+      </c>
+      <c r="P307" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q307" s="12">
+        <v>10</v>
+      </c>
+      <c r="R307" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S307" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A308" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C308" s="4">
+        <v>8</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E308" s="4">
+        <v>8</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G308" s="4">
+        <v>8</v>
+      </c>
+      <c r="H308" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I308" s="4">
+        <v>8</v>
+      </c>
+      <c r="J308" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K308" s="4">
+        <v>8</v>
+      </c>
+      <c r="L308" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M308" s="12">
+        <v>8</v>
+      </c>
+      <c r="N308" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O308" s="12">
+        <v>8</v>
+      </c>
+      <c r="P308" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q308" s="12">
+        <v>8</v>
+      </c>
+      <c r="R308" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S308" s="12"/>
+    </row>
+    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A309" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C309" s="4">
+        <v>6</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E309" s="4">
+        <v>8</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G309" s="4">
+        <v>7</v>
+      </c>
+      <c r="H309" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I309" s="4">
+        <v>8</v>
+      </c>
+      <c r="J309" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K309" s="4">
+        <v>8</v>
+      </c>
+      <c r="L309" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M309" s="12">
+        <v>8</v>
+      </c>
+      <c r="N309" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O309" s="12"/>
+      <c r="P309" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q309" s="12"/>
+      <c r="R309" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S309" s="12"/>
+    </row>
+    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A310" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C310" s="4">
+        <v>8</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E310" s="4">
+        <v>8</v>
+      </c>
+      <c r="F310" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G310" s="4"/>
+      <c r="H310" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I310" s="4">
+        <v>8</v>
+      </c>
+      <c r="J310" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K310" s="4">
+        <v>6</v>
+      </c>
+      <c r="L310" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M310" s="12">
+        <v>7</v>
+      </c>
+      <c r="N310" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O310" s="4">
+        <v>8</v>
+      </c>
+      <c r="P310" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q310" s="12"/>
+      <c r="R310" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S310" s="12"/>
+    </row>
+    <row r="311" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A311" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C311" s="23">
+        <v>8</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E311" s="23">
+        <v>8</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G311" s="23">
+        <v>7</v>
+      </c>
+      <c r="H311" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I311" s="23">
+        <v>8</v>
+      </c>
+      <c r="J311" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K311" s="23"/>
+      <c r="L311" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="M311" s="24">
+        <v>7</v>
+      </c>
+      <c r="N311" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O311" s="24"/>
+      <c r="P311" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q311" s="24"/>
+      <c r="R311" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S311" s="24"/>
+    </row>
+    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A312" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B312" s="44"/>
+      <c r="C312" s="44">
+        <f>SUM(C307:C311)</f>
+        <v>40</v>
+      </c>
+      <c r="D312" s="44"/>
+      <c r="E312" s="44">
+        <f>SUM(E307:E311)</f>
+        <v>42</v>
+      </c>
+      <c r="F312" s="44"/>
+      <c r="G312" s="44">
+        <f>SUM(G307:G311)</f>
+        <v>32</v>
+      </c>
+      <c r="H312" s="44"/>
+      <c r="I312" s="44">
+        <f>SUM(I307:I311)</f>
+        <v>42</v>
+      </c>
+      <c r="J312" s="44"/>
+      <c r="K312" s="44">
+        <f>SUM(K307:K311)</f>
+        <v>32</v>
+      </c>
+      <c r="L312" s="44"/>
+      <c r="M312" s="45">
+        <f>SUM(M307:M311)</f>
+        <v>40</v>
+      </c>
+      <c r="N312" s="60"/>
+      <c r="O312" s="45">
+        <f>SUM(O307:O311)</f>
+        <v>26</v>
+      </c>
+      <c r="P312" s="60"/>
+      <c r="Q312" s="45">
+        <f>SUM(Q307:Q311)</f>
+        <v>18</v>
+      </c>
+      <c r="R312" s="60"/>
+      <c r="S312" s="45">
+        <f>SUM(S307:S311)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A313" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B313" s="39"/>
+      <c r="C313" s="39">
+        <v>0</v>
+      </c>
+      <c r="D313" s="39"/>
+      <c r="E313" s="39">
+        <v>2</v>
+      </c>
+      <c r="F313" s="39"/>
+      <c r="G313" s="39">
+        <v>-3</v>
+      </c>
+      <c r="H313" s="39"/>
+      <c r="I313" s="39">
+        <v>2</v>
+      </c>
+      <c r="J313" s="39"/>
+      <c r="K313" s="39">
+        <v>0</v>
+      </c>
+      <c r="L313" s="39"/>
+      <c r="M313" s="40">
+        <v>0</v>
+      </c>
+      <c r="N313" s="61"/>
+      <c r="O313" s="40">
+        <v>0</v>
+      </c>
+      <c r="P313" s="61"/>
+      <c r="Q313" s="40">
+        <v>0</v>
+      </c>
+      <c r="R313" s="61"/>
+      <c r="S313" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A314" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B314" s="42"/>
+      <c r="C314" s="42">
+        <v>4</v>
+      </c>
+      <c r="D314" s="42"/>
+      <c r="E314" s="42">
+        <v>7</v>
+      </c>
+      <c r="F314" s="42"/>
+      <c r="G314" s="42">
+        <v>4</v>
+      </c>
+      <c r="H314" s="42"/>
+      <c r="I314" s="42">
+        <v>5</v>
+      </c>
+      <c r="J314" s="42"/>
+      <c r="K314" s="42">
+        <v>3</v>
+      </c>
+      <c r="L314" s="42"/>
+      <c r="M314" s="43">
+        <v>0</v>
+      </c>
+      <c r="N314" s="62"/>
+      <c r="O314" s="43">
+        <v>0</v>
+      </c>
+      <c r="P314" s="62"/>
+      <c r="Q314" s="43">
+        <v>0</v>
+      </c>
+      <c r="R314" s="62"/>
+      <c r="S314" s="43">
+        <v>0</v>
+      </c>
+      <c r="T314" s="63"/>
+    </row>
+    <row r="315" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A316" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B316" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C316" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D316" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E316" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F316" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G316" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H316" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I316" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J316" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K316" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L316" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M316" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N316" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O316" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P316" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q316" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R316" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S316" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A317" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C317" s="4">
+        <v>10</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E317" s="4">
+        <v>10</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G317" s="4">
+        <v>10</v>
+      </c>
+      <c r="H317" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I317" s="4">
+        <v>10</v>
+      </c>
+      <c r="J317" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K317" s="4">
+        <v>10</v>
+      </c>
+      <c r="L317" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M317" s="12">
+        <v>10</v>
+      </c>
+      <c r="N317" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O317" s="12">
+        <v>10</v>
+      </c>
+      <c r="P317" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q317" s="12">
+        <v>10</v>
+      </c>
+      <c r="R317" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S317" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A318" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C318" s="4">
+        <v>8</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E318" s="4">
+        <v>8</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G318" s="4">
+        <v>8</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I318" s="4">
+        <v>8</v>
+      </c>
+      <c r="J318" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K318" s="4">
+        <v>8</v>
+      </c>
+      <c r="L318" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M318" s="12">
+        <v>8</v>
+      </c>
+      <c r="N318" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O318" s="12">
+        <v>8</v>
+      </c>
+      <c r="P318" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q318" s="12">
+        <v>8</v>
+      </c>
+      <c r="R318" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S318" s="12"/>
+    </row>
+    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A319" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C319" s="4">
+        <v>6</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E319" s="4">
+        <v>8</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G319" s="4">
+        <v>7</v>
+      </c>
+      <c r="H319" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I319" s="4">
+        <v>8</v>
+      </c>
+      <c r="J319" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K319" s="4">
+        <v>8</v>
+      </c>
+      <c r="L319" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M319" s="12">
+        <v>8</v>
+      </c>
+      <c r="N319" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O319" s="12"/>
+      <c r="P319" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q319" s="12"/>
+      <c r="R319" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S319" s="12"/>
+    </row>
+    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A320" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C320" s="4">
+        <v>8</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E320" s="4">
+        <v>8</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G320" s="4">
+        <v>7</v>
+      </c>
+      <c r="H320" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I320" s="4">
+        <v>8</v>
+      </c>
+      <c r="J320" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K320" s="4">
+        <v>6</v>
+      </c>
+      <c r="L320" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M320" s="12">
+        <v>7</v>
+      </c>
+      <c r="N320" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O320" s="12"/>
+      <c r="P320" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q320" s="12"/>
+      <c r="R320" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S320" s="12"/>
+    </row>
+    <row r="321" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A321" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C321" s="23">
+        <v>8</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E321" s="23">
+        <v>8</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G321" s="23">
+        <v>7</v>
+      </c>
+      <c r="H321" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I321" s="23">
+        <v>8</v>
+      </c>
+      <c r="J321" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K321" s="23"/>
+      <c r="L321" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="M321" s="24">
+        <v>7</v>
+      </c>
+      <c r="N321" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O321" s="24"/>
+      <c r="P321" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q321" s="24"/>
+      <c r="R321" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S321" s="24"/>
+    </row>
+    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A322" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B322" s="44"/>
+      <c r="C322" s="44">
+        <f>SUM(C317:C321)</f>
+        <v>40</v>
+      </c>
+      <c r="D322" s="44"/>
+      <c r="E322" s="44">
+        <f>SUM(E317:E321)</f>
+        <v>42</v>
+      </c>
+      <c r="F322" s="44"/>
+      <c r="G322" s="44">
+        <f>SUM(G317:G321)</f>
+        <v>39</v>
+      </c>
+      <c r="H322" s="44"/>
+      <c r="I322" s="44">
+        <f>SUM(I317:I321)</f>
+        <v>42</v>
+      </c>
+      <c r="J322" s="44"/>
+      <c r="K322" s="44">
+        <f>SUM(K317:K321)</f>
+        <v>32</v>
+      </c>
+      <c r="L322" s="44"/>
+      <c r="M322" s="45">
+        <f>SUM(M317:M321)</f>
+        <v>40</v>
+      </c>
+      <c r="N322" s="60"/>
+      <c r="O322" s="45">
+        <f>SUM(O317:O321)</f>
+        <v>18</v>
+      </c>
+      <c r="P322" s="60"/>
+      <c r="Q322" s="45">
+        <f>SUM(Q317:Q321)</f>
+        <v>18</v>
+      </c>
+      <c r="R322" s="60"/>
+      <c r="S322" s="45">
+        <f>SUM(S317:S321)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A323" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B323" s="39"/>
+      <c r="C323" s="39">
+        <v>0</v>
+      </c>
+      <c r="D323" s="39"/>
+      <c r="E323" s="39">
+        <v>2</v>
+      </c>
+      <c r="F323" s="39"/>
+      <c r="G323" s="39">
+        <v>4</v>
+      </c>
+      <c r="H323" s="39"/>
+      <c r="I323" s="39">
+        <v>2</v>
+      </c>
+      <c r="J323" s="39"/>
+      <c r="K323" s="39">
+        <v>0</v>
+      </c>
+      <c r="L323" s="39"/>
+      <c r="M323" s="40">
+        <v>0</v>
+      </c>
+      <c r="N323" s="61"/>
+      <c r="O323" s="40">
+        <v>0</v>
+      </c>
+      <c r="P323" s="61"/>
+      <c r="Q323" s="40">
+        <v>0</v>
+      </c>
+      <c r="R323" s="61"/>
+      <c r="S323" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A324" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B324" s="42"/>
+      <c r="C324" s="42">
+        <v>4</v>
+      </c>
+      <c r="D324" s="42"/>
+      <c r="E324" s="42">
+        <v>9</v>
+      </c>
+      <c r="F324" s="42"/>
+      <c r="G324" s="42">
+        <v>8</v>
+      </c>
+      <c r="H324" s="42"/>
+      <c r="I324" s="42">
+        <v>7</v>
+      </c>
+      <c r="J324" s="42"/>
+      <c r="K324" s="42">
+        <v>3</v>
+      </c>
+      <c r="L324" s="42"/>
+      <c r="M324" s="43">
+        <v>0</v>
+      </c>
+      <c r="N324" s="62"/>
+      <c r="O324" s="43">
+        <v>0</v>
+      </c>
+      <c r="P324" s="62"/>
+      <c r="Q324" s="43">
+        <v>0</v>
+      </c>
+      <c r="R324" s="62"/>
+      <c r="S324" s="43">
+        <v>0</v>
+      </c>
+      <c r="T324" s="63"/>
+    </row>
+    <row r="325" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A326" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B326" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C326" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D326" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E326" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F326" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G326" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H326" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I326" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J326" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K326" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L326" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M326" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N326" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O326" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P326" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q326" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R326" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="S326" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A327" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C327" s="4">
+        <v>10</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E327" s="4">
+        <v>10</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G327" s="4">
+        <v>10</v>
+      </c>
+      <c r="H327" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I327" s="4">
+        <v>10</v>
+      </c>
+      <c r="J327" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K327" s="4">
+        <v>10</v>
+      </c>
+      <c r="L327" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M327" s="12">
+        <v>10</v>
+      </c>
+      <c r="N327" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O327" s="12">
+        <v>10</v>
+      </c>
+      <c r="P327" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q327" s="12">
+        <v>10</v>
+      </c>
+      <c r="R327" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="S327" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A328" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C328" s="4">
+        <v>8</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E328" s="4">
+        <v>8</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G328" s="4">
+        <v>8</v>
+      </c>
+      <c r="H328" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I328" s="4">
+        <v>8</v>
+      </c>
+      <c r="J328" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K328" s="4">
+        <v>8</v>
+      </c>
+      <c r="L328" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M328" s="12">
+        <v>8</v>
+      </c>
+      <c r="N328" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O328" s="12">
+        <v>8</v>
+      </c>
+      <c r="P328" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q328" s="12">
+        <v>8</v>
+      </c>
+      <c r="R328" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S328" s="12"/>
+    </row>
+    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A329" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C329" s="4">
+        <v>6</v>
+      </c>
+      <c r="D329" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E329" s="4"/>
+      <c r="F329" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G329" s="4">
+        <v>7</v>
+      </c>
+      <c r="H329" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I329" s="4"/>
+      <c r="J329" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K329" s="4">
+        <v>8</v>
+      </c>
+      <c r="L329" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M329" s="12">
+        <v>8</v>
+      </c>
+      <c r="N329" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O329" s="4">
+        <v>8</v>
+      </c>
+      <c r="P329" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q329" s="12">
+        <v>8</v>
+      </c>
+      <c r="R329" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S329" s="12"/>
+    </row>
+    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A330" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C330" s="4">
+        <v>8</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E330" s="4">
+        <v>8</v>
+      </c>
+      <c r="F330" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G330" s="4"/>
+      <c r="H330" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I330" s="4">
+        <v>8</v>
+      </c>
+      <c r="J330" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K330" s="4">
+        <v>6</v>
+      </c>
+      <c r="L330" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M330" s="12">
+        <v>7</v>
+      </c>
+      <c r="N330" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O330" s="4">
+        <v>8</v>
+      </c>
+      <c r="P330" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q330" s="12"/>
+      <c r="R330" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S330" s="12"/>
+    </row>
+    <row r="331" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A331" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C331" s="23">
+        <v>8</v>
+      </c>
+      <c r="D331" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E331" s="23">
+        <v>8</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G331" s="23">
+        <v>7</v>
+      </c>
+      <c r="H331" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I331" s="23">
+        <v>8</v>
+      </c>
+      <c r="J331" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K331" s="23"/>
+      <c r="L331" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="M331" s="24">
+        <v>7</v>
+      </c>
+      <c r="N331" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="O331" s="24"/>
+      <c r="P331" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q331" s="24"/>
+      <c r="R331" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="S331" s="24"/>
+    </row>
+    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A332" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B332" s="44"/>
+      <c r="C332" s="44">
+        <f>SUM(C327:C331)</f>
+        <v>40</v>
+      </c>
+      <c r="D332" s="44"/>
+      <c r="E332" s="44">
+        <f>SUM(E327:E331)</f>
+        <v>34</v>
+      </c>
+      <c r="F332" s="44"/>
+      <c r="G332" s="44">
+        <f>SUM(G327:G331)</f>
+        <v>32</v>
+      </c>
+      <c r="H332" s="44"/>
+      <c r="I332" s="44">
+        <f>SUM(I327:I331)</f>
+        <v>34</v>
+      </c>
+      <c r="J332" s="44"/>
+      <c r="K332" s="44">
+        <f>SUM(K327:K331)</f>
+        <v>32</v>
+      </c>
+      <c r="L332" s="44"/>
+      <c r="M332" s="45">
+        <f>SUM(M327:M331)</f>
+        <v>40</v>
+      </c>
+      <c r="N332" s="60"/>
+      <c r="O332" s="45">
+        <f>SUM(O327:O331)</f>
+        <v>34</v>
+      </c>
+      <c r="P332" s="60"/>
+      <c r="Q332" s="45">
+        <f>SUM(Q327:Q331)</f>
+        <v>26</v>
+      </c>
+      <c r="R332" s="60"/>
+      <c r="S332" s="45">
+        <f>SUM(S327:S331)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A333" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B333" s="39"/>
+      <c r="C333" s="39">
+        <v>0</v>
+      </c>
+      <c r="D333" s="39"/>
+      <c r="E333" s="39">
+        <v>-6</v>
+      </c>
+      <c r="F333" s="39"/>
+      <c r="G333" s="39">
+        <v>-3</v>
+      </c>
+      <c r="H333" s="39"/>
+      <c r="I333" s="39">
+        <v>-6</v>
+      </c>
+      <c r="J333" s="39"/>
+      <c r="K333" s="39">
+        <v>0</v>
+      </c>
+      <c r="L333" s="39"/>
+      <c r="M333" s="40">
+        <v>0</v>
+      </c>
+      <c r="N333" s="61"/>
+      <c r="O333" s="40">
+        <v>0</v>
+      </c>
+      <c r="P333" s="61"/>
+      <c r="Q333" s="40">
+        <v>0</v>
+      </c>
+      <c r="R333" s="61"/>
+      <c r="S333" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A334" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B334" s="42"/>
+      <c r="C334" s="42">
+        <v>4</v>
+      </c>
+      <c r="D334" s="42"/>
+      <c r="E334" s="42">
+        <v>3</v>
+      </c>
+      <c r="F334" s="42"/>
+      <c r="G334" s="42">
+        <v>5</v>
+      </c>
+      <c r="H334" s="42"/>
+      <c r="I334" s="42">
+        <v>1</v>
+      </c>
+      <c r="J334" s="42"/>
+      <c r="K334" s="42">
+        <v>3</v>
+      </c>
+      <c r="L334" s="42"/>
+      <c r="M334" s="43">
+        <v>0</v>
+      </c>
+      <c r="N334" s="62"/>
+      <c r="O334" s="43">
+        <v>0</v>
+      </c>
+      <c r="P334" s="62"/>
+      <c r="Q334" s="43">
+        <v>0</v>
+      </c>
+      <c r="R334" s="62"/>
+      <c r="S334" s="43">
+        <v>0</v>
+      </c>
+      <c r="T334" s="63"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1823" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12E2B44C-A5E5-4570-A212-CC3A6D07A3E9}"/>
+  <xr:revisionPtr revIDLastSave="1848" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{916C54FA-CE03-4E80-8F30-509F033F1F11}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="30" windowWidth="54180" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="0" yWindow="30" windowWidth="41625" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -814,8 +814,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFB2F0FC"/>
       <color rgb="FFFDF5D3"/>
-      <color rgb="FFB2F0FC"/>
       <color rgb="FFE3F7A3"/>
       <color rgb="FFF9E7F7"/>
       <color rgb="FFFCCDC4"/>
@@ -10084,10 +10084,10 @@
         <v>9</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G228" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H228" s="4" t="s">
         <v>30</v>
@@ -10139,10 +10139,10 @@
         <v>8</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G229" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>12</v>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G230" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>12</v>
@@ -10240,7 +10240,7 @@
       <c r="E231" s="23">
         <v>8</v>
       </c>
-      <c r="F231" s="4" t="s">
+      <c r="F231" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G231" s="23"/>
@@ -10258,10 +10258,12 @@
         <v>67</v>
       </c>
       <c r="M231" s="24"/>
-      <c r="N231" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="O231" s="24"/>
+      <c r="N231" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O231" s="24">
+        <v>8</v>
+      </c>
       <c r="P231" s="23" t="s">
         <v>13</v>
       </c>
@@ -10288,7 +10290,7 @@
       <c r="F232" s="44"/>
       <c r="G232" s="44">
         <f>SUM(G227:G231)</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H232" s="44"/>
       <c r="I232" s="44">
@@ -10308,7 +10310,7 @@
       <c r="N232" s="60"/>
       <c r="O232" s="45">
         <f>SUM(O227:O231)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="P232" s="60"/>
       <c r="Q232" s="45">
@@ -10335,7 +10337,7 @@
       </c>
       <c r="F233" s="39"/>
       <c r="G233" s="39">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H233" s="39"/>
       <c r="I233" s="39">
@@ -10842,7 +10844,7 @@
       </c>
       <c r="F244" s="42"/>
       <c r="G244" s="42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H244" s="42"/>
       <c r="I244" s="42">
@@ -11308,7 +11310,7 @@
       </c>
       <c r="F254" s="42"/>
       <c r="G254" s="42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H254" s="42"/>
       <c r="I254" s="42">
@@ -11774,7 +11776,7 @@
       </c>
       <c r="F264" s="42"/>
       <c r="G264" s="42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H264" s="42"/>
       <c r="I264" s="42">
@@ -12240,7 +12242,7 @@
       </c>
       <c r="F274" s="42"/>
       <c r="G274" s="42">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="H274" s="42"/>
       <c r="I274" s="42">
@@ -12706,7 +12708,7 @@
       </c>
       <c r="F284" s="42"/>
       <c r="G284" s="42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H284" s="42"/>
       <c r="I284" s="42">
@@ -13172,7 +13174,7 @@
       </c>
       <c r="F294" s="42"/>
       <c r="G294" s="42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H294" s="42"/>
       <c r="I294" s="42">
@@ -13638,7 +13640,7 @@
       </c>
       <c r="F304" s="42"/>
       <c r="G304" s="42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H304" s="42"/>
       <c r="I304" s="42">
@@ -14104,7 +14106,7 @@
       </c>
       <c r="F314" s="42"/>
       <c r="G314" s="42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H314" s="42"/>
       <c r="I314" s="42">
@@ -14570,7 +14572,7 @@
       </c>
       <c r="F324" s="42"/>
       <c r="G324" s="42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H324" s="42"/>
       <c r="I324" s="42">
@@ -15036,7 +15038,7 @@
       </c>
       <c r="F334" s="42"/>
       <c r="G334" s="42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H334" s="42"/>
       <c r="I334" s="42">

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1848" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{916C54FA-CE03-4E80-8F30-509F033F1F11}"/>
+  <xr:revisionPtr revIDLastSave="1882" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1513535-137F-44DC-9C61-5E5E320657D5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="30" windowWidth="41625" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="3000" yWindow="45" windowWidth="35175" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="85">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>07:00-15:45 (NO)</t>
+  </si>
+  <si>
+    <t>Alice</t>
   </si>
 </sst>
 </file>
@@ -5566,7 +5569,7 @@
         <v>18</v>
       </c>
       <c r="R126" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S126" s="10" t="s">
         <v>18</v>
@@ -5622,7 +5625,7 @@
         <v>13</v>
       </c>
       <c r="Q127" s="12"/>
-      <c r="R127" s="23" t="s">
+      <c r="R127" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S127" s="12"/>
@@ -6024,7 +6027,7 @@
         <v>18</v>
       </c>
       <c r="R136" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S136" s="10" t="s">
         <v>18</v>
@@ -6078,7 +6081,7 @@
         <v>13</v>
       </c>
       <c r="Q137" s="12"/>
-      <c r="R137" s="23" t="s">
+      <c r="R137" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S137" s="12"/>
@@ -6474,7 +6477,7 @@
         <v>18</v>
       </c>
       <c r="R146" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S146" s="10" t="s">
         <v>18</v>
@@ -6528,7 +6531,7 @@
         <v>13</v>
       </c>
       <c r="Q147" s="12"/>
-      <c r="R147" s="23" t="s">
+      <c r="R147" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S147" s="12"/>
@@ -6924,7 +6927,7 @@
         <v>18</v>
       </c>
       <c r="R156" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S156" s="10" t="s">
         <v>18</v>
@@ -6976,7 +6979,7 @@
         <v>13</v>
       </c>
       <c r="Q157" s="12"/>
-      <c r="R157" s="23" t="s">
+      <c r="R157" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S157" s="12"/>
@@ -7360,7 +7363,7 @@
         <v>18</v>
       </c>
       <c r="R166" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S166" s="10" t="s">
         <v>18</v>
@@ -7412,7 +7415,7 @@
         <v>13</v>
       </c>
       <c r="Q167" s="12"/>
-      <c r="R167" s="23" t="s">
+      <c r="R167" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S167" s="12"/>
@@ -7808,7 +7811,7 @@
         <v>18</v>
       </c>
       <c r="R176" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S176" s="10" t="s">
         <v>18</v>
@@ -7858,7 +7861,7 @@
         <v>13</v>
       </c>
       <c r="Q177" s="12"/>
-      <c r="R177" s="23" t="s">
+      <c r="R177" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S177" s="12"/>
@@ -8244,7 +8247,7 @@
         <v>18</v>
       </c>
       <c r="R186" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S186" s="10" t="s">
         <v>18</v>
@@ -8294,7 +8297,7 @@
       <c r="Q187" s="12">
         <v>8</v>
       </c>
-      <c r="R187" s="23" t="s">
+      <c r="R187" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S187" s="12"/>
@@ -8676,7 +8679,7 @@
         <v>18</v>
       </c>
       <c r="R196" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S196" s="10" t="s">
         <v>18</v>
@@ -8726,7 +8729,7 @@
       <c r="Q197" s="12">
         <v>8</v>
       </c>
-      <c r="R197" s="23" t="s">
+      <c r="R197" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S197" s="12"/>
@@ -9110,7 +9113,7 @@
         <v>18</v>
       </c>
       <c r="R206" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S206" s="10" t="s">
         <v>18</v>
@@ -9162,7 +9165,7 @@
       <c r="Q207" s="12">
         <v>8</v>
       </c>
-      <c r="R207" s="23" t="s">
+      <c r="R207" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S207" s="12"/>
@@ -9552,7 +9555,7 @@
         <v>18</v>
       </c>
       <c r="R216" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S216" s="10" t="s">
         <v>18</v>
@@ -9606,12 +9609,10 @@
       <c r="Q217" s="12">
         <v>8</v>
       </c>
-      <c r="R217" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="S217" s="12">
-        <v>8</v>
-      </c>
+      <c r="R217" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="S217" s="12"/>
     </row>
     <row r="218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
@@ -9864,7 +9865,7 @@
       <c r="R222" s="60"/>
       <c r="S222" s="45">
         <f>SUM(S217:S221)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:20" x14ac:dyDescent="0.25">
@@ -10004,7 +10005,7 @@
         <v>18</v>
       </c>
       <c r="R226" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S226" s="10" t="s">
         <v>18</v>
@@ -10061,11 +10062,9 @@
         <v>10</v>
       </c>
       <c r="R227" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="S227" s="12">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="S227" s="12"/>
     </row>
     <row r="228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
@@ -10320,7 +10319,7 @@
       <c r="R232" s="60"/>
       <c r="S232" s="45">
         <f>SUM(S227:S231)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:20" x14ac:dyDescent="0.25">
@@ -10460,7 +10459,7 @@
         <v>18</v>
       </c>
       <c r="R236" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S236" s="10" t="s">
         <v>18</v>
@@ -10926,7 +10925,7 @@
         <v>18</v>
       </c>
       <c r="R246" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S246" s="10" t="s">
         <v>18</v>
@@ -11392,7 +11391,7 @@
         <v>18</v>
       </c>
       <c r="R256" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S256" s="10" t="s">
         <v>18</v>
@@ -11858,7 +11857,7 @@
         <v>18</v>
       </c>
       <c r="R266" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S266" s="10" t="s">
         <v>18</v>
@@ -12324,7 +12323,7 @@
         <v>18</v>
       </c>
       <c r="R276" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S276" s="10" t="s">
         <v>18</v>
@@ -12790,7 +12789,7 @@
         <v>18</v>
       </c>
       <c r="R286" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S286" s="10" t="s">
         <v>18</v>
@@ -13256,7 +13255,7 @@
         <v>18</v>
       </c>
       <c r="R296" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S296" s="10" t="s">
         <v>18</v>
@@ -13722,7 +13721,7 @@
         <v>18</v>
       </c>
       <c r="R306" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S306" s="10" t="s">
         <v>18</v>
@@ -14188,7 +14187,7 @@
         <v>18</v>
       </c>
       <c r="R316" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S316" s="10" t="s">
         <v>18</v>
@@ -14654,7 +14653,7 @@
         <v>18</v>
       </c>
       <c r="R326" s="8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S326" s="10" t="s">
         <v>18</v>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1882" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1513535-137F-44DC-9C61-5E5E320657D5}"/>
+  <xr:revisionPtr revIDLastSave="1888" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{817FC90A-A8F7-4910-869C-8B7664AED075}"/>
   <bookViews>
     <workbookView xWindow="3000" yWindow="45" windowWidth="35175" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="84">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -261,9 +261,6 @@
   </si>
   <si>
     <t>07:00-13:45</t>
-  </si>
-  <si>
-    <t>Vakans</t>
   </si>
   <si>
     <t>Vecka 36 (31 aug-4 sep)</t>
@@ -5563,13 +5560,13 @@
         <v>18</v>
       </c>
       <c r="P126" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q126" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R126" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S126" s="10" t="s">
         <v>18</v>
@@ -6021,13 +6018,13 @@
         <v>18</v>
       </c>
       <c r="P136" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q136" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R136" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S136" s="10" t="s">
         <v>18</v>
@@ -6471,13 +6468,13 @@
         <v>18</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q146" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R146" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S146" s="10" t="s">
         <v>18</v>
@@ -6921,13 +6918,13 @@
         <v>18</v>
       </c>
       <c r="P156" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q156" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R156" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S156" s="10" t="s">
         <v>18</v>
@@ -7357,13 +7354,13 @@
         <v>18</v>
       </c>
       <c r="P166" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q166" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R166" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S166" s="10" t="s">
         <v>18</v>
@@ -7805,13 +7802,13 @@
         <v>18</v>
       </c>
       <c r="P176" s="8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q176" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R176" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S176" s="10" t="s">
         <v>18</v>
@@ -8241,13 +8238,13 @@
         <v>18</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q186" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R186" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S186" s="10" t="s">
         <v>18</v>
@@ -8673,13 +8670,13 @@
         <v>18</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q196" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R196" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S196" s="10" t="s">
         <v>18</v>
@@ -9107,13 +9104,13 @@
         <v>18</v>
       </c>
       <c r="P206" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q206" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R206" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S206" s="10" t="s">
         <v>18</v>
@@ -9549,13 +9546,13 @@
         <v>18</v>
       </c>
       <c r="P216" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q216" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R216" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S216" s="10" t="s">
         <v>18</v>
@@ -9999,13 +9996,13 @@
         <v>18</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q226" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R226" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S226" s="10" t="s">
         <v>18</v>
@@ -10453,13 +10450,13 @@
         <v>18</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q236" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R236" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S236" s="10" t="s">
         <v>18</v>
@@ -10614,7 +10611,7 @@
         <v>8</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M239" s="12">
         <v>8</v>
@@ -10919,13 +10916,13 @@
         <v>18</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q246" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R246" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S246" s="10" t="s">
         <v>18</v>
@@ -11082,7 +11079,7 @@
         <v>8</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M249" s="12">
         <v>8</v>
@@ -11385,13 +11382,13 @@
         <v>18</v>
       </c>
       <c r="P256" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q256" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R256" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S256" s="10" t="s">
         <v>18</v>
@@ -11548,7 +11545,7 @@
         <v>8</v>
       </c>
       <c r="L259" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M259" s="12">
         <v>8</v>
@@ -11806,7 +11803,7 @@
     <row r="265" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B266" s="8" t="s">
         <v>2</v>
@@ -11851,13 +11848,13 @@
         <v>18</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q266" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R266" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S266" s="10" t="s">
         <v>18</v>
@@ -12014,7 +12011,7 @@
         <v>8</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M269" s="12">
         <v>8</v>
@@ -12272,7 +12269,7 @@
     <row r="275" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B276" s="8" t="s">
         <v>2</v>
@@ -12317,13 +12314,13 @@
         <v>18</v>
       </c>
       <c r="P276" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q276" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R276" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S276" s="10" t="s">
         <v>18</v>
@@ -12478,7 +12475,7 @@
         <v>8</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M279" s="12">
         <v>8</v>
@@ -12738,7 +12735,7 @@
     <row r="285" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B286" s="8" t="s">
         <v>2</v>
@@ -12783,13 +12780,13 @@
         <v>18</v>
       </c>
       <c r="P286" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q286" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R286" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S286" s="10" t="s">
         <v>18</v>
@@ -12944,7 +12941,7 @@
         <v>8</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M289" s="12">
         <v>8</v>
@@ -13204,7 +13201,7 @@
     <row r="295" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A296" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B296" s="8" t="s">
         <v>2</v>
@@ -13249,13 +13246,13 @@
         <v>18</v>
       </c>
       <c r="P296" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q296" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R296" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S296" s="10" t="s">
         <v>18</v>
@@ -13412,7 +13409,7 @@
         <v>8</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M299" s="12">
         <v>8</v>
@@ -13670,7 +13667,7 @@
     <row r="305" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A306" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B306" s="8" t="s">
         <v>2</v>
@@ -13715,13 +13712,13 @@
         <v>18</v>
       </c>
       <c r="P306" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q306" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R306" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S306" s="10" t="s">
         <v>18</v>
@@ -13878,7 +13875,7 @@
         <v>8</v>
       </c>
       <c r="L309" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M309" s="12">
         <v>8</v>
@@ -14136,7 +14133,7 @@
     <row r="315" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A316" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B316" s="8" t="s">
         <v>2</v>
@@ -14181,13 +14178,13 @@
         <v>18</v>
       </c>
       <c r="P316" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q316" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R316" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S316" s="10" t="s">
         <v>18</v>
@@ -14344,7 +14341,7 @@
         <v>8</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M319" s="12">
         <v>8</v>
@@ -14602,7 +14599,7 @@
     <row r="325" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A326" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B326" s="8" t="s">
         <v>2</v>
@@ -14647,13 +14644,13 @@
         <v>18</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q326" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R326" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S326" s="10" t="s">
         <v>18</v>
@@ -14806,7 +14803,7 @@
         <v>8</v>
       </c>
       <c r="L329" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M329" s="12">
         <v>8</v>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1888" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{817FC90A-A8F7-4910-869C-8B7664AED075}"/>
+  <xr:revisionPtr revIDLastSave="1900" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7D4BEBF-E353-4287-9549-D17099FB3EC0}"/>
   <bookViews>
     <workbookView xWindow="3000" yWindow="45" windowWidth="35175" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="J224" s="42"/>
       <c r="K224" s="42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L224" s="42"/>
       <c r="M224" s="43">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="J234" s="42"/>
       <c r="K234" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L234" s="42"/>
       <c r="M234" s="43">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="J244" s="42"/>
       <c r="K244" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L244" s="42"/>
       <c r="M244" s="43">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="J254" s="42"/>
       <c r="K254" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L254" s="42"/>
       <c r="M254" s="43">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="J264" s="42"/>
       <c r="K264" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L264" s="42"/>
       <c r="M264" s="43">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="J274" s="42"/>
       <c r="K274" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L274" s="42"/>
       <c r="M274" s="43">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="J284" s="42"/>
       <c r="K284" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L284" s="42"/>
       <c r="M284" s="43">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="J294" s="42"/>
       <c r="K294" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L294" s="42"/>
       <c r="M294" s="43">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="J304" s="42"/>
       <c r="K304" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L304" s="42"/>
       <c r="M304" s="43">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="J314" s="42"/>
       <c r="K314" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L314" s="42"/>
       <c r="M314" s="43">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="J324" s="42"/>
       <c r="K324" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L324" s="42"/>
       <c r="M324" s="43">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="J334" s="42"/>
       <c r="K334" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L334" s="42"/>
       <c r="M334" s="43">

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1900" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7D4BEBF-E353-4287-9549-D17099FB3EC0}"/>
+  <xr:revisionPtr revIDLastSave="1921" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22320335-9D47-4D51-89FA-738EC9F32A46}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="45" windowWidth="35175" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="1200" yWindow="15" windowWidth="35160" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -11798,7 +11798,7 @@
       <c r="S264" s="43">
         <v>0</v>
       </c>
-      <c r="T264" s="63"/>
+      <c r="T264" s="46"/>
     </row>
     <row r="265" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="266" spans="1:20" x14ac:dyDescent="0.25">
@@ -12068,15 +12068,15 @@
         <v>7</v>
       </c>
       <c r="N270" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="O270" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="O270" s="12">
+        <v>8</v>
+      </c>
       <c r="P270" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q270" s="12">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="Q270" s="12"/>
       <c r="R270" s="23" t="s">
         <v>13</v>
       </c>
@@ -12170,12 +12170,12 @@
       <c r="N272" s="60"/>
       <c r="O272" s="45">
         <f>SUM(O267:O271)</f>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="P272" s="60"/>
       <c r="Q272" s="45">
         <f>SUM(Q267:Q271)</f>
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R272" s="60"/>
       <c r="S272" s="45">
@@ -12264,7 +12264,7 @@
       <c r="S274" s="43">
         <v>0</v>
       </c>
-      <c r="T274" s="63"/>
+      <c r="T274" s="46"/>
     </row>
     <row r="275" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="276" spans="1:20" x14ac:dyDescent="0.25">
@@ -12946,16 +12946,16 @@
       <c r="M289" s="12">
         <v>8</v>
       </c>
-      <c r="N289" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="O289" s="12"/>
+      <c r="N289" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O289" s="4">
+        <v>8</v>
+      </c>
       <c r="P289" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q289" s="4">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="Q289" s="4"/>
       <c r="R289" s="23" t="s">
         <v>13</v>
       </c>
@@ -13000,15 +13000,15 @@
         <v>7</v>
       </c>
       <c r="N290" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O290" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="O290" s="4">
+        <v>8</v>
+      </c>
       <c r="P290" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q290" s="4">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="Q290" s="4"/>
       <c r="R290" s="23" t="s">
         <v>13</v>
       </c>
@@ -13102,12 +13102,12 @@
       <c r="N292" s="60"/>
       <c r="O292" s="45">
         <f>SUM(O287:O291)</f>
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="P292" s="60"/>
       <c r="Q292" s="45">
         <f>SUM(Q287:Q291)</f>
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="R292" s="60"/>
       <c r="S292" s="45">

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1921" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22320335-9D47-4D51-89FA-738EC9F32A46}"/>
+  <xr:revisionPtr revIDLastSave="1980" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23C1D531-455F-45B5-A196-A9DA44DB74D1}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="15" windowWidth="35160" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="2610" yWindow="315" windowWidth="37080" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="85">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -284,13 +284,16 @@
     <t>Vecka 42 (12 okt-16 okt)</t>
   </si>
   <si>
-    <t>Emilia</t>
-  </si>
-  <si>
     <t>07:00-15:45 (NO)</t>
   </si>
   <si>
     <t>Alice</t>
+  </si>
+  <si>
+    <t>Vakans</t>
+  </si>
+  <si>
+    <t>08:00-12:15</t>
   </si>
 </sst>
 </file>
@@ -408,7 +411,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -629,11 +632,111 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -804,6 +907,51 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5560,13 +5708,13 @@
         <v>18</v>
       </c>
       <c r="P126" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q126" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R126" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S126" s="10" t="s">
         <v>18</v>
@@ -6018,13 +6166,13 @@
         <v>18</v>
       </c>
       <c r="P136" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q136" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R136" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S136" s="10" t="s">
         <v>18</v>
@@ -6468,13 +6616,13 @@
         <v>18</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q146" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R146" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S146" s="10" t="s">
         <v>18</v>
@@ -6918,13 +7066,13 @@
         <v>18</v>
       </c>
       <c r="P156" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q156" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R156" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S156" s="10" t="s">
         <v>18</v>
@@ -7354,13 +7502,13 @@
         <v>18</v>
       </c>
       <c r="P166" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q166" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R166" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S166" s="10" t="s">
         <v>18</v>
@@ -7802,13 +7950,13 @@
         <v>18</v>
       </c>
       <c r="P176" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q176" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R176" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S176" s="10" t="s">
         <v>18</v>
@@ -8238,13 +8386,13 @@
         <v>18</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q186" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R186" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S186" s="10" t="s">
         <v>18</v>
@@ -8670,13 +8818,13 @@
         <v>18</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q196" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R196" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S196" s="10" t="s">
         <v>18</v>
@@ -9104,13 +9252,13 @@
         <v>18</v>
       </c>
       <c r="P206" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q206" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R206" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S206" s="10" t="s">
         <v>18</v>
@@ -9546,13 +9694,13 @@
         <v>18</v>
       </c>
       <c r="P216" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q216" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R216" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S216" s="10" t="s">
         <v>18</v>
@@ -9996,13 +10144,13 @@
         <v>18</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q226" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R226" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S226" s="10" t="s">
         <v>18</v>
@@ -10450,13 +10598,13 @@
         <v>18</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q236" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R236" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S236" s="10" t="s">
         <v>18</v>
@@ -10611,7 +10759,7 @@
         <v>8</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M239" s="12">
         <v>8</v>
@@ -10916,13 +11064,13 @@
         <v>18</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q246" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R246" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S246" s="10" t="s">
         <v>18</v>
@@ -11079,7 +11227,7 @@
         <v>8</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M249" s="12">
         <v>8</v>
@@ -11382,13 +11530,13 @@
         <v>18</v>
       </c>
       <c r="P256" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q256" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R256" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S256" s="10" t="s">
         <v>18</v>
@@ -11545,7 +11693,7 @@
         <v>8</v>
       </c>
       <c r="L259" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M259" s="12">
         <v>8</v>
@@ -11848,13 +11996,13 @@
         <v>18</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q266" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R266" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S266" s="10" t="s">
         <v>18</v>
@@ -12011,7 +12159,7 @@
         <v>8</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M269" s="12">
         <v>8</v>
@@ -12314,13 +12462,13 @@
         <v>18</v>
       </c>
       <c r="P276" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q276" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R276" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S276" s="10" t="s">
         <v>18</v>
@@ -12373,10 +12521,10 @@
         <v>10</v>
       </c>
       <c r="P277" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Q277" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R277" s="4" t="s">
         <v>12</v>
@@ -12432,15 +12580,15 @@
         <v>8</v>
       </c>
       <c r="P278" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q278" s="12">
-        <v>8</v>
-      </c>
-      <c r="R278" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="S278" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="Q278" s="12"/>
+      <c r="R278" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S278" s="12">
+        <v>5</v>
+      </c>
     </row>
     <row r="279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A279" s="11" t="s">
@@ -12452,10 +12600,12 @@
       <c r="C279" s="4">
         <v>6</v>
       </c>
-      <c r="D279" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E279" s="4"/>
+      <c r="D279" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E279" s="4">
+        <v>8</v>
+      </c>
       <c r="F279" s="4" t="s">
         <v>16</v>
       </c>
@@ -12475,7 +12625,7 @@
         <v>8</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M279" s="12">
         <v>8</v>
@@ -12543,10 +12693,12 @@
         <v>13</v>
       </c>
       <c r="Q280" s="12"/>
-      <c r="R280" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="S280" s="12"/>
+      <c r="R280" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="S280" s="12">
+        <v>5</v>
+      </c>
     </row>
     <row r="281" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="22" t="s">
@@ -12611,7 +12763,7 @@
       <c r="D282" s="44"/>
       <c r="E282" s="44">
         <f>SUM(E277:E281)</f>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F282" s="44"/>
       <c r="G282" s="44">
@@ -12641,12 +12793,12 @@
       <c r="P282" s="60"/>
       <c r="Q282" s="45">
         <f>SUM(Q277:Q281)</f>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R282" s="60"/>
       <c r="S282" s="45">
         <f>SUM(S277:S281)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="283" spans="1:20" x14ac:dyDescent="0.25">
@@ -12659,7 +12811,7 @@
       </c>
       <c r="D283" s="39"/>
       <c r="E283" s="39">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="F283" s="39"/>
       <c r="G283" s="39">
@@ -12700,7 +12852,7 @@
       </c>
       <c r="D284" s="42"/>
       <c r="E284" s="42">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F284" s="42"/>
       <c r="G284" s="42">
@@ -12730,7 +12882,7 @@
       <c r="S284" s="43">
         <v>0</v>
       </c>
-      <c r="T284" s="63"/>
+      <c r="T284" s="46"/>
     </row>
     <row r="285" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="286" spans="1:20" x14ac:dyDescent="0.25">
@@ -12776,17 +12928,17 @@
       <c r="N286" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="O286" s="10" t="s">
+      <c r="O286" s="68" t="s">
         <v>18</v>
       </c>
       <c r="P286" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q286" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R286" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S286" s="10" t="s">
         <v>18</v>
@@ -12835,14 +12987,14 @@
       <c r="N287" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="O287" s="12">
+      <c r="O287" s="66">
         <v>10</v>
       </c>
       <c r="P287" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Q287" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R287" s="4" t="s">
         <v>12</v>
@@ -12894,19 +13046,19 @@
       <c r="N288" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O288" s="12">
+      <c r="O288" s="66">
         <v>8</v>
       </c>
       <c r="P288" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q288" s="12">
-        <v>8</v>
-      </c>
-      <c r="R288" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="S288" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="Q288" s="12"/>
+      <c r="R288" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S288" s="12">
+        <v>5</v>
+      </c>
     </row>
     <row r="289" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A289" s="11" t="s">
@@ -12930,10 +13082,12 @@
       <c r="G289" s="4">
         <v>7</v>
       </c>
-      <c r="H289" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I289" s="4"/>
+      <c r="H289" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I289" s="4">
+        <v>8</v>
+      </c>
       <c r="J289" s="4" t="s">
         <v>12</v>
       </c>
@@ -12941,7 +13095,7 @@
         <v>8</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M289" s="12">
         <v>8</v>
@@ -12949,13 +13103,13 @@
       <c r="N289" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O289" s="4">
-        <v>8</v>
-      </c>
-      <c r="P289" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q289" s="4"/>
+      <c r="O289" s="66">
+        <v>8</v>
+      </c>
+      <c r="P289" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q289" s="12"/>
       <c r="R289" s="23" t="s">
         <v>13</v>
       </c>
@@ -13002,17 +13156,19 @@
       <c r="N290" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O290" s="4">
-        <v>8</v>
-      </c>
-      <c r="P290" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q290" s="4"/>
-      <c r="R290" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="S290" s="12"/>
+      <c r="O290" s="66">
+        <v>8</v>
+      </c>
+      <c r="P290" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q290" s="12"/>
+      <c r="R290" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="S290" s="12">
+        <v>4</v>
+      </c>
     </row>
     <row r="291" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="22" t="s">
@@ -13055,7 +13211,7 @@
       <c r="N291" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="O291" s="24"/>
+      <c r="O291" s="69"/>
       <c r="P291" s="23" t="s">
         <v>13</v>
       </c>
@@ -13087,7 +13243,7 @@
       <c r="H292" s="44"/>
       <c r="I292" s="44">
         <f>SUM(I287:I291)</f>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J292" s="44"/>
       <c r="K292" s="44">
@@ -13100,19 +13256,19 @@
         <v>40</v>
       </c>
       <c r="N292" s="60"/>
-      <c r="O292" s="45">
+      <c r="O292" s="70">
         <f>SUM(O287:O291)</f>
         <v>34</v>
       </c>
       <c r="P292" s="60"/>
       <c r="Q292" s="45">
         <f>SUM(Q287:Q291)</f>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R292" s="60"/>
       <c r="S292" s="45">
         <f>SUM(S287:S291)</f>
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="293" spans="1:20" x14ac:dyDescent="0.25">
@@ -13133,7 +13289,7 @@
       </c>
       <c r="H293" s="39"/>
       <c r="I293" s="39">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="J293" s="39"/>
       <c r="K293" s="39">
@@ -13144,7 +13300,7 @@
         <v>0</v>
       </c>
       <c r="N293" s="61"/>
-      <c r="O293" s="40">
+      <c r="O293" s="71">
         <v>0</v>
       </c>
       <c r="P293" s="61"/>
@@ -13166,7 +13322,7 @@
       </c>
       <c r="D294" s="42"/>
       <c r="E294" s="42">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F294" s="42"/>
       <c r="G294" s="42">
@@ -13174,7 +13330,7 @@
       </c>
       <c r="H294" s="42"/>
       <c r="I294" s="42">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J294" s="42"/>
       <c r="K294" s="42">
@@ -13185,7 +13341,7 @@
         <v>0</v>
       </c>
       <c r="N294" s="62"/>
-      <c r="O294" s="43">
+      <c r="O294" s="72">
         <v>0</v>
       </c>
       <c r="P294" s="62"/>
@@ -13196,7 +13352,7 @@
       <c r="S294" s="43">
         <v>0</v>
       </c>
-      <c r="T294" s="63"/>
+      <c r="T294" s="46"/>
     </row>
     <row r="295" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="296" spans="1:20" x14ac:dyDescent="0.25">
@@ -13246,13 +13402,13 @@
         <v>18</v>
       </c>
       <c r="P296" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q296" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R296" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S296" s="10" t="s">
         <v>18</v>
@@ -13305,10 +13461,10 @@
         <v>10</v>
       </c>
       <c r="P297" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Q297" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R297" s="4" t="s">
         <v>12</v>
@@ -13364,15 +13520,15 @@
         <v>8</v>
       </c>
       <c r="P298" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q298" s="12">
-        <v>8</v>
-      </c>
-      <c r="R298" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="S298" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="Q298" s="12"/>
+      <c r="R298" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S298" s="12">
+        <v>5</v>
+      </c>
     </row>
     <row r="299" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A299" s="11" t="s">
@@ -13409,7 +13565,7 @@
         <v>8</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M299" s="12">
         <v>8</v>
@@ -13573,12 +13729,12 @@
       <c r="P302" s="60"/>
       <c r="Q302" s="45">
         <f>SUM(Q297:Q301)</f>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R302" s="60"/>
       <c r="S302" s="45">
         <f>SUM(S297:S301)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="303" spans="1:20" x14ac:dyDescent="0.25">
@@ -13632,7 +13788,7 @@
       </c>
       <c r="D304" s="42"/>
       <c r="E304" s="42">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F304" s="42"/>
       <c r="G304" s="42">
@@ -13640,7 +13796,7 @@
       </c>
       <c r="H304" s="42"/>
       <c r="I304" s="42">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J304" s="42"/>
       <c r="K304" s="42">
@@ -13662,7 +13818,7 @@
       <c r="S304" s="43">
         <v>0</v>
       </c>
-      <c r="T304" s="63"/>
+      <c r="T304" s="46"/>
     </row>
     <row r="305" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="306" spans="1:20" x14ac:dyDescent="0.25">
@@ -13705,20 +13861,20 @@
       <c r="M306" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N306" s="8" t="s">
+      <c r="N306" s="73" t="s">
         <v>72</v>
       </c>
       <c r="O306" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P306" s="8" t="s">
-        <v>81</v>
+      <c r="P306" s="76" t="s">
+        <v>83</v>
       </c>
       <c r="Q306" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R306" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S306" s="10" t="s">
         <v>18</v>
@@ -13764,17 +13920,17 @@
       <c r="M307" s="12">
         <v>10</v>
       </c>
-      <c r="N307" s="4" t="s">
+      <c r="N307" s="74" t="s">
         <v>29</v>
       </c>
       <c r="O307" s="12">
         <v>10</v>
       </c>
-      <c r="P307" s="4" t="s">
-        <v>29</v>
+      <c r="P307" s="77" t="s">
+        <v>12</v>
       </c>
       <c r="Q307" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R307" s="4" t="s">
         <v>12</v>
@@ -13823,18 +13979,16 @@
       <c r="M308" s="12">
         <v>8</v>
       </c>
-      <c r="N308" s="4" t="s">
+      <c r="N308" s="74" t="s">
         <v>12</v>
       </c>
       <c r="O308" s="12">
         <v>8</v>
       </c>
-      <c r="P308" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q308" s="12">
-        <v>8</v>
-      </c>
+      <c r="P308" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q308" s="12"/>
       <c r="R308" s="23" t="s">
         <v>13</v>
       </c>
@@ -13875,16 +14029,16 @@
         <v>8</v>
       </c>
       <c r="L309" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M309" s="12">
         <v>8</v>
       </c>
-      <c r="N309" s="23" t="s">
+      <c r="N309" s="75" t="s">
         <v>13</v>
       </c>
       <c r="O309" s="12"/>
-      <c r="P309" s="23" t="s">
+      <c r="P309" s="67" t="s">
         <v>13</v>
       </c>
       <c r="Q309" s="12"/>
@@ -13931,13 +14085,13 @@
       <c r="M310" s="12">
         <v>7</v>
       </c>
-      <c r="N310" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O310" s="4">
-        <v>8</v>
-      </c>
-      <c r="P310" s="23" t="s">
+      <c r="N310" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="O310" s="12">
+        <v>8</v>
+      </c>
+      <c r="P310" s="67" t="s">
         <v>13</v>
       </c>
       <c r="Q310" s="12"/>
@@ -13984,11 +14138,11 @@
       <c r="M311" s="24">
         <v>7</v>
       </c>
-      <c r="N311" s="23" t="s">
+      <c r="N311" s="75" t="s">
         <v>13</v>
       </c>
       <c r="O311" s="24"/>
-      <c r="P311" s="23" t="s">
+      <c r="P311" s="67" t="s">
         <v>13</v>
       </c>
       <c r="Q311" s="24"/>
@@ -14036,10 +14190,10 @@
         <f>SUM(O307:O311)</f>
         <v>26</v>
       </c>
-      <c r="P312" s="60"/>
+      <c r="P312" s="78"/>
       <c r="Q312" s="45">
         <f>SUM(Q307:Q311)</f>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R312" s="60"/>
       <c r="S312" s="45">
@@ -14079,7 +14233,7 @@
       <c r="O313" s="40">
         <v>0</v>
       </c>
-      <c r="P313" s="61"/>
+      <c r="P313" s="79"/>
       <c r="Q313" s="40">
         <v>0</v>
       </c>
@@ -14098,7 +14252,7 @@
       </c>
       <c r="D314" s="42"/>
       <c r="E314" s="42">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F314" s="42"/>
       <c r="G314" s="42">
@@ -14106,7 +14260,7 @@
       </c>
       <c r="H314" s="42"/>
       <c r="I314" s="42">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J314" s="42"/>
       <c r="K314" s="42">
@@ -14120,7 +14274,7 @@
       <c r="O314" s="43">
         <v>0</v>
       </c>
-      <c r="P314" s="62"/>
+      <c r="P314" s="80"/>
       <c r="Q314" s="43">
         <v>0</v>
       </c>
@@ -14178,13 +14332,13 @@
         <v>18</v>
       </c>
       <c r="P316" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q316" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R316" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S316" s="10" t="s">
         <v>18</v>
@@ -14237,10 +14391,10 @@
         <v>10</v>
       </c>
       <c r="P317" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Q317" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R317" s="4" t="s">
         <v>12</v>
@@ -14296,11 +14450,9 @@
         <v>8</v>
       </c>
       <c r="P318" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q318" s="12">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="Q318" s="12"/>
       <c r="R318" s="23" t="s">
         <v>13</v>
       </c>
@@ -14341,7 +14493,7 @@
         <v>8</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M319" s="12">
         <v>8</v>
@@ -14505,7 +14657,7 @@
       <c r="P322" s="60"/>
       <c r="Q322" s="45">
         <f>SUM(Q317:Q321)</f>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R322" s="60"/>
       <c r="S322" s="45">
@@ -14564,7 +14716,7 @@
       </c>
       <c r="D324" s="42"/>
       <c r="E324" s="42">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F324" s="42"/>
       <c r="G324" s="42">
@@ -14572,7 +14724,7 @@
       </c>
       <c r="H324" s="42"/>
       <c r="I324" s="42">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J324" s="42"/>
       <c r="K324" s="42">
@@ -14637,20 +14789,20 @@
       <c r="M326" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N326" s="8" t="s">
+      <c r="N326" s="73" t="s">
         <v>72</v>
       </c>
       <c r="O326" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P326" s="8" t="s">
-        <v>81</v>
+      <c r="P326" s="76" t="s">
+        <v>83</v>
       </c>
       <c r="Q326" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R326" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S326" s="10" t="s">
         <v>18</v>
@@ -14696,17 +14848,17 @@
       <c r="M327" s="12">
         <v>10</v>
       </c>
-      <c r="N327" s="4" t="s">
+      <c r="N327" s="74" t="s">
         <v>29</v>
       </c>
       <c r="O327" s="12">
         <v>10</v>
       </c>
-      <c r="P327" s="4" t="s">
-        <v>29</v>
+      <c r="P327" s="77" t="s">
+        <v>12</v>
       </c>
       <c r="Q327" s="12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R327" s="4" t="s">
         <v>12</v>
@@ -14755,18 +14907,16 @@
       <c r="M328" s="12">
         <v>8</v>
       </c>
-      <c r="N328" s="4" t="s">
+      <c r="N328" s="74" t="s">
         <v>12</v>
       </c>
       <c r="O328" s="12">
         <v>8</v>
       </c>
-      <c r="P328" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q328" s="12">
-        <v>8</v>
-      </c>
+      <c r="P328" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q328" s="12"/>
       <c r="R328" s="23" t="s">
         <v>13</v>
       </c>
@@ -14803,23 +14953,21 @@
         <v>8</v>
       </c>
       <c r="L329" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M329" s="12">
         <v>8</v>
       </c>
-      <c r="N329" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O329" s="4">
-        <v>8</v>
-      </c>
-      <c r="P329" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q329" s="12">
-        <v>8</v>
-      </c>
+      <c r="N329" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="O329" s="12">
+        <v>8</v>
+      </c>
+      <c r="P329" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q329" s="12"/>
       <c r="R329" s="23" t="s">
         <v>13</v>
       </c>
@@ -14863,13 +15011,13 @@
       <c r="M330" s="12">
         <v>7</v>
       </c>
-      <c r="N330" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O330" s="4">
-        <v>8</v>
-      </c>
-      <c r="P330" s="23" t="s">
+      <c r="N330" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="O330" s="12">
+        <v>8</v>
+      </c>
+      <c r="P330" s="67" t="s">
         <v>13</v>
       </c>
       <c r="Q330" s="12"/>
@@ -14916,11 +15064,11 @@
       <c r="M331" s="24">
         <v>7</v>
       </c>
-      <c r="N331" s="23" t="s">
+      <c r="N331" s="75" t="s">
         <v>13</v>
       </c>
       <c r="O331" s="24"/>
-      <c r="P331" s="23" t="s">
+      <c r="P331" s="67" t="s">
         <v>13</v>
       </c>
       <c r="Q331" s="24"/>
@@ -14968,10 +15116,10 @@
         <f>SUM(O327:O331)</f>
         <v>34</v>
       </c>
-      <c r="P332" s="60"/>
+      <c r="P332" s="78"/>
       <c r="Q332" s="45">
         <f>SUM(Q327:Q331)</f>
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="R332" s="60"/>
       <c r="S332" s="45">
@@ -15011,7 +15159,7 @@
       <c r="O333" s="40">
         <v>0</v>
       </c>
-      <c r="P333" s="61"/>
+      <c r="P333" s="79"/>
       <c r="Q333" s="40">
         <v>0</v>
       </c>
@@ -15030,7 +15178,7 @@
       </c>
       <c r="D334" s="42"/>
       <c r="E334" s="42">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F334" s="42"/>
       <c r="G334" s="42">
@@ -15038,7 +15186,7 @@
       </c>
       <c r="H334" s="42"/>
       <c r="I334" s="42">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J334" s="42"/>
       <c r="K334" s="42">
@@ -15052,7 +15200,7 @@
       <c r="O334" s="43">
         <v>0</v>
       </c>
-      <c r="P334" s="62"/>
+      <c r="P334" s="80"/>
       <c r="Q334" s="43">
         <v>0</v>
       </c>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1980" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23C1D531-455F-45B5-A196-A9DA44DB74D1}"/>
+  <xr:revisionPtr revIDLastSave="1981" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E66E0ECE-8701-43F3-90B7-6249326C2656}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="315" windowWidth="37080" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="8505" yWindow="315" windowWidth="37080" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -266,9 +266,6 @@
     <t>Vecka 36 (31 aug-4 sep)</t>
   </si>
   <si>
-    <t>Vecka 37 (7sep-11 sep)</t>
-  </si>
-  <si>
     <t>Vecka 38 (14 sep-18 sep)</t>
   </si>
   <si>
@@ -294,6 +291,9 @@
   </si>
   <si>
     <t>08:00-12:15</t>
+  </si>
+  <si>
+    <t>Vecka 37 (7 sep-11 sep)</t>
   </si>
 </sst>
 </file>
@@ -5708,13 +5708,13 @@
         <v>18</v>
       </c>
       <c r="P126" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q126" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R126" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S126" s="10" t="s">
         <v>18</v>
@@ -6166,13 +6166,13 @@
         <v>18</v>
       </c>
       <c r="P136" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q136" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R136" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S136" s="10" t="s">
         <v>18</v>
@@ -6616,13 +6616,13 @@
         <v>18</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q146" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R146" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S146" s="10" t="s">
         <v>18</v>
@@ -7066,13 +7066,13 @@
         <v>18</v>
       </c>
       <c r="P156" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q156" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R156" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S156" s="10" t="s">
         <v>18</v>
@@ -7502,13 +7502,13 @@
         <v>18</v>
       </c>
       <c r="P166" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q166" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R166" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S166" s="10" t="s">
         <v>18</v>
@@ -7950,13 +7950,13 @@
         <v>18</v>
       </c>
       <c r="P176" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q176" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R176" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S176" s="10" t="s">
         <v>18</v>
@@ -8386,13 +8386,13 @@
         <v>18</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q186" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R186" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S186" s="10" t="s">
         <v>18</v>
@@ -8818,13 +8818,13 @@
         <v>18</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q196" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R196" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S196" s="10" t="s">
         <v>18</v>
@@ -9252,13 +9252,13 @@
         <v>18</v>
       </c>
       <c r="P206" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q206" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R206" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S206" s="10" t="s">
         <v>18</v>
@@ -9694,13 +9694,13 @@
         <v>18</v>
       </c>
       <c r="P216" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q216" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R216" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S216" s="10" t="s">
         <v>18</v>
@@ -10144,13 +10144,13 @@
         <v>18</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q226" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R226" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S226" s="10" t="s">
         <v>18</v>
@@ -10598,13 +10598,13 @@
         <v>18</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q236" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R236" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S236" s="10" t="s">
         <v>18</v>
@@ -10759,7 +10759,7 @@
         <v>8</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M239" s="12">
         <v>8</v>
@@ -11064,13 +11064,13 @@
         <v>18</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q246" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R246" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S246" s="10" t="s">
         <v>18</v>
@@ -11227,7 +11227,7 @@
         <v>8</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M249" s="12">
         <v>8</v>
@@ -11530,13 +11530,13 @@
         <v>18</v>
       </c>
       <c r="P256" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q256" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R256" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S256" s="10" t="s">
         <v>18</v>
@@ -11693,7 +11693,7 @@
         <v>8</v>
       </c>
       <c r="L259" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M259" s="12">
         <v>8</v>
@@ -11996,13 +11996,13 @@
         <v>18</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q266" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R266" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S266" s="10" t="s">
         <v>18</v>
@@ -12159,7 +12159,7 @@
         <v>8</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M269" s="12">
         <v>8</v>
@@ -12417,7 +12417,7 @@
     <row r="275" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B276" s="8" t="s">
         <v>2</v>
@@ -12462,13 +12462,13 @@
         <v>18</v>
       </c>
       <c r="P276" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q276" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R276" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S276" s="10" t="s">
         <v>18</v>
@@ -12625,7 +12625,7 @@
         <v>8</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M279" s="12">
         <v>8</v>
@@ -12694,7 +12694,7 @@
       </c>
       <c r="Q280" s="12"/>
       <c r="R280" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S280" s="12">
         <v>5</v>
@@ -12887,7 +12887,7 @@
     <row r="285" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B286" s="8" t="s">
         <v>2</v>
@@ -12932,13 +12932,13 @@
         <v>18</v>
       </c>
       <c r="P286" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q286" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R286" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S286" s="10" t="s">
         <v>18</v>
@@ -13095,7 +13095,7 @@
         <v>8</v>
       </c>
       <c r="L289" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M289" s="12">
         <v>8</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="Q290" s="12"/>
       <c r="R290" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S290" s="12">
         <v>4</v>
@@ -13357,7 +13357,7 @@
     <row r="295" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A296" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B296" s="8" t="s">
         <v>2</v>
@@ -13402,13 +13402,13 @@
         <v>18</v>
       </c>
       <c r="P296" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q296" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R296" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S296" s="10" t="s">
         <v>18</v>
@@ -13565,7 +13565,7 @@
         <v>8</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M299" s="12">
         <v>8</v>
@@ -13823,7 +13823,7 @@
     <row r="305" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A306" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B306" s="8" t="s">
         <v>2</v>
@@ -13868,13 +13868,13 @@
         <v>18</v>
       </c>
       <c r="P306" s="76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q306" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R306" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S306" s="10" t="s">
         <v>18</v>
@@ -14029,7 +14029,7 @@
         <v>8</v>
       </c>
       <c r="L309" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M309" s="12">
         <v>8</v>
@@ -14287,7 +14287,7 @@
     <row r="315" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A316" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B316" s="8" t="s">
         <v>2</v>
@@ -14332,13 +14332,13 @@
         <v>18</v>
       </c>
       <c r="P316" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q316" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R316" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S316" s="10" t="s">
         <v>18</v>
@@ -14493,7 +14493,7 @@
         <v>8</v>
       </c>
       <c r="L319" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M319" s="12">
         <v>8</v>
@@ -14751,7 +14751,7 @@
     <row r="325" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A326" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B326" s="8" t="s">
         <v>2</v>
@@ -14796,13 +14796,13 @@
         <v>18</v>
       </c>
       <c r="P326" s="76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q326" s="10" t="s">
         <v>18</v>
       </c>
       <c r="R326" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S326" s="10" t="s">
         <v>18</v>
@@ -14953,7 +14953,7 @@
         <v>8</v>
       </c>
       <c r="L329" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M329" s="12">
         <v>8</v>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1981" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E66E0ECE-8701-43F3-90B7-6249326C2656}"/>
+  <xr:revisionPtr revIDLastSave="1992" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4781AA34-6B3E-40E0-BD2F-B656EC54DB08}"/>
   <bookViews>
-    <workbookView xWindow="8505" yWindow="315" windowWidth="37080" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="2730" yWindow="315" windowWidth="37080" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -12210,10 +12210,10 @@
         <v>6</v>
       </c>
       <c r="L270" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M270" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N270" s="23" t="s">
         <v>12</v>
@@ -12313,7 +12313,7 @@
       <c r="L272" s="44"/>
       <c r="M272" s="45">
         <f>SUM(M267:M271)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N272" s="60"/>
       <c r="O272" s="45">
@@ -12357,7 +12357,7 @@
       </c>
       <c r="L273" s="39"/>
       <c r="M273" s="40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N273" s="61"/>
       <c r="O273" s="40">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="L274" s="42"/>
       <c r="M274" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N274" s="62"/>
       <c r="O274" s="43">
@@ -12697,7 +12697,7 @@
         <v>83</v>
       </c>
       <c r="S280" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12798,7 +12798,7 @@
       <c r="R282" s="60"/>
       <c r="S282" s="45">
         <f>SUM(S277:S281)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="283" spans="1:20" x14ac:dyDescent="0.25">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="L284" s="42"/>
       <c r="M284" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N284" s="62"/>
       <c r="O284" s="43">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="L294" s="42"/>
       <c r="M294" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N294" s="62"/>
       <c r="O294" s="72">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="L304" s="42"/>
       <c r="M304" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N304" s="62"/>
       <c r="O304" s="43">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="L314" s="42"/>
       <c r="M314" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N314" s="62"/>
       <c r="O314" s="43">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="L324" s="42"/>
       <c r="M324" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N324" s="62"/>
       <c r="O324" s="43">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="L334" s="42"/>
       <c r="M334" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N334" s="62"/>
       <c r="O334" s="43">
